--- a/models/lead_acid_recycling/build/out/built.xlsx
+++ b/models/lead_acid_recycling/build/out/built.xlsx
@@ -16,6 +16,7 @@
     <sheet name="IN_SCEN" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="ENG_SCEN" sheetId="8" state="hidden" r:id="rId8"/>
     <sheet name="ENG_OPS" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet name="ENG_CAPEX" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1654,6 +1655,5101 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>چرخهٔ عمر دارایی‌ها و CAPEX</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>موتور محاسبات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>برنامه تزریق سرمایه‌گذاری، جایگزینی تجهیزات، استهلاک و ارزش دفتری دارایی‌ها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>دوره (t)</t>
+        </is>
+      </c>
+      <c r="D7" s="5">
+        <f>'IN_MACRO'!D$23</f>
+        <v/>
+      </c>
+      <c r="E7" s="5">
+        <f>'IN_MACRO'!E$23</f>
+        <v/>
+      </c>
+      <c r="F7" s="5">
+        <f>'IN_MACRO'!F$23</f>
+        <v/>
+      </c>
+      <c r="G7" s="5">
+        <f>'IN_MACRO'!G$23</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
+        <f>'IN_MACRO'!H$23</f>
+        <v/>
+      </c>
+      <c r="I7" s="5">
+        <f>'IN_MACRO'!I$23</f>
+        <v/>
+      </c>
+      <c r="J7" s="5">
+        <f>'IN_MACRO'!J$23</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
+        <f>'IN_MACRO'!K$23</f>
+        <v/>
+      </c>
+      <c r="L7" s="5">
+        <f>'IN_MACRO'!L$23</f>
+        <v/>
+      </c>
+      <c r="M7" s="5">
+        <f>'IN_MACRO'!M$23</f>
+        <v/>
+      </c>
+      <c r="N7" s="5">
+        <f>'IN_MACRO'!N$23</f>
+        <v/>
+      </c>
+      <c r="O7" s="5">
+        <f>'IN_MACRO'!O$23</f>
+        <v/>
+      </c>
+      <c r="P7" s="5">
+        <f>'IN_MACRO'!P$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>سال تقویمی</t>
+        </is>
+      </c>
+      <c r="D8" s="5">
+        <f>'IN_MACRO'!D$24</f>
+        <v/>
+      </c>
+      <c r="E8" s="5">
+        <f>'IN_MACRO'!E$24</f>
+        <v/>
+      </c>
+      <c r="F8" s="5">
+        <f>'IN_MACRO'!F$24</f>
+        <v/>
+      </c>
+      <c r="G8" s="5">
+        <f>'IN_MACRO'!G$24</f>
+        <v/>
+      </c>
+      <c r="H8" s="5">
+        <f>'IN_MACRO'!H$24</f>
+        <v/>
+      </c>
+      <c r="I8" s="5">
+        <f>'IN_MACRO'!I$24</f>
+        <v/>
+      </c>
+      <c r="J8" s="5">
+        <f>'IN_MACRO'!J$24</f>
+        <v/>
+      </c>
+      <c r="K8" s="5">
+        <f>'IN_MACRO'!K$24</f>
+        <v/>
+      </c>
+      <c r="L8" s="5">
+        <f>'IN_MACRO'!L$24</f>
+        <v/>
+      </c>
+      <c r="M8" s="5">
+        <f>'IN_MACRO'!M$24</f>
+        <v/>
+      </c>
+      <c r="N8" s="5">
+        <f>'IN_MACRO'!N$24</f>
+        <v/>
+      </c>
+      <c r="O8" s="5">
+        <f>'IN_MACRO'!O$24</f>
+        <v/>
+      </c>
+      <c r="P8" s="5">
+        <f>'IN_MACRO'!P$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>الف) برنامه تزریق سرمایه‌گذاری ثابت</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
+      <c r="P9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری زمین</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap.0</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$9*'ENG_SCEN'!$D$36)*(IF('IN_MACRO'!$D$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$D$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$D$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="E10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$9*'ENG_SCEN'!$E$36)*(IF('IN_MACRO'!$E$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$E$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$E$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="F10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$9*'ENG_SCEN'!$F$36)*(IF('IN_MACRO'!$F$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$F$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$F$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="G10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$9*'ENG_SCEN'!$G$36)*(IF('IN_MACRO'!$G$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$G$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$G$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="H10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$9*'ENG_SCEN'!$H$36)*(IF('IN_MACRO'!$H$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$H$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$H$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="I10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$9*'ENG_SCEN'!$I$36)*(IF('IN_MACRO'!$I$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$I$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$I$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="J10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$9*'ENG_SCEN'!$J$36)*(IF('IN_MACRO'!$J$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$J$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$J$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="K10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$9*'ENG_SCEN'!$K$36)*(IF('IN_MACRO'!$K$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$K$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$K$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="L10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$9*'ENG_SCEN'!$L$36)*(IF('IN_MACRO'!$L$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$L$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$L$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="M10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$9*'ENG_SCEN'!$M$36)*(IF('IN_MACRO'!$M$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$M$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$M$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="N10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$9*'ENG_SCEN'!$N$36)*(IF('IN_MACRO'!$N$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$N$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$N$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="O10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$9*'ENG_SCEN'!$O$36)*(IF('IN_MACRO'!$O$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$O$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$O$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="P10" s="14">
+        <f>'IN_FIN'!$D$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$9*'ENG_SCEN'!$P$36)*(IF('IN_MACRO'!$P$23=0,'IN_FIN'!$J$9,IF('IN_MACRO'!$P$23=1,'IN_FIN'!$K$9,IF('IN_MACRO'!$P$23=2,'IN_FIN'!$L$9,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری محوطه‌سازی و ساختمان</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap.1</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$10*'ENG_SCEN'!$D$36)*(IF('IN_MACRO'!$D$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$D$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$D$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$10*'ENG_SCEN'!$E$36)*(IF('IN_MACRO'!$E$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$E$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$E$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="F11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$10*'ENG_SCEN'!$F$36)*(IF('IN_MACRO'!$F$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$F$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$F$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="G11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$10*'ENG_SCEN'!$G$36)*(IF('IN_MACRO'!$G$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$G$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$G$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="H11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$10*'ENG_SCEN'!$H$36)*(IF('IN_MACRO'!$H$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$H$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$H$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="I11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$10*'ENG_SCEN'!$I$36)*(IF('IN_MACRO'!$I$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$I$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$I$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="J11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$10*'ENG_SCEN'!$J$36)*(IF('IN_MACRO'!$J$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$J$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$J$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="K11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$10*'ENG_SCEN'!$K$36)*(IF('IN_MACRO'!$K$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$K$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$K$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="L11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$10*'ENG_SCEN'!$L$36)*(IF('IN_MACRO'!$L$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$L$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$L$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="M11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$10*'ENG_SCEN'!$M$36)*(IF('IN_MACRO'!$M$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$M$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$M$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="N11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$10*'ENG_SCEN'!$N$36)*(IF('IN_MACRO'!$N$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$N$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$N$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="O11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$10*'ENG_SCEN'!$O$36)*(IF('IN_MACRO'!$O$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$O$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$O$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="P11" s="14">
+        <f>'IN_FIN'!$D$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$10*'ENG_SCEN'!$P$36)*(IF('IN_MACRO'!$P$23=0,'IN_FIN'!$J$10,IF('IN_MACRO'!$P$23=1,'IN_FIN'!$K$10,IF('IN_MACRO'!$P$23=2,'IN_FIN'!$L$10,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری ماشین‌آلات وارداتی</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap.2</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$11*'ENG_SCEN'!$D$36)*(IF('IN_MACRO'!$D$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$D$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$D$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="E12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$11*'ENG_SCEN'!$E$36)*(IF('IN_MACRO'!$E$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$E$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$E$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="F12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$11*'ENG_SCEN'!$F$36)*(IF('IN_MACRO'!$F$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$F$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$F$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="G12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$11*'ENG_SCEN'!$G$36)*(IF('IN_MACRO'!$G$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$G$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$G$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="H12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$11*'ENG_SCEN'!$H$36)*(IF('IN_MACRO'!$H$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$H$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$H$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="I12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$11*'ENG_SCEN'!$I$36)*(IF('IN_MACRO'!$I$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$I$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$I$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="J12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$11*'ENG_SCEN'!$J$36)*(IF('IN_MACRO'!$J$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$J$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$J$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="K12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$11*'ENG_SCEN'!$K$36)*(IF('IN_MACRO'!$K$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$K$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$K$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="L12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$11*'ENG_SCEN'!$L$36)*(IF('IN_MACRO'!$L$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$L$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$L$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="M12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$11*'ENG_SCEN'!$M$36)*(IF('IN_MACRO'!$M$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$M$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$M$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="N12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$11*'ENG_SCEN'!$N$36)*(IF('IN_MACRO'!$N$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$N$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$N$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="O12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$11*'ENG_SCEN'!$O$36)*(IF('IN_MACRO'!$O$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$O$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$O$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="P12" s="14">
+        <f>'IN_FIN'!$D$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$11*'ENG_SCEN'!$P$36)*(IF('IN_MACRO'!$P$23=0,'IN_FIN'!$J$11,IF('IN_MACRO'!$P$23=1,'IN_FIN'!$K$11,IF('IN_MACRO'!$P$23=2,'IN_FIN'!$L$11,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری ماشین‌آلات داخلی</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap.3</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$12*'ENG_SCEN'!$D$36)*(IF('IN_MACRO'!$D$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$D$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$D$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="E13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$12*'ENG_SCEN'!$E$36)*(IF('IN_MACRO'!$E$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$E$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$E$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="F13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$12*'ENG_SCEN'!$F$36)*(IF('IN_MACRO'!$F$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$F$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$F$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="G13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$12*'ENG_SCEN'!$G$36)*(IF('IN_MACRO'!$G$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$G$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$G$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="H13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$12*'ENG_SCEN'!$H$36)*(IF('IN_MACRO'!$H$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$H$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$H$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="I13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$12*'ENG_SCEN'!$I$36)*(IF('IN_MACRO'!$I$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$I$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$I$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="J13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$12*'ENG_SCEN'!$J$36)*(IF('IN_MACRO'!$J$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$J$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$J$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="K13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$12*'ENG_SCEN'!$K$36)*(IF('IN_MACRO'!$K$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$K$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$K$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="L13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$12*'ENG_SCEN'!$L$36)*(IF('IN_MACRO'!$L$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$L$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$L$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="M13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$12*'ENG_SCEN'!$M$36)*(IF('IN_MACRO'!$M$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$M$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$M$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="N13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$12*'ENG_SCEN'!$N$36)*(IF('IN_MACRO'!$N$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$N$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$N$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="O13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$12*'ENG_SCEN'!$O$36)*(IF('IN_MACRO'!$O$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$O$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$O$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="P13" s="14">
+        <f>'IN_FIN'!$D$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$12*'ENG_SCEN'!$P$36)*(IF('IN_MACRO'!$P$23=0,'IN_FIN'!$J$12,IF('IN_MACRO'!$P$23=1,'IN_FIN'!$K$12,IF('IN_MACRO'!$P$23=2,'IN_FIN'!$L$12,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری تأسیسات و تجهیزات جانبی</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap.4</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$13*'ENG_SCEN'!$D$36)*(IF('IN_MACRO'!$D$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$D$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$D$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="E14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$13*'ENG_SCEN'!$E$36)*(IF('IN_MACRO'!$E$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$E$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$E$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="F14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$13*'ENG_SCEN'!$F$36)*(IF('IN_MACRO'!$F$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$F$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$F$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="G14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$13*'ENG_SCEN'!$G$36)*(IF('IN_MACRO'!$G$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$G$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$G$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="H14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$13*'ENG_SCEN'!$H$36)*(IF('IN_MACRO'!$H$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$H$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$H$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="I14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$13*'ENG_SCEN'!$I$36)*(IF('IN_MACRO'!$I$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$I$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$I$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="J14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$13*'ENG_SCEN'!$J$36)*(IF('IN_MACRO'!$J$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$J$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$J$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="K14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$13*'ENG_SCEN'!$K$36)*(IF('IN_MACRO'!$K$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$K$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$K$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="L14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$13*'ENG_SCEN'!$L$36)*(IF('IN_MACRO'!$L$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$L$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$L$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="M14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$13*'ENG_SCEN'!$M$36)*(IF('IN_MACRO'!$M$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$M$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$M$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="N14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$13*'ENG_SCEN'!$N$36)*(IF('IN_MACRO'!$N$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$N$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$N$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="O14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$13*'ENG_SCEN'!$O$36)*(IF('IN_MACRO'!$O$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$O$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$O$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="P14" s="14">
+        <f>'IN_FIN'!$D$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$13*'ENG_SCEN'!$P$36)*(IF('IN_MACRO'!$P$23=0,'IN_FIN'!$J$13,IF('IN_MACRO'!$P$23=1,'IN_FIN'!$K$13,IF('IN_MACRO'!$P$23=2,'IN_FIN'!$L$13,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری تصفیه‌خانه و تجهیزات زیست‌محیطی</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap.5</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$14*'ENG_SCEN'!$D$36)*(IF('IN_MACRO'!$D$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$D$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$D$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$14*'ENG_SCEN'!$E$36)*(IF('IN_MACRO'!$E$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$E$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$E$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="F15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$14*'ENG_SCEN'!$F$36)*(IF('IN_MACRO'!$F$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$F$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$F$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="G15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$14*'ENG_SCEN'!$G$36)*(IF('IN_MACRO'!$G$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$G$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$G$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="H15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$14*'ENG_SCEN'!$H$36)*(IF('IN_MACRO'!$H$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$H$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$H$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="I15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$14*'ENG_SCEN'!$I$36)*(IF('IN_MACRO'!$I$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$I$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$I$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="J15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$14*'ENG_SCEN'!$J$36)*(IF('IN_MACRO'!$J$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$J$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$J$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="K15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$14*'ENG_SCEN'!$K$36)*(IF('IN_MACRO'!$K$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$K$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$K$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="L15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$14*'ENG_SCEN'!$L$36)*(IF('IN_MACRO'!$L$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$L$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$L$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="M15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$14*'ENG_SCEN'!$M$36)*(IF('IN_MACRO'!$M$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$M$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$M$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="N15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$14*'ENG_SCEN'!$N$36)*(IF('IN_MACRO'!$N$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$N$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$N$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="O15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$14*'ENG_SCEN'!$O$36)*(IF('IN_MACRO'!$O$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$O$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$O$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="P15" s="14">
+        <f>'IN_FIN'!$D$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$14*'ENG_SCEN'!$P$36)*(IF('IN_MACRO'!$P$23=0,'IN_FIN'!$J$14,IF('IN_MACRO'!$P$23=1,'IN_FIN'!$K$14,IF('IN_MACRO'!$P$23=2,'IN_FIN'!$L$14,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری تجهیزات حمل‌ونقل داخلی</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap.6</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$15*'ENG_SCEN'!$D$36)*(IF('IN_MACRO'!$D$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$D$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$D$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="E16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$15*'ENG_SCEN'!$E$36)*(IF('IN_MACRO'!$E$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$E$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$E$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="F16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$15*'ENG_SCEN'!$F$36)*(IF('IN_MACRO'!$F$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$F$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$F$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="G16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$15*'ENG_SCEN'!$G$36)*(IF('IN_MACRO'!$G$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$G$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$G$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="H16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$15*'ENG_SCEN'!$H$36)*(IF('IN_MACRO'!$H$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$H$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$H$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="I16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$15*'ENG_SCEN'!$I$36)*(IF('IN_MACRO'!$I$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$I$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$I$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="J16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$15*'ENG_SCEN'!$J$36)*(IF('IN_MACRO'!$J$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$J$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$J$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="K16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$15*'ENG_SCEN'!$K$36)*(IF('IN_MACRO'!$K$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$K$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$K$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="L16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$15*'ENG_SCEN'!$L$36)*(IF('IN_MACRO'!$L$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$L$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$L$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="M16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$15*'ENG_SCEN'!$M$36)*(IF('IN_MACRO'!$M$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$M$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$M$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="N16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$15*'ENG_SCEN'!$N$36)*(IF('IN_MACRO'!$N$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$N$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$N$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="O16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$15*'ENG_SCEN'!$O$36)*(IF('IN_MACRO'!$O$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$O$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$O$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="P16" s="14">
+        <f>'IN_FIN'!$D$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$15*'ENG_SCEN'!$P$36)*(IF('IN_MACRO'!$P$23=0,'IN_FIN'!$J$15,IF('IN_MACRO'!$P$23=1,'IN_FIN'!$K$15,IF('IN_MACRO'!$P$23=2,'IN_FIN'!$L$15,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری آزمایشگاه و ابزار دقیق</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap.7</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$16*'ENG_SCEN'!$D$36)*(IF('IN_MACRO'!$D$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$D$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$D$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="E17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$16*'ENG_SCEN'!$E$36)*(IF('IN_MACRO'!$E$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$E$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$E$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="F17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$16*'ENG_SCEN'!$F$36)*(IF('IN_MACRO'!$F$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$F$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$F$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="G17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$16*'ENG_SCEN'!$G$36)*(IF('IN_MACRO'!$G$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$G$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$G$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="H17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$16*'ENG_SCEN'!$H$36)*(IF('IN_MACRO'!$H$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$H$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$H$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="I17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$16*'ENG_SCEN'!$I$36)*(IF('IN_MACRO'!$I$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$I$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$I$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="J17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$16*'ENG_SCEN'!$J$36)*(IF('IN_MACRO'!$J$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$J$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$J$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="K17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$16*'ENG_SCEN'!$K$36)*(IF('IN_MACRO'!$K$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$K$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$K$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="L17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$16*'ENG_SCEN'!$L$36)*(IF('IN_MACRO'!$L$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$L$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$L$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="M17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$16*'ENG_SCEN'!$M$36)*(IF('IN_MACRO'!$M$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$M$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$M$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="N17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$16*'ENG_SCEN'!$N$36)*(IF('IN_MACRO'!$N$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$N$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$N$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="O17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$16*'ENG_SCEN'!$O$36)*(IF('IN_MACRO'!$O$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$O$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$O$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="P17" s="14">
+        <f>'IN_FIN'!$D$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$16*'ENG_SCEN'!$P$36)*(IF('IN_MACRO'!$P$23=0,'IN_FIN'!$J$16,IF('IN_MACRO'!$P$23=1,'IN_FIN'!$K$16,IF('IN_MACRO'!$P$23=2,'IN_FIN'!$L$16,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری مهندسی، نصب و راه‌اندازی</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap.8</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$17*'ENG_SCEN'!$D$36)*(IF('IN_MACRO'!$D$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$D$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$D$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="E18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$17*'ENG_SCEN'!$E$36)*(IF('IN_MACRO'!$E$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$E$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$E$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="F18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$17*'ENG_SCEN'!$F$36)*(IF('IN_MACRO'!$F$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$F$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$F$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="G18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$17*'ENG_SCEN'!$G$36)*(IF('IN_MACRO'!$G$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$G$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$G$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="H18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$17*'ENG_SCEN'!$H$36)*(IF('IN_MACRO'!$H$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$H$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$H$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="I18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$17*'ENG_SCEN'!$I$36)*(IF('IN_MACRO'!$I$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$I$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$I$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="J18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$17*'ENG_SCEN'!$J$36)*(IF('IN_MACRO'!$J$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$J$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$J$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="K18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$17*'ENG_SCEN'!$K$36)*(IF('IN_MACRO'!$K$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$K$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$K$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="L18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$17*'ENG_SCEN'!$L$36)*(IF('IN_MACRO'!$L$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$L$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$L$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="M18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$17*'ENG_SCEN'!$M$36)*(IF('IN_MACRO'!$M$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$M$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$M$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="N18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$17*'ENG_SCEN'!$N$36)*(IF('IN_MACRO'!$N$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$N$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$N$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="O18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$17*'ENG_SCEN'!$O$36)*(IF('IN_MACRO'!$O$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$O$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$O$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="P18" s="14">
+        <f>'IN_FIN'!$D$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$17*'ENG_SCEN'!$P$36)*(IF('IN_MACRO'!$P$23=0,'IN_FIN'!$J$17,IF('IN_MACRO'!$P$23=1,'IN_FIN'!$K$17,IF('IN_MACRO'!$P$23=2,'IN_FIN'!$L$17,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری هزینه‌های پیش از بهره‌برداری</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap.9</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$18*'ENG_SCEN'!$D$36)*(IF('IN_MACRO'!$D$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$D$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$D$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="E19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$18*'ENG_SCEN'!$E$36)*(IF('IN_MACRO'!$E$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$E$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$E$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="F19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$18*'ENG_SCEN'!$F$36)*(IF('IN_MACRO'!$F$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$F$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$F$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="G19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$18*'ENG_SCEN'!$G$36)*(IF('IN_MACRO'!$G$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$G$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$G$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="H19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$18*'ENG_SCEN'!$H$36)*(IF('IN_MACRO'!$H$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$H$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$H$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="I19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$18*'ENG_SCEN'!$I$36)*(IF('IN_MACRO'!$I$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$I$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$I$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="J19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$18*'ENG_SCEN'!$J$36)*(IF('IN_MACRO'!$J$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$J$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$J$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="K19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$18*'ENG_SCEN'!$K$36)*(IF('IN_MACRO'!$K$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$K$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$K$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="L19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$18*'ENG_SCEN'!$L$36)*(IF('IN_MACRO'!$L$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$L$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$L$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="M19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$18*'ENG_SCEN'!$M$36)*(IF('IN_MACRO'!$M$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$M$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$M$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="N19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$18*'ENG_SCEN'!$N$36)*(IF('IN_MACRO'!$N$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$N$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$N$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="O19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$18*'ENG_SCEN'!$O$36)*(IF('IN_MACRO'!$O$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$O$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$O$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="P19" s="14">
+        <f>'IN_FIN'!$D$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$18*'ENG_SCEN'!$P$36)*(IF('IN_MACRO'!$P$23=0,'IN_FIN'!$J$18,IF('IN_MACRO'!$P$23=1,'IN_FIN'!$K$18,IF('IN_MACRO'!$P$23=2,'IN_FIN'!$L$18,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری ذخیره احتیاطی فیزیکی</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap.10</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$19*'ENG_SCEN'!$D$36)*(IF('IN_MACRO'!$D$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$D$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$D$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="E20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$19*'ENG_SCEN'!$E$36)*(IF('IN_MACRO'!$E$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$E$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$E$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="F20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$19*'ENG_SCEN'!$F$36)*(IF('IN_MACRO'!$F$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$F$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$F$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="G20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$19*'ENG_SCEN'!$G$36)*(IF('IN_MACRO'!$G$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$G$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$G$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="H20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$19*'ENG_SCEN'!$H$36)*(IF('IN_MACRO'!$H$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$H$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$H$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="I20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$19*'ENG_SCEN'!$I$36)*(IF('IN_MACRO'!$I$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$I$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$I$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="J20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$19*'ENG_SCEN'!$J$36)*(IF('IN_MACRO'!$J$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$J$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$J$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="K20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$19*'ENG_SCEN'!$K$36)*(IF('IN_MACRO'!$K$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$K$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$K$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="L20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$19*'ENG_SCEN'!$L$36)*(IF('IN_MACRO'!$L$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$L$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$L$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="M20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$19*'ENG_SCEN'!$M$36)*(IF('IN_MACRO'!$M$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$M$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$M$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="N20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$19*'ENG_SCEN'!$N$36)*(IF('IN_MACRO'!$N$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$N$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$N$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="O20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$19*'ENG_SCEN'!$O$36)*(IF('IN_MACRO'!$O$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$O$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$O$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+      <c r="P20" s="14">
+        <f>'IN_FIN'!$D$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$19*'ENG_SCEN'!$P$36)*(IF('IN_MACRO'!$P$23=0,'IN_FIN'!$J$19,IF('IN_MACRO'!$P$23=1,'IN_FIN'!$K$19,IF('IN_MACRO'!$P$23=2,'IN_FIN'!$L$19,0))))*'ENG_SCEN'!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>جمع سرمایه‌گذاری ثابت</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap_total</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D21" s="14">
+        <f>'ENG_CAPEX'!$D$10+'ENG_CAPEX'!$D$11+'ENG_CAPEX'!$D$12+'ENG_CAPEX'!$D$13+'ENG_CAPEX'!$D$14+'ENG_CAPEX'!$D$15+'ENG_CAPEX'!$D$16+'ENG_CAPEX'!$D$17+'ENG_CAPEX'!$D$18+'ENG_CAPEX'!$D$19+'ENG_CAPEX'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E21" s="14">
+        <f>'ENG_CAPEX'!$E$10+'ENG_CAPEX'!$E$11+'ENG_CAPEX'!$E$12+'ENG_CAPEX'!$E$13+'ENG_CAPEX'!$E$14+'ENG_CAPEX'!$E$15+'ENG_CAPEX'!$E$16+'ENG_CAPEX'!$E$17+'ENG_CAPEX'!$E$18+'ENG_CAPEX'!$E$19+'ENG_CAPEX'!$E$20</f>
+        <v/>
+      </c>
+      <c r="F21" s="14">
+        <f>'ENG_CAPEX'!$F$10+'ENG_CAPEX'!$F$11+'ENG_CAPEX'!$F$12+'ENG_CAPEX'!$F$13+'ENG_CAPEX'!$F$14+'ENG_CAPEX'!$F$15+'ENG_CAPEX'!$F$16+'ENG_CAPEX'!$F$17+'ENG_CAPEX'!$F$18+'ENG_CAPEX'!$F$19+'ENG_CAPEX'!$F$20</f>
+        <v/>
+      </c>
+      <c r="G21" s="14">
+        <f>'ENG_CAPEX'!$G$10+'ENG_CAPEX'!$G$11+'ENG_CAPEX'!$G$12+'ENG_CAPEX'!$G$13+'ENG_CAPEX'!$G$14+'ENG_CAPEX'!$G$15+'ENG_CAPEX'!$G$16+'ENG_CAPEX'!$G$17+'ENG_CAPEX'!$G$18+'ENG_CAPEX'!$G$19+'ENG_CAPEX'!$G$20</f>
+        <v/>
+      </c>
+      <c r="H21" s="14">
+        <f>'ENG_CAPEX'!$H$10+'ENG_CAPEX'!$H$11+'ENG_CAPEX'!$H$12+'ENG_CAPEX'!$H$13+'ENG_CAPEX'!$H$14+'ENG_CAPEX'!$H$15+'ENG_CAPEX'!$H$16+'ENG_CAPEX'!$H$17+'ENG_CAPEX'!$H$18+'ENG_CAPEX'!$H$19+'ENG_CAPEX'!$H$20</f>
+        <v/>
+      </c>
+      <c r="I21" s="14">
+        <f>'ENG_CAPEX'!$I$10+'ENG_CAPEX'!$I$11+'ENG_CAPEX'!$I$12+'ENG_CAPEX'!$I$13+'ENG_CAPEX'!$I$14+'ENG_CAPEX'!$I$15+'ENG_CAPEX'!$I$16+'ENG_CAPEX'!$I$17+'ENG_CAPEX'!$I$18+'ENG_CAPEX'!$I$19+'ENG_CAPEX'!$I$20</f>
+        <v/>
+      </c>
+      <c r="J21" s="14">
+        <f>'ENG_CAPEX'!$J$10+'ENG_CAPEX'!$J$11+'ENG_CAPEX'!$J$12+'ENG_CAPEX'!$J$13+'ENG_CAPEX'!$J$14+'ENG_CAPEX'!$J$15+'ENG_CAPEX'!$J$16+'ENG_CAPEX'!$J$17+'ENG_CAPEX'!$J$18+'ENG_CAPEX'!$J$19+'ENG_CAPEX'!$J$20</f>
+        <v/>
+      </c>
+      <c r="K21" s="14">
+        <f>'ENG_CAPEX'!$K$10+'ENG_CAPEX'!$K$11+'ENG_CAPEX'!$K$12+'ENG_CAPEX'!$K$13+'ENG_CAPEX'!$K$14+'ENG_CAPEX'!$K$15+'ENG_CAPEX'!$K$16+'ENG_CAPEX'!$K$17+'ENG_CAPEX'!$K$18+'ENG_CAPEX'!$K$19+'ENG_CAPEX'!$K$20</f>
+        <v/>
+      </c>
+      <c r="L21" s="14">
+        <f>'ENG_CAPEX'!$L$10+'ENG_CAPEX'!$L$11+'ENG_CAPEX'!$L$12+'ENG_CAPEX'!$L$13+'ENG_CAPEX'!$L$14+'ENG_CAPEX'!$L$15+'ENG_CAPEX'!$L$16+'ENG_CAPEX'!$L$17+'ENG_CAPEX'!$L$18+'ENG_CAPEX'!$L$19+'ENG_CAPEX'!$L$20</f>
+        <v/>
+      </c>
+      <c r="M21" s="14">
+        <f>'ENG_CAPEX'!$M$10+'ENG_CAPEX'!$M$11+'ENG_CAPEX'!$M$12+'ENG_CAPEX'!$M$13+'ENG_CAPEX'!$M$14+'ENG_CAPEX'!$M$15+'ENG_CAPEX'!$M$16+'ENG_CAPEX'!$M$17+'ENG_CAPEX'!$M$18+'ENG_CAPEX'!$M$19+'ENG_CAPEX'!$M$20</f>
+        <v/>
+      </c>
+      <c r="N21" s="14">
+        <f>'ENG_CAPEX'!$N$10+'ENG_CAPEX'!$N$11+'ENG_CAPEX'!$N$12+'ENG_CAPEX'!$N$13+'ENG_CAPEX'!$N$14+'ENG_CAPEX'!$N$15+'ENG_CAPEX'!$N$16+'ENG_CAPEX'!$N$17+'ENG_CAPEX'!$N$18+'ENG_CAPEX'!$N$19+'ENG_CAPEX'!$N$20</f>
+        <v/>
+      </c>
+      <c r="O21" s="14">
+        <f>'ENG_CAPEX'!$O$10+'ENG_CAPEX'!$O$11+'ENG_CAPEX'!$O$12+'ENG_CAPEX'!$O$13+'ENG_CAPEX'!$O$14+'ENG_CAPEX'!$O$15+'ENG_CAPEX'!$O$16+'ENG_CAPEX'!$O$17+'ENG_CAPEX'!$O$18+'ENG_CAPEX'!$O$19+'ENG_CAPEX'!$O$20</f>
+        <v/>
+      </c>
+      <c r="P21" s="14">
+        <f>'ENG_CAPEX'!$P$10+'ENG_CAPEX'!$P$11+'ENG_CAPEX'!$P$12+'ENG_CAPEX'!$P$13+'ENG_CAPEX'!$P$14+'ENG_CAPEX'!$P$15+'ENG_CAPEX'!$P$16+'ENG_CAPEX'!$P$17+'ENG_CAPEX'!$P$18+'ENG_CAPEX'!$P$19+'ENG_CAPEX'!$P$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>مانده تجمعی تزریق سرمایه‌گذاری</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.cap_cum</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D22" s="14">
+        <f>'ENG_CAPEX'!$D$21</f>
+        <v/>
+      </c>
+      <c r="E22" s="14">
+        <f>'ENG_CAPEX'!$D$22+'ENG_CAPEX'!$E$21</f>
+        <v/>
+      </c>
+      <c r="F22" s="14">
+        <f>'ENG_CAPEX'!$E$22+'ENG_CAPEX'!$F$21</f>
+        <v/>
+      </c>
+      <c r="G22" s="14">
+        <f>'ENG_CAPEX'!$F$22+'ENG_CAPEX'!$G$21</f>
+        <v/>
+      </c>
+      <c r="H22" s="14">
+        <f>'ENG_CAPEX'!$G$22+'ENG_CAPEX'!$H$21</f>
+        <v/>
+      </c>
+      <c r="I22" s="14">
+        <f>'ENG_CAPEX'!$H$22+'ENG_CAPEX'!$I$21</f>
+        <v/>
+      </c>
+      <c r="J22" s="14">
+        <f>'ENG_CAPEX'!$I$22+'ENG_CAPEX'!$J$21</f>
+        <v/>
+      </c>
+      <c r="K22" s="14">
+        <f>'ENG_CAPEX'!$J$22+'ENG_CAPEX'!$K$21</f>
+        <v/>
+      </c>
+      <c r="L22" s="14">
+        <f>'ENG_CAPEX'!$K$22+'ENG_CAPEX'!$L$21</f>
+        <v/>
+      </c>
+      <c r="M22" s="14">
+        <f>'ENG_CAPEX'!$L$22+'ENG_CAPEX'!$M$21</f>
+        <v/>
+      </c>
+      <c r="N22" s="14">
+        <f>'ENG_CAPEX'!$M$22+'ENG_CAPEX'!$N$21</f>
+        <v/>
+      </c>
+      <c r="O22" s="14">
+        <f>'ENG_CAPEX'!$N$22+'ENG_CAPEX'!$O$21</f>
+        <v/>
+      </c>
+      <c r="P22" s="14">
+        <f>'ENG_CAPEX'!$O$22+'ENG_CAPEX'!$P$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>سهم ارزیِ وزنیِ CAPEX</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.fxsh</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+      <c r="E23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+      <c r="F23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+      <c r="I23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+      <c r="J23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+      <c r="K23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+      <c r="L23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+      <c r="M23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+      <c r="N23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+      <c r="O23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+      <c r="P23" s="11">
+        <f>IFERROR((('IN_FIN'!$D$9*'IN_FIN'!$E$9)+('IN_FIN'!$D$10*'IN_FIN'!$E$10)+('IN_FIN'!$D$11*'IN_FIN'!$E$11)+('IN_FIN'!$D$12*'IN_FIN'!$E$12)+('IN_FIN'!$D$13*'IN_FIN'!$E$13)+('IN_FIN'!$D$14*'IN_FIN'!$E$14)+('IN_FIN'!$D$15*'IN_FIN'!$E$15)+('IN_FIN'!$D$16*'IN_FIN'!$E$16)+('IN_FIN'!$D$17*'IN_FIN'!$E$17)+('IN_FIN'!$D$18*'IN_FIN'!$E$18)+('IN_FIN'!$D$19*'IN_FIN'!$E$19))/('IN_FIN'!$D$9+'IN_FIN'!$D$10+'IN_FIN'!$D$11+'IN_FIN'!$D$12+'IN_FIN'!$D$13+'IN_FIN'!$D$14+'IN_FIN'!$D$15+'IN_FIN'!$D$16+'IN_FIN'!$D$17+'IN_FIN'!$D$18+'IN_FIN'!$D$19),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>ب) سود سرمایه‌گذاری حین ساخت (IDC)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="7" t="n"/>
+      <c r="O25" s="7" t="n"/>
+      <c r="P25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>مانده تسهیلات در ابتدای دوره (دوره ساخت)</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.debt_open</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D26" s="14">
+        <f>'IN_FIN'!$D$24*(0)</f>
+        <v/>
+      </c>
+      <c r="E26" s="14">
+        <f>'IN_FIN'!$D$24*('ENG_CAPEX'!$D$22+'ENG_CAPEX'!$D$28)</f>
+        <v/>
+      </c>
+      <c r="F26" s="14">
+        <f>'IN_FIN'!$D$24*('ENG_CAPEX'!$E$22+'ENG_CAPEX'!$E$28)</f>
+        <v/>
+      </c>
+      <c r="G26" s="14">
+        <f>'IN_FIN'!$D$24*('ENG_CAPEX'!$F$22+'ENG_CAPEX'!$F$28)</f>
+        <v/>
+      </c>
+      <c r="H26" s="14">
+        <f>'IN_FIN'!$D$24*('ENG_CAPEX'!$G$22+'ENG_CAPEX'!$G$28)</f>
+        <v/>
+      </c>
+      <c r="I26" s="14">
+        <f>'IN_FIN'!$D$24*('ENG_CAPEX'!$H$22+'ENG_CAPEX'!$H$28)</f>
+        <v/>
+      </c>
+      <c r="J26" s="14">
+        <f>'IN_FIN'!$D$24*('ENG_CAPEX'!$I$22+'ENG_CAPEX'!$I$28)</f>
+        <v/>
+      </c>
+      <c r="K26" s="14">
+        <f>'IN_FIN'!$D$24*('ENG_CAPEX'!$J$22+'ENG_CAPEX'!$J$28)</f>
+        <v/>
+      </c>
+      <c r="L26" s="14">
+        <f>'IN_FIN'!$D$24*('ENG_CAPEX'!$K$22+'ENG_CAPEX'!$K$28)</f>
+        <v/>
+      </c>
+      <c r="M26" s="14">
+        <f>'IN_FIN'!$D$24*('ENG_CAPEX'!$L$22+'ENG_CAPEX'!$L$28)</f>
+        <v/>
+      </c>
+      <c r="N26" s="14">
+        <f>'IN_FIN'!$D$24*('ENG_CAPEX'!$M$22+'ENG_CAPEX'!$M$28)</f>
+        <v/>
+      </c>
+      <c r="O26" s="14">
+        <f>'IN_FIN'!$D$24*('ENG_CAPEX'!$N$22+'ENG_CAPEX'!$N$28)</f>
+        <v/>
+      </c>
+      <c r="P26" s="14">
+        <f>'IN_FIN'!$D$24*('ENG_CAPEX'!$O$22+'ENG_CAPEX'!$O$28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IDC (سرمایه‌ای‌شده)</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.idc</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D27" s="14">
+        <f>IF('IN_MACRO'!$D$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$D$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$D$21/2),0)</f>
+        <v/>
+      </c>
+      <c r="E27" s="14">
+        <f>IF('IN_MACRO'!$E$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$E$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$E$21/2),0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="14">
+        <f>IF('IN_MACRO'!$F$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$F$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$F$21/2),0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="14">
+        <f>IF('IN_MACRO'!$G$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$G$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$G$21/2),0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="14">
+        <f>IF('IN_MACRO'!$H$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$H$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$H$21/2),0)</f>
+        <v/>
+      </c>
+      <c r="I27" s="14">
+        <f>IF('IN_MACRO'!$I$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$I$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$I$21/2),0)</f>
+        <v/>
+      </c>
+      <c r="J27" s="14">
+        <f>IF('IN_MACRO'!$J$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$J$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$J$21/2),0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="14">
+        <f>IF('IN_MACRO'!$K$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$K$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$K$21/2),0)</f>
+        <v/>
+      </c>
+      <c r="L27" s="14">
+        <f>IF('IN_MACRO'!$L$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$L$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$L$21/2),0)</f>
+        <v/>
+      </c>
+      <c r="M27" s="14">
+        <f>IF('IN_MACRO'!$M$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$M$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$M$21/2),0)</f>
+        <v/>
+      </c>
+      <c r="N27" s="14">
+        <f>IF('IN_MACRO'!$N$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$N$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$N$21/2),0)</f>
+        <v/>
+      </c>
+      <c r="O27" s="14">
+        <f>IF('IN_MACRO'!$O$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$O$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$O$21/2),0)</f>
+        <v/>
+      </c>
+      <c r="P27" s="14">
+        <f>IF('IN_MACRO'!$P$33=1,'IN_FIN'!$D$25*('ENG_CAPEX'!$P$26+'IN_FIN'!$D$24*'ENG_CAPEX'!$P$21/2),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>مانده تجمعی IDC</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.idc_cum</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D28" s="14">
+        <f>'ENG_CAPEX'!$D$27</f>
+        <v/>
+      </c>
+      <c r="E28" s="14">
+        <f>'ENG_CAPEX'!$D$28+'ENG_CAPEX'!$E$27</f>
+        <v/>
+      </c>
+      <c r="F28" s="14">
+        <f>'ENG_CAPEX'!$E$28+'ENG_CAPEX'!$F$27</f>
+        <v/>
+      </c>
+      <c r="G28" s="14">
+        <f>'ENG_CAPEX'!$F$28+'ENG_CAPEX'!$G$27</f>
+        <v/>
+      </c>
+      <c r="H28" s="14">
+        <f>'ENG_CAPEX'!$G$28+'ENG_CAPEX'!$H$27</f>
+        <v/>
+      </c>
+      <c r="I28" s="14">
+        <f>'ENG_CAPEX'!$H$28+'ENG_CAPEX'!$I$27</f>
+        <v/>
+      </c>
+      <c r="J28" s="14">
+        <f>'ENG_CAPEX'!$I$28+'ENG_CAPEX'!$J$27</f>
+        <v/>
+      </c>
+      <c r="K28" s="14">
+        <f>'ENG_CAPEX'!$J$28+'ENG_CAPEX'!$K$27</f>
+        <v/>
+      </c>
+      <c r="L28" s="14">
+        <f>'ENG_CAPEX'!$K$28+'ENG_CAPEX'!$L$27</f>
+        <v/>
+      </c>
+      <c r="M28" s="14">
+        <f>'ENG_CAPEX'!$L$28+'ENG_CAPEX'!$M$27</f>
+        <v/>
+      </c>
+      <c r="N28" s="14">
+        <f>'ENG_CAPEX'!$M$28+'ENG_CAPEX'!$N$27</f>
+        <v/>
+      </c>
+      <c r="O28" s="14">
+        <f>'ENG_CAPEX'!$N$28+'ENG_CAPEX'!$O$27</f>
+        <v/>
+      </c>
+      <c r="P28" s="14">
+        <f>'ENG_CAPEX'!$O$28+'ENG_CAPEX'!$P$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>ج) جایگزینی دارایی‌ها</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
+      <c r="K30" s="7" t="n"/>
+      <c r="L30" s="7" t="n"/>
+      <c r="M30" s="7" t="n"/>
+      <c r="N30" s="7" t="n"/>
+      <c r="O30" s="7" t="n"/>
+      <c r="P30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>جایگزینی زمین</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.repl.0</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$D$23=0),0,IF(AND(MOD('IN_MACRO'!$D$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$9*'ENG_SCEN'!$D$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="E31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$E$23=0),0,IF(AND(MOD('IN_MACRO'!$E$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$9*'ENG_SCEN'!$E$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="F31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$F$23=0),0,IF(AND(MOD('IN_MACRO'!$F$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$9*'ENG_SCEN'!$F$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="G31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$G$23=0),0,IF(AND(MOD('IN_MACRO'!$G$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$9*'ENG_SCEN'!$G$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="H31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$H$23=0),0,IF(AND(MOD('IN_MACRO'!$H$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$9*'ENG_SCEN'!$H$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="I31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$I$23=0),0,IF(AND(MOD('IN_MACRO'!$I$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$9*'ENG_SCEN'!$I$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="J31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$J$23=0),0,IF(AND(MOD('IN_MACRO'!$J$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$9*'ENG_SCEN'!$J$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="K31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$K$23=0),0,IF(AND(MOD('IN_MACRO'!$K$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$9*'ENG_SCEN'!$K$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="L31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$L$23=0),0,IF(AND(MOD('IN_MACRO'!$L$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$9*'ENG_SCEN'!$L$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="M31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$M$23=0),0,IF(AND(MOD('IN_MACRO'!$M$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$9*'ENG_SCEN'!$M$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="N31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$N$23=0),0,IF(AND(MOD('IN_MACRO'!$N$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$9*'ENG_SCEN'!$N$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="O31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$O$23=0),0,IF(AND(MOD('IN_MACRO'!$O$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$9*'ENG_SCEN'!$O$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="P31" s="14">
+        <f>IF(OR('IN_FIN'!$F$9&lt;=0,'IN_FIN'!$G$9&lt;=0,'IN_MACRO'!$P$23=0),0,IF(AND(MOD('IN_MACRO'!$P$23,'IN_FIN'!$G$9)=0,'IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$9*'IN_FIN'!$H$9*((1-'IN_FIN'!$E$9)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$9*'ENG_SCEN'!$P$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>جایگزینی محوطه‌سازی و ساختمان</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.repl.1</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$D$23=0),0,IF(AND(MOD('IN_MACRO'!$D$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$10*'ENG_SCEN'!$D$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="E32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$E$23=0),0,IF(AND(MOD('IN_MACRO'!$E$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$10*'ENG_SCEN'!$E$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="F32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$F$23=0),0,IF(AND(MOD('IN_MACRO'!$F$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$10*'ENG_SCEN'!$F$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="G32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$G$23=0),0,IF(AND(MOD('IN_MACRO'!$G$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$10*'ENG_SCEN'!$G$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="H32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$H$23=0),0,IF(AND(MOD('IN_MACRO'!$H$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$10*'ENG_SCEN'!$H$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="I32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$I$23=0),0,IF(AND(MOD('IN_MACRO'!$I$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$10*'ENG_SCEN'!$I$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="J32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$J$23=0),0,IF(AND(MOD('IN_MACRO'!$J$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$10*'ENG_SCEN'!$J$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="K32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$K$23=0),0,IF(AND(MOD('IN_MACRO'!$K$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$10*'ENG_SCEN'!$K$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="L32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$L$23=0),0,IF(AND(MOD('IN_MACRO'!$L$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$10*'ENG_SCEN'!$L$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="M32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$M$23=0),0,IF(AND(MOD('IN_MACRO'!$M$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$10*'ENG_SCEN'!$M$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="N32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$N$23=0),0,IF(AND(MOD('IN_MACRO'!$N$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$10*'ENG_SCEN'!$N$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="O32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$O$23=0),0,IF(AND(MOD('IN_MACRO'!$O$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$10*'ENG_SCEN'!$O$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="P32" s="14">
+        <f>IF(OR('IN_FIN'!$F$10&lt;=0,'IN_FIN'!$G$10&lt;=0,'IN_MACRO'!$P$23=0),0,IF(AND(MOD('IN_MACRO'!$P$23,'IN_FIN'!$G$10)=0,'IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$10*'IN_FIN'!$H$10*((1-'IN_FIN'!$E$10)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$10*'ENG_SCEN'!$P$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>جایگزینی ماشین‌آلات وارداتی</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.repl.2</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$D$23=0),0,IF(AND(MOD('IN_MACRO'!$D$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$11*'ENG_SCEN'!$D$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="E33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$E$23=0),0,IF(AND(MOD('IN_MACRO'!$E$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$11*'ENG_SCEN'!$E$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="F33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$F$23=0),0,IF(AND(MOD('IN_MACRO'!$F$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$11*'ENG_SCEN'!$F$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="G33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$G$23=0),0,IF(AND(MOD('IN_MACRO'!$G$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$11*'ENG_SCEN'!$G$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="H33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$H$23=0),0,IF(AND(MOD('IN_MACRO'!$H$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$11*'ENG_SCEN'!$H$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="I33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$I$23=0),0,IF(AND(MOD('IN_MACRO'!$I$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$11*'ENG_SCEN'!$I$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="J33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$J$23=0),0,IF(AND(MOD('IN_MACRO'!$J$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$11*'ENG_SCEN'!$J$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="K33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$K$23=0),0,IF(AND(MOD('IN_MACRO'!$K$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$11*'ENG_SCEN'!$K$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="L33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$L$23=0),0,IF(AND(MOD('IN_MACRO'!$L$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$11*'ENG_SCEN'!$L$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="M33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$M$23=0),0,IF(AND(MOD('IN_MACRO'!$M$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$11*'ENG_SCEN'!$M$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="N33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$N$23=0),0,IF(AND(MOD('IN_MACRO'!$N$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$11*'ENG_SCEN'!$N$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="O33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$O$23=0),0,IF(AND(MOD('IN_MACRO'!$O$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$11*'ENG_SCEN'!$O$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="P33" s="14">
+        <f>IF(OR('IN_FIN'!$F$11&lt;=0,'IN_FIN'!$G$11&lt;=0,'IN_MACRO'!$P$23=0),0,IF(AND(MOD('IN_MACRO'!$P$23,'IN_FIN'!$G$11)=0,'IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$11*'IN_FIN'!$H$11*((1-'IN_FIN'!$E$11)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$11*'ENG_SCEN'!$P$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>جایگزینی ماشین‌آلات داخلی</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.repl.3</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$D$23=0),0,IF(AND(MOD('IN_MACRO'!$D$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$12*'ENG_SCEN'!$D$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="E34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$E$23=0),0,IF(AND(MOD('IN_MACRO'!$E$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$12*'ENG_SCEN'!$E$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="F34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$F$23=0),0,IF(AND(MOD('IN_MACRO'!$F$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$12*'ENG_SCEN'!$F$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="G34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$G$23=0),0,IF(AND(MOD('IN_MACRO'!$G$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$12*'ENG_SCEN'!$G$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="H34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$H$23=0),0,IF(AND(MOD('IN_MACRO'!$H$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$12*'ENG_SCEN'!$H$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="I34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$I$23=0),0,IF(AND(MOD('IN_MACRO'!$I$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$12*'ENG_SCEN'!$I$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="J34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$J$23=0),0,IF(AND(MOD('IN_MACRO'!$J$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$12*'ENG_SCEN'!$J$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="K34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$K$23=0),0,IF(AND(MOD('IN_MACRO'!$K$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$12*'ENG_SCEN'!$K$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="L34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$L$23=0),0,IF(AND(MOD('IN_MACRO'!$L$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$12*'ENG_SCEN'!$L$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="M34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$M$23=0),0,IF(AND(MOD('IN_MACRO'!$M$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$12*'ENG_SCEN'!$M$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="N34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$N$23=0),0,IF(AND(MOD('IN_MACRO'!$N$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$12*'ENG_SCEN'!$N$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="O34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$O$23=0),0,IF(AND(MOD('IN_MACRO'!$O$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$12*'ENG_SCEN'!$O$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="P34" s="14">
+        <f>IF(OR('IN_FIN'!$F$12&lt;=0,'IN_FIN'!$G$12&lt;=0,'IN_MACRO'!$P$23=0),0,IF(AND(MOD('IN_MACRO'!$P$23,'IN_FIN'!$G$12)=0,'IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$12*'IN_FIN'!$H$12*((1-'IN_FIN'!$E$12)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$12*'ENG_SCEN'!$P$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>جایگزینی تأسیسات و تجهیزات جانبی</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.repl.4</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$D$23=0),0,IF(AND(MOD('IN_MACRO'!$D$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$13*'ENG_SCEN'!$D$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="E35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$E$23=0),0,IF(AND(MOD('IN_MACRO'!$E$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$13*'ENG_SCEN'!$E$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="F35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$F$23=0),0,IF(AND(MOD('IN_MACRO'!$F$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$13*'ENG_SCEN'!$F$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="G35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$G$23=0),0,IF(AND(MOD('IN_MACRO'!$G$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$13*'ENG_SCEN'!$G$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="H35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$H$23=0),0,IF(AND(MOD('IN_MACRO'!$H$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$13*'ENG_SCEN'!$H$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="I35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$I$23=0),0,IF(AND(MOD('IN_MACRO'!$I$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$13*'ENG_SCEN'!$I$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="J35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$J$23=0),0,IF(AND(MOD('IN_MACRO'!$J$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$13*'ENG_SCEN'!$J$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="K35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$K$23=0),0,IF(AND(MOD('IN_MACRO'!$K$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$13*'ENG_SCEN'!$K$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="L35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$L$23=0),0,IF(AND(MOD('IN_MACRO'!$L$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$13*'ENG_SCEN'!$L$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="M35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$M$23=0),0,IF(AND(MOD('IN_MACRO'!$M$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$13*'ENG_SCEN'!$M$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="N35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$N$23=0),0,IF(AND(MOD('IN_MACRO'!$N$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$13*'ENG_SCEN'!$N$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="O35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$O$23=0),0,IF(AND(MOD('IN_MACRO'!$O$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$13*'ENG_SCEN'!$O$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="P35" s="14">
+        <f>IF(OR('IN_FIN'!$F$13&lt;=0,'IN_FIN'!$G$13&lt;=0,'IN_MACRO'!$P$23=0),0,IF(AND(MOD('IN_MACRO'!$P$23,'IN_FIN'!$G$13)=0,'IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$13*'IN_FIN'!$H$13*((1-'IN_FIN'!$E$13)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$13*'ENG_SCEN'!$P$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>جایگزینی تصفیه‌خانه و تجهیزات زیست‌محیطی</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.repl.5</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$D$23=0),0,IF(AND(MOD('IN_MACRO'!$D$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$14*'ENG_SCEN'!$D$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="E36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$E$23=0),0,IF(AND(MOD('IN_MACRO'!$E$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$14*'ENG_SCEN'!$E$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="F36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$F$23=0),0,IF(AND(MOD('IN_MACRO'!$F$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$14*'ENG_SCEN'!$F$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="G36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$G$23=0),0,IF(AND(MOD('IN_MACRO'!$G$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$14*'ENG_SCEN'!$G$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="H36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$H$23=0),0,IF(AND(MOD('IN_MACRO'!$H$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$14*'ENG_SCEN'!$H$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="I36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$I$23=0),0,IF(AND(MOD('IN_MACRO'!$I$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$14*'ENG_SCEN'!$I$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="J36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$J$23=0),0,IF(AND(MOD('IN_MACRO'!$J$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$14*'ENG_SCEN'!$J$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="K36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$K$23=0),0,IF(AND(MOD('IN_MACRO'!$K$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$14*'ENG_SCEN'!$K$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="L36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$L$23=0),0,IF(AND(MOD('IN_MACRO'!$L$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$14*'ENG_SCEN'!$L$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="M36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$M$23=0),0,IF(AND(MOD('IN_MACRO'!$M$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$14*'ENG_SCEN'!$M$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="N36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$N$23=0),0,IF(AND(MOD('IN_MACRO'!$N$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$14*'ENG_SCEN'!$N$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="O36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$O$23=0),0,IF(AND(MOD('IN_MACRO'!$O$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$14*'ENG_SCEN'!$O$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="P36" s="14">
+        <f>IF(OR('IN_FIN'!$F$14&lt;=0,'IN_FIN'!$G$14&lt;=0,'IN_MACRO'!$P$23=0),0,IF(AND(MOD('IN_MACRO'!$P$23,'IN_FIN'!$G$14)=0,'IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$14*'IN_FIN'!$H$14*((1-'IN_FIN'!$E$14)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$14*'ENG_SCEN'!$P$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>جایگزینی تجهیزات حمل‌ونقل داخلی</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.repl.6</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$D$23=0),0,IF(AND(MOD('IN_MACRO'!$D$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$15*'ENG_SCEN'!$D$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="E37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$E$23=0),0,IF(AND(MOD('IN_MACRO'!$E$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$15*'ENG_SCEN'!$E$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="F37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$F$23=0),0,IF(AND(MOD('IN_MACRO'!$F$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$15*'ENG_SCEN'!$F$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="G37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$G$23=0),0,IF(AND(MOD('IN_MACRO'!$G$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$15*'ENG_SCEN'!$G$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="H37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$H$23=0),0,IF(AND(MOD('IN_MACRO'!$H$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$15*'ENG_SCEN'!$H$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="I37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$I$23=0),0,IF(AND(MOD('IN_MACRO'!$I$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$15*'ENG_SCEN'!$I$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="J37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$J$23=0),0,IF(AND(MOD('IN_MACRO'!$J$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$15*'ENG_SCEN'!$J$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="K37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$K$23=0),0,IF(AND(MOD('IN_MACRO'!$K$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$15*'ENG_SCEN'!$K$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="L37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$L$23=0),0,IF(AND(MOD('IN_MACRO'!$L$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$15*'ENG_SCEN'!$L$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="M37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$M$23=0),0,IF(AND(MOD('IN_MACRO'!$M$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$15*'ENG_SCEN'!$M$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="N37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$N$23=0),0,IF(AND(MOD('IN_MACRO'!$N$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$15*'ENG_SCEN'!$N$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="O37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$O$23=0),0,IF(AND(MOD('IN_MACRO'!$O$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$15*'ENG_SCEN'!$O$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="P37" s="14">
+        <f>IF(OR('IN_FIN'!$F$15&lt;=0,'IN_FIN'!$G$15&lt;=0,'IN_MACRO'!$P$23=0),0,IF(AND(MOD('IN_MACRO'!$P$23,'IN_FIN'!$G$15)=0,'IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$15*'IN_FIN'!$H$15*((1-'IN_FIN'!$E$15)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$15*'ENG_SCEN'!$P$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>جایگزینی آزمایشگاه و ابزار دقیق</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.repl.7</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$D$23=0),0,IF(AND(MOD('IN_MACRO'!$D$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$16*'ENG_SCEN'!$D$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="E38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$E$23=0),0,IF(AND(MOD('IN_MACRO'!$E$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$16*'ENG_SCEN'!$E$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="F38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$F$23=0),0,IF(AND(MOD('IN_MACRO'!$F$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$16*'ENG_SCEN'!$F$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="G38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$G$23=0),0,IF(AND(MOD('IN_MACRO'!$G$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$16*'ENG_SCEN'!$G$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="H38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$H$23=0),0,IF(AND(MOD('IN_MACRO'!$H$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$16*'ENG_SCEN'!$H$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="I38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$I$23=0),0,IF(AND(MOD('IN_MACRO'!$I$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$16*'ENG_SCEN'!$I$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="J38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$J$23=0),0,IF(AND(MOD('IN_MACRO'!$J$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$16*'ENG_SCEN'!$J$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="K38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$K$23=0),0,IF(AND(MOD('IN_MACRO'!$K$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$16*'ENG_SCEN'!$K$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="L38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$L$23=0),0,IF(AND(MOD('IN_MACRO'!$L$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$16*'ENG_SCEN'!$L$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="M38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$M$23=0),0,IF(AND(MOD('IN_MACRO'!$M$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$16*'ENG_SCEN'!$M$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="N38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$N$23=0),0,IF(AND(MOD('IN_MACRO'!$N$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$16*'ENG_SCEN'!$N$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="O38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$O$23=0),0,IF(AND(MOD('IN_MACRO'!$O$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$16*'ENG_SCEN'!$O$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="P38" s="14">
+        <f>IF(OR('IN_FIN'!$F$16&lt;=0,'IN_FIN'!$G$16&lt;=0,'IN_MACRO'!$P$23=0),0,IF(AND(MOD('IN_MACRO'!$P$23,'IN_FIN'!$G$16)=0,'IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$16*'IN_FIN'!$H$16*((1-'IN_FIN'!$E$16)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$16*'ENG_SCEN'!$P$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>جایگزینی مهندسی، نصب و راه‌اندازی</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.repl.8</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$D$23=0),0,IF(AND(MOD('IN_MACRO'!$D$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$17*'ENG_SCEN'!$D$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="E39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$E$23=0),0,IF(AND(MOD('IN_MACRO'!$E$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$17*'ENG_SCEN'!$E$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="F39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$F$23=0),0,IF(AND(MOD('IN_MACRO'!$F$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$17*'ENG_SCEN'!$F$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="G39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$G$23=0),0,IF(AND(MOD('IN_MACRO'!$G$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$17*'ENG_SCEN'!$G$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="H39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$H$23=0),0,IF(AND(MOD('IN_MACRO'!$H$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$17*'ENG_SCEN'!$H$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="I39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$I$23=0),0,IF(AND(MOD('IN_MACRO'!$I$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$17*'ENG_SCEN'!$I$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="J39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$J$23=0),0,IF(AND(MOD('IN_MACRO'!$J$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$17*'ENG_SCEN'!$J$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="K39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$K$23=0),0,IF(AND(MOD('IN_MACRO'!$K$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$17*'ENG_SCEN'!$K$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="L39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$L$23=0),0,IF(AND(MOD('IN_MACRO'!$L$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$17*'ENG_SCEN'!$L$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="M39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$M$23=0),0,IF(AND(MOD('IN_MACRO'!$M$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$17*'ENG_SCEN'!$M$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="N39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$N$23=0),0,IF(AND(MOD('IN_MACRO'!$N$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$17*'ENG_SCEN'!$N$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="O39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$O$23=0),0,IF(AND(MOD('IN_MACRO'!$O$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$17*'ENG_SCEN'!$O$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="P39" s="14">
+        <f>IF(OR('IN_FIN'!$F$17&lt;=0,'IN_FIN'!$G$17&lt;=0,'IN_MACRO'!$P$23=0),0,IF(AND(MOD('IN_MACRO'!$P$23,'IN_FIN'!$G$17)=0,'IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$17*'IN_FIN'!$H$17*((1-'IN_FIN'!$E$17)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$17*'ENG_SCEN'!$P$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>جایگزینی هزینه‌های پیش از بهره‌برداری</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.repl.9</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$D$23=0),0,IF(AND(MOD('IN_MACRO'!$D$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$18*'ENG_SCEN'!$D$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="E40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$E$23=0),0,IF(AND(MOD('IN_MACRO'!$E$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$18*'ENG_SCEN'!$E$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="F40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$F$23=0),0,IF(AND(MOD('IN_MACRO'!$F$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$18*'ENG_SCEN'!$F$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="G40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$G$23=0),0,IF(AND(MOD('IN_MACRO'!$G$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$18*'ENG_SCEN'!$G$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="H40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$H$23=0),0,IF(AND(MOD('IN_MACRO'!$H$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$18*'ENG_SCEN'!$H$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="I40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$I$23=0),0,IF(AND(MOD('IN_MACRO'!$I$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$18*'ENG_SCEN'!$I$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="J40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$J$23=0),0,IF(AND(MOD('IN_MACRO'!$J$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$18*'ENG_SCEN'!$J$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="K40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$K$23=0),0,IF(AND(MOD('IN_MACRO'!$K$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$18*'ENG_SCEN'!$K$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="L40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$L$23=0),0,IF(AND(MOD('IN_MACRO'!$L$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$18*'ENG_SCEN'!$L$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="M40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$M$23=0),0,IF(AND(MOD('IN_MACRO'!$M$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$18*'ENG_SCEN'!$M$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="N40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$N$23=0),0,IF(AND(MOD('IN_MACRO'!$N$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$18*'ENG_SCEN'!$N$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="O40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$O$23=0),0,IF(AND(MOD('IN_MACRO'!$O$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$18*'ENG_SCEN'!$O$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="P40" s="14">
+        <f>IF(OR('IN_FIN'!$F$18&lt;=0,'IN_FIN'!$G$18&lt;=0,'IN_MACRO'!$P$23=0),0,IF(AND(MOD('IN_MACRO'!$P$23,'IN_FIN'!$G$18)=0,'IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$18*'IN_FIN'!$H$18*((1-'IN_FIN'!$E$18)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$18*'ENG_SCEN'!$P$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>جایگزینی ذخیره احتیاطی فیزیکی</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.repl.10</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$D$23=0),0,IF(AND(MOD('IN_MACRO'!$D$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$D$32+'IN_FIN'!$E$19*'ENG_SCEN'!$D$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="E41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$E$23=0),0,IF(AND(MOD('IN_MACRO'!$E$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$E$32+'IN_FIN'!$E$19*'ENG_SCEN'!$E$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="F41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$F$23=0),0,IF(AND(MOD('IN_MACRO'!$F$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$F$32+'IN_FIN'!$E$19*'ENG_SCEN'!$F$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="G41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$G$23=0),0,IF(AND(MOD('IN_MACRO'!$G$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$G$32+'IN_FIN'!$E$19*'ENG_SCEN'!$G$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="H41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$H$23=0),0,IF(AND(MOD('IN_MACRO'!$H$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$H$32+'IN_FIN'!$E$19*'ENG_SCEN'!$H$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="I41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$I$23=0),0,IF(AND(MOD('IN_MACRO'!$I$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$I$32+'IN_FIN'!$E$19*'ENG_SCEN'!$I$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="J41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$J$23=0),0,IF(AND(MOD('IN_MACRO'!$J$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$J$32+'IN_FIN'!$E$19*'ENG_SCEN'!$J$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="K41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$K$23=0),0,IF(AND(MOD('IN_MACRO'!$K$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$K$32+'IN_FIN'!$E$19*'ENG_SCEN'!$K$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="L41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$L$23=0),0,IF(AND(MOD('IN_MACRO'!$L$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$L$32+'IN_FIN'!$E$19*'ENG_SCEN'!$L$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="M41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$M$23=0),0,IF(AND(MOD('IN_MACRO'!$M$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$M$32+'IN_FIN'!$E$19*'ENG_SCEN'!$M$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="N41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$N$23=0),0,IF(AND(MOD('IN_MACRO'!$N$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$N$32+'IN_FIN'!$E$19*'ENG_SCEN'!$N$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="O41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$O$23=0),0,IF(AND(MOD('IN_MACRO'!$O$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$O$32+'IN_FIN'!$E$19*'ENG_SCEN'!$O$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+      <c r="P41" s="14">
+        <f>IF(OR('IN_FIN'!$F$19&lt;=0,'IN_FIN'!$G$19&lt;=0,'IN_MACRO'!$P$23=0),0,IF(AND(MOD('IN_MACRO'!$P$23,'IN_FIN'!$G$19)=0,'IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$11),'IN_FIN'!$D$19*'IN_FIN'!$H$19*((1-'IN_FIN'!$E$19)*'ENG_SCEN'!$P$32+'IN_FIN'!$E$19*'ENG_SCEN'!$P$36)*'ENG_SCEN'!$G$16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>جمع جایگزینی دارایی‌ها</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.repl_total</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D42" s="14">
+        <f>'ENG_CAPEX'!$D$31+'ENG_CAPEX'!$D$32+'ENG_CAPEX'!$D$33+'ENG_CAPEX'!$D$34+'ENG_CAPEX'!$D$35+'ENG_CAPEX'!$D$36+'ENG_CAPEX'!$D$37+'ENG_CAPEX'!$D$38+'ENG_CAPEX'!$D$39+'ENG_CAPEX'!$D$40+'ENG_CAPEX'!$D$41</f>
+        <v/>
+      </c>
+      <c r="E42" s="14">
+        <f>'ENG_CAPEX'!$E$31+'ENG_CAPEX'!$E$32+'ENG_CAPEX'!$E$33+'ENG_CAPEX'!$E$34+'ENG_CAPEX'!$E$35+'ENG_CAPEX'!$E$36+'ENG_CAPEX'!$E$37+'ENG_CAPEX'!$E$38+'ENG_CAPEX'!$E$39+'ENG_CAPEX'!$E$40+'ENG_CAPEX'!$E$41</f>
+        <v/>
+      </c>
+      <c r="F42" s="14">
+        <f>'ENG_CAPEX'!$F$31+'ENG_CAPEX'!$F$32+'ENG_CAPEX'!$F$33+'ENG_CAPEX'!$F$34+'ENG_CAPEX'!$F$35+'ENG_CAPEX'!$F$36+'ENG_CAPEX'!$F$37+'ENG_CAPEX'!$F$38+'ENG_CAPEX'!$F$39+'ENG_CAPEX'!$F$40+'ENG_CAPEX'!$F$41</f>
+        <v/>
+      </c>
+      <c r="G42" s="14">
+        <f>'ENG_CAPEX'!$G$31+'ENG_CAPEX'!$G$32+'ENG_CAPEX'!$G$33+'ENG_CAPEX'!$G$34+'ENG_CAPEX'!$G$35+'ENG_CAPEX'!$G$36+'ENG_CAPEX'!$G$37+'ENG_CAPEX'!$G$38+'ENG_CAPEX'!$G$39+'ENG_CAPEX'!$G$40+'ENG_CAPEX'!$G$41</f>
+        <v/>
+      </c>
+      <c r="H42" s="14">
+        <f>'ENG_CAPEX'!$H$31+'ENG_CAPEX'!$H$32+'ENG_CAPEX'!$H$33+'ENG_CAPEX'!$H$34+'ENG_CAPEX'!$H$35+'ENG_CAPEX'!$H$36+'ENG_CAPEX'!$H$37+'ENG_CAPEX'!$H$38+'ENG_CAPEX'!$H$39+'ENG_CAPEX'!$H$40+'ENG_CAPEX'!$H$41</f>
+        <v/>
+      </c>
+      <c r="I42" s="14">
+        <f>'ENG_CAPEX'!$I$31+'ENG_CAPEX'!$I$32+'ENG_CAPEX'!$I$33+'ENG_CAPEX'!$I$34+'ENG_CAPEX'!$I$35+'ENG_CAPEX'!$I$36+'ENG_CAPEX'!$I$37+'ENG_CAPEX'!$I$38+'ENG_CAPEX'!$I$39+'ENG_CAPEX'!$I$40+'ENG_CAPEX'!$I$41</f>
+        <v/>
+      </c>
+      <c r="J42" s="14">
+        <f>'ENG_CAPEX'!$J$31+'ENG_CAPEX'!$J$32+'ENG_CAPEX'!$J$33+'ENG_CAPEX'!$J$34+'ENG_CAPEX'!$J$35+'ENG_CAPEX'!$J$36+'ENG_CAPEX'!$J$37+'ENG_CAPEX'!$J$38+'ENG_CAPEX'!$J$39+'ENG_CAPEX'!$J$40+'ENG_CAPEX'!$J$41</f>
+        <v/>
+      </c>
+      <c r="K42" s="14">
+        <f>'ENG_CAPEX'!$K$31+'ENG_CAPEX'!$K$32+'ENG_CAPEX'!$K$33+'ENG_CAPEX'!$K$34+'ENG_CAPEX'!$K$35+'ENG_CAPEX'!$K$36+'ENG_CAPEX'!$K$37+'ENG_CAPEX'!$K$38+'ENG_CAPEX'!$K$39+'ENG_CAPEX'!$K$40+'ENG_CAPEX'!$K$41</f>
+        <v/>
+      </c>
+      <c r="L42" s="14">
+        <f>'ENG_CAPEX'!$L$31+'ENG_CAPEX'!$L$32+'ENG_CAPEX'!$L$33+'ENG_CAPEX'!$L$34+'ENG_CAPEX'!$L$35+'ENG_CAPEX'!$L$36+'ENG_CAPEX'!$L$37+'ENG_CAPEX'!$L$38+'ENG_CAPEX'!$L$39+'ENG_CAPEX'!$L$40+'ENG_CAPEX'!$L$41</f>
+        <v/>
+      </c>
+      <c r="M42" s="14">
+        <f>'ENG_CAPEX'!$M$31+'ENG_CAPEX'!$M$32+'ENG_CAPEX'!$M$33+'ENG_CAPEX'!$M$34+'ENG_CAPEX'!$M$35+'ENG_CAPEX'!$M$36+'ENG_CAPEX'!$M$37+'ENG_CAPEX'!$M$38+'ENG_CAPEX'!$M$39+'ENG_CAPEX'!$M$40+'ENG_CAPEX'!$M$41</f>
+        <v/>
+      </c>
+      <c r="N42" s="14">
+        <f>'ENG_CAPEX'!$N$31+'ENG_CAPEX'!$N$32+'ENG_CAPEX'!$N$33+'ENG_CAPEX'!$N$34+'ENG_CAPEX'!$N$35+'ENG_CAPEX'!$N$36+'ENG_CAPEX'!$N$37+'ENG_CAPEX'!$N$38+'ENG_CAPEX'!$N$39+'ENG_CAPEX'!$N$40+'ENG_CAPEX'!$N$41</f>
+        <v/>
+      </c>
+      <c r="O42" s="14">
+        <f>'ENG_CAPEX'!$O$31+'ENG_CAPEX'!$O$32+'ENG_CAPEX'!$O$33+'ENG_CAPEX'!$O$34+'ENG_CAPEX'!$O$35+'ENG_CAPEX'!$O$36+'ENG_CAPEX'!$O$37+'ENG_CAPEX'!$O$38+'ENG_CAPEX'!$O$39+'ENG_CAPEX'!$O$40+'ENG_CAPEX'!$O$41</f>
+        <v/>
+      </c>
+      <c r="P42" s="14">
+        <f>'ENG_CAPEX'!$P$31+'ENG_CAPEX'!$P$32+'ENG_CAPEX'!$P$33+'ENG_CAPEX'!$P$34+'ENG_CAPEX'!$P$35+'ENG_CAPEX'!$P$36+'ENG_CAPEX'!$P$37+'ENG_CAPEX'!$P$38+'ENG_CAPEX'!$P$39+'ENG_CAPEX'!$P$40+'ENG_CAPEX'!$P$41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>د) دارایی‌های ثابت و استهلاک</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
+      <c r="J44" s="7" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+      <c r="O44" s="7" t="n"/>
+      <c r="P44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>اضافات دارایی (CAPEX + جایگزینی + IDC)</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.add</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D45" s="14">
+        <f>'ENG_CAPEX'!$D$21+'ENG_CAPEX'!$D$42+'ENG_CAPEX'!$D$27</f>
+        <v/>
+      </c>
+      <c r="E45" s="14">
+        <f>'ENG_CAPEX'!$E$21+'ENG_CAPEX'!$E$42+'ENG_CAPEX'!$E$27</f>
+        <v/>
+      </c>
+      <c r="F45" s="14">
+        <f>'ENG_CAPEX'!$F$21+'ENG_CAPEX'!$F$42+'ENG_CAPEX'!$F$27</f>
+        <v/>
+      </c>
+      <c r="G45" s="14">
+        <f>'ENG_CAPEX'!$G$21+'ENG_CAPEX'!$G$42+'ENG_CAPEX'!$G$27</f>
+        <v/>
+      </c>
+      <c r="H45" s="14">
+        <f>'ENG_CAPEX'!$H$21+'ENG_CAPEX'!$H$42+'ENG_CAPEX'!$H$27</f>
+        <v/>
+      </c>
+      <c r="I45" s="14">
+        <f>'ENG_CAPEX'!$I$21+'ENG_CAPEX'!$I$42+'ENG_CAPEX'!$I$27</f>
+        <v/>
+      </c>
+      <c r="J45" s="14">
+        <f>'ENG_CAPEX'!$J$21+'ENG_CAPEX'!$J$42+'ENG_CAPEX'!$J$27</f>
+        <v/>
+      </c>
+      <c r="K45" s="14">
+        <f>'ENG_CAPEX'!$K$21+'ENG_CAPEX'!$K$42+'ENG_CAPEX'!$K$27</f>
+        <v/>
+      </c>
+      <c r="L45" s="14">
+        <f>'ENG_CAPEX'!$L$21+'ENG_CAPEX'!$L$42+'ENG_CAPEX'!$L$27</f>
+        <v/>
+      </c>
+      <c r="M45" s="14">
+        <f>'ENG_CAPEX'!$M$21+'ENG_CAPEX'!$M$42+'ENG_CAPEX'!$M$27</f>
+        <v/>
+      </c>
+      <c r="N45" s="14">
+        <f>'ENG_CAPEX'!$N$21+'ENG_CAPEX'!$N$42+'ENG_CAPEX'!$N$27</f>
+        <v/>
+      </c>
+      <c r="O45" s="14">
+        <f>'ENG_CAPEX'!$O$21+'ENG_CAPEX'!$O$42+'ENG_CAPEX'!$O$27</f>
+        <v/>
+      </c>
+      <c r="P45" s="14">
+        <f>'ENG_CAPEX'!$P$21+'ENG_CAPEX'!$P$42+'ENG_CAPEX'!$P$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ناخالص دارایی‌های ثابت - افتتاحیه</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.gross_open</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D46" s="14">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E46" s="14">
+        <f>'ENG_CAPEX'!$D$47</f>
+        <v/>
+      </c>
+      <c r="F46" s="14">
+        <f>'ENG_CAPEX'!$E$47</f>
+        <v/>
+      </c>
+      <c r="G46" s="14">
+        <f>'ENG_CAPEX'!$F$47</f>
+        <v/>
+      </c>
+      <c r="H46" s="14">
+        <f>'ENG_CAPEX'!$G$47</f>
+        <v/>
+      </c>
+      <c r="I46" s="14">
+        <f>'ENG_CAPEX'!$H$47</f>
+        <v/>
+      </c>
+      <c r="J46" s="14">
+        <f>'ENG_CAPEX'!$I$47</f>
+        <v/>
+      </c>
+      <c r="K46" s="14">
+        <f>'ENG_CAPEX'!$J$47</f>
+        <v/>
+      </c>
+      <c r="L46" s="14">
+        <f>'ENG_CAPEX'!$K$47</f>
+        <v/>
+      </c>
+      <c r="M46" s="14">
+        <f>'ENG_CAPEX'!$L$47</f>
+        <v/>
+      </c>
+      <c r="N46" s="14">
+        <f>'ENG_CAPEX'!$M$47</f>
+        <v/>
+      </c>
+      <c r="O46" s="14">
+        <f>'ENG_CAPEX'!$N$47</f>
+        <v/>
+      </c>
+      <c r="P46" s="14">
+        <f>'ENG_CAPEX'!$O$47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ناخالص دارایی‌های ثابت - اختتامیه</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.gross</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D47" s="14">
+        <f>'ENG_CAPEX'!$D$46+'ENG_CAPEX'!$D$45</f>
+        <v/>
+      </c>
+      <c r="E47" s="14">
+        <f>'ENG_CAPEX'!$E$46+'ENG_CAPEX'!$E$45</f>
+        <v/>
+      </c>
+      <c r="F47" s="14">
+        <f>'ENG_CAPEX'!$F$46+'ENG_CAPEX'!$F$45</f>
+        <v/>
+      </c>
+      <c r="G47" s="14">
+        <f>'ENG_CAPEX'!$G$46+'ENG_CAPEX'!$G$45</f>
+        <v/>
+      </c>
+      <c r="H47" s="14">
+        <f>'ENG_CAPEX'!$H$46+'ENG_CAPEX'!$H$45</f>
+        <v/>
+      </c>
+      <c r="I47" s="14">
+        <f>'ENG_CAPEX'!$I$46+'ENG_CAPEX'!$I$45</f>
+        <v/>
+      </c>
+      <c r="J47" s="14">
+        <f>'ENG_CAPEX'!$J$46+'ENG_CAPEX'!$J$45</f>
+        <v/>
+      </c>
+      <c r="K47" s="14">
+        <f>'ENG_CAPEX'!$K$46+'ENG_CAPEX'!$K$45</f>
+        <v/>
+      </c>
+      <c r="L47" s="14">
+        <f>'ENG_CAPEX'!$L$46+'ENG_CAPEX'!$L$45</f>
+        <v/>
+      </c>
+      <c r="M47" s="14">
+        <f>'ENG_CAPEX'!$M$46+'ENG_CAPEX'!$M$45</f>
+        <v/>
+      </c>
+      <c r="N47" s="14">
+        <f>'ENG_CAPEX'!$N$46+'ENG_CAPEX'!$N$45</f>
+        <v/>
+      </c>
+      <c r="O47" s="14">
+        <f>'ENG_CAPEX'!$O$46+'ENG_CAPEX'!$O$45</f>
+        <v/>
+      </c>
+      <c r="P47" s="14">
+        <f>'ENG_CAPEX'!$P$46+'ENG_CAPEX'!$P$45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ناخالص طبقهٔ زمین</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.grossc.0</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D48" s="14">
+        <f>('ENG_CAPEX'!$D$10+'ENG_CAPEX'!$D$31)</f>
+        <v/>
+      </c>
+      <c r="E48" s="14">
+        <f>'ENG_CAPEX'!$D$48+('ENG_CAPEX'!$E$10+'ENG_CAPEX'!$E$31)</f>
+        <v/>
+      </c>
+      <c r="F48" s="14">
+        <f>'ENG_CAPEX'!$E$48+('ENG_CAPEX'!$F$10+'ENG_CAPEX'!$F$31)</f>
+        <v/>
+      </c>
+      <c r="G48" s="14">
+        <f>'ENG_CAPEX'!$F$48+('ENG_CAPEX'!$G$10+'ENG_CAPEX'!$G$31)</f>
+        <v/>
+      </c>
+      <c r="H48" s="14">
+        <f>'ENG_CAPEX'!$G$48+('ENG_CAPEX'!$H$10+'ENG_CAPEX'!$H$31)</f>
+        <v/>
+      </c>
+      <c r="I48" s="14">
+        <f>'ENG_CAPEX'!$H$48+('ENG_CAPEX'!$I$10+'ENG_CAPEX'!$I$31)</f>
+        <v/>
+      </c>
+      <c r="J48" s="14">
+        <f>'ENG_CAPEX'!$I$48+('ENG_CAPEX'!$J$10+'ENG_CAPEX'!$J$31)</f>
+        <v/>
+      </c>
+      <c r="K48" s="14">
+        <f>'ENG_CAPEX'!$J$48+('ENG_CAPEX'!$K$10+'ENG_CAPEX'!$K$31)</f>
+        <v/>
+      </c>
+      <c r="L48" s="14">
+        <f>'ENG_CAPEX'!$K$48+('ENG_CAPEX'!$L$10+'ENG_CAPEX'!$L$31)</f>
+        <v/>
+      </c>
+      <c r="M48" s="14">
+        <f>'ENG_CAPEX'!$L$48+('ENG_CAPEX'!$M$10+'ENG_CAPEX'!$M$31)</f>
+        <v/>
+      </c>
+      <c r="N48" s="14">
+        <f>'ENG_CAPEX'!$M$48+('ENG_CAPEX'!$N$10+'ENG_CAPEX'!$N$31)</f>
+        <v/>
+      </c>
+      <c r="O48" s="14">
+        <f>'ENG_CAPEX'!$N$48+('ENG_CAPEX'!$O$10+'ENG_CAPEX'!$O$31)</f>
+        <v/>
+      </c>
+      <c r="P48" s="14">
+        <f>'ENG_CAPEX'!$O$48+('ENG_CAPEX'!$P$10+'ENG_CAPEX'!$P$31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ناخالص طبقهٔ محوطه‌سازی و ساختمان</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.grossc.1</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D49" s="14">
+        <f>('ENG_CAPEX'!$D$11+'ENG_CAPEX'!$D$32)</f>
+        <v/>
+      </c>
+      <c r="E49" s="14">
+        <f>'ENG_CAPEX'!$D$49+('ENG_CAPEX'!$E$11+'ENG_CAPEX'!$E$32)</f>
+        <v/>
+      </c>
+      <c r="F49" s="14">
+        <f>'ENG_CAPEX'!$E$49+('ENG_CAPEX'!$F$11+'ENG_CAPEX'!$F$32)</f>
+        <v/>
+      </c>
+      <c r="G49" s="14">
+        <f>'ENG_CAPEX'!$F$49+('ENG_CAPEX'!$G$11+'ENG_CAPEX'!$G$32)</f>
+        <v/>
+      </c>
+      <c r="H49" s="14">
+        <f>'ENG_CAPEX'!$G$49+('ENG_CAPEX'!$H$11+'ENG_CAPEX'!$H$32)</f>
+        <v/>
+      </c>
+      <c r="I49" s="14">
+        <f>'ENG_CAPEX'!$H$49+('ENG_CAPEX'!$I$11+'ENG_CAPEX'!$I$32)</f>
+        <v/>
+      </c>
+      <c r="J49" s="14">
+        <f>'ENG_CAPEX'!$I$49+('ENG_CAPEX'!$J$11+'ENG_CAPEX'!$J$32)</f>
+        <v/>
+      </c>
+      <c r="K49" s="14">
+        <f>'ENG_CAPEX'!$J$49+('ENG_CAPEX'!$K$11+'ENG_CAPEX'!$K$32)</f>
+        <v/>
+      </c>
+      <c r="L49" s="14">
+        <f>'ENG_CAPEX'!$K$49+('ENG_CAPEX'!$L$11+'ENG_CAPEX'!$L$32)</f>
+        <v/>
+      </c>
+      <c r="M49" s="14">
+        <f>'ENG_CAPEX'!$L$49+('ENG_CAPEX'!$M$11+'ENG_CAPEX'!$M$32)</f>
+        <v/>
+      </c>
+      <c r="N49" s="14">
+        <f>'ENG_CAPEX'!$M$49+('ENG_CAPEX'!$N$11+'ENG_CAPEX'!$N$32)</f>
+        <v/>
+      </c>
+      <c r="O49" s="14">
+        <f>'ENG_CAPEX'!$N$49+('ENG_CAPEX'!$O$11+'ENG_CAPEX'!$O$32)</f>
+        <v/>
+      </c>
+      <c r="P49" s="14">
+        <f>'ENG_CAPEX'!$O$49+('ENG_CAPEX'!$P$11+'ENG_CAPEX'!$P$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ناخالص طبقهٔ ماشین‌آلات وارداتی</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.grossc.2</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D50" s="14">
+        <f>('ENG_CAPEX'!$D$12+'ENG_CAPEX'!$D$33)</f>
+        <v/>
+      </c>
+      <c r="E50" s="14">
+        <f>'ENG_CAPEX'!$D$50+('ENG_CAPEX'!$E$12+'ENG_CAPEX'!$E$33)</f>
+        <v/>
+      </c>
+      <c r="F50" s="14">
+        <f>'ENG_CAPEX'!$E$50+('ENG_CAPEX'!$F$12+'ENG_CAPEX'!$F$33)</f>
+        <v/>
+      </c>
+      <c r="G50" s="14">
+        <f>'ENG_CAPEX'!$F$50+('ENG_CAPEX'!$G$12+'ENG_CAPEX'!$G$33)</f>
+        <v/>
+      </c>
+      <c r="H50" s="14">
+        <f>'ENG_CAPEX'!$G$50+('ENG_CAPEX'!$H$12+'ENG_CAPEX'!$H$33)</f>
+        <v/>
+      </c>
+      <c r="I50" s="14">
+        <f>'ENG_CAPEX'!$H$50+('ENG_CAPEX'!$I$12+'ENG_CAPEX'!$I$33)</f>
+        <v/>
+      </c>
+      <c r="J50" s="14">
+        <f>'ENG_CAPEX'!$I$50+('ENG_CAPEX'!$J$12+'ENG_CAPEX'!$J$33)</f>
+        <v/>
+      </c>
+      <c r="K50" s="14">
+        <f>'ENG_CAPEX'!$J$50+('ENG_CAPEX'!$K$12+'ENG_CAPEX'!$K$33)</f>
+        <v/>
+      </c>
+      <c r="L50" s="14">
+        <f>'ENG_CAPEX'!$K$50+('ENG_CAPEX'!$L$12+'ENG_CAPEX'!$L$33)</f>
+        <v/>
+      </c>
+      <c r="M50" s="14">
+        <f>'ENG_CAPEX'!$L$50+('ENG_CAPEX'!$M$12+'ENG_CAPEX'!$M$33)</f>
+        <v/>
+      </c>
+      <c r="N50" s="14">
+        <f>'ENG_CAPEX'!$M$50+('ENG_CAPEX'!$N$12+'ENG_CAPEX'!$N$33)</f>
+        <v/>
+      </c>
+      <c r="O50" s="14">
+        <f>'ENG_CAPEX'!$N$50+('ENG_CAPEX'!$O$12+'ENG_CAPEX'!$O$33)</f>
+        <v/>
+      </c>
+      <c r="P50" s="14">
+        <f>'ENG_CAPEX'!$O$50+('ENG_CAPEX'!$P$12+'ENG_CAPEX'!$P$33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ناخالص طبقهٔ ماشین‌آلات داخلی</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.grossc.3</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D51" s="14">
+        <f>('ENG_CAPEX'!$D$13+'ENG_CAPEX'!$D$34)</f>
+        <v/>
+      </c>
+      <c r="E51" s="14">
+        <f>'ENG_CAPEX'!$D$51+('ENG_CAPEX'!$E$13+'ENG_CAPEX'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="F51" s="14">
+        <f>'ENG_CAPEX'!$E$51+('ENG_CAPEX'!$F$13+'ENG_CAPEX'!$F$34)</f>
+        <v/>
+      </c>
+      <c r="G51" s="14">
+        <f>'ENG_CAPEX'!$F$51+('ENG_CAPEX'!$G$13+'ENG_CAPEX'!$G$34)</f>
+        <v/>
+      </c>
+      <c r="H51" s="14">
+        <f>'ENG_CAPEX'!$G$51+('ENG_CAPEX'!$H$13+'ENG_CAPEX'!$H$34)</f>
+        <v/>
+      </c>
+      <c r="I51" s="14">
+        <f>'ENG_CAPEX'!$H$51+('ENG_CAPEX'!$I$13+'ENG_CAPEX'!$I$34)</f>
+        <v/>
+      </c>
+      <c r="J51" s="14">
+        <f>'ENG_CAPEX'!$I$51+('ENG_CAPEX'!$J$13+'ENG_CAPEX'!$J$34)</f>
+        <v/>
+      </c>
+      <c r="K51" s="14">
+        <f>'ENG_CAPEX'!$J$51+('ENG_CAPEX'!$K$13+'ENG_CAPEX'!$K$34)</f>
+        <v/>
+      </c>
+      <c r="L51" s="14">
+        <f>'ENG_CAPEX'!$K$51+('ENG_CAPEX'!$L$13+'ENG_CAPEX'!$L$34)</f>
+        <v/>
+      </c>
+      <c r="M51" s="14">
+        <f>'ENG_CAPEX'!$L$51+('ENG_CAPEX'!$M$13+'ENG_CAPEX'!$M$34)</f>
+        <v/>
+      </c>
+      <c r="N51" s="14">
+        <f>'ENG_CAPEX'!$M$51+('ENG_CAPEX'!$N$13+'ENG_CAPEX'!$N$34)</f>
+        <v/>
+      </c>
+      <c r="O51" s="14">
+        <f>'ENG_CAPEX'!$N$51+('ENG_CAPEX'!$O$13+'ENG_CAPEX'!$O$34)</f>
+        <v/>
+      </c>
+      <c r="P51" s="14">
+        <f>'ENG_CAPEX'!$O$51+('ENG_CAPEX'!$P$13+'ENG_CAPEX'!$P$34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ناخالص طبقهٔ تأسیسات و تجهیزات جانبی</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.grossc.4</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D52" s="14">
+        <f>('ENG_CAPEX'!$D$14+'ENG_CAPEX'!$D$35)</f>
+        <v/>
+      </c>
+      <c r="E52" s="14">
+        <f>'ENG_CAPEX'!$D$52+('ENG_CAPEX'!$E$14+'ENG_CAPEX'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="F52" s="14">
+        <f>'ENG_CAPEX'!$E$52+('ENG_CAPEX'!$F$14+'ENG_CAPEX'!$F$35)</f>
+        <v/>
+      </c>
+      <c r="G52" s="14">
+        <f>'ENG_CAPEX'!$F$52+('ENG_CAPEX'!$G$14+'ENG_CAPEX'!$G$35)</f>
+        <v/>
+      </c>
+      <c r="H52" s="14">
+        <f>'ENG_CAPEX'!$G$52+('ENG_CAPEX'!$H$14+'ENG_CAPEX'!$H$35)</f>
+        <v/>
+      </c>
+      <c r="I52" s="14">
+        <f>'ENG_CAPEX'!$H$52+('ENG_CAPEX'!$I$14+'ENG_CAPEX'!$I$35)</f>
+        <v/>
+      </c>
+      <c r="J52" s="14">
+        <f>'ENG_CAPEX'!$I$52+('ENG_CAPEX'!$J$14+'ENG_CAPEX'!$J$35)</f>
+        <v/>
+      </c>
+      <c r="K52" s="14">
+        <f>'ENG_CAPEX'!$J$52+('ENG_CAPEX'!$K$14+'ENG_CAPEX'!$K$35)</f>
+        <v/>
+      </c>
+      <c r="L52" s="14">
+        <f>'ENG_CAPEX'!$K$52+('ENG_CAPEX'!$L$14+'ENG_CAPEX'!$L$35)</f>
+        <v/>
+      </c>
+      <c r="M52" s="14">
+        <f>'ENG_CAPEX'!$L$52+('ENG_CAPEX'!$M$14+'ENG_CAPEX'!$M$35)</f>
+        <v/>
+      </c>
+      <c r="N52" s="14">
+        <f>'ENG_CAPEX'!$M$52+('ENG_CAPEX'!$N$14+'ENG_CAPEX'!$N$35)</f>
+        <v/>
+      </c>
+      <c r="O52" s="14">
+        <f>'ENG_CAPEX'!$N$52+('ENG_CAPEX'!$O$14+'ENG_CAPEX'!$O$35)</f>
+        <v/>
+      </c>
+      <c r="P52" s="14">
+        <f>'ENG_CAPEX'!$O$52+('ENG_CAPEX'!$P$14+'ENG_CAPEX'!$P$35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ناخالص طبقهٔ تصفیه‌خانه و تجهیزات زیست‌محیطی</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.grossc.5</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D53" s="14">
+        <f>('ENG_CAPEX'!$D$15+'ENG_CAPEX'!$D$36)</f>
+        <v/>
+      </c>
+      <c r="E53" s="14">
+        <f>'ENG_CAPEX'!$D$53+('ENG_CAPEX'!$E$15+'ENG_CAPEX'!$E$36)</f>
+        <v/>
+      </c>
+      <c r="F53" s="14">
+        <f>'ENG_CAPEX'!$E$53+('ENG_CAPEX'!$F$15+'ENG_CAPEX'!$F$36)</f>
+        <v/>
+      </c>
+      <c r="G53" s="14">
+        <f>'ENG_CAPEX'!$F$53+('ENG_CAPEX'!$G$15+'ENG_CAPEX'!$G$36)</f>
+        <v/>
+      </c>
+      <c r="H53" s="14">
+        <f>'ENG_CAPEX'!$G$53+('ENG_CAPEX'!$H$15+'ENG_CAPEX'!$H$36)</f>
+        <v/>
+      </c>
+      <c r="I53" s="14">
+        <f>'ENG_CAPEX'!$H$53+('ENG_CAPEX'!$I$15+'ENG_CAPEX'!$I$36)</f>
+        <v/>
+      </c>
+      <c r="J53" s="14">
+        <f>'ENG_CAPEX'!$I$53+('ENG_CAPEX'!$J$15+'ENG_CAPEX'!$J$36)</f>
+        <v/>
+      </c>
+      <c r="K53" s="14">
+        <f>'ENG_CAPEX'!$J$53+('ENG_CAPEX'!$K$15+'ENG_CAPEX'!$K$36)</f>
+        <v/>
+      </c>
+      <c r="L53" s="14">
+        <f>'ENG_CAPEX'!$K$53+('ENG_CAPEX'!$L$15+'ENG_CAPEX'!$L$36)</f>
+        <v/>
+      </c>
+      <c r="M53" s="14">
+        <f>'ENG_CAPEX'!$L$53+('ENG_CAPEX'!$M$15+'ENG_CAPEX'!$M$36)</f>
+        <v/>
+      </c>
+      <c r="N53" s="14">
+        <f>'ENG_CAPEX'!$M$53+('ENG_CAPEX'!$N$15+'ENG_CAPEX'!$N$36)</f>
+        <v/>
+      </c>
+      <c r="O53" s="14">
+        <f>'ENG_CAPEX'!$N$53+('ENG_CAPEX'!$O$15+'ENG_CAPEX'!$O$36)</f>
+        <v/>
+      </c>
+      <c r="P53" s="14">
+        <f>'ENG_CAPEX'!$O$53+('ENG_CAPEX'!$P$15+'ENG_CAPEX'!$P$36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ناخالص طبقهٔ تجهیزات حمل‌ونقل داخلی</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.grossc.6</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D54" s="14">
+        <f>('ENG_CAPEX'!$D$16+'ENG_CAPEX'!$D$37)</f>
+        <v/>
+      </c>
+      <c r="E54" s="14">
+        <f>'ENG_CAPEX'!$D$54+('ENG_CAPEX'!$E$16+'ENG_CAPEX'!$E$37)</f>
+        <v/>
+      </c>
+      <c r="F54" s="14">
+        <f>'ENG_CAPEX'!$E$54+('ENG_CAPEX'!$F$16+'ENG_CAPEX'!$F$37)</f>
+        <v/>
+      </c>
+      <c r="G54" s="14">
+        <f>'ENG_CAPEX'!$F$54+('ENG_CAPEX'!$G$16+'ENG_CAPEX'!$G$37)</f>
+        <v/>
+      </c>
+      <c r="H54" s="14">
+        <f>'ENG_CAPEX'!$G$54+('ENG_CAPEX'!$H$16+'ENG_CAPEX'!$H$37)</f>
+        <v/>
+      </c>
+      <c r="I54" s="14">
+        <f>'ENG_CAPEX'!$H$54+('ENG_CAPEX'!$I$16+'ENG_CAPEX'!$I$37)</f>
+        <v/>
+      </c>
+      <c r="J54" s="14">
+        <f>'ENG_CAPEX'!$I$54+('ENG_CAPEX'!$J$16+'ENG_CAPEX'!$J$37)</f>
+        <v/>
+      </c>
+      <c r="K54" s="14">
+        <f>'ENG_CAPEX'!$J$54+('ENG_CAPEX'!$K$16+'ENG_CAPEX'!$K$37)</f>
+        <v/>
+      </c>
+      <c r="L54" s="14">
+        <f>'ENG_CAPEX'!$K$54+('ENG_CAPEX'!$L$16+'ENG_CAPEX'!$L$37)</f>
+        <v/>
+      </c>
+      <c r="M54" s="14">
+        <f>'ENG_CAPEX'!$L$54+('ENG_CAPEX'!$M$16+'ENG_CAPEX'!$M$37)</f>
+        <v/>
+      </c>
+      <c r="N54" s="14">
+        <f>'ENG_CAPEX'!$M$54+('ENG_CAPEX'!$N$16+'ENG_CAPEX'!$N$37)</f>
+        <v/>
+      </c>
+      <c r="O54" s="14">
+        <f>'ENG_CAPEX'!$N$54+('ENG_CAPEX'!$O$16+'ENG_CAPEX'!$O$37)</f>
+        <v/>
+      </c>
+      <c r="P54" s="14">
+        <f>'ENG_CAPEX'!$O$54+('ENG_CAPEX'!$P$16+'ENG_CAPEX'!$P$37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ناخالص طبقهٔ آزمایشگاه و ابزار دقیق</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.grossc.7</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D55" s="14">
+        <f>('ENG_CAPEX'!$D$17+'ENG_CAPEX'!$D$38)</f>
+        <v/>
+      </c>
+      <c r="E55" s="14">
+        <f>'ENG_CAPEX'!$D$55+('ENG_CAPEX'!$E$17+'ENG_CAPEX'!$E$38)</f>
+        <v/>
+      </c>
+      <c r="F55" s="14">
+        <f>'ENG_CAPEX'!$E$55+('ENG_CAPEX'!$F$17+'ENG_CAPEX'!$F$38)</f>
+        <v/>
+      </c>
+      <c r="G55" s="14">
+        <f>'ENG_CAPEX'!$F$55+('ENG_CAPEX'!$G$17+'ENG_CAPEX'!$G$38)</f>
+        <v/>
+      </c>
+      <c r="H55" s="14">
+        <f>'ENG_CAPEX'!$G$55+('ENG_CAPEX'!$H$17+'ENG_CAPEX'!$H$38)</f>
+        <v/>
+      </c>
+      <c r="I55" s="14">
+        <f>'ENG_CAPEX'!$H$55+('ENG_CAPEX'!$I$17+'ENG_CAPEX'!$I$38)</f>
+        <v/>
+      </c>
+      <c r="J55" s="14">
+        <f>'ENG_CAPEX'!$I$55+('ENG_CAPEX'!$J$17+'ENG_CAPEX'!$J$38)</f>
+        <v/>
+      </c>
+      <c r="K55" s="14">
+        <f>'ENG_CAPEX'!$J$55+('ENG_CAPEX'!$K$17+'ENG_CAPEX'!$K$38)</f>
+        <v/>
+      </c>
+      <c r="L55" s="14">
+        <f>'ENG_CAPEX'!$K$55+('ENG_CAPEX'!$L$17+'ENG_CAPEX'!$L$38)</f>
+        <v/>
+      </c>
+      <c r="M55" s="14">
+        <f>'ENG_CAPEX'!$L$55+('ENG_CAPEX'!$M$17+'ENG_CAPEX'!$M$38)</f>
+        <v/>
+      </c>
+      <c r="N55" s="14">
+        <f>'ENG_CAPEX'!$M$55+('ENG_CAPEX'!$N$17+'ENG_CAPEX'!$N$38)</f>
+        <v/>
+      </c>
+      <c r="O55" s="14">
+        <f>'ENG_CAPEX'!$N$55+('ENG_CAPEX'!$O$17+'ENG_CAPEX'!$O$38)</f>
+        <v/>
+      </c>
+      <c r="P55" s="14">
+        <f>'ENG_CAPEX'!$O$55+('ENG_CAPEX'!$P$17+'ENG_CAPEX'!$P$38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ناخالص طبقهٔ مهندسی، نصب و راه‌اندازی</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.grossc.8</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D56" s="14">
+        <f>('ENG_CAPEX'!$D$18+'ENG_CAPEX'!$D$39)</f>
+        <v/>
+      </c>
+      <c r="E56" s="14">
+        <f>'ENG_CAPEX'!$D$56+('ENG_CAPEX'!$E$18+'ENG_CAPEX'!$E$39)</f>
+        <v/>
+      </c>
+      <c r="F56" s="14">
+        <f>'ENG_CAPEX'!$E$56+('ENG_CAPEX'!$F$18+'ENG_CAPEX'!$F$39)</f>
+        <v/>
+      </c>
+      <c r="G56" s="14">
+        <f>'ENG_CAPEX'!$F$56+('ENG_CAPEX'!$G$18+'ENG_CAPEX'!$G$39)</f>
+        <v/>
+      </c>
+      <c r="H56" s="14">
+        <f>'ENG_CAPEX'!$G$56+('ENG_CAPEX'!$H$18+'ENG_CAPEX'!$H$39)</f>
+        <v/>
+      </c>
+      <c r="I56" s="14">
+        <f>'ENG_CAPEX'!$H$56+('ENG_CAPEX'!$I$18+'ENG_CAPEX'!$I$39)</f>
+        <v/>
+      </c>
+      <c r="J56" s="14">
+        <f>'ENG_CAPEX'!$I$56+('ENG_CAPEX'!$J$18+'ENG_CAPEX'!$J$39)</f>
+        <v/>
+      </c>
+      <c r="K56" s="14">
+        <f>'ENG_CAPEX'!$J$56+('ENG_CAPEX'!$K$18+'ENG_CAPEX'!$K$39)</f>
+        <v/>
+      </c>
+      <c r="L56" s="14">
+        <f>'ENG_CAPEX'!$K$56+('ENG_CAPEX'!$L$18+'ENG_CAPEX'!$L$39)</f>
+        <v/>
+      </c>
+      <c r="M56" s="14">
+        <f>'ENG_CAPEX'!$L$56+('ENG_CAPEX'!$M$18+'ENG_CAPEX'!$M$39)</f>
+        <v/>
+      </c>
+      <c r="N56" s="14">
+        <f>'ENG_CAPEX'!$M$56+('ENG_CAPEX'!$N$18+'ENG_CAPEX'!$N$39)</f>
+        <v/>
+      </c>
+      <c r="O56" s="14">
+        <f>'ENG_CAPEX'!$N$56+('ENG_CAPEX'!$O$18+'ENG_CAPEX'!$O$39)</f>
+        <v/>
+      </c>
+      <c r="P56" s="14">
+        <f>'ENG_CAPEX'!$O$56+('ENG_CAPEX'!$P$18+'ENG_CAPEX'!$P$39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ناخالص طبقهٔ هزینه‌های پیش از بهره‌برداری</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.grossc.9</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D57" s="14">
+        <f>('ENG_CAPEX'!$D$19+'ENG_CAPEX'!$D$40)</f>
+        <v/>
+      </c>
+      <c r="E57" s="14">
+        <f>'ENG_CAPEX'!$D$57+('ENG_CAPEX'!$E$19+'ENG_CAPEX'!$E$40)</f>
+        <v/>
+      </c>
+      <c r="F57" s="14">
+        <f>'ENG_CAPEX'!$E$57+('ENG_CAPEX'!$F$19+'ENG_CAPEX'!$F$40)</f>
+        <v/>
+      </c>
+      <c r="G57" s="14">
+        <f>'ENG_CAPEX'!$F$57+('ENG_CAPEX'!$G$19+'ENG_CAPEX'!$G$40)</f>
+        <v/>
+      </c>
+      <c r="H57" s="14">
+        <f>'ENG_CAPEX'!$G$57+('ENG_CAPEX'!$H$19+'ENG_CAPEX'!$H$40)</f>
+        <v/>
+      </c>
+      <c r="I57" s="14">
+        <f>'ENG_CAPEX'!$H$57+('ENG_CAPEX'!$I$19+'ENG_CAPEX'!$I$40)</f>
+        <v/>
+      </c>
+      <c r="J57" s="14">
+        <f>'ENG_CAPEX'!$I$57+('ENG_CAPEX'!$J$19+'ENG_CAPEX'!$J$40)</f>
+        <v/>
+      </c>
+      <c r="K57" s="14">
+        <f>'ENG_CAPEX'!$J$57+('ENG_CAPEX'!$K$19+'ENG_CAPEX'!$K$40)</f>
+        <v/>
+      </c>
+      <c r="L57" s="14">
+        <f>'ENG_CAPEX'!$K$57+('ENG_CAPEX'!$L$19+'ENG_CAPEX'!$L$40)</f>
+        <v/>
+      </c>
+      <c r="M57" s="14">
+        <f>'ENG_CAPEX'!$L$57+('ENG_CAPEX'!$M$19+'ENG_CAPEX'!$M$40)</f>
+        <v/>
+      </c>
+      <c r="N57" s="14">
+        <f>'ENG_CAPEX'!$M$57+('ENG_CAPEX'!$N$19+'ENG_CAPEX'!$N$40)</f>
+        <v/>
+      </c>
+      <c r="O57" s="14">
+        <f>'ENG_CAPEX'!$N$57+('ENG_CAPEX'!$O$19+'ENG_CAPEX'!$O$40)</f>
+        <v/>
+      </c>
+      <c r="P57" s="14">
+        <f>'ENG_CAPEX'!$O$57+('ENG_CAPEX'!$P$19+'ENG_CAPEX'!$P$40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ناخالص طبقهٔ ذخیره احتیاطی فیزیکی</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.grossc.10</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D58" s="14">
+        <f>('ENG_CAPEX'!$D$20+'ENG_CAPEX'!$D$41)</f>
+        <v/>
+      </c>
+      <c r="E58" s="14">
+        <f>'ENG_CAPEX'!$D$58+('ENG_CAPEX'!$E$20+'ENG_CAPEX'!$E$41)</f>
+        <v/>
+      </c>
+      <c r="F58" s="14">
+        <f>'ENG_CAPEX'!$E$58+('ENG_CAPEX'!$F$20+'ENG_CAPEX'!$F$41)</f>
+        <v/>
+      </c>
+      <c r="G58" s="14">
+        <f>'ENG_CAPEX'!$F$58+('ENG_CAPEX'!$G$20+'ENG_CAPEX'!$G$41)</f>
+        <v/>
+      </c>
+      <c r="H58" s="14">
+        <f>'ENG_CAPEX'!$G$58+('ENG_CAPEX'!$H$20+'ENG_CAPEX'!$H$41)</f>
+        <v/>
+      </c>
+      <c r="I58" s="14">
+        <f>'ENG_CAPEX'!$H$58+('ENG_CAPEX'!$I$20+'ENG_CAPEX'!$I$41)</f>
+        <v/>
+      </c>
+      <c r="J58" s="14">
+        <f>'ENG_CAPEX'!$I$58+('ENG_CAPEX'!$J$20+'ENG_CAPEX'!$J$41)</f>
+        <v/>
+      </c>
+      <c r="K58" s="14">
+        <f>'ENG_CAPEX'!$J$58+('ENG_CAPEX'!$K$20+'ENG_CAPEX'!$K$41)</f>
+        <v/>
+      </c>
+      <c r="L58" s="14">
+        <f>'ENG_CAPEX'!$K$58+('ENG_CAPEX'!$L$20+'ENG_CAPEX'!$L$41)</f>
+        <v/>
+      </c>
+      <c r="M58" s="14">
+        <f>'ENG_CAPEX'!$L$58+('ENG_CAPEX'!$M$20+'ENG_CAPEX'!$M$41)</f>
+        <v/>
+      </c>
+      <c r="N58" s="14">
+        <f>'ENG_CAPEX'!$M$58+('ENG_CAPEX'!$N$20+'ENG_CAPEX'!$N$41)</f>
+        <v/>
+      </c>
+      <c r="O58" s="14">
+        <f>'ENG_CAPEX'!$N$58+('ENG_CAPEX'!$O$20+'ENG_CAPEX'!$O$41)</f>
+        <v/>
+      </c>
+      <c r="P58" s="14">
+        <f>'ENG_CAPEX'!$O$58+('ENG_CAPEX'!$P$20+'ENG_CAPEX'!$P$41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>استهلاک زمین</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.dep.0</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$D$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$D$48-0)))</f>
+        <v/>
+      </c>
+      <c r="E59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$E$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$E$48-'ENG_CAPEX'!$D$70)))</f>
+        <v/>
+      </c>
+      <c r="F59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$F$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$F$48-'ENG_CAPEX'!$E$70)))</f>
+        <v/>
+      </c>
+      <c r="G59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$G$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$G$48-'ENG_CAPEX'!$F$70)))</f>
+        <v/>
+      </c>
+      <c r="H59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$H$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$H$48-'ENG_CAPEX'!$G$70)))</f>
+        <v/>
+      </c>
+      <c r="I59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$I$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$I$48-'ENG_CAPEX'!$H$70)))</f>
+        <v/>
+      </c>
+      <c r="J59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$J$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$J$48-'ENG_CAPEX'!$I$70)))</f>
+        <v/>
+      </c>
+      <c r="K59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$K$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$K$48-'ENG_CAPEX'!$J$70)))</f>
+        <v/>
+      </c>
+      <c r="L59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$L$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$L$48-'ENG_CAPEX'!$K$70)))</f>
+        <v/>
+      </c>
+      <c r="M59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$M$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$M$48-'ENG_CAPEX'!$L$70)))</f>
+        <v/>
+      </c>
+      <c r="N59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$N$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$N$48-'ENG_CAPEX'!$M$70)))</f>
+        <v/>
+      </c>
+      <c r="O59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$O$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$O$48-'ENG_CAPEX'!$N$70)))</f>
+        <v/>
+      </c>
+      <c r="P59" s="14">
+        <f>IF('IN_FIN'!$F$9&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$P$48/'IN_FIN'!$F$9,'ENG_CAPEX'!$P$48-'ENG_CAPEX'!$O$70)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>استهلاک محوطه‌سازی و ساختمان</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.dep.1</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$D$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$D$49-0)))</f>
+        <v/>
+      </c>
+      <c r="E60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$E$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$E$49-'ENG_CAPEX'!$D$71)))</f>
+        <v/>
+      </c>
+      <c r="F60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$F$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$F$49-'ENG_CAPEX'!$E$71)))</f>
+        <v/>
+      </c>
+      <c r="G60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$G$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$G$49-'ENG_CAPEX'!$F$71)))</f>
+        <v/>
+      </c>
+      <c r="H60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$H$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$H$49-'ENG_CAPEX'!$G$71)))</f>
+        <v/>
+      </c>
+      <c r="I60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$I$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$I$49-'ENG_CAPEX'!$H$71)))</f>
+        <v/>
+      </c>
+      <c r="J60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$J$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$J$49-'ENG_CAPEX'!$I$71)))</f>
+        <v/>
+      </c>
+      <c r="K60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$K$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$K$49-'ENG_CAPEX'!$J$71)))</f>
+        <v/>
+      </c>
+      <c r="L60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$L$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$L$49-'ENG_CAPEX'!$K$71)))</f>
+        <v/>
+      </c>
+      <c r="M60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$M$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$M$49-'ENG_CAPEX'!$L$71)))</f>
+        <v/>
+      </c>
+      <c r="N60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$N$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$N$49-'ENG_CAPEX'!$M$71)))</f>
+        <v/>
+      </c>
+      <c r="O60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$O$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$O$49-'ENG_CAPEX'!$N$71)))</f>
+        <v/>
+      </c>
+      <c r="P60" s="14">
+        <f>IF('IN_FIN'!$F$10&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$P$49/'IN_FIN'!$F$10,'ENG_CAPEX'!$P$49-'ENG_CAPEX'!$O$71)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>استهلاک ماشین‌آلات وارداتی</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.dep.2</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$D$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$D$50-0)))</f>
+        <v/>
+      </c>
+      <c r="E61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$E$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$E$50-'ENG_CAPEX'!$D$72)))</f>
+        <v/>
+      </c>
+      <c r="F61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$F$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$F$50-'ENG_CAPEX'!$E$72)))</f>
+        <v/>
+      </c>
+      <c r="G61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$G$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$G$50-'ENG_CAPEX'!$F$72)))</f>
+        <v/>
+      </c>
+      <c r="H61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$H$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$H$50-'ENG_CAPEX'!$G$72)))</f>
+        <v/>
+      </c>
+      <c r="I61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$I$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$I$50-'ENG_CAPEX'!$H$72)))</f>
+        <v/>
+      </c>
+      <c r="J61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$J$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$J$50-'ENG_CAPEX'!$I$72)))</f>
+        <v/>
+      </c>
+      <c r="K61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$K$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$K$50-'ENG_CAPEX'!$J$72)))</f>
+        <v/>
+      </c>
+      <c r="L61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$L$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$L$50-'ENG_CAPEX'!$K$72)))</f>
+        <v/>
+      </c>
+      <c r="M61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$M$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$M$50-'ENG_CAPEX'!$L$72)))</f>
+        <v/>
+      </c>
+      <c r="N61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$N$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$N$50-'ENG_CAPEX'!$M$72)))</f>
+        <v/>
+      </c>
+      <c r="O61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$O$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$O$50-'ENG_CAPEX'!$N$72)))</f>
+        <v/>
+      </c>
+      <c r="P61" s="14">
+        <f>IF('IN_FIN'!$F$11&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$P$50/'IN_FIN'!$F$11,'ENG_CAPEX'!$P$50-'ENG_CAPEX'!$O$72)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>استهلاک ماشین‌آلات داخلی</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.dep.3</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$D$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$D$51-0)))</f>
+        <v/>
+      </c>
+      <c r="E62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$E$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$E$51-'ENG_CAPEX'!$D$73)))</f>
+        <v/>
+      </c>
+      <c r="F62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$F$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$F$51-'ENG_CAPEX'!$E$73)))</f>
+        <v/>
+      </c>
+      <c r="G62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$G$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$G$51-'ENG_CAPEX'!$F$73)))</f>
+        <v/>
+      </c>
+      <c r="H62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$H$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$H$51-'ENG_CAPEX'!$G$73)))</f>
+        <v/>
+      </c>
+      <c r="I62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$I$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$I$51-'ENG_CAPEX'!$H$73)))</f>
+        <v/>
+      </c>
+      <c r="J62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$J$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$J$51-'ENG_CAPEX'!$I$73)))</f>
+        <v/>
+      </c>
+      <c r="K62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$K$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$K$51-'ENG_CAPEX'!$J$73)))</f>
+        <v/>
+      </c>
+      <c r="L62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$L$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$L$51-'ENG_CAPEX'!$K$73)))</f>
+        <v/>
+      </c>
+      <c r="M62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$M$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$M$51-'ENG_CAPEX'!$L$73)))</f>
+        <v/>
+      </c>
+      <c r="N62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$N$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$N$51-'ENG_CAPEX'!$M$73)))</f>
+        <v/>
+      </c>
+      <c r="O62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$O$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$O$51-'ENG_CAPEX'!$N$73)))</f>
+        <v/>
+      </c>
+      <c r="P62" s="14">
+        <f>IF('IN_FIN'!$F$12&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$P$51/'IN_FIN'!$F$12,'ENG_CAPEX'!$P$51-'ENG_CAPEX'!$O$73)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>استهلاک تأسیسات و تجهیزات جانبی</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.dep.4</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$D$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$D$52-0)))</f>
+        <v/>
+      </c>
+      <c r="E63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$E$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$E$52-'ENG_CAPEX'!$D$74)))</f>
+        <v/>
+      </c>
+      <c r="F63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$F$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$F$52-'ENG_CAPEX'!$E$74)))</f>
+        <v/>
+      </c>
+      <c r="G63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$G$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$G$52-'ENG_CAPEX'!$F$74)))</f>
+        <v/>
+      </c>
+      <c r="H63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$H$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$H$52-'ENG_CAPEX'!$G$74)))</f>
+        <v/>
+      </c>
+      <c r="I63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$I$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$I$52-'ENG_CAPEX'!$H$74)))</f>
+        <v/>
+      </c>
+      <c r="J63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$J$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$J$52-'ENG_CAPEX'!$I$74)))</f>
+        <v/>
+      </c>
+      <c r="K63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$K$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$K$52-'ENG_CAPEX'!$J$74)))</f>
+        <v/>
+      </c>
+      <c r="L63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$L$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$L$52-'ENG_CAPEX'!$K$74)))</f>
+        <v/>
+      </c>
+      <c r="M63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$M$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$M$52-'ENG_CAPEX'!$L$74)))</f>
+        <v/>
+      </c>
+      <c r="N63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$N$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$N$52-'ENG_CAPEX'!$M$74)))</f>
+        <v/>
+      </c>
+      <c r="O63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$O$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$O$52-'ENG_CAPEX'!$N$74)))</f>
+        <v/>
+      </c>
+      <c r="P63" s="14">
+        <f>IF('IN_FIN'!$F$13&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$P$52/'IN_FIN'!$F$13,'ENG_CAPEX'!$P$52-'ENG_CAPEX'!$O$74)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>استهلاک تصفیه‌خانه و تجهیزات زیست‌محیطی</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.dep.5</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$D$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$D$53-0)))</f>
+        <v/>
+      </c>
+      <c r="E64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$E$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$E$53-'ENG_CAPEX'!$D$75)))</f>
+        <v/>
+      </c>
+      <c r="F64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$F$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$F$53-'ENG_CAPEX'!$E$75)))</f>
+        <v/>
+      </c>
+      <c r="G64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$G$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$G$53-'ENG_CAPEX'!$F$75)))</f>
+        <v/>
+      </c>
+      <c r="H64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$H$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$H$53-'ENG_CAPEX'!$G$75)))</f>
+        <v/>
+      </c>
+      <c r="I64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$I$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$I$53-'ENG_CAPEX'!$H$75)))</f>
+        <v/>
+      </c>
+      <c r="J64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$J$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$J$53-'ENG_CAPEX'!$I$75)))</f>
+        <v/>
+      </c>
+      <c r="K64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$K$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$K$53-'ENG_CAPEX'!$J$75)))</f>
+        <v/>
+      </c>
+      <c r="L64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$L$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$L$53-'ENG_CAPEX'!$K$75)))</f>
+        <v/>
+      </c>
+      <c r="M64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$M$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$M$53-'ENG_CAPEX'!$L$75)))</f>
+        <v/>
+      </c>
+      <c r="N64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$N$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$N$53-'ENG_CAPEX'!$M$75)))</f>
+        <v/>
+      </c>
+      <c r="O64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$O$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$O$53-'ENG_CAPEX'!$N$75)))</f>
+        <v/>
+      </c>
+      <c r="P64" s="14">
+        <f>IF('IN_FIN'!$F$14&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$P$53/'IN_FIN'!$F$14,'ENG_CAPEX'!$P$53-'ENG_CAPEX'!$O$75)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>استهلاک تجهیزات حمل‌ونقل داخلی</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.dep.6</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$D$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$D$54-0)))</f>
+        <v/>
+      </c>
+      <c r="E65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$E$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$E$54-'ENG_CAPEX'!$D$76)))</f>
+        <v/>
+      </c>
+      <c r="F65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$F$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$F$54-'ENG_CAPEX'!$E$76)))</f>
+        <v/>
+      </c>
+      <c r="G65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$G$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$G$54-'ENG_CAPEX'!$F$76)))</f>
+        <v/>
+      </c>
+      <c r="H65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$H$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$H$54-'ENG_CAPEX'!$G$76)))</f>
+        <v/>
+      </c>
+      <c r="I65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$I$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$I$54-'ENG_CAPEX'!$H$76)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$J$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$J$54-'ENG_CAPEX'!$I$76)))</f>
+        <v/>
+      </c>
+      <c r="K65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$K$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$K$54-'ENG_CAPEX'!$J$76)))</f>
+        <v/>
+      </c>
+      <c r="L65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$L$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$L$54-'ENG_CAPEX'!$K$76)))</f>
+        <v/>
+      </c>
+      <c r="M65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$M$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$M$54-'ENG_CAPEX'!$L$76)))</f>
+        <v/>
+      </c>
+      <c r="N65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$N$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$N$54-'ENG_CAPEX'!$M$76)))</f>
+        <v/>
+      </c>
+      <c r="O65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$O$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$O$54-'ENG_CAPEX'!$N$76)))</f>
+        <v/>
+      </c>
+      <c r="P65" s="14">
+        <f>IF('IN_FIN'!$F$15&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$P$54/'IN_FIN'!$F$15,'ENG_CAPEX'!$P$54-'ENG_CAPEX'!$O$76)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>استهلاک آزمایشگاه و ابزار دقیق</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.dep.7</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$D$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$D$55-0)))</f>
+        <v/>
+      </c>
+      <c r="E66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$E$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$E$55-'ENG_CAPEX'!$D$77)))</f>
+        <v/>
+      </c>
+      <c r="F66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$F$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$F$55-'ENG_CAPEX'!$E$77)))</f>
+        <v/>
+      </c>
+      <c r="G66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$G$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$G$55-'ENG_CAPEX'!$F$77)))</f>
+        <v/>
+      </c>
+      <c r="H66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$H$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$H$55-'ENG_CAPEX'!$G$77)))</f>
+        <v/>
+      </c>
+      <c r="I66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$I$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$I$55-'ENG_CAPEX'!$H$77)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$J$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$J$55-'ENG_CAPEX'!$I$77)))</f>
+        <v/>
+      </c>
+      <c r="K66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$K$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$K$55-'ENG_CAPEX'!$J$77)))</f>
+        <v/>
+      </c>
+      <c r="L66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$L$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$L$55-'ENG_CAPEX'!$K$77)))</f>
+        <v/>
+      </c>
+      <c r="M66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$M$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$M$55-'ENG_CAPEX'!$L$77)))</f>
+        <v/>
+      </c>
+      <c r="N66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$N$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$N$55-'ENG_CAPEX'!$M$77)))</f>
+        <v/>
+      </c>
+      <c r="O66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$O$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$O$55-'ENG_CAPEX'!$N$77)))</f>
+        <v/>
+      </c>
+      <c r="P66" s="14">
+        <f>IF('IN_FIN'!$F$16&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$P$55/'IN_FIN'!$F$16,'ENG_CAPEX'!$P$55-'ENG_CAPEX'!$O$77)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>استهلاک مهندسی، نصب و راه‌اندازی</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.dep.8</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$D$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$D$56-0)))</f>
+        <v/>
+      </c>
+      <c r="E67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$E$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$E$56-'ENG_CAPEX'!$D$78)))</f>
+        <v/>
+      </c>
+      <c r="F67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$F$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$F$56-'ENG_CAPEX'!$E$78)))</f>
+        <v/>
+      </c>
+      <c r="G67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$G$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$G$56-'ENG_CAPEX'!$F$78)))</f>
+        <v/>
+      </c>
+      <c r="H67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$H$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$H$56-'ENG_CAPEX'!$G$78)))</f>
+        <v/>
+      </c>
+      <c r="I67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$I$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$I$56-'ENG_CAPEX'!$H$78)))</f>
+        <v/>
+      </c>
+      <c r="J67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$J$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$J$56-'ENG_CAPEX'!$I$78)))</f>
+        <v/>
+      </c>
+      <c r="K67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$K$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$K$56-'ENG_CAPEX'!$J$78)))</f>
+        <v/>
+      </c>
+      <c r="L67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$L$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$L$56-'ENG_CAPEX'!$K$78)))</f>
+        <v/>
+      </c>
+      <c r="M67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$M$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$M$56-'ENG_CAPEX'!$L$78)))</f>
+        <v/>
+      </c>
+      <c r="N67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$N$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$N$56-'ENG_CAPEX'!$M$78)))</f>
+        <v/>
+      </c>
+      <c r="O67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$O$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$O$56-'ENG_CAPEX'!$N$78)))</f>
+        <v/>
+      </c>
+      <c r="P67" s="14">
+        <f>IF('IN_FIN'!$F$17&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$P$56/'IN_FIN'!$F$17,'ENG_CAPEX'!$P$56-'ENG_CAPEX'!$O$78)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>استهلاک هزینه‌های پیش از بهره‌برداری</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.dep.9</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$D$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$D$57-0)))</f>
+        <v/>
+      </c>
+      <c r="E68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$E$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$E$57-'ENG_CAPEX'!$D$79)))</f>
+        <v/>
+      </c>
+      <c r="F68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$F$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$F$57-'ENG_CAPEX'!$E$79)))</f>
+        <v/>
+      </c>
+      <c r="G68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$G$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$G$57-'ENG_CAPEX'!$F$79)))</f>
+        <v/>
+      </c>
+      <c r="H68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$H$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$H$57-'ENG_CAPEX'!$G$79)))</f>
+        <v/>
+      </c>
+      <c r="I68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$I$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$I$57-'ENG_CAPEX'!$H$79)))</f>
+        <v/>
+      </c>
+      <c r="J68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$J$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$J$57-'ENG_CAPEX'!$I$79)))</f>
+        <v/>
+      </c>
+      <c r="K68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$K$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$K$57-'ENG_CAPEX'!$J$79)))</f>
+        <v/>
+      </c>
+      <c r="L68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$L$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$L$57-'ENG_CAPEX'!$K$79)))</f>
+        <v/>
+      </c>
+      <c r="M68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$M$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$M$57-'ENG_CAPEX'!$L$79)))</f>
+        <v/>
+      </c>
+      <c r="N68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$N$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$N$57-'ENG_CAPEX'!$M$79)))</f>
+        <v/>
+      </c>
+      <c r="O68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$O$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$O$57-'ENG_CAPEX'!$N$79)))</f>
+        <v/>
+      </c>
+      <c r="P68" s="14">
+        <f>IF('IN_FIN'!$F$18&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$P$57/'IN_FIN'!$F$18,'ENG_CAPEX'!$P$57-'ENG_CAPEX'!$O$79)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>استهلاک ذخیره احتیاطی فیزیکی</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.dep.10</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$D$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$D$58-0)))</f>
+        <v/>
+      </c>
+      <c r="E69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$E$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$E$58-'ENG_CAPEX'!$D$80)))</f>
+        <v/>
+      </c>
+      <c r="F69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$F$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$F$58-'ENG_CAPEX'!$E$80)))</f>
+        <v/>
+      </c>
+      <c r="G69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$G$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$G$58-'ENG_CAPEX'!$F$80)))</f>
+        <v/>
+      </c>
+      <c r="H69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$H$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$H$58-'ENG_CAPEX'!$G$80)))</f>
+        <v/>
+      </c>
+      <c r="I69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$I$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$I$58-'ENG_CAPEX'!$H$80)))</f>
+        <v/>
+      </c>
+      <c r="J69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$J$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$J$58-'ENG_CAPEX'!$I$80)))</f>
+        <v/>
+      </c>
+      <c r="K69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$K$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$K$58-'ENG_CAPEX'!$J$80)))</f>
+        <v/>
+      </c>
+      <c r="L69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$L$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$L$58-'ENG_CAPEX'!$K$80)))</f>
+        <v/>
+      </c>
+      <c r="M69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$M$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$M$58-'ENG_CAPEX'!$L$80)))</f>
+        <v/>
+      </c>
+      <c r="N69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$N$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$N$58-'ENG_CAPEX'!$M$80)))</f>
+        <v/>
+      </c>
+      <c r="O69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$O$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$O$58-'ENG_CAPEX'!$N$80)))</f>
+        <v/>
+      </c>
+      <c r="P69" s="14">
+        <f>IF('IN_FIN'!$F$19&lt;=0,0,MAX(0,MIN('ENG_CAPEX'!$P$58/'IN_FIN'!$F$19,'ENG_CAPEX'!$P$58-'ENG_CAPEX'!$O$80)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>استهلاک انباشتهٔ طبقهٔ زمین</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.adepc.0</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D70" s="14">
+        <f>'ENG_CAPEX'!$D$59</f>
+        <v/>
+      </c>
+      <c r="E70" s="14">
+        <f>'ENG_CAPEX'!$D$70+'ENG_CAPEX'!$E$59</f>
+        <v/>
+      </c>
+      <c r="F70" s="14">
+        <f>'ENG_CAPEX'!$E$70+'ENG_CAPEX'!$F$59</f>
+        <v/>
+      </c>
+      <c r="G70" s="14">
+        <f>'ENG_CAPEX'!$F$70+'ENG_CAPEX'!$G$59</f>
+        <v/>
+      </c>
+      <c r="H70" s="14">
+        <f>'ENG_CAPEX'!$G$70+'ENG_CAPEX'!$H$59</f>
+        <v/>
+      </c>
+      <c r="I70" s="14">
+        <f>'ENG_CAPEX'!$H$70+'ENG_CAPEX'!$I$59</f>
+        <v/>
+      </c>
+      <c r="J70" s="14">
+        <f>'ENG_CAPEX'!$I$70+'ENG_CAPEX'!$J$59</f>
+        <v/>
+      </c>
+      <c r="K70" s="14">
+        <f>'ENG_CAPEX'!$J$70+'ENG_CAPEX'!$K$59</f>
+        <v/>
+      </c>
+      <c r="L70" s="14">
+        <f>'ENG_CAPEX'!$K$70+'ENG_CAPEX'!$L$59</f>
+        <v/>
+      </c>
+      <c r="M70" s="14">
+        <f>'ENG_CAPEX'!$L$70+'ENG_CAPEX'!$M$59</f>
+        <v/>
+      </c>
+      <c r="N70" s="14">
+        <f>'ENG_CAPEX'!$M$70+'ENG_CAPEX'!$N$59</f>
+        <v/>
+      </c>
+      <c r="O70" s="14">
+        <f>'ENG_CAPEX'!$N$70+'ENG_CAPEX'!$O$59</f>
+        <v/>
+      </c>
+      <c r="P70" s="14">
+        <f>'ENG_CAPEX'!$O$70+'ENG_CAPEX'!$P$59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>استهلاک انباشتهٔ طبقهٔ محوطه‌سازی و ساختمان</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.adepc.1</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D71" s="14">
+        <f>'ENG_CAPEX'!$D$60</f>
+        <v/>
+      </c>
+      <c r="E71" s="14">
+        <f>'ENG_CAPEX'!$D$71+'ENG_CAPEX'!$E$60</f>
+        <v/>
+      </c>
+      <c r="F71" s="14">
+        <f>'ENG_CAPEX'!$E$71+'ENG_CAPEX'!$F$60</f>
+        <v/>
+      </c>
+      <c r="G71" s="14">
+        <f>'ENG_CAPEX'!$F$71+'ENG_CAPEX'!$G$60</f>
+        <v/>
+      </c>
+      <c r="H71" s="14">
+        <f>'ENG_CAPEX'!$G$71+'ENG_CAPEX'!$H$60</f>
+        <v/>
+      </c>
+      <c r="I71" s="14">
+        <f>'ENG_CAPEX'!$H$71+'ENG_CAPEX'!$I$60</f>
+        <v/>
+      </c>
+      <c r="J71" s="14">
+        <f>'ENG_CAPEX'!$I$71+'ENG_CAPEX'!$J$60</f>
+        <v/>
+      </c>
+      <c r="K71" s="14">
+        <f>'ENG_CAPEX'!$J$71+'ENG_CAPEX'!$K$60</f>
+        <v/>
+      </c>
+      <c r="L71" s="14">
+        <f>'ENG_CAPEX'!$K$71+'ENG_CAPEX'!$L$60</f>
+        <v/>
+      </c>
+      <c r="M71" s="14">
+        <f>'ENG_CAPEX'!$L$71+'ENG_CAPEX'!$M$60</f>
+        <v/>
+      </c>
+      <c r="N71" s="14">
+        <f>'ENG_CAPEX'!$M$71+'ENG_CAPEX'!$N$60</f>
+        <v/>
+      </c>
+      <c r="O71" s="14">
+        <f>'ENG_CAPEX'!$N$71+'ENG_CAPEX'!$O$60</f>
+        <v/>
+      </c>
+      <c r="P71" s="14">
+        <f>'ENG_CAPEX'!$O$71+'ENG_CAPEX'!$P$60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>استهلاک انباشتهٔ طبقهٔ ماشین‌آلات وارداتی</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.adepc.2</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D72" s="14">
+        <f>'ENG_CAPEX'!$D$61</f>
+        <v/>
+      </c>
+      <c r="E72" s="14">
+        <f>'ENG_CAPEX'!$D$72+'ENG_CAPEX'!$E$61</f>
+        <v/>
+      </c>
+      <c r="F72" s="14">
+        <f>'ENG_CAPEX'!$E$72+'ENG_CAPEX'!$F$61</f>
+        <v/>
+      </c>
+      <c r="G72" s="14">
+        <f>'ENG_CAPEX'!$F$72+'ENG_CAPEX'!$G$61</f>
+        <v/>
+      </c>
+      <c r="H72" s="14">
+        <f>'ENG_CAPEX'!$G$72+'ENG_CAPEX'!$H$61</f>
+        <v/>
+      </c>
+      <c r="I72" s="14">
+        <f>'ENG_CAPEX'!$H$72+'ENG_CAPEX'!$I$61</f>
+        <v/>
+      </c>
+      <c r="J72" s="14">
+        <f>'ENG_CAPEX'!$I$72+'ENG_CAPEX'!$J$61</f>
+        <v/>
+      </c>
+      <c r="K72" s="14">
+        <f>'ENG_CAPEX'!$J$72+'ENG_CAPEX'!$K$61</f>
+        <v/>
+      </c>
+      <c r="L72" s="14">
+        <f>'ENG_CAPEX'!$K$72+'ENG_CAPEX'!$L$61</f>
+        <v/>
+      </c>
+      <c r="M72" s="14">
+        <f>'ENG_CAPEX'!$L$72+'ENG_CAPEX'!$M$61</f>
+        <v/>
+      </c>
+      <c r="N72" s="14">
+        <f>'ENG_CAPEX'!$M$72+'ENG_CAPEX'!$N$61</f>
+        <v/>
+      </c>
+      <c r="O72" s="14">
+        <f>'ENG_CAPEX'!$N$72+'ENG_CAPEX'!$O$61</f>
+        <v/>
+      </c>
+      <c r="P72" s="14">
+        <f>'ENG_CAPEX'!$O$72+'ENG_CAPEX'!$P$61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>استهلاک انباشتهٔ طبقهٔ ماشین‌آلات داخلی</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.adepc.3</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D73" s="14">
+        <f>'ENG_CAPEX'!$D$62</f>
+        <v/>
+      </c>
+      <c r="E73" s="14">
+        <f>'ENG_CAPEX'!$D$73+'ENG_CAPEX'!$E$62</f>
+        <v/>
+      </c>
+      <c r="F73" s="14">
+        <f>'ENG_CAPEX'!$E$73+'ENG_CAPEX'!$F$62</f>
+        <v/>
+      </c>
+      <c r="G73" s="14">
+        <f>'ENG_CAPEX'!$F$73+'ENG_CAPEX'!$G$62</f>
+        <v/>
+      </c>
+      <c r="H73" s="14">
+        <f>'ENG_CAPEX'!$G$73+'ENG_CAPEX'!$H$62</f>
+        <v/>
+      </c>
+      <c r="I73" s="14">
+        <f>'ENG_CAPEX'!$H$73+'ENG_CAPEX'!$I$62</f>
+        <v/>
+      </c>
+      <c r="J73" s="14">
+        <f>'ENG_CAPEX'!$I$73+'ENG_CAPEX'!$J$62</f>
+        <v/>
+      </c>
+      <c r="K73" s="14">
+        <f>'ENG_CAPEX'!$J$73+'ENG_CAPEX'!$K$62</f>
+        <v/>
+      </c>
+      <c r="L73" s="14">
+        <f>'ENG_CAPEX'!$K$73+'ENG_CAPEX'!$L$62</f>
+        <v/>
+      </c>
+      <c r="M73" s="14">
+        <f>'ENG_CAPEX'!$L$73+'ENG_CAPEX'!$M$62</f>
+        <v/>
+      </c>
+      <c r="N73" s="14">
+        <f>'ENG_CAPEX'!$M$73+'ENG_CAPEX'!$N$62</f>
+        <v/>
+      </c>
+      <c r="O73" s="14">
+        <f>'ENG_CAPEX'!$N$73+'ENG_CAPEX'!$O$62</f>
+        <v/>
+      </c>
+      <c r="P73" s="14">
+        <f>'ENG_CAPEX'!$O$73+'ENG_CAPEX'!$P$62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>استهلاک انباشتهٔ طبقهٔ تأسیسات و تجهیزات جانبی</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.adepc.4</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D74" s="14">
+        <f>'ENG_CAPEX'!$D$63</f>
+        <v/>
+      </c>
+      <c r="E74" s="14">
+        <f>'ENG_CAPEX'!$D$74+'ENG_CAPEX'!$E$63</f>
+        <v/>
+      </c>
+      <c r="F74" s="14">
+        <f>'ENG_CAPEX'!$E$74+'ENG_CAPEX'!$F$63</f>
+        <v/>
+      </c>
+      <c r="G74" s="14">
+        <f>'ENG_CAPEX'!$F$74+'ENG_CAPEX'!$G$63</f>
+        <v/>
+      </c>
+      <c r="H74" s="14">
+        <f>'ENG_CAPEX'!$G$74+'ENG_CAPEX'!$H$63</f>
+        <v/>
+      </c>
+      <c r="I74" s="14">
+        <f>'ENG_CAPEX'!$H$74+'ENG_CAPEX'!$I$63</f>
+        <v/>
+      </c>
+      <c r="J74" s="14">
+        <f>'ENG_CAPEX'!$I$74+'ENG_CAPEX'!$J$63</f>
+        <v/>
+      </c>
+      <c r="K74" s="14">
+        <f>'ENG_CAPEX'!$J$74+'ENG_CAPEX'!$K$63</f>
+        <v/>
+      </c>
+      <c r="L74" s="14">
+        <f>'ENG_CAPEX'!$K$74+'ENG_CAPEX'!$L$63</f>
+        <v/>
+      </c>
+      <c r="M74" s="14">
+        <f>'ENG_CAPEX'!$L$74+'ENG_CAPEX'!$M$63</f>
+        <v/>
+      </c>
+      <c r="N74" s="14">
+        <f>'ENG_CAPEX'!$M$74+'ENG_CAPEX'!$N$63</f>
+        <v/>
+      </c>
+      <c r="O74" s="14">
+        <f>'ENG_CAPEX'!$N$74+'ENG_CAPEX'!$O$63</f>
+        <v/>
+      </c>
+      <c r="P74" s="14">
+        <f>'ENG_CAPEX'!$O$74+'ENG_CAPEX'!$P$63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>استهلاک انباشتهٔ طبقهٔ تصفیه‌خانه و تجهیزات زیست‌محیطی</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.adepc.5</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D75" s="14">
+        <f>'ENG_CAPEX'!$D$64</f>
+        <v/>
+      </c>
+      <c r="E75" s="14">
+        <f>'ENG_CAPEX'!$D$75+'ENG_CAPEX'!$E$64</f>
+        <v/>
+      </c>
+      <c r="F75" s="14">
+        <f>'ENG_CAPEX'!$E$75+'ENG_CAPEX'!$F$64</f>
+        <v/>
+      </c>
+      <c r="G75" s="14">
+        <f>'ENG_CAPEX'!$F$75+'ENG_CAPEX'!$G$64</f>
+        <v/>
+      </c>
+      <c r="H75" s="14">
+        <f>'ENG_CAPEX'!$G$75+'ENG_CAPEX'!$H$64</f>
+        <v/>
+      </c>
+      <c r="I75" s="14">
+        <f>'ENG_CAPEX'!$H$75+'ENG_CAPEX'!$I$64</f>
+        <v/>
+      </c>
+      <c r="J75" s="14">
+        <f>'ENG_CAPEX'!$I$75+'ENG_CAPEX'!$J$64</f>
+        <v/>
+      </c>
+      <c r="K75" s="14">
+        <f>'ENG_CAPEX'!$J$75+'ENG_CAPEX'!$K$64</f>
+        <v/>
+      </c>
+      <c r="L75" s="14">
+        <f>'ENG_CAPEX'!$K$75+'ENG_CAPEX'!$L$64</f>
+        <v/>
+      </c>
+      <c r="M75" s="14">
+        <f>'ENG_CAPEX'!$L$75+'ENG_CAPEX'!$M$64</f>
+        <v/>
+      </c>
+      <c r="N75" s="14">
+        <f>'ENG_CAPEX'!$M$75+'ENG_CAPEX'!$N$64</f>
+        <v/>
+      </c>
+      <c r="O75" s="14">
+        <f>'ENG_CAPEX'!$N$75+'ENG_CAPEX'!$O$64</f>
+        <v/>
+      </c>
+      <c r="P75" s="14">
+        <f>'ENG_CAPEX'!$O$75+'ENG_CAPEX'!$P$64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>استهلاک انباشتهٔ طبقهٔ تجهیزات حمل‌ونقل داخلی</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.adepc.6</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D76" s="14">
+        <f>'ENG_CAPEX'!$D$65</f>
+        <v/>
+      </c>
+      <c r="E76" s="14">
+        <f>'ENG_CAPEX'!$D$76+'ENG_CAPEX'!$E$65</f>
+        <v/>
+      </c>
+      <c r="F76" s="14">
+        <f>'ENG_CAPEX'!$E$76+'ENG_CAPEX'!$F$65</f>
+        <v/>
+      </c>
+      <c r="G76" s="14">
+        <f>'ENG_CAPEX'!$F$76+'ENG_CAPEX'!$G$65</f>
+        <v/>
+      </c>
+      <c r="H76" s="14">
+        <f>'ENG_CAPEX'!$G$76+'ENG_CAPEX'!$H$65</f>
+        <v/>
+      </c>
+      <c r="I76" s="14">
+        <f>'ENG_CAPEX'!$H$76+'ENG_CAPEX'!$I$65</f>
+        <v/>
+      </c>
+      <c r="J76" s="14">
+        <f>'ENG_CAPEX'!$I$76+'ENG_CAPEX'!$J$65</f>
+        <v/>
+      </c>
+      <c r="K76" s="14">
+        <f>'ENG_CAPEX'!$J$76+'ENG_CAPEX'!$K$65</f>
+        <v/>
+      </c>
+      <c r="L76" s="14">
+        <f>'ENG_CAPEX'!$K$76+'ENG_CAPEX'!$L$65</f>
+        <v/>
+      </c>
+      <c r="M76" s="14">
+        <f>'ENG_CAPEX'!$L$76+'ENG_CAPEX'!$M$65</f>
+        <v/>
+      </c>
+      <c r="N76" s="14">
+        <f>'ENG_CAPEX'!$M$76+'ENG_CAPEX'!$N$65</f>
+        <v/>
+      </c>
+      <c r="O76" s="14">
+        <f>'ENG_CAPEX'!$N$76+'ENG_CAPEX'!$O$65</f>
+        <v/>
+      </c>
+      <c r="P76" s="14">
+        <f>'ENG_CAPEX'!$O$76+'ENG_CAPEX'!$P$65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>استهلاک انباشتهٔ طبقهٔ آزمایشگاه و ابزار دقیق</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.adepc.7</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D77" s="14">
+        <f>'ENG_CAPEX'!$D$66</f>
+        <v/>
+      </c>
+      <c r="E77" s="14">
+        <f>'ENG_CAPEX'!$D$77+'ENG_CAPEX'!$E$66</f>
+        <v/>
+      </c>
+      <c r="F77" s="14">
+        <f>'ENG_CAPEX'!$E$77+'ENG_CAPEX'!$F$66</f>
+        <v/>
+      </c>
+      <c r="G77" s="14">
+        <f>'ENG_CAPEX'!$F$77+'ENG_CAPEX'!$G$66</f>
+        <v/>
+      </c>
+      <c r="H77" s="14">
+        <f>'ENG_CAPEX'!$G$77+'ENG_CAPEX'!$H$66</f>
+        <v/>
+      </c>
+      <c r="I77" s="14">
+        <f>'ENG_CAPEX'!$H$77+'ENG_CAPEX'!$I$66</f>
+        <v/>
+      </c>
+      <c r="J77" s="14">
+        <f>'ENG_CAPEX'!$I$77+'ENG_CAPEX'!$J$66</f>
+        <v/>
+      </c>
+      <c r="K77" s="14">
+        <f>'ENG_CAPEX'!$J$77+'ENG_CAPEX'!$K$66</f>
+        <v/>
+      </c>
+      <c r="L77" s="14">
+        <f>'ENG_CAPEX'!$K$77+'ENG_CAPEX'!$L$66</f>
+        <v/>
+      </c>
+      <c r="M77" s="14">
+        <f>'ENG_CAPEX'!$L$77+'ENG_CAPEX'!$M$66</f>
+        <v/>
+      </c>
+      <c r="N77" s="14">
+        <f>'ENG_CAPEX'!$M$77+'ENG_CAPEX'!$N$66</f>
+        <v/>
+      </c>
+      <c r="O77" s="14">
+        <f>'ENG_CAPEX'!$N$77+'ENG_CAPEX'!$O$66</f>
+        <v/>
+      </c>
+      <c r="P77" s="14">
+        <f>'ENG_CAPEX'!$O$77+'ENG_CAPEX'!$P$66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>استهلاک انباشتهٔ طبقهٔ مهندسی، نصب و راه‌اندازی</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.adepc.8</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D78" s="14">
+        <f>'ENG_CAPEX'!$D$67</f>
+        <v/>
+      </c>
+      <c r="E78" s="14">
+        <f>'ENG_CAPEX'!$D$78+'ENG_CAPEX'!$E$67</f>
+        <v/>
+      </c>
+      <c r="F78" s="14">
+        <f>'ENG_CAPEX'!$E$78+'ENG_CAPEX'!$F$67</f>
+        <v/>
+      </c>
+      <c r="G78" s="14">
+        <f>'ENG_CAPEX'!$F$78+'ENG_CAPEX'!$G$67</f>
+        <v/>
+      </c>
+      <c r="H78" s="14">
+        <f>'ENG_CAPEX'!$G$78+'ENG_CAPEX'!$H$67</f>
+        <v/>
+      </c>
+      <c r="I78" s="14">
+        <f>'ENG_CAPEX'!$H$78+'ENG_CAPEX'!$I$67</f>
+        <v/>
+      </c>
+      <c r="J78" s="14">
+        <f>'ENG_CAPEX'!$I$78+'ENG_CAPEX'!$J$67</f>
+        <v/>
+      </c>
+      <c r="K78" s="14">
+        <f>'ENG_CAPEX'!$J$78+'ENG_CAPEX'!$K$67</f>
+        <v/>
+      </c>
+      <c r="L78" s="14">
+        <f>'ENG_CAPEX'!$K$78+'ENG_CAPEX'!$L$67</f>
+        <v/>
+      </c>
+      <c r="M78" s="14">
+        <f>'ENG_CAPEX'!$L$78+'ENG_CAPEX'!$M$67</f>
+        <v/>
+      </c>
+      <c r="N78" s="14">
+        <f>'ENG_CAPEX'!$M$78+'ENG_CAPEX'!$N$67</f>
+        <v/>
+      </c>
+      <c r="O78" s="14">
+        <f>'ENG_CAPEX'!$N$78+'ENG_CAPEX'!$O$67</f>
+        <v/>
+      </c>
+      <c r="P78" s="14">
+        <f>'ENG_CAPEX'!$O$78+'ENG_CAPEX'!$P$67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>استهلاک انباشتهٔ طبقهٔ هزینه‌های پیش از بهره‌برداری</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.adepc.9</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D79" s="14">
+        <f>'ENG_CAPEX'!$D$68</f>
+        <v/>
+      </c>
+      <c r="E79" s="14">
+        <f>'ENG_CAPEX'!$D$79+'ENG_CAPEX'!$E$68</f>
+        <v/>
+      </c>
+      <c r="F79" s="14">
+        <f>'ENG_CAPEX'!$E$79+'ENG_CAPEX'!$F$68</f>
+        <v/>
+      </c>
+      <c r="G79" s="14">
+        <f>'ENG_CAPEX'!$F$79+'ENG_CAPEX'!$G$68</f>
+        <v/>
+      </c>
+      <c r="H79" s="14">
+        <f>'ENG_CAPEX'!$G$79+'ENG_CAPEX'!$H$68</f>
+        <v/>
+      </c>
+      <c r="I79" s="14">
+        <f>'ENG_CAPEX'!$H$79+'ENG_CAPEX'!$I$68</f>
+        <v/>
+      </c>
+      <c r="J79" s="14">
+        <f>'ENG_CAPEX'!$I$79+'ENG_CAPEX'!$J$68</f>
+        <v/>
+      </c>
+      <c r="K79" s="14">
+        <f>'ENG_CAPEX'!$J$79+'ENG_CAPEX'!$K$68</f>
+        <v/>
+      </c>
+      <c r="L79" s="14">
+        <f>'ENG_CAPEX'!$K$79+'ENG_CAPEX'!$L$68</f>
+        <v/>
+      </c>
+      <c r="M79" s="14">
+        <f>'ENG_CAPEX'!$L$79+'ENG_CAPEX'!$M$68</f>
+        <v/>
+      </c>
+      <c r="N79" s="14">
+        <f>'ENG_CAPEX'!$M$79+'ENG_CAPEX'!$N$68</f>
+        <v/>
+      </c>
+      <c r="O79" s="14">
+        <f>'ENG_CAPEX'!$N$79+'ENG_CAPEX'!$O$68</f>
+        <v/>
+      </c>
+      <c r="P79" s="14">
+        <f>'ENG_CAPEX'!$O$79+'ENG_CAPEX'!$P$68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>استهلاک انباشتهٔ طبقهٔ ذخیره احتیاطی فیزیکی</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.adepc.10</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D80" s="14">
+        <f>'ENG_CAPEX'!$D$69</f>
+        <v/>
+      </c>
+      <c r="E80" s="14">
+        <f>'ENG_CAPEX'!$D$80+'ENG_CAPEX'!$E$69</f>
+        <v/>
+      </c>
+      <c r="F80" s="14">
+        <f>'ENG_CAPEX'!$E$80+'ENG_CAPEX'!$F$69</f>
+        <v/>
+      </c>
+      <c r="G80" s="14">
+        <f>'ENG_CAPEX'!$F$80+'ENG_CAPEX'!$G$69</f>
+        <v/>
+      </c>
+      <c r="H80" s="14">
+        <f>'ENG_CAPEX'!$G$80+'ENG_CAPEX'!$H$69</f>
+        <v/>
+      </c>
+      <c r="I80" s="14">
+        <f>'ENG_CAPEX'!$H$80+'ENG_CAPEX'!$I$69</f>
+        <v/>
+      </c>
+      <c r="J80" s="14">
+        <f>'ENG_CAPEX'!$I$80+'ENG_CAPEX'!$J$69</f>
+        <v/>
+      </c>
+      <c r="K80" s="14">
+        <f>'ENG_CAPEX'!$J$80+'ENG_CAPEX'!$K$69</f>
+        <v/>
+      </c>
+      <c r="L80" s="14">
+        <f>'ENG_CAPEX'!$K$80+'ENG_CAPEX'!$L$69</f>
+        <v/>
+      </c>
+      <c r="M80" s="14">
+        <f>'ENG_CAPEX'!$L$80+'ENG_CAPEX'!$M$69</f>
+        <v/>
+      </c>
+      <c r="N80" s="14">
+        <f>'ENG_CAPEX'!$M$80+'ENG_CAPEX'!$N$69</f>
+        <v/>
+      </c>
+      <c r="O80" s="14">
+        <f>'ENG_CAPEX'!$N$80+'ENG_CAPEX'!$O$69</f>
+        <v/>
+      </c>
+      <c r="P80" s="14">
+        <f>'ENG_CAPEX'!$O$80+'ENG_CAPEX'!$P$69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>جمع استهلاک سالانه</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.dep_total</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D81" s="14">
+        <f>'ENG_CAPEX'!$D$59+'ENG_CAPEX'!$D$60+'ENG_CAPEX'!$D$61+'ENG_CAPEX'!$D$62+'ENG_CAPEX'!$D$63+'ENG_CAPEX'!$D$64+'ENG_CAPEX'!$D$65+'ENG_CAPEX'!$D$66+'ENG_CAPEX'!$D$67+'ENG_CAPEX'!$D$68+'ENG_CAPEX'!$D$69</f>
+        <v/>
+      </c>
+      <c r="E81" s="14">
+        <f>'ENG_CAPEX'!$E$59+'ENG_CAPEX'!$E$60+'ENG_CAPEX'!$E$61+'ENG_CAPEX'!$E$62+'ENG_CAPEX'!$E$63+'ENG_CAPEX'!$E$64+'ENG_CAPEX'!$E$65+'ENG_CAPEX'!$E$66+'ENG_CAPEX'!$E$67+'ENG_CAPEX'!$E$68+'ENG_CAPEX'!$E$69</f>
+        <v/>
+      </c>
+      <c r="F81" s="14">
+        <f>'ENG_CAPEX'!$F$59+'ENG_CAPEX'!$F$60+'ENG_CAPEX'!$F$61+'ENG_CAPEX'!$F$62+'ENG_CAPEX'!$F$63+'ENG_CAPEX'!$F$64+'ENG_CAPEX'!$F$65+'ENG_CAPEX'!$F$66+'ENG_CAPEX'!$F$67+'ENG_CAPEX'!$F$68+'ENG_CAPEX'!$F$69</f>
+        <v/>
+      </c>
+      <c r="G81" s="14">
+        <f>'ENG_CAPEX'!$G$59+'ENG_CAPEX'!$G$60+'ENG_CAPEX'!$G$61+'ENG_CAPEX'!$G$62+'ENG_CAPEX'!$G$63+'ENG_CAPEX'!$G$64+'ENG_CAPEX'!$G$65+'ENG_CAPEX'!$G$66+'ENG_CAPEX'!$G$67+'ENG_CAPEX'!$G$68+'ENG_CAPEX'!$G$69</f>
+        <v/>
+      </c>
+      <c r="H81" s="14">
+        <f>'ENG_CAPEX'!$H$59+'ENG_CAPEX'!$H$60+'ENG_CAPEX'!$H$61+'ENG_CAPEX'!$H$62+'ENG_CAPEX'!$H$63+'ENG_CAPEX'!$H$64+'ENG_CAPEX'!$H$65+'ENG_CAPEX'!$H$66+'ENG_CAPEX'!$H$67+'ENG_CAPEX'!$H$68+'ENG_CAPEX'!$H$69</f>
+        <v/>
+      </c>
+      <c r="I81" s="14">
+        <f>'ENG_CAPEX'!$I$59+'ENG_CAPEX'!$I$60+'ENG_CAPEX'!$I$61+'ENG_CAPEX'!$I$62+'ENG_CAPEX'!$I$63+'ENG_CAPEX'!$I$64+'ENG_CAPEX'!$I$65+'ENG_CAPEX'!$I$66+'ENG_CAPEX'!$I$67+'ENG_CAPEX'!$I$68+'ENG_CAPEX'!$I$69</f>
+        <v/>
+      </c>
+      <c r="J81" s="14">
+        <f>'ENG_CAPEX'!$J$59+'ENG_CAPEX'!$J$60+'ENG_CAPEX'!$J$61+'ENG_CAPEX'!$J$62+'ENG_CAPEX'!$J$63+'ENG_CAPEX'!$J$64+'ENG_CAPEX'!$J$65+'ENG_CAPEX'!$J$66+'ENG_CAPEX'!$J$67+'ENG_CAPEX'!$J$68+'ENG_CAPEX'!$J$69</f>
+        <v/>
+      </c>
+      <c r="K81" s="14">
+        <f>'ENG_CAPEX'!$K$59+'ENG_CAPEX'!$K$60+'ENG_CAPEX'!$K$61+'ENG_CAPEX'!$K$62+'ENG_CAPEX'!$K$63+'ENG_CAPEX'!$K$64+'ENG_CAPEX'!$K$65+'ENG_CAPEX'!$K$66+'ENG_CAPEX'!$K$67+'ENG_CAPEX'!$K$68+'ENG_CAPEX'!$K$69</f>
+        <v/>
+      </c>
+      <c r="L81" s="14">
+        <f>'ENG_CAPEX'!$L$59+'ENG_CAPEX'!$L$60+'ENG_CAPEX'!$L$61+'ENG_CAPEX'!$L$62+'ENG_CAPEX'!$L$63+'ENG_CAPEX'!$L$64+'ENG_CAPEX'!$L$65+'ENG_CAPEX'!$L$66+'ENG_CAPEX'!$L$67+'ENG_CAPEX'!$L$68+'ENG_CAPEX'!$L$69</f>
+        <v/>
+      </c>
+      <c r="M81" s="14">
+        <f>'ENG_CAPEX'!$M$59+'ENG_CAPEX'!$M$60+'ENG_CAPEX'!$M$61+'ENG_CAPEX'!$M$62+'ENG_CAPEX'!$M$63+'ENG_CAPEX'!$M$64+'ENG_CAPEX'!$M$65+'ENG_CAPEX'!$M$66+'ENG_CAPEX'!$M$67+'ENG_CAPEX'!$M$68+'ENG_CAPEX'!$M$69</f>
+        <v/>
+      </c>
+      <c r="N81" s="14">
+        <f>'ENG_CAPEX'!$N$59+'ENG_CAPEX'!$N$60+'ENG_CAPEX'!$N$61+'ENG_CAPEX'!$N$62+'ENG_CAPEX'!$N$63+'ENG_CAPEX'!$N$64+'ENG_CAPEX'!$N$65+'ENG_CAPEX'!$N$66+'ENG_CAPEX'!$N$67+'ENG_CAPEX'!$N$68+'ENG_CAPEX'!$N$69</f>
+        <v/>
+      </c>
+      <c r="O81" s="14">
+        <f>'ENG_CAPEX'!$O$59+'ENG_CAPEX'!$O$60+'ENG_CAPEX'!$O$61+'ENG_CAPEX'!$O$62+'ENG_CAPEX'!$O$63+'ENG_CAPEX'!$O$64+'ENG_CAPEX'!$O$65+'ENG_CAPEX'!$O$66+'ENG_CAPEX'!$O$67+'ENG_CAPEX'!$O$68+'ENG_CAPEX'!$O$69</f>
+        <v/>
+      </c>
+      <c r="P81" s="14">
+        <f>'ENG_CAPEX'!$P$59+'ENG_CAPEX'!$P$60+'ENG_CAPEX'!$P$61+'ENG_CAPEX'!$P$62+'ENG_CAPEX'!$P$63+'ENG_CAPEX'!$P$64+'ENG_CAPEX'!$P$65+'ENG_CAPEX'!$P$66+'ENG_CAPEX'!$P$67+'ENG_CAPEX'!$P$68+'ENG_CAPEX'!$P$69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>استهلاک انباشته - افتتاحیه</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.accumdep_open</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D82" s="14">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E82" s="14">
+        <f>'ENG_CAPEX'!$D$83</f>
+        <v/>
+      </c>
+      <c r="F82" s="14">
+        <f>'ENG_CAPEX'!$E$83</f>
+        <v/>
+      </c>
+      <c r="G82" s="14">
+        <f>'ENG_CAPEX'!$F$83</f>
+        <v/>
+      </c>
+      <c r="H82" s="14">
+        <f>'ENG_CAPEX'!$G$83</f>
+        <v/>
+      </c>
+      <c r="I82" s="14">
+        <f>'ENG_CAPEX'!$H$83</f>
+        <v/>
+      </c>
+      <c r="J82" s="14">
+        <f>'ENG_CAPEX'!$I$83</f>
+        <v/>
+      </c>
+      <c r="K82" s="14">
+        <f>'ENG_CAPEX'!$J$83</f>
+        <v/>
+      </c>
+      <c r="L82" s="14">
+        <f>'ENG_CAPEX'!$K$83</f>
+        <v/>
+      </c>
+      <c r="M82" s="14">
+        <f>'ENG_CAPEX'!$L$83</f>
+        <v/>
+      </c>
+      <c r="N82" s="14">
+        <f>'ENG_CAPEX'!$M$83</f>
+        <v/>
+      </c>
+      <c r="O82" s="14">
+        <f>'ENG_CAPEX'!$N$83</f>
+        <v/>
+      </c>
+      <c r="P82" s="14">
+        <f>'ENG_CAPEX'!$O$83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>استهلاک انباشته - اختتامیه</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.accumdep</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D83" s="14">
+        <f>'ENG_CAPEX'!$D$82+'ENG_CAPEX'!$D$81</f>
+        <v/>
+      </c>
+      <c r="E83" s="14">
+        <f>'ENG_CAPEX'!$E$82+'ENG_CAPEX'!$E$81</f>
+        <v/>
+      </c>
+      <c r="F83" s="14">
+        <f>'ENG_CAPEX'!$F$82+'ENG_CAPEX'!$F$81</f>
+        <v/>
+      </c>
+      <c r="G83" s="14">
+        <f>'ENG_CAPEX'!$G$82+'ENG_CAPEX'!$G$81</f>
+        <v/>
+      </c>
+      <c r="H83" s="14">
+        <f>'ENG_CAPEX'!$H$82+'ENG_CAPEX'!$H$81</f>
+        <v/>
+      </c>
+      <c r="I83" s="14">
+        <f>'ENG_CAPEX'!$I$82+'ENG_CAPEX'!$I$81</f>
+        <v/>
+      </c>
+      <c r="J83" s="14">
+        <f>'ENG_CAPEX'!$J$82+'ENG_CAPEX'!$J$81</f>
+        <v/>
+      </c>
+      <c r="K83" s="14">
+        <f>'ENG_CAPEX'!$K$82+'ENG_CAPEX'!$K$81</f>
+        <v/>
+      </c>
+      <c r="L83" s="14">
+        <f>'ENG_CAPEX'!$L$82+'ENG_CAPEX'!$L$81</f>
+        <v/>
+      </c>
+      <c r="M83" s="14">
+        <f>'ENG_CAPEX'!$M$82+'ENG_CAPEX'!$M$81</f>
+        <v/>
+      </c>
+      <c r="N83" s="14">
+        <f>'ENG_CAPEX'!$N$82+'ENG_CAPEX'!$N$81</f>
+        <v/>
+      </c>
+      <c r="O83" s="14">
+        <f>'ENG_CAPEX'!$O$82+'ENG_CAPEX'!$O$81</f>
+        <v/>
+      </c>
+      <c r="P83" s="14">
+        <f>'ENG_CAPEX'!$P$82+'ENG_CAPEX'!$P$81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ارزش دفتری خالص (NBV)</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.nbv</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D84" s="14">
+        <f>'ENG_CAPEX'!$D$47-'ENG_CAPEX'!$D$83</f>
+        <v/>
+      </c>
+      <c r="E84" s="14">
+        <f>'ENG_CAPEX'!$E$47-'ENG_CAPEX'!$E$83</f>
+        <v/>
+      </c>
+      <c r="F84" s="14">
+        <f>'ENG_CAPEX'!$F$47-'ENG_CAPEX'!$F$83</f>
+        <v/>
+      </c>
+      <c r="G84" s="14">
+        <f>'ENG_CAPEX'!$G$47-'ENG_CAPEX'!$G$83</f>
+        <v/>
+      </c>
+      <c r="H84" s="14">
+        <f>'ENG_CAPEX'!$H$47-'ENG_CAPEX'!$H$83</f>
+        <v/>
+      </c>
+      <c r="I84" s="14">
+        <f>'ENG_CAPEX'!$I$47-'ENG_CAPEX'!$I$83</f>
+        <v/>
+      </c>
+      <c r="J84" s="14">
+        <f>'ENG_CAPEX'!$J$47-'ENG_CAPEX'!$J$83</f>
+        <v/>
+      </c>
+      <c r="K84" s="14">
+        <f>'ENG_CAPEX'!$K$47-'ENG_CAPEX'!$K$83</f>
+        <v/>
+      </c>
+      <c r="L84" s="14">
+        <f>'ENG_CAPEX'!$L$47-'ENG_CAPEX'!$L$83</f>
+        <v/>
+      </c>
+      <c r="M84" s="14">
+        <f>'ENG_CAPEX'!$M$47-'ENG_CAPEX'!$M$83</f>
+        <v/>
+      </c>
+      <c r="N84" s="14">
+        <f>'ENG_CAPEX'!$N$47-'ENG_CAPEX'!$N$83</f>
+        <v/>
+      </c>
+      <c r="O84" s="14">
+        <f>'ENG_CAPEX'!$O$47-'ENG_CAPEX'!$O$83</f>
+        <v/>
+      </c>
+      <c r="P84" s="14">
+        <f>'ENG_CAPEX'!$P$47-'ENG_CAPEX'!$P$83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ارزش اسقاط برآوردی در پایان افق</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX.salvage</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D85" s="14">
+        <f>IF('IN_MACRO'!$D$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$D$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$D$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$D$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$D$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$D$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$D$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$D$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$D$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$D$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$D$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$D$32))</f>
+        <v/>
+      </c>
+      <c r="E85" s="14">
+        <f>IF('IN_MACRO'!$E$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$E$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$E$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$E$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$E$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$E$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$E$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$E$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$E$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$E$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$E$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$E$32))</f>
+        <v/>
+      </c>
+      <c r="F85" s="14">
+        <f>IF('IN_MACRO'!$F$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$F$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$F$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$F$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$F$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$F$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$F$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$F$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$F$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$F$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$F$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$F$32))</f>
+        <v/>
+      </c>
+      <c r="G85" s="14">
+        <f>IF('IN_MACRO'!$G$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$G$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$G$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$G$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$G$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$G$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$G$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$G$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$G$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$G$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$G$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$G$32))</f>
+        <v/>
+      </c>
+      <c r="H85" s="14">
+        <f>IF('IN_MACRO'!$H$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$H$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$H$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$H$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$H$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$H$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$H$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$H$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$H$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$H$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$H$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$H$32))</f>
+        <v/>
+      </c>
+      <c r="I85" s="14">
+        <f>IF('IN_MACRO'!$I$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$I$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$I$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$I$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$I$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$I$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$I$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$I$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$I$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$I$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$I$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$I$32))</f>
+        <v/>
+      </c>
+      <c r="J85" s="14">
+        <f>IF('IN_MACRO'!$J$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$J$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$J$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$J$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$J$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$J$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$J$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$J$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$J$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$J$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$J$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$J$32))</f>
+        <v/>
+      </c>
+      <c r="K85" s="14">
+        <f>IF('IN_MACRO'!$K$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$K$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$K$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$K$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$K$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$K$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$K$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$K$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$K$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$K$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$K$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$K$32))</f>
+        <v/>
+      </c>
+      <c r="L85" s="14">
+        <f>IF('IN_MACRO'!$L$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$L$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$L$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$L$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$L$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$L$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$L$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$L$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$L$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$L$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$L$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$L$32))</f>
+        <v/>
+      </c>
+      <c r="M85" s="14">
+        <f>IF('IN_MACRO'!$M$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$M$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$M$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$M$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$M$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$M$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$M$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$M$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$M$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$M$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$M$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$M$32))</f>
+        <v/>
+      </c>
+      <c r="N85" s="14">
+        <f>IF('IN_MACRO'!$N$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$N$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$N$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$N$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$N$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$N$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$N$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$N$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$N$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$N$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$N$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$N$32))</f>
+        <v/>
+      </c>
+      <c r="O85" s="14">
+        <f>IF('IN_MACRO'!$O$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$O$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$O$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$O$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$O$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$O$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$O$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$O$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$O$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$O$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$O$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$O$32))</f>
+        <v/>
+      </c>
+      <c r="P85" s="14">
+        <f>IF('IN_MACRO'!$P$23&lt;'IN_MACRO'!$D$11,0,('IN_FIN'!$D$9*'IN_FIN'!$I$9*'ENG_SCEN'!$P$32)+('IN_FIN'!$D$10*'IN_FIN'!$I$10*'ENG_SCEN'!$P$32)+('IN_FIN'!$D$11*'IN_FIN'!$I$11*'ENG_SCEN'!$P$32)+('IN_FIN'!$D$12*'IN_FIN'!$I$12*'ENG_SCEN'!$P$32)+('IN_FIN'!$D$13*'IN_FIN'!$I$13*'ENG_SCEN'!$P$32)+('IN_FIN'!$D$14*'IN_FIN'!$I$14*'ENG_SCEN'!$P$32)+('IN_FIN'!$D$15*'IN_FIN'!$I$15*'ENG_SCEN'!$P$32)+('IN_FIN'!$D$16*'IN_FIN'!$I$16*'ENG_SCEN'!$P$32)+('IN_FIN'!$D$17*'IN_FIN'!$I$17*'ENG_SCEN'!$P$32)+('IN_FIN'!$D$18*'IN_FIN'!$I$18*'ENG_SCEN'!$P$32)+('IN_FIN'!$D$19*'IN_FIN'!$I$19*'ENG_SCEN'!$P$32))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9071,55 +14167,55 @@
         </is>
       </c>
       <c r="D48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|0@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$D$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="E48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|1@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$E$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="F48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|2@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$F$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="G48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|3@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$G$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="H48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|4@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$H$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="I48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|5@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$I$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="J48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|6@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$J$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="K48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|7@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$K$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="L48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|8@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$L$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="M48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|9@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$M$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="N48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|10@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$N$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="O48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|11@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$O$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="P48" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|12@@*'IN_SCEN'!$D$18</f>
+        <f>'ENG_CAPEX'!$P$81*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
     </row>
@@ -9416,55 +14512,55 @@
         </is>
       </c>
       <c r="D53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|0@@+@@ENG_CAPEX|CAPEX.repl_total|0@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$D$21+'ENG_CAPEX'!$D$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="E53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|1@@+@@ENG_CAPEX|CAPEX.repl_total|1@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$E$21+'ENG_CAPEX'!$E$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="F53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|2@@+@@ENG_CAPEX|CAPEX.repl_total|2@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$F$21+'ENG_CAPEX'!$F$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="G53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|3@@+@@ENG_CAPEX|CAPEX.repl_total|3@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$G$21+'ENG_CAPEX'!$G$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="H53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|4@@+@@ENG_CAPEX|CAPEX.repl_total|4@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$H$21+'ENG_CAPEX'!$H$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="I53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|5@@+@@ENG_CAPEX|CAPEX.repl_total|5@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$I$21+'ENG_CAPEX'!$I$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="J53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|6@@+@@ENG_CAPEX|CAPEX.repl_total|6@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$J$21+'ENG_CAPEX'!$J$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="K53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|7@@+@@ENG_CAPEX|CAPEX.repl_total|7@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$K$21+'ENG_CAPEX'!$K$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="L53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|8@@+@@ENG_CAPEX|CAPEX.repl_total|8@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$L$21+'ENG_CAPEX'!$L$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="M53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|9@@+@@ENG_CAPEX|CAPEX.repl_total|9@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$M$21+'ENG_CAPEX'!$M$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="N53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|10@@+@@ENG_CAPEX|CAPEX.repl_total|10@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$N$21+'ENG_CAPEX'!$N$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="O53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|11@@+@@ENG_CAPEX|CAPEX.repl_total|11@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$O$21+'ENG_CAPEX'!$O$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
       <c r="P53" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|12@@+@@ENG_CAPEX|CAPEX.repl_total|12@@)*'IN_SCEN'!$D$18</f>
+        <f>('ENG_CAPEX'!$P$21+'ENG_CAPEX'!$P$42)*'IN_SCEN'!$D$18</f>
         <v/>
       </c>
     </row>
@@ -11041,55 +16137,55 @@
         </is>
       </c>
       <c r="D82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|0@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$D$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="E82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|1@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$E$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="F82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|2@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$F$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="G82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|3@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$G$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="H82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|4@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$H$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="I82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|5@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$I$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="J82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|6@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$J$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="K82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|7@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$K$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="L82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|8@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$L$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="M82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|9@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$M$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="N82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|10@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$N$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="O82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|11@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$O$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="P82" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|12@@*'IN_SCEN'!$E$18</f>
+        <f>'ENG_CAPEX'!$P$81*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
     </row>
@@ -11386,55 +16482,55 @@
         </is>
       </c>
       <c r="D87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|0@@+@@ENG_CAPEX|CAPEX.repl_total|0@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$D$21+'ENG_CAPEX'!$D$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="E87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|1@@+@@ENG_CAPEX|CAPEX.repl_total|1@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$E$21+'ENG_CAPEX'!$E$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="F87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|2@@+@@ENG_CAPEX|CAPEX.repl_total|2@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$F$21+'ENG_CAPEX'!$F$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="G87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|3@@+@@ENG_CAPEX|CAPEX.repl_total|3@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$G$21+'ENG_CAPEX'!$G$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="H87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|4@@+@@ENG_CAPEX|CAPEX.repl_total|4@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$H$21+'ENG_CAPEX'!$H$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="I87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|5@@+@@ENG_CAPEX|CAPEX.repl_total|5@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$I$21+'ENG_CAPEX'!$I$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="J87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|6@@+@@ENG_CAPEX|CAPEX.repl_total|6@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$J$21+'ENG_CAPEX'!$J$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="K87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|7@@+@@ENG_CAPEX|CAPEX.repl_total|7@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$K$21+'ENG_CAPEX'!$K$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="L87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|8@@+@@ENG_CAPEX|CAPEX.repl_total|8@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$L$21+'ENG_CAPEX'!$L$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="M87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|9@@+@@ENG_CAPEX|CAPEX.repl_total|9@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$M$21+'ENG_CAPEX'!$M$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="N87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|10@@+@@ENG_CAPEX|CAPEX.repl_total|10@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$N$21+'ENG_CAPEX'!$N$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="O87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|11@@+@@ENG_CAPEX|CAPEX.repl_total|11@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$O$21+'ENG_CAPEX'!$O$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
       <c r="P87" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|12@@+@@ENG_CAPEX|CAPEX.repl_total|12@@)*'IN_SCEN'!$E$18</f>
+        <f>('ENG_CAPEX'!$P$21+'ENG_CAPEX'!$P$42)*'IN_SCEN'!$E$18</f>
         <v/>
       </c>
     </row>
@@ -13011,55 +18107,55 @@
         </is>
       </c>
       <c r="D116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|0@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$D$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="E116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|1@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$E$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="F116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|2@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$F$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="G116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|3@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$G$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="H116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|4@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$H$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="I116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|5@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$I$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="J116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|6@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$J$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="K116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|7@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$K$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="L116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|8@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$L$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="M116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|9@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$M$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="N116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|10@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$N$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="O116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|11@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$O$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="P116" s="14">
-        <f>@@ENG_CAPEX|CAPEX.dep_total|12@@*'IN_SCEN'!$F$18</f>
+        <f>'ENG_CAPEX'!$P$81*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
     </row>
@@ -13356,55 +18452,55 @@
         </is>
       </c>
       <c r="D121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|0@@+@@ENG_CAPEX|CAPEX.repl_total|0@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$D$21+'ENG_CAPEX'!$D$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="E121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|1@@+@@ENG_CAPEX|CAPEX.repl_total|1@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$E$21+'ENG_CAPEX'!$E$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="F121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|2@@+@@ENG_CAPEX|CAPEX.repl_total|2@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$F$21+'ENG_CAPEX'!$F$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="G121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|3@@+@@ENG_CAPEX|CAPEX.repl_total|3@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$G$21+'ENG_CAPEX'!$G$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="H121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|4@@+@@ENG_CAPEX|CAPEX.repl_total|4@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$H$21+'ENG_CAPEX'!$H$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="I121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|5@@+@@ENG_CAPEX|CAPEX.repl_total|5@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$I$21+'ENG_CAPEX'!$I$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="J121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|6@@+@@ENG_CAPEX|CAPEX.repl_total|6@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$J$21+'ENG_CAPEX'!$J$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="K121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|7@@+@@ENG_CAPEX|CAPEX.repl_total|7@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$K$21+'ENG_CAPEX'!$K$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="L121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|8@@+@@ENG_CAPEX|CAPEX.repl_total|8@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$L$21+'ENG_CAPEX'!$L$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="M121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|9@@+@@ENG_CAPEX|CAPEX.repl_total|9@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$M$21+'ENG_CAPEX'!$M$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="N121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|10@@+@@ENG_CAPEX|CAPEX.repl_total|10@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$N$21+'ENG_CAPEX'!$N$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="O121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|11@@+@@ENG_CAPEX|CAPEX.repl_total|11@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$O$21+'ENG_CAPEX'!$O$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
       <c r="P121" s="14">
-        <f>(@@ENG_CAPEX|CAPEX.cap_total|12@@+@@ENG_CAPEX|CAPEX.repl_total|12@@)*'IN_SCEN'!$F$18</f>
+        <f>('ENG_CAPEX'!$P$21+'ENG_CAPEX'!$P$42)*'IN_SCEN'!$F$18</f>
         <v/>
       </c>
     </row>

--- a/models/lead_acid_recycling/build/out/built.xlsx
+++ b/models/lead_acid_recycling/build/out/built.xlsx
@@ -17,6 +17,7 @@
     <sheet name="ENG_SCEN" sheetId="8" state="hidden" r:id="rId8"/>
     <sheet name="ENG_OPS" sheetId="9" state="hidden" r:id="rId9"/>
     <sheet name="ENG_CAPEX" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet name="ENG_ALLOC" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -130,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,6 +161,7 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6750,6 +6752,3355 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>تخصیص مراکز هزینه (تولیدی و خدماتی)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>موتور محاسبات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>تخصیص هزینه‌های مراکز خدماتی به ایستگاه‌های ۱ تا ۶ بر اساس محرک‌های هزینه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>دوره (t)</t>
+        </is>
+      </c>
+      <c r="D7" s="5">
+        <f>'IN_MACRO'!D$23</f>
+        <v/>
+      </c>
+      <c r="E7" s="5">
+        <f>'IN_MACRO'!E$23</f>
+        <v/>
+      </c>
+      <c r="F7" s="5">
+        <f>'IN_MACRO'!F$23</f>
+        <v/>
+      </c>
+      <c r="G7" s="5">
+        <f>'IN_MACRO'!G$23</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
+        <f>'IN_MACRO'!H$23</f>
+        <v/>
+      </c>
+      <c r="I7" s="5">
+        <f>'IN_MACRO'!I$23</f>
+        <v/>
+      </c>
+      <c r="J7" s="5">
+        <f>'IN_MACRO'!J$23</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
+        <f>'IN_MACRO'!K$23</f>
+        <v/>
+      </c>
+      <c r="L7" s="5">
+        <f>'IN_MACRO'!L$23</f>
+        <v/>
+      </c>
+      <c r="M7" s="5">
+        <f>'IN_MACRO'!M$23</f>
+        <v/>
+      </c>
+      <c r="N7" s="5">
+        <f>'IN_MACRO'!N$23</f>
+        <v/>
+      </c>
+      <c r="O7" s="5">
+        <f>'IN_MACRO'!O$23</f>
+        <v/>
+      </c>
+      <c r="P7" s="5">
+        <f>'IN_MACRO'!P$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>سال تقویمی</t>
+        </is>
+      </c>
+      <c r="D8" s="5">
+        <f>'IN_MACRO'!D$24</f>
+        <v/>
+      </c>
+      <c r="E8" s="5">
+        <f>'IN_MACRO'!E$24</f>
+        <v/>
+      </c>
+      <c r="F8" s="5">
+        <f>'IN_MACRO'!F$24</f>
+        <v/>
+      </c>
+      <c r="G8" s="5">
+        <f>'IN_MACRO'!G$24</f>
+        <v/>
+      </c>
+      <c r="H8" s="5">
+        <f>'IN_MACRO'!H$24</f>
+        <v/>
+      </c>
+      <c r="I8" s="5">
+        <f>'IN_MACRO'!I$24</f>
+        <v/>
+      </c>
+      <c r="J8" s="5">
+        <f>'IN_MACRO'!J$24</f>
+        <v/>
+      </c>
+      <c r="K8" s="5">
+        <f>'IN_MACRO'!K$24</f>
+        <v/>
+      </c>
+      <c r="L8" s="5">
+        <f>'IN_MACRO'!L$24</f>
+        <v/>
+      </c>
+      <c r="M8" s="5">
+        <f>'IN_MACRO'!M$24</f>
+        <v/>
+      </c>
+      <c r="N8" s="5">
+        <f>'IN_MACRO'!N$24</f>
+        <v/>
+      </c>
+      <c r="O8" s="5">
+        <f>'IN_MACRO'!O$24</f>
+        <v/>
+      </c>
+      <c r="P8" s="5">
+        <f>'IN_MACRO'!P$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>الف) هزینه مستقیم مراکز خدماتی</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
+      <c r="P9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>هزینه مرکز 1: نگهداری و تعمیرات مرکزی</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>ALC.cost.1</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$D$32*'IN_MACRO'!$D$34</f>
+        <v/>
+      </c>
+      <c r="E10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$E$32*'IN_MACRO'!$E$34</f>
+        <v/>
+      </c>
+      <c r="F10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$F$32*'IN_MACRO'!$F$34</f>
+        <v/>
+      </c>
+      <c r="G10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$G$32*'IN_MACRO'!$G$34</f>
+        <v/>
+      </c>
+      <c r="H10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$H$32*'IN_MACRO'!$H$34</f>
+        <v/>
+      </c>
+      <c r="I10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$I$32*'IN_MACRO'!$I$34</f>
+        <v/>
+      </c>
+      <c r="J10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$J$32*'IN_MACRO'!$J$34</f>
+        <v/>
+      </c>
+      <c r="K10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$K$32*'IN_MACRO'!$K$34</f>
+        <v/>
+      </c>
+      <c r="L10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$L$32*'IN_MACRO'!$L$34</f>
+        <v/>
+      </c>
+      <c r="M10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$M$32*'IN_MACRO'!$M$34</f>
+        <v/>
+      </c>
+      <c r="N10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$N$32*'IN_MACRO'!$N$34</f>
+        <v/>
+      </c>
+      <c r="O10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$O$32*'IN_MACRO'!$O$34</f>
+        <v/>
+      </c>
+      <c r="P10" s="14">
+        <f>'IN_COST'!$F$23*'ENG_SCEN'!$P$32*'IN_MACRO'!$P$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>هزینه مرکز 2: منابع انسانی و خدمات پشتیبانی</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>ALC.cost.2</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$D$32*'IN_MACRO'!$D$34</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$E$32*'IN_MACRO'!$E$34</f>
+        <v/>
+      </c>
+      <c r="F11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$F$32*'IN_MACRO'!$F$34</f>
+        <v/>
+      </c>
+      <c r="G11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$G$32*'IN_MACRO'!$G$34</f>
+        <v/>
+      </c>
+      <c r="H11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$H$32*'IN_MACRO'!$H$34</f>
+        <v/>
+      </c>
+      <c r="I11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$I$32*'IN_MACRO'!$I$34</f>
+        <v/>
+      </c>
+      <c r="J11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$J$32*'IN_MACRO'!$J$34</f>
+        <v/>
+      </c>
+      <c r="K11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$K$32*'IN_MACRO'!$K$34</f>
+        <v/>
+      </c>
+      <c r="L11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$L$32*'IN_MACRO'!$L$34</f>
+        <v/>
+      </c>
+      <c r="M11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$M$32*'IN_MACRO'!$M$34</f>
+        <v/>
+      </c>
+      <c r="N11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$N$32*'IN_MACRO'!$N$34</f>
+        <v/>
+      </c>
+      <c r="O11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$O$32*'IN_MACRO'!$O$34</f>
+        <v/>
+      </c>
+      <c r="P11" s="14">
+        <f>'IN_COST'!$F$24*'ENG_SCEN'!$P$32*'IN_MACRO'!$P$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>هزینه مرکز 3: لجستیک و انبارداری</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>ALC.cost.3</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$D$32*'IN_MACRO'!$D$34</f>
+        <v/>
+      </c>
+      <c r="E12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$E$32*'IN_MACRO'!$E$34</f>
+        <v/>
+      </c>
+      <c r="F12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$F$32*'IN_MACRO'!$F$34</f>
+        <v/>
+      </c>
+      <c r="G12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$G$32*'IN_MACRO'!$G$34</f>
+        <v/>
+      </c>
+      <c r="H12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$H$32*'IN_MACRO'!$H$34</f>
+        <v/>
+      </c>
+      <c r="I12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$I$32*'IN_MACRO'!$I$34</f>
+        <v/>
+      </c>
+      <c r="J12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$J$32*'IN_MACRO'!$J$34</f>
+        <v/>
+      </c>
+      <c r="K12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$K$32*'IN_MACRO'!$K$34</f>
+        <v/>
+      </c>
+      <c r="L12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$L$32*'IN_MACRO'!$L$34</f>
+        <v/>
+      </c>
+      <c r="M12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$M$32*'IN_MACRO'!$M$34</f>
+        <v/>
+      </c>
+      <c r="N12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$N$32*'IN_MACRO'!$N$34</f>
+        <v/>
+      </c>
+      <c r="O12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$O$32*'IN_MACRO'!$O$34</f>
+        <v/>
+      </c>
+      <c r="P12" s="14">
+        <f>'IN_COST'!$F$25*'ENG_SCEN'!$P$32*'IN_MACRO'!$P$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>هزینه مرکز 4: تصفیه‌خانه و محیط‌زیست</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>ALC.cost.4</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$D$32*'IN_MACRO'!$D$34</f>
+        <v/>
+      </c>
+      <c r="E13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$E$32*'IN_MACRO'!$E$34</f>
+        <v/>
+      </c>
+      <c r="F13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$F$32*'IN_MACRO'!$F$34</f>
+        <v/>
+      </c>
+      <c r="G13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$G$32*'IN_MACRO'!$G$34</f>
+        <v/>
+      </c>
+      <c r="H13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$H$32*'IN_MACRO'!$H$34</f>
+        <v/>
+      </c>
+      <c r="I13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$I$32*'IN_MACRO'!$I$34</f>
+        <v/>
+      </c>
+      <c r="J13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$J$32*'IN_MACRO'!$J$34</f>
+        <v/>
+      </c>
+      <c r="K13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$K$32*'IN_MACRO'!$K$34</f>
+        <v/>
+      </c>
+      <c r="L13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$L$32*'IN_MACRO'!$L$34</f>
+        <v/>
+      </c>
+      <c r="M13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$M$32*'IN_MACRO'!$M$34</f>
+        <v/>
+      </c>
+      <c r="N13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$N$32*'IN_MACRO'!$N$34</f>
+        <v/>
+      </c>
+      <c r="O13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$O$32*'IN_MACRO'!$O$34</f>
+        <v/>
+      </c>
+      <c r="P13" s="14">
+        <f>'IN_COST'!$F$26*'ENG_SCEN'!$P$32*'IN_MACRO'!$P$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>هزینه مرکز 5: آزمایشگاه و کنترل کیفیت</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>ALC.cost.5</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$D$32*'IN_MACRO'!$D$34</f>
+        <v/>
+      </c>
+      <c r="E14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$E$32*'IN_MACRO'!$E$34</f>
+        <v/>
+      </c>
+      <c r="F14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$F$32*'IN_MACRO'!$F$34</f>
+        <v/>
+      </c>
+      <c r="G14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$G$32*'IN_MACRO'!$G$34</f>
+        <v/>
+      </c>
+      <c r="H14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$H$32*'IN_MACRO'!$H$34</f>
+        <v/>
+      </c>
+      <c r="I14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$I$32*'IN_MACRO'!$I$34</f>
+        <v/>
+      </c>
+      <c r="J14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$J$32*'IN_MACRO'!$J$34</f>
+        <v/>
+      </c>
+      <c r="K14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$K$32*'IN_MACRO'!$K$34</f>
+        <v/>
+      </c>
+      <c r="L14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$L$32*'IN_MACRO'!$L$34</f>
+        <v/>
+      </c>
+      <c r="M14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$M$32*'IN_MACRO'!$M$34</f>
+        <v/>
+      </c>
+      <c r="N14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$N$32*'IN_MACRO'!$N$34</f>
+        <v/>
+      </c>
+      <c r="O14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$O$32*'IN_MACRO'!$O$34</f>
+        <v/>
+      </c>
+      <c r="P14" s="14">
+        <f>'IN_COST'!$F$27*'ENG_SCEN'!$P$32*'IN_MACRO'!$P$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>ب) جمع محرک و وزن تخصیص هر مرکز</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="7" t="n"/>
+      <c r="O16" s="7" t="n"/>
+      <c r="P16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>جمع محرک مرکز 1</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>ALC.dtot.1</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>─</t>
+        </is>
+      </c>
+      <c r="D17" s="14">
+        <f>SUM(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$23,'IN_TECH'!$B$47:$B$52,0),0))</f>
+        <v/>
+      </c>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="14" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>جمع محرک مرکز 2</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>ALC.dtot.2</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>─</t>
+        </is>
+      </c>
+      <c r="D18" s="14">
+        <f>SUM(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$24,'IN_TECH'!$B$47:$B$52,0),0))</f>
+        <v/>
+      </c>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="14" t="n"/>
+      <c r="P18" s="14" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>جمع محرک مرکز 3</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>ALC.dtot.3</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>─</t>
+        </is>
+      </c>
+      <c r="D19" s="14">
+        <f>SUM(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$25,'IN_TECH'!$B$47:$B$52,0),0))</f>
+        <v/>
+      </c>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
+      <c r="N19" s="14" t="n"/>
+      <c r="O19" s="14" t="n"/>
+      <c r="P19" s="14" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>جمع محرک مرکز 4</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>ALC.dtot.4</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>─</t>
+        </is>
+      </c>
+      <c r="D20" s="14">
+        <f>SUM(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$26,'IN_TECH'!$B$47:$B$52,0),0))</f>
+        <v/>
+      </c>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="14" t="n"/>
+      <c r="O20" s="14" t="n"/>
+      <c r="P20" s="14" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>جمع محرک مرکز 5</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>ALC.dtot.5</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>─</t>
+        </is>
+      </c>
+      <c r="D21" s="14">
+        <f>SUM(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$27,'IN_TECH'!$B$47:$B$52,0),0))</f>
+        <v/>
+      </c>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
+      <c r="N21" s="14" t="n"/>
+      <c r="O21" s="14" t="n"/>
+      <c r="P21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>وزن تخصیص مرکز 1 به ایستگاه‌ها</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>ALC.w.1</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D22" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$23,'IN_TECH'!$B$47:$B$52,0),1)/'ENG_ALLOC'!$D$17,0)</f>
+        <v/>
+      </c>
+      <c r="E22" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$23,'IN_TECH'!$B$47:$B$52,0),2)/'ENG_ALLOC'!$D$17,0)</f>
+        <v/>
+      </c>
+      <c r="F22" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$23,'IN_TECH'!$B$47:$B$52,0),3)/'ENG_ALLOC'!$D$17,0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$23,'IN_TECH'!$B$47:$B$52,0),4)/'ENG_ALLOC'!$D$17,0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$23,'IN_TECH'!$B$47:$B$52,0),5)/'ENG_ALLOC'!$D$17,0)</f>
+        <v/>
+      </c>
+      <c r="I22" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$23,'IN_TECH'!$B$47:$B$52,0),6)/'ENG_ALLOC'!$D$17,0)</f>
+        <v/>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="25" t="n"/>
+      <c r="M22" s="25" t="n"/>
+      <c r="N22" s="25" t="n"/>
+      <c r="O22" s="25" t="n"/>
+      <c r="P22" s="25" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>وزن تخصیص مرکز 2 به ایستگاه‌ها</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>ALC.w.2</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D23" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$24,'IN_TECH'!$B$47:$B$52,0),1)/'ENG_ALLOC'!$D$18,0)</f>
+        <v/>
+      </c>
+      <c r="E23" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$24,'IN_TECH'!$B$47:$B$52,0),2)/'ENG_ALLOC'!$D$18,0)</f>
+        <v/>
+      </c>
+      <c r="F23" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$24,'IN_TECH'!$B$47:$B$52,0),3)/'ENG_ALLOC'!$D$18,0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$24,'IN_TECH'!$B$47:$B$52,0),4)/'ENG_ALLOC'!$D$18,0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$24,'IN_TECH'!$B$47:$B$52,0),5)/'ENG_ALLOC'!$D$18,0)</f>
+        <v/>
+      </c>
+      <c r="I23" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$24,'IN_TECH'!$B$47:$B$52,0),6)/'ENG_ALLOC'!$D$18,0)</f>
+        <v/>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="25" t="n"/>
+      <c r="L23" s="25" t="n"/>
+      <c r="M23" s="25" t="n"/>
+      <c r="N23" s="25" t="n"/>
+      <c r="O23" s="25" t="n"/>
+      <c r="P23" s="25" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>وزن تخصیص مرکز 3 به ایستگاه‌ها</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>ALC.w.3</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D24" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$25,'IN_TECH'!$B$47:$B$52,0),1)/'ENG_ALLOC'!$D$19,0)</f>
+        <v/>
+      </c>
+      <c r="E24" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$25,'IN_TECH'!$B$47:$B$52,0),2)/'ENG_ALLOC'!$D$19,0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$25,'IN_TECH'!$B$47:$B$52,0),3)/'ENG_ALLOC'!$D$19,0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$25,'IN_TECH'!$B$47:$B$52,0),4)/'ENG_ALLOC'!$D$19,0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$25,'IN_TECH'!$B$47:$B$52,0),5)/'ENG_ALLOC'!$D$19,0)</f>
+        <v/>
+      </c>
+      <c r="I24" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$25,'IN_TECH'!$B$47:$B$52,0),6)/'ENG_ALLOC'!$D$19,0)</f>
+        <v/>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="25" t="n"/>
+      <c r="L24" s="25" t="n"/>
+      <c r="M24" s="25" t="n"/>
+      <c r="N24" s="25" t="n"/>
+      <c r="O24" s="25" t="n"/>
+      <c r="P24" s="25" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>وزن تخصیص مرکز 4 به ایستگاه‌ها</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>ALC.w.4</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D25" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$26,'IN_TECH'!$B$47:$B$52,0),1)/'ENG_ALLOC'!$D$20,0)</f>
+        <v/>
+      </c>
+      <c r="E25" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$26,'IN_TECH'!$B$47:$B$52,0),2)/'ENG_ALLOC'!$D$20,0)</f>
+        <v/>
+      </c>
+      <c r="F25" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$26,'IN_TECH'!$B$47:$B$52,0),3)/'ENG_ALLOC'!$D$20,0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$26,'IN_TECH'!$B$47:$B$52,0),4)/'ENG_ALLOC'!$D$20,0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$26,'IN_TECH'!$B$47:$B$52,0),5)/'ENG_ALLOC'!$D$20,0)</f>
+        <v/>
+      </c>
+      <c r="I25" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$26,'IN_TECH'!$B$47:$B$52,0),6)/'ENG_ALLOC'!$D$20,0)</f>
+        <v/>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="25" t="n"/>
+      <c r="L25" s="25" t="n"/>
+      <c r="M25" s="25" t="n"/>
+      <c r="N25" s="25" t="n"/>
+      <c r="O25" s="25" t="n"/>
+      <c r="P25" s="25" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>وزن تخصیص مرکز 5 به ایستگاه‌ها</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>ALC.w.5</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D26" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$27,'IN_TECH'!$B$47:$B$52,0),1)/'ENG_ALLOC'!$D$21,0)</f>
+        <v/>
+      </c>
+      <c r="E26" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$27,'IN_TECH'!$B$47:$B$52,0),2)/'ENG_ALLOC'!$D$21,0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$27,'IN_TECH'!$B$47:$B$52,0),3)/'ENG_ALLOC'!$D$21,0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$27,'IN_TECH'!$B$47:$B$52,0),4)/'ENG_ALLOC'!$D$21,0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$27,'IN_TECH'!$B$47:$B$52,0),5)/'ENG_ALLOC'!$D$21,0)</f>
+        <v/>
+      </c>
+      <c r="I26" s="25">
+        <f>IFERROR(INDEX('IN_TECH'!$D$47:$I$52,MATCH('IN_COST'!$E$27,'IN_TECH'!$B$47:$B$52,0),6)/'ENG_ALLOC'!$D$21,0)</f>
+        <v/>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="25" t="n"/>
+      <c r="L26" s="25" t="n"/>
+      <c r="M26" s="25" t="n"/>
+      <c r="N26" s="25" t="n"/>
+      <c r="O26" s="25" t="n"/>
+      <c r="P26" s="25" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>ج) ماتریس تخصیص (مرکز × ایستگاه × سال)</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
+      <c r="N28" s="7" t="n"/>
+      <c r="O28" s="7" t="n"/>
+      <c r="P28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>مرکز 1 ← ایستگاه 1</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D29" s="14">
+        <f>'ENG_ALLOC'!$D$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+      <c r="E29" s="14">
+        <f>'ENG_ALLOC'!$E$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+      <c r="F29" s="14">
+        <f>'ENG_ALLOC'!$F$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+      <c r="G29" s="14">
+        <f>'ENG_ALLOC'!$G$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+      <c r="H29" s="14">
+        <f>'ENG_ALLOC'!$H$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+      <c r="I29" s="14">
+        <f>'ENG_ALLOC'!$I$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+      <c r="J29" s="14">
+        <f>'ENG_ALLOC'!$J$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+      <c r="K29" s="14">
+        <f>'ENG_ALLOC'!$K$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+      <c r="L29" s="14">
+        <f>'ENG_ALLOC'!$L$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+      <c r="M29" s="14">
+        <f>'ENG_ALLOC'!$M$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+      <c r="N29" s="14">
+        <f>'ENG_ALLOC'!$N$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+      <c r="O29" s="14">
+        <f>'ENG_ALLOC'!$O$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+      <c r="P29" s="14">
+        <f>'ENG_ALLOC'!$P$10*'ENG_ALLOC'!$D$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>مرکز 1 ← ایستگاه 2</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D30" s="14">
+        <f>'ENG_ALLOC'!$D$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+      <c r="E30" s="14">
+        <f>'ENG_ALLOC'!$E$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+      <c r="F30" s="14">
+        <f>'ENG_ALLOC'!$F$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+      <c r="G30" s="14">
+        <f>'ENG_ALLOC'!$G$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+      <c r="H30" s="14">
+        <f>'ENG_ALLOC'!$H$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+      <c r="I30" s="14">
+        <f>'ENG_ALLOC'!$I$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+      <c r="J30" s="14">
+        <f>'ENG_ALLOC'!$J$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+      <c r="K30" s="14">
+        <f>'ENG_ALLOC'!$K$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+      <c r="L30" s="14">
+        <f>'ENG_ALLOC'!$L$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+      <c r="M30" s="14">
+        <f>'ENG_ALLOC'!$M$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+      <c r="N30" s="14">
+        <f>'ENG_ALLOC'!$N$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+      <c r="O30" s="14">
+        <f>'ENG_ALLOC'!$O$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+      <c r="P30" s="14">
+        <f>'ENG_ALLOC'!$P$10*'ENG_ALLOC'!$E$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>مرکز 1 ← ایستگاه 3</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D31" s="14">
+        <f>'ENG_ALLOC'!$D$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+      <c r="E31" s="14">
+        <f>'ENG_ALLOC'!$E$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+      <c r="F31" s="14">
+        <f>'ENG_ALLOC'!$F$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+      <c r="G31" s="14">
+        <f>'ENG_ALLOC'!$G$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+      <c r="H31" s="14">
+        <f>'ENG_ALLOC'!$H$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+      <c r="I31" s="14">
+        <f>'ENG_ALLOC'!$I$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+      <c r="J31" s="14">
+        <f>'ENG_ALLOC'!$J$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+      <c r="K31" s="14">
+        <f>'ENG_ALLOC'!$K$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+      <c r="L31" s="14">
+        <f>'ENG_ALLOC'!$L$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+      <c r="M31" s="14">
+        <f>'ENG_ALLOC'!$M$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+      <c r="N31" s="14">
+        <f>'ENG_ALLOC'!$N$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+      <c r="O31" s="14">
+        <f>'ENG_ALLOC'!$O$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+      <c r="P31" s="14">
+        <f>'ENG_ALLOC'!$P$10*'ENG_ALLOC'!$F$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>مرکز 1 ← ایستگاه 4</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D32" s="14">
+        <f>'ENG_ALLOC'!$D$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+      <c r="E32" s="14">
+        <f>'ENG_ALLOC'!$E$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+      <c r="F32" s="14">
+        <f>'ENG_ALLOC'!$F$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+      <c r="G32" s="14">
+        <f>'ENG_ALLOC'!$G$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+      <c r="H32" s="14">
+        <f>'ENG_ALLOC'!$H$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+      <c r="I32" s="14">
+        <f>'ENG_ALLOC'!$I$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+      <c r="J32" s="14">
+        <f>'ENG_ALLOC'!$J$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+      <c r="K32" s="14">
+        <f>'ENG_ALLOC'!$K$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+      <c r="L32" s="14">
+        <f>'ENG_ALLOC'!$L$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+      <c r="M32" s="14">
+        <f>'ENG_ALLOC'!$M$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+      <c r="N32" s="14">
+        <f>'ENG_ALLOC'!$N$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+      <c r="O32" s="14">
+        <f>'ENG_ALLOC'!$O$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+      <c r="P32" s="14">
+        <f>'ENG_ALLOC'!$P$10*'ENG_ALLOC'!$G$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>مرکز 1 ← ایستگاه 5</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D33" s="14">
+        <f>'ENG_ALLOC'!$D$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+      <c r="E33" s="14">
+        <f>'ENG_ALLOC'!$E$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+      <c r="F33" s="14">
+        <f>'ENG_ALLOC'!$F$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+      <c r="G33" s="14">
+        <f>'ENG_ALLOC'!$G$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+      <c r="H33" s="14">
+        <f>'ENG_ALLOC'!$H$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+      <c r="I33" s="14">
+        <f>'ENG_ALLOC'!$I$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+      <c r="J33" s="14">
+        <f>'ENG_ALLOC'!$J$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+      <c r="K33" s="14">
+        <f>'ENG_ALLOC'!$K$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+      <c r="L33" s="14">
+        <f>'ENG_ALLOC'!$L$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+      <c r="M33" s="14">
+        <f>'ENG_ALLOC'!$M$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+      <c r="N33" s="14">
+        <f>'ENG_ALLOC'!$N$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+      <c r="O33" s="14">
+        <f>'ENG_ALLOC'!$O$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+      <c r="P33" s="14">
+        <f>'ENG_ALLOC'!$P$10*'ENG_ALLOC'!$H$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>مرکز 1 ← ایستگاه 6</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D34" s="14">
+        <f>'ENG_ALLOC'!$D$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+      <c r="E34" s="14">
+        <f>'ENG_ALLOC'!$E$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+      <c r="F34" s="14">
+        <f>'ENG_ALLOC'!$F$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+      <c r="G34" s="14">
+        <f>'ENG_ALLOC'!$G$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+      <c r="H34" s="14">
+        <f>'ENG_ALLOC'!$H$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+      <c r="I34" s="14">
+        <f>'ENG_ALLOC'!$I$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+      <c r="J34" s="14">
+        <f>'ENG_ALLOC'!$J$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+      <c r="K34" s="14">
+        <f>'ENG_ALLOC'!$K$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+      <c r="L34" s="14">
+        <f>'ENG_ALLOC'!$L$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+      <c r="M34" s="14">
+        <f>'ENG_ALLOC'!$M$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+      <c r="N34" s="14">
+        <f>'ENG_ALLOC'!$N$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+      <c r="O34" s="14">
+        <f>'ENG_ALLOC'!$O$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+      <c r="P34" s="14">
+        <f>'ENG_ALLOC'!$P$10*'ENG_ALLOC'!$I$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>مرکز 2 ← ایستگاه 1</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D35" s="14">
+        <f>'ENG_ALLOC'!$D$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+      <c r="E35" s="14">
+        <f>'ENG_ALLOC'!$E$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+      <c r="F35" s="14">
+        <f>'ENG_ALLOC'!$F$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+      <c r="G35" s="14">
+        <f>'ENG_ALLOC'!$G$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+      <c r="H35" s="14">
+        <f>'ENG_ALLOC'!$H$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+      <c r="I35" s="14">
+        <f>'ENG_ALLOC'!$I$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+      <c r="J35" s="14">
+        <f>'ENG_ALLOC'!$J$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+      <c r="K35" s="14">
+        <f>'ENG_ALLOC'!$K$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+      <c r="L35" s="14">
+        <f>'ENG_ALLOC'!$L$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+      <c r="M35" s="14">
+        <f>'ENG_ALLOC'!$M$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+      <c r="N35" s="14">
+        <f>'ENG_ALLOC'!$N$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+      <c r="O35" s="14">
+        <f>'ENG_ALLOC'!$O$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+      <c r="P35" s="14">
+        <f>'ENG_ALLOC'!$P$11*'ENG_ALLOC'!$D$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>مرکز 2 ← ایستگاه 2</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D36" s="14">
+        <f>'ENG_ALLOC'!$D$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+      <c r="E36" s="14">
+        <f>'ENG_ALLOC'!$E$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+      <c r="F36" s="14">
+        <f>'ENG_ALLOC'!$F$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+      <c r="G36" s="14">
+        <f>'ENG_ALLOC'!$G$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+      <c r="H36" s="14">
+        <f>'ENG_ALLOC'!$H$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+      <c r="I36" s="14">
+        <f>'ENG_ALLOC'!$I$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+      <c r="J36" s="14">
+        <f>'ENG_ALLOC'!$J$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+      <c r="K36" s="14">
+        <f>'ENG_ALLOC'!$K$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+      <c r="L36" s="14">
+        <f>'ENG_ALLOC'!$L$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+      <c r="M36" s="14">
+        <f>'ENG_ALLOC'!$M$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+      <c r="N36" s="14">
+        <f>'ENG_ALLOC'!$N$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+      <c r="O36" s="14">
+        <f>'ENG_ALLOC'!$O$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+      <c r="P36" s="14">
+        <f>'ENG_ALLOC'!$P$11*'ENG_ALLOC'!$E$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>مرکز 2 ← ایستگاه 3</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D37" s="14">
+        <f>'ENG_ALLOC'!$D$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+      <c r="E37" s="14">
+        <f>'ENG_ALLOC'!$E$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+      <c r="F37" s="14">
+        <f>'ENG_ALLOC'!$F$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+      <c r="G37" s="14">
+        <f>'ENG_ALLOC'!$G$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+      <c r="H37" s="14">
+        <f>'ENG_ALLOC'!$H$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+      <c r="I37" s="14">
+        <f>'ENG_ALLOC'!$I$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+      <c r="J37" s="14">
+        <f>'ENG_ALLOC'!$J$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+      <c r="K37" s="14">
+        <f>'ENG_ALLOC'!$K$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+      <c r="L37" s="14">
+        <f>'ENG_ALLOC'!$L$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+      <c r="M37" s="14">
+        <f>'ENG_ALLOC'!$M$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+      <c r="N37" s="14">
+        <f>'ENG_ALLOC'!$N$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+      <c r="O37" s="14">
+        <f>'ENG_ALLOC'!$O$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+      <c r="P37" s="14">
+        <f>'ENG_ALLOC'!$P$11*'ENG_ALLOC'!$F$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>مرکز 2 ← ایستگاه 4</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D38" s="14">
+        <f>'ENG_ALLOC'!$D$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+      <c r="E38" s="14">
+        <f>'ENG_ALLOC'!$E$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+      <c r="F38" s="14">
+        <f>'ENG_ALLOC'!$F$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+      <c r="G38" s="14">
+        <f>'ENG_ALLOC'!$G$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+      <c r="H38" s="14">
+        <f>'ENG_ALLOC'!$H$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+      <c r="I38" s="14">
+        <f>'ENG_ALLOC'!$I$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+      <c r="J38" s="14">
+        <f>'ENG_ALLOC'!$J$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+      <c r="K38" s="14">
+        <f>'ENG_ALLOC'!$K$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+      <c r="L38" s="14">
+        <f>'ENG_ALLOC'!$L$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+      <c r="M38" s="14">
+        <f>'ENG_ALLOC'!$M$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+      <c r="N38" s="14">
+        <f>'ENG_ALLOC'!$N$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+      <c r="O38" s="14">
+        <f>'ENG_ALLOC'!$O$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+      <c r="P38" s="14">
+        <f>'ENG_ALLOC'!$P$11*'ENG_ALLOC'!$G$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>مرکز 2 ← ایستگاه 5</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D39" s="14">
+        <f>'ENG_ALLOC'!$D$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+      <c r="E39" s="14">
+        <f>'ENG_ALLOC'!$E$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+      <c r="F39" s="14">
+        <f>'ENG_ALLOC'!$F$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+      <c r="G39" s="14">
+        <f>'ENG_ALLOC'!$G$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+      <c r="H39" s="14">
+        <f>'ENG_ALLOC'!$H$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+      <c r="I39" s="14">
+        <f>'ENG_ALLOC'!$I$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+      <c r="J39" s="14">
+        <f>'ENG_ALLOC'!$J$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+      <c r="K39" s="14">
+        <f>'ENG_ALLOC'!$K$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+      <c r="L39" s="14">
+        <f>'ENG_ALLOC'!$L$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+      <c r="M39" s="14">
+        <f>'ENG_ALLOC'!$M$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+      <c r="N39" s="14">
+        <f>'ENG_ALLOC'!$N$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+      <c r="O39" s="14">
+        <f>'ENG_ALLOC'!$O$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+      <c r="P39" s="14">
+        <f>'ENG_ALLOC'!$P$11*'ENG_ALLOC'!$H$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>مرکز 2 ← ایستگاه 6</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D40" s="14">
+        <f>'ENG_ALLOC'!$D$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+      <c r="E40" s="14">
+        <f>'ENG_ALLOC'!$E$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+      <c r="F40" s="14">
+        <f>'ENG_ALLOC'!$F$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+      <c r="G40" s="14">
+        <f>'ENG_ALLOC'!$G$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+      <c r="H40" s="14">
+        <f>'ENG_ALLOC'!$H$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+      <c r="I40" s="14">
+        <f>'ENG_ALLOC'!$I$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+      <c r="J40" s="14">
+        <f>'ENG_ALLOC'!$J$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+      <c r="K40" s="14">
+        <f>'ENG_ALLOC'!$K$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+      <c r="L40" s="14">
+        <f>'ENG_ALLOC'!$L$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+      <c r="M40" s="14">
+        <f>'ENG_ALLOC'!$M$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+      <c r="N40" s="14">
+        <f>'ENG_ALLOC'!$N$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+      <c r="O40" s="14">
+        <f>'ENG_ALLOC'!$O$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+      <c r="P40" s="14">
+        <f>'ENG_ALLOC'!$P$11*'ENG_ALLOC'!$I$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>مرکز 3 ← ایستگاه 1</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D41" s="14">
+        <f>'ENG_ALLOC'!$D$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+      <c r="E41" s="14">
+        <f>'ENG_ALLOC'!$E$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+      <c r="F41" s="14">
+        <f>'ENG_ALLOC'!$F$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+      <c r="G41" s="14">
+        <f>'ENG_ALLOC'!$G$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+      <c r="H41" s="14">
+        <f>'ENG_ALLOC'!$H$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+      <c r="I41" s="14">
+        <f>'ENG_ALLOC'!$I$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+      <c r="J41" s="14">
+        <f>'ENG_ALLOC'!$J$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+      <c r="K41" s="14">
+        <f>'ENG_ALLOC'!$K$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+      <c r="L41" s="14">
+        <f>'ENG_ALLOC'!$L$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+      <c r="M41" s="14">
+        <f>'ENG_ALLOC'!$M$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+      <c r="N41" s="14">
+        <f>'ENG_ALLOC'!$N$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+      <c r="O41" s="14">
+        <f>'ENG_ALLOC'!$O$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+      <c r="P41" s="14">
+        <f>'ENG_ALLOC'!$P$12*'ENG_ALLOC'!$D$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>مرکز 3 ← ایستگاه 2</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D42" s="14">
+        <f>'ENG_ALLOC'!$D$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+      <c r="E42" s="14">
+        <f>'ENG_ALLOC'!$E$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+      <c r="F42" s="14">
+        <f>'ENG_ALLOC'!$F$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+      <c r="G42" s="14">
+        <f>'ENG_ALLOC'!$G$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+      <c r="H42" s="14">
+        <f>'ENG_ALLOC'!$H$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+      <c r="I42" s="14">
+        <f>'ENG_ALLOC'!$I$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+      <c r="J42" s="14">
+        <f>'ENG_ALLOC'!$J$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+      <c r="K42" s="14">
+        <f>'ENG_ALLOC'!$K$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+      <c r="L42" s="14">
+        <f>'ENG_ALLOC'!$L$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+      <c r="M42" s="14">
+        <f>'ENG_ALLOC'!$M$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+      <c r="N42" s="14">
+        <f>'ENG_ALLOC'!$N$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+      <c r="O42" s="14">
+        <f>'ENG_ALLOC'!$O$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+      <c r="P42" s="14">
+        <f>'ENG_ALLOC'!$P$12*'ENG_ALLOC'!$E$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>مرکز 3 ← ایستگاه 3</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D43" s="14">
+        <f>'ENG_ALLOC'!$D$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+      <c r="E43" s="14">
+        <f>'ENG_ALLOC'!$E$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+      <c r="F43" s="14">
+        <f>'ENG_ALLOC'!$F$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+      <c r="G43" s="14">
+        <f>'ENG_ALLOC'!$G$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+      <c r="H43" s="14">
+        <f>'ENG_ALLOC'!$H$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+      <c r="I43" s="14">
+        <f>'ENG_ALLOC'!$I$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+      <c r="J43" s="14">
+        <f>'ENG_ALLOC'!$J$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+      <c r="K43" s="14">
+        <f>'ENG_ALLOC'!$K$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+      <c r="L43" s="14">
+        <f>'ENG_ALLOC'!$L$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+      <c r="M43" s="14">
+        <f>'ENG_ALLOC'!$M$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+      <c r="N43" s="14">
+        <f>'ENG_ALLOC'!$N$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+      <c r="O43" s="14">
+        <f>'ENG_ALLOC'!$O$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+      <c r="P43" s="14">
+        <f>'ENG_ALLOC'!$P$12*'ENG_ALLOC'!$F$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>مرکز 3 ← ایستگاه 4</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D44" s="14">
+        <f>'ENG_ALLOC'!$D$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+      <c r="E44" s="14">
+        <f>'ENG_ALLOC'!$E$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+      <c r="F44" s="14">
+        <f>'ENG_ALLOC'!$F$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+      <c r="G44" s="14">
+        <f>'ENG_ALLOC'!$G$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+      <c r="H44" s="14">
+        <f>'ENG_ALLOC'!$H$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+      <c r="I44" s="14">
+        <f>'ENG_ALLOC'!$I$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+      <c r="J44" s="14">
+        <f>'ENG_ALLOC'!$J$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+      <c r="K44" s="14">
+        <f>'ENG_ALLOC'!$K$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+      <c r="L44" s="14">
+        <f>'ENG_ALLOC'!$L$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+      <c r="M44" s="14">
+        <f>'ENG_ALLOC'!$M$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+      <c r="N44" s="14">
+        <f>'ENG_ALLOC'!$N$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+      <c r="O44" s="14">
+        <f>'ENG_ALLOC'!$O$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+      <c r="P44" s="14">
+        <f>'ENG_ALLOC'!$P$12*'ENG_ALLOC'!$G$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>مرکز 3 ← ایستگاه 5</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D45" s="14">
+        <f>'ENG_ALLOC'!$D$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+      <c r="E45" s="14">
+        <f>'ENG_ALLOC'!$E$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+      <c r="F45" s="14">
+        <f>'ENG_ALLOC'!$F$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+      <c r="G45" s="14">
+        <f>'ENG_ALLOC'!$G$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+      <c r="H45" s="14">
+        <f>'ENG_ALLOC'!$H$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+      <c r="I45" s="14">
+        <f>'ENG_ALLOC'!$I$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+      <c r="J45" s="14">
+        <f>'ENG_ALLOC'!$J$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+      <c r="K45" s="14">
+        <f>'ENG_ALLOC'!$K$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+      <c r="L45" s="14">
+        <f>'ENG_ALLOC'!$L$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+      <c r="M45" s="14">
+        <f>'ENG_ALLOC'!$M$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+      <c r="N45" s="14">
+        <f>'ENG_ALLOC'!$N$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+      <c r="O45" s="14">
+        <f>'ENG_ALLOC'!$O$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+      <c r="P45" s="14">
+        <f>'ENG_ALLOC'!$P$12*'ENG_ALLOC'!$H$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>مرکز 3 ← ایستگاه 6</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D46" s="14">
+        <f>'ENG_ALLOC'!$D$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+      <c r="E46" s="14">
+        <f>'ENG_ALLOC'!$E$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+      <c r="F46" s="14">
+        <f>'ENG_ALLOC'!$F$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+      <c r="G46" s="14">
+        <f>'ENG_ALLOC'!$G$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+      <c r="H46" s="14">
+        <f>'ENG_ALLOC'!$H$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+      <c r="I46" s="14">
+        <f>'ENG_ALLOC'!$I$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+      <c r="J46" s="14">
+        <f>'ENG_ALLOC'!$J$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+      <c r="K46" s="14">
+        <f>'ENG_ALLOC'!$K$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+      <c r="L46" s="14">
+        <f>'ENG_ALLOC'!$L$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+      <c r="M46" s="14">
+        <f>'ENG_ALLOC'!$M$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+      <c r="N46" s="14">
+        <f>'ENG_ALLOC'!$N$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+      <c r="O46" s="14">
+        <f>'ENG_ALLOC'!$O$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+      <c r="P46" s="14">
+        <f>'ENG_ALLOC'!$P$12*'ENG_ALLOC'!$I$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>مرکز 4 ← ایستگاه 1</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D47" s="14">
+        <f>'ENG_ALLOC'!$D$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+      <c r="E47" s="14">
+        <f>'ENG_ALLOC'!$E$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+      <c r="F47" s="14">
+        <f>'ENG_ALLOC'!$F$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+      <c r="G47" s="14">
+        <f>'ENG_ALLOC'!$G$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+      <c r="H47" s="14">
+        <f>'ENG_ALLOC'!$H$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+      <c r="I47" s="14">
+        <f>'ENG_ALLOC'!$I$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+      <c r="J47" s="14">
+        <f>'ENG_ALLOC'!$J$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+      <c r="K47" s="14">
+        <f>'ENG_ALLOC'!$K$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+      <c r="L47" s="14">
+        <f>'ENG_ALLOC'!$L$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+      <c r="M47" s="14">
+        <f>'ENG_ALLOC'!$M$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+      <c r="N47" s="14">
+        <f>'ENG_ALLOC'!$N$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+      <c r="O47" s="14">
+        <f>'ENG_ALLOC'!$O$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+      <c r="P47" s="14">
+        <f>'ENG_ALLOC'!$P$13*'ENG_ALLOC'!$D$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>مرکز 4 ← ایستگاه 2</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D48" s="14">
+        <f>'ENG_ALLOC'!$D$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+      <c r="E48" s="14">
+        <f>'ENG_ALLOC'!$E$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+      <c r="F48" s="14">
+        <f>'ENG_ALLOC'!$F$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+      <c r="G48" s="14">
+        <f>'ENG_ALLOC'!$G$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+      <c r="H48" s="14">
+        <f>'ENG_ALLOC'!$H$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+      <c r="I48" s="14">
+        <f>'ENG_ALLOC'!$I$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+      <c r="J48" s="14">
+        <f>'ENG_ALLOC'!$J$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+      <c r="K48" s="14">
+        <f>'ENG_ALLOC'!$K$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+      <c r="L48" s="14">
+        <f>'ENG_ALLOC'!$L$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+      <c r="M48" s="14">
+        <f>'ENG_ALLOC'!$M$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+      <c r="N48" s="14">
+        <f>'ENG_ALLOC'!$N$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+      <c r="O48" s="14">
+        <f>'ENG_ALLOC'!$O$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+      <c r="P48" s="14">
+        <f>'ENG_ALLOC'!$P$13*'ENG_ALLOC'!$E$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>مرکز 4 ← ایستگاه 3</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D49" s="14">
+        <f>'ENG_ALLOC'!$D$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+      <c r="E49" s="14">
+        <f>'ENG_ALLOC'!$E$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+      <c r="F49" s="14">
+        <f>'ENG_ALLOC'!$F$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+      <c r="G49" s="14">
+        <f>'ENG_ALLOC'!$G$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+      <c r="H49" s="14">
+        <f>'ENG_ALLOC'!$H$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+      <c r="I49" s="14">
+        <f>'ENG_ALLOC'!$I$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+      <c r="J49" s="14">
+        <f>'ENG_ALLOC'!$J$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+      <c r="K49" s="14">
+        <f>'ENG_ALLOC'!$K$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+      <c r="L49" s="14">
+        <f>'ENG_ALLOC'!$L$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+      <c r="M49" s="14">
+        <f>'ENG_ALLOC'!$M$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+      <c r="N49" s="14">
+        <f>'ENG_ALLOC'!$N$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+      <c r="O49" s="14">
+        <f>'ENG_ALLOC'!$O$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+      <c r="P49" s="14">
+        <f>'ENG_ALLOC'!$P$13*'ENG_ALLOC'!$F$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>مرکز 4 ← ایستگاه 4</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D50" s="14">
+        <f>'ENG_ALLOC'!$D$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+      <c r="E50" s="14">
+        <f>'ENG_ALLOC'!$E$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+      <c r="F50" s="14">
+        <f>'ENG_ALLOC'!$F$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+      <c r="G50" s="14">
+        <f>'ENG_ALLOC'!$G$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+      <c r="H50" s="14">
+        <f>'ENG_ALLOC'!$H$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+      <c r="I50" s="14">
+        <f>'ENG_ALLOC'!$I$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+      <c r="J50" s="14">
+        <f>'ENG_ALLOC'!$J$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+      <c r="K50" s="14">
+        <f>'ENG_ALLOC'!$K$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+      <c r="L50" s="14">
+        <f>'ENG_ALLOC'!$L$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+      <c r="M50" s="14">
+        <f>'ENG_ALLOC'!$M$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+      <c r="N50" s="14">
+        <f>'ENG_ALLOC'!$N$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+      <c r="O50" s="14">
+        <f>'ENG_ALLOC'!$O$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+      <c r="P50" s="14">
+        <f>'ENG_ALLOC'!$P$13*'ENG_ALLOC'!$G$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>مرکز 4 ← ایستگاه 5</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D51" s="14">
+        <f>'ENG_ALLOC'!$D$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+      <c r="E51" s="14">
+        <f>'ENG_ALLOC'!$E$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+      <c r="F51" s="14">
+        <f>'ENG_ALLOC'!$F$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+      <c r="G51" s="14">
+        <f>'ENG_ALLOC'!$G$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+      <c r="H51" s="14">
+        <f>'ENG_ALLOC'!$H$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+      <c r="I51" s="14">
+        <f>'ENG_ALLOC'!$I$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+      <c r="J51" s="14">
+        <f>'ENG_ALLOC'!$J$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+      <c r="K51" s="14">
+        <f>'ENG_ALLOC'!$K$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+      <c r="L51" s="14">
+        <f>'ENG_ALLOC'!$L$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+      <c r="M51" s="14">
+        <f>'ENG_ALLOC'!$M$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+      <c r="N51" s="14">
+        <f>'ENG_ALLOC'!$N$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+      <c r="O51" s="14">
+        <f>'ENG_ALLOC'!$O$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+      <c r="P51" s="14">
+        <f>'ENG_ALLOC'!$P$13*'ENG_ALLOC'!$H$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>مرکز 4 ← ایستگاه 6</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D52" s="14">
+        <f>'ENG_ALLOC'!$D$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+      <c r="E52" s="14">
+        <f>'ENG_ALLOC'!$E$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+      <c r="F52" s="14">
+        <f>'ENG_ALLOC'!$F$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+      <c r="G52" s="14">
+        <f>'ENG_ALLOC'!$G$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+      <c r="H52" s="14">
+        <f>'ENG_ALLOC'!$H$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+      <c r="I52" s="14">
+        <f>'ENG_ALLOC'!$I$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+      <c r="J52" s="14">
+        <f>'ENG_ALLOC'!$J$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+      <c r="K52" s="14">
+        <f>'ENG_ALLOC'!$K$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+      <c r="L52" s="14">
+        <f>'ENG_ALLOC'!$L$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+      <c r="M52" s="14">
+        <f>'ENG_ALLOC'!$M$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+      <c r="N52" s="14">
+        <f>'ENG_ALLOC'!$N$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+      <c r="O52" s="14">
+        <f>'ENG_ALLOC'!$O$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+      <c r="P52" s="14">
+        <f>'ENG_ALLOC'!$P$13*'ENG_ALLOC'!$I$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>مرکز 5 ← ایستگاه 1</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D53" s="14">
+        <f>'ENG_ALLOC'!$D$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="E53" s="14">
+        <f>'ENG_ALLOC'!$E$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="F53" s="14">
+        <f>'ENG_ALLOC'!$F$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="G53" s="14">
+        <f>'ENG_ALLOC'!$G$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="H53" s="14">
+        <f>'ENG_ALLOC'!$H$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="I53" s="14">
+        <f>'ENG_ALLOC'!$I$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="J53" s="14">
+        <f>'ENG_ALLOC'!$J$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="K53" s="14">
+        <f>'ENG_ALLOC'!$K$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="L53" s="14">
+        <f>'ENG_ALLOC'!$L$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="M53" s="14">
+        <f>'ENG_ALLOC'!$M$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="N53" s="14">
+        <f>'ENG_ALLOC'!$N$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="O53" s="14">
+        <f>'ENG_ALLOC'!$O$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="P53" s="14">
+        <f>'ENG_ALLOC'!$P$14*'ENG_ALLOC'!$D$26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>مرکز 5 ← ایستگاه 2</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D54" s="14">
+        <f>'ENG_ALLOC'!$D$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="E54" s="14">
+        <f>'ENG_ALLOC'!$E$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="F54" s="14">
+        <f>'ENG_ALLOC'!$F$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="G54" s="14">
+        <f>'ENG_ALLOC'!$G$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="H54" s="14">
+        <f>'ENG_ALLOC'!$H$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="I54" s="14">
+        <f>'ENG_ALLOC'!$I$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="J54" s="14">
+        <f>'ENG_ALLOC'!$J$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="K54" s="14">
+        <f>'ENG_ALLOC'!$K$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="L54" s="14">
+        <f>'ENG_ALLOC'!$L$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="M54" s="14">
+        <f>'ENG_ALLOC'!$M$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="N54" s="14">
+        <f>'ENG_ALLOC'!$N$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="O54" s="14">
+        <f>'ENG_ALLOC'!$O$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="P54" s="14">
+        <f>'ENG_ALLOC'!$P$14*'ENG_ALLOC'!$E$26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>مرکز 5 ← ایستگاه 3</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D55" s="14">
+        <f>'ENG_ALLOC'!$D$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="E55" s="14">
+        <f>'ENG_ALLOC'!$E$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="F55" s="14">
+        <f>'ENG_ALLOC'!$F$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="G55" s="14">
+        <f>'ENG_ALLOC'!$G$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="H55" s="14">
+        <f>'ENG_ALLOC'!$H$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="I55" s="14">
+        <f>'ENG_ALLOC'!$I$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="J55" s="14">
+        <f>'ENG_ALLOC'!$J$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="K55" s="14">
+        <f>'ENG_ALLOC'!$K$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="L55" s="14">
+        <f>'ENG_ALLOC'!$L$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="M55" s="14">
+        <f>'ENG_ALLOC'!$M$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="N55" s="14">
+        <f>'ENG_ALLOC'!$N$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="O55" s="14">
+        <f>'ENG_ALLOC'!$O$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="P55" s="14">
+        <f>'ENG_ALLOC'!$P$14*'ENG_ALLOC'!$F$26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>مرکز 5 ← ایستگاه 4</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D56" s="14">
+        <f>'ENG_ALLOC'!$D$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="E56" s="14">
+        <f>'ENG_ALLOC'!$E$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="F56" s="14">
+        <f>'ENG_ALLOC'!$F$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="G56" s="14">
+        <f>'ENG_ALLOC'!$G$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="H56" s="14">
+        <f>'ENG_ALLOC'!$H$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="I56" s="14">
+        <f>'ENG_ALLOC'!$I$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="J56" s="14">
+        <f>'ENG_ALLOC'!$J$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="K56" s="14">
+        <f>'ENG_ALLOC'!$K$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="L56" s="14">
+        <f>'ENG_ALLOC'!$L$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="M56" s="14">
+        <f>'ENG_ALLOC'!$M$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="N56" s="14">
+        <f>'ENG_ALLOC'!$N$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="O56" s="14">
+        <f>'ENG_ALLOC'!$O$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="P56" s="14">
+        <f>'ENG_ALLOC'!$P$14*'ENG_ALLOC'!$G$26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>مرکز 5 ← ایستگاه 5</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D57" s="14">
+        <f>'ENG_ALLOC'!$D$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="E57" s="14">
+        <f>'ENG_ALLOC'!$E$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="F57" s="14">
+        <f>'ENG_ALLOC'!$F$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="G57" s="14">
+        <f>'ENG_ALLOC'!$G$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="H57" s="14">
+        <f>'ENG_ALLOC'!$H$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="I57" s="14">
+        <f>'ENG_ALLOC'!$I$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="J57" s="14">
+        <f>'ENG_ALLOC'!$J$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="K57" s="14">
+        <f>'ENG_ALLOC'!$K$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="L57" s="14">
+        <f>'ENG_ALLOC'!$L$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="M57" s="14">
+        <f>'ENG_ALLOC'!$M$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="N57" s="14">
+        <f>'ENG_ALLOC'!$N$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="O57" s="14">
+        <f>'ENG_ALLOC'!$O$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="P57" s="14">
+        <f>'ENG_ALLOC'!$P$14*'ENG_ALLOC'!$H$26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>مرکز 5 ← ایستگاه 6</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D58" s="14">
+        <f>'ENG_ALLOC'!$D$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="E58" s="14">
+        <f>'ENG_ALLOC'!$E$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="F58" s="14">
+        <f>'ENG_ALLOC'!$F$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="G58" s="14">
+        <f>'ENG_ALLOC'!$G$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="H58" s="14">
+        <f>'ENG_ALLOC'!$H$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="I58" s="14">
+        <f>'ENG_ALLOC'!$I$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="J58" s="14">
+        <f>'ENG_ALLOC'!$J$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="K58" s="14">
+        <f>'ENG_ALLOC'!$K$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="L58" s="14">
+        <f>'ENG_ALLOC'!$L$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="M58" s="14">
+        <f>'ENG_ALLOC'!$M$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="N58" s="14">
+        <f>'ENG_ALLOC'!$N$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="O58" s="14">
+        <f>'ENG_ALLOC'!$O$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="P58" s="14">
+        <f>'ENG_ALLOC'!$P$14*'ENG_ALLOC'!$I$26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>د) جمع تخصیص‌یافته به هر ایستگاه</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
+      <c r="J60" s="7" t="n"/>
+      <c r="K60" s="7" t="n"/>
+      <c r="L60" s="7" t="n"/>
+      <c r="M60" s="7" t="n"/>
+      <c r="N60" s="7" t="n"/>
+      <c r="O60" s="7" t="n"/>
+      <c r="P60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>سهم ایستگاه 1 از مراکز خدماتی</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>ALC.station.0</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D61" s="14">
+        <f>D29+D35+D41+D47+D53</f>
+        <v/>
+      </c>
+      <c r="E61" s="14">
+        <f>E29+E35+E41+E47+E53</f>
+        <v/>
+      </c>
+      <c r="F61" s="14">
+        <f>F29+F35+F41+F47+F53</f>
+        <v/>
+      </c>
+      <c r="G61" s="14">
+        <f>G29+G35+G41+G47+G53</f>
+        <v/>
+      </c>
+      <c r="H61" s="14">
+        <f>H29+H35+H41+H47+H53</f>
+        <v/>
+      </c>
+      <c r="I61" s="14">
+        <f>I29+I35+I41+I47+I53</f>
+        <v/>
+      </c>
+      <c r="J61" s="14">
+        <f>J29+J35+J41+J47+J53</f>
+        <v/>
+      </c>
+      <c r="K61" s="14">
+        <f>K29+K35+K41+K47+K53</f>
+        <v/>
+      </c>
+      <c r="L61" s="14">
+        <f>L29+L35+L41+L47+L53</f>
+        <v/>
+      </c>
+      <c r="M61" s="14">
+        <f>M29+M35+M41+M47+M53</f>
+        <v/>
+      </c>
+      <c r="N61" s="14">
+        <f>N29+N35+N41+N47+N53</f>
+        <v/>
+      </c>
+      <c r="O61" s="14">
+        <f>O29+O35+O41+O47+O53</f>
+        <v/>
+      </c>
+      <c r="P61" s="14">
+        <f>P29+P35+P41+P47+P53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>سهم ایستگاه 2 از مراکز خدماتی</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>ALC.station.1</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D62" s="14">
+        <f>D30+D36+D42+D48+D54</f>
+        <v/>
+      </c>
+      <c r="E62" s="14">
+        <f>E30+E36+E42+E48+E54</f>
+        <v/>
+      </c>
+      <c r="F62" s="14">
+        <f>F30+F36+F42+F48+F54</f>
+        <v/>
+      </c>
+      <c r="G62" s="14">
+        <f>G30+G36+G42+G48+G54</f>
+        <v/>
+      </c>
+      <c r="H62" s="14">
+        <f>H30+H36+H42+H48+H54</f>
+        <v/>
+      </c>
+      <c r="I62" s="14">
+        <f>I30+I36+I42+I48+I54</f>
+        <v/>
+      </c>
+      <c r="J62" s="14">
+        <f>J30+J36+J42+J48+J54</f>
+        <v/>
+      </c>
+      <c r="K62" s="14">
+        <f>K30+K36+K42+K48+K54</f>
+        <v/>
+      </c>
+      <c r="L62" s="14">
+        <f>L30+L36+L42+L48+L54</f>
+        <v/>
+      </c>
+      <c r="M62" s="14">
+        <f>M30+M36+M42+M48+M54</f>
+        <v/>
+      </c>
+      <c r="N62" s="14">
+        <f>N30+N36+N42+N48+N54</f>
+        <v/>
+      </c>
+      <c r="O62" s="14">
+        <f>O30+O36+O42+O48+O54</f>
+        <v/>
+      </c>
+      <c r="P62" s="14">
+        <f>P30+P36+P42+P48+P54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>سهم ایستگاه 3 از مراکز خدماتی</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>ALC.station.2</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D63" s="14">
+        <f>D31+D37+D43+D49+D55</f>
+        <v/>
+      </c>
+      <c r="E63" s="14">
+        <f>E31+E37+E43+E49+E55</f>
+        <v/>
+      </c>
+      <c r="F63" s="14">
+        <f>F31+F37+F43+F49+F55</f>
+        <v/>
+      </c>
+      <c r="G63" s="14">
+        <f>G31+G37+G43+G49+G55</f>
+        <v/>
+      </c>
+      <c r="H63" s="14">
+        <f>H31+H37+H43+H49+H55</f>
+        <v/>
+      </c>
+      <c r="I63" s="14">
+        <f>I31+I37+I43+I49+I55</f>
+        <v/>
+      </c>
+      <c r="J63" s="14">
+        <f>J31+J37+J43+J49+J55</f>
+        <v/>
+      </c>
+      <c r="K63" s="14">
+        <f>K31+K37+K43+K49+K55</f>
+        <v/>
+      </c>
+      <c r="L63" s="14">
+        <f>L31+L37+L43+L49+L55</f>
+        <v/>
+      </c>
+      <c r="M63" s="14">
+        <f>M31+M37+M43+M49+M55</f>
+        <v/>
+      </c>
+      <c r="N63" s="14">
+        <f>N31+N37+N43+N49+N55</f>
+        <v/>
+      </c>
+      <c r="O63" s="14">
+        <f>O31+O37+O43+O49+O55</f>
+        <v/>
+      </c>
+      <c r="P63" s="14">
+        <f>P31+P37+P43+P49+P55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>سهم ایستگاه 4 از مراکز خدماتی</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>ALC.station.3</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D64" s="14">
+        <f>D32+D38+D44+D50+D56</f>
+        <v/>
+      </c>
+      <c r="E64" s="14">
+        <f>E32+E38+E44+E50+E56</f>
+        <v/>
+      </c>
+      <c r="F64" s="14">
+        <f>F32+F38+F44+F50+F56</f>
+        <v/>
+      </c>
+      <c r="G64" s="14">
+        <f>G32+G38+G44+G50+G56</f>
+        <v/>
+      </c>
+      <c r="H64" s="14">
+        <f>H32+H38+H44+H50+H56</f>
+        <v/>
+      </c>
+      <c r="I64" s="14">
+        <f>I32+I38+I44+I50+I56</f>
+        <v/>
+      </c>
+      <c r="J64" s="14">
+        <f>J32+J38+J44+J50+J56</f>
+        <v/>
+      </c>
+      <c r="K64" s="14">
+        <f>K32+K38+K44+K50+K56</f>
+        <v/>
+      </c>
+      <c r="L64" s="14">
+        <f>L32+L38+L44+L50+L56</f>
+        <v/>
+      </c>
+      <c r="M64" s="14">
+        <f>M32+M38+M44+M50+M56</f>
+        <v/>
+      </c>
+      <c r="N64" s="14">
+        <f>N32+N38+N44+N50+N56</f>
+        <v/>
+      </c>
+      <c r="O64" s="14">
+        <f>O32+O38+O44+O50+O56</f>
+        <v/>
+      </c>
+      <c r="P64" s="14">
+        <f>P32+P38+P44+P50+P56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>سهم ایستگاه 5 از مراکز خدماتی</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>ALC.station.4</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D65" s="14">
+        <f>D33+D39+D45+D51+D57</f>
+        <v/>
+      </c>
+      <c r="E65" s="14">
+        <f>E33+E39+E45+E51+E57</f>
+        <v/>
+      </c>
+      <c r="F65" s="14">
+        <f>F33+F39+F45+F51+F57</f>
+        <v/>
+      </c>
+      <c r="G65" s="14">
+        <f>G33+G39+G45+G51+G57</f>
+        <v/>
+      </c>
+      <c r="H65" s="14">
+        <f>H33+H39+H45+H51+H57</f>
+        <v/>
+      </c>
+      <c r="I65" s="14">
+        <f>I33+I39+I45+I51+I57</f>
+        <v/>
+      </c>
+      <c r="J65" s="14">
+        <f>J33+J39+J45+J51+J57</f>
+        <v/>
+      </c>
+      <c r="K65" s="14">
+        <f>K33+K39+K45+K51+K57</f>
+        <v/>
+      </c>
+      <c r="L65" s="14">
+        <f>L33+L39+L45+L51+L57</f>
+        <v/>
+      </c>
+      <c r="M65" s="14">
+        <f>M33+M39+M45+M51+M57</f>
+        <v/>
+      </c>
+      <c r="N65" s="14">
+        <f>N33+N39+N45+N51+N57</f>
+        <v/>
+      </c>
+      <c r="O65" s="14">
+        <f>O33+O39+O45+O51+O57</f>
+        <v/>
+      </c>
+      <c r="P65" s="14">
+        <f>P33+P39+P45+P51+P57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>سهم ایستگاه 6 از مراکز خدماتی</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>ALC.station.5</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D66" s="14">
+        <f>D34+D40+D46+D52+D58</f>
+        <v/>
+      </c>
+      <c r="E66" s="14">
+        <f>E34+E40+E46+E52+E58</f>
+        <v/>
+      </c>
+      <c r="F66" s="14">
+        <f>F34+F40+F46+F52+F58</f>
+        <v/>
+      </c>
+      <c r="G66" s="14">
+        <f>G34+G40+G46+G52+G58</f>
+        <v/>
+      </c>
+      <c r="H66" s="14">
+        <f>H34+H40+H46+H52+H58</f>
+        <v/>
+      </c>
+      <c r="I66" s="14">
+        <f>I34+I40+I46+I52+I58</f>
+        <v/>
+      </c>
+      <c r="J66" s="14">
+        <f>J34+J40+J46+J52+J58</f>
+        <v/>
+      </c>
+      <c r="K66" s="14">
+        <f>K34+K40+K46+K52+K58</f>
+        <v/>
+      </c>
+      <c r="L66" s="14">
+        <f>L34+L40+L46+L52+L58</f>
+        <v/>
+      </c>
+      <c r="M66" s="14">
+        <f>M34+M40+M46+M52+M58</f>
+        <v/>
+      </c>
+      <c r="N66" s="14">
+        <f>N34+N40+N46+N52+N58</f>
+        <v/>
+      </c>
+      <c r="O66" s="14">
+        <f>O34+O40+O46+O52+O58</f>
+        <v/>
+      </c>
+      <c r="P66" s="14">
+        <f>P34+P40+P46+P52+P58</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/models/lead_acid_recycling/build/out/built.xlsx
+++ b/models/lead_acid_recycling/build/out/built.xlsx
@@ -18,6 +18,7 @@
     <sheet name="ENG_OPS" sheetId="9" state="hidden" r:id="rId9"/>
     <sheet name="ENG_CAPEX" sheetId="10" state="hidden" r:id="rId10"/>
     <sheet name="ENG_ALLOC" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet name="ENG_WC" sheetId="12" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10101,6 +10102,1467 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>سرمایه در گردش و چرخه تبدیل نقد</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>موتور محاسبات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>مانده موجودی‌ها، دریافتنی‌ها و پرداختنی‌ها و استنتاج چرخه تبدیل نقد (CCC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>دوره (t)</t>
+        </is>
+      </c>
+      <c r="D7" s="5">
+        <f>'IN_MACRO'!D$23</f>
+        <v/>
+      </c>
+      <c r="E7" s="5">
+        <f>'IN_MACRO'!E$23</f>
+        <v/>
+      </c>
+      <c r="F7" s="5">
+        <f>'IN_MACRO'!F$23</f>
+        <v/>
+      </c>
+      <c r="G7" s="5">
+        <f>'IN_MACRO'!G$23</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
+        <f>'IN_MACRO'!H$23</f>
+        <v/>
+      </c>
+      <c r="I7" s="5">
+        <f>'IN_MACRO'!I$23</f>
+        <v/>
+      </c>
+      <c r="J7" s="5">
+        <f>'IN_MACRO'!J$23</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
+        <f>'IN_MACRO'!K$23</f>
+        <v/>
+      </c>
+      <c r="L7" s="5">
+        <f>'IN_MACRO'!L$23</f>
+        <v/>
+      </c>
+      <c r="M7" s="5">
+        <f>'IN_MACRO'!M$23</f>
+        <v/>
+      </c>
+      <c r="N7" s="5">
+        <f>'IN_MACRO'!N$23</f>
+        <v/>
+      </c>
+      <c r="O7" s="5">
+        <f>'IN_MACRO'!O$23</f>
+        <v/>
+      </c>
+      <c r="P7" s="5">
+        <f>'IN_MACRO'!P$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>سال تقویمی</t>
+        </is>
+      </c>
+      <c r="D8" s="5">
+        <f>'IN_MACRO'!D$24</f>
+        <v/>
+      </c>
+      <c r="E8" s="5">
+        <f>'IN_MACRO'!E$24</f>
+        <v/>
+      </c>
+      <c r="F8" s="5">
+        <f>'IN_MACRO'!F$24</f>
+        <v/>
+      </c>
+      <c r="G8" s="5">
+        <f>'IN_MACRO'!G$24</f>
+        <v/>
+      </c>
+      <c r="H8" s="5">
+        <f>'IN_MACRO'!H$24</f>
+        <v/>
+      </c>
+      <c r="I8" s="5">
+        <f>'IN_MACRO'!I$24</f>
+        <v/>
+      </c>
+      <c r="J8" s="5">
+        <f>'IN_MACRO'!J$24</f>
+        <v/>
+      </c>
+      <c r="K8" s="5">
+        <f>'IN_MACRO'!K$24</f>
+        <v/>
+      </c>
+      <c r="L8" s="5">
+        <f>'IN_MACRO'!L$24</f>
+        <v/>
+      </c>
+      <c r="M8" s="5">
+        <f>'IN_MACRO'!M$24</f>
+        <v/>
+      </c>
+      <c r="N8" s="5">
+        <f>'IN_MACRO'!N$24</f>
+        <v/>
+      </c>
+      <c r="O8" s="5">
+        <f>'IN_MACRO'!O$24</f>
+        <v/>
+      </c>
+      <c r="P8" s="5">
+        <f>'IN_MACRO'!P$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>الف) اجزای سرمایه در گردش</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
+      <c r="P9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>موجودی مواد اولیه</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>WC.inv_rm</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D10" s="14">
+        <f>@@ENG_COST|EC.rm|0@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+      <c r="E10" s="14">
+        <f>@@ENG_COST|EC.rm|1@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+      <c r="F10" s="14">
+        <f>@@ENG_COST|EC.rm|2@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+      <c r="G10" s="14">
+        <f>@@ENG_COST|EC.rm|3@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+      <c r="H10" s="14">
+        <f>@@ENG_COST|EC.rm|4@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+      <c r="I10" s="14">
+        <f>@@ENG_COST|EC.rm|5@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+      <c r="J10" s="14">
+        <f>@@ENG_COST|EC.rm|6@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+      <c r="K10" s="14">
+        <f>@@ENG_COST|EC.rm|7@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+      <c r="L10" s="14">
+        <f>@@ENG_COST|EC.rm|8@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+      <c r="M10" s="14">
+        <f>@@ENG_COST|EC.rm|9@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+      <c r="N10" s="14">
+        <f>@@ENG_COST|EC.rm|10@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+      <c r="O10" s="14">
+        <f>@@ENG_COST|EC.rm|11@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+      <c r="P10" s="14">
+        <f>@@ENG_COST|EC.rm|12@@/365*'IN_WC'!$D$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>موجودی کالای در جریان ساخت</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>WC.inv_wip</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D11" s="14">
+        <f>(@@ENG_COST|EC.dpc|0@@+@@ENG_COST|EC.opc|0@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>(@@ENG_COST|EC.dpc|1@@+@@ENG_COST|EC.opc|1@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+      <c r="F11" s="14">
+        <f>(@@ENG_COST|EC.dpc|2@@+@@ENG_COST|EC.opc|2@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+      <c r="G11" s="14">
+        <f>(@@ENG_COST|EC.dpc|3@@+@@ENG_COST|EC.opc|3@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+      <c r="H11" s="14">
+        <f>(@@ENG_COST|EC.dpc|4@@+@@ENG_COST|EC.opc|4@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+      <c r="I11" s="14">
+        <f>(@@ENG_COST|EC.dpc|5@@+@@ENG_COST|EC.opc|5@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+      <c r="J11" s="14">
+        <f>(@@ENG_COST|EC.dpc|6@@+@@ENG_COST|EC.opc|6@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+      <c r="K11" s="14">
+        <f>(@@ENG_COST|EC.dpc|7@@+@@ENG_COST|EC.opc|7@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+      <c r="L11" s="14">
+        <f>(@@ENG_COST|EC.dpc|8@@+@@ENG_COST|EC.opc|8@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+      <c r="M11" s="14">
+        <f>(@@ENG_COST|EC.dpc|9@@+@@ENG_COST|EC.opc|9@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+      <c r="N11" s="14">
+        <f>(@@ENG_COST|EC.dpc|10@@+@@ENG_COST|EC.opc|10@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+      <c r="O11" s="14">
+        <f>(@@ENG_COST|EC.dpc|11@@+@@ENG_COST|EC.opc|11@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+      <c r="P11" s="14">
+        <f>(@@ENG_COST|EC.dpc|12@@+@@ENG_COST|EC.opc|12@@)/365*'IN_WC'!$D$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>موجودی محصول نهایی</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>WC.inv_fg</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D12" s="14">
+        <f>(@@ENG_COST|EC.dpc|0@@+@@ENG_COST|EC.opc|0@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+      <c r="E12" s="14">
+        <f>(@@ENG_COST|EC.dpc|1@@+@@ENG_COST|EC.opc|1@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+      <c r="F12" s="14">
+        <f>(@@ENG_COST|EC.dpc|2@@+@@ENG_COST|EC.opc|2@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+      <c r="G12" s="14">
+        <f>(@@ENG_COST|EC.dpc|3@@+@@ENG_COST|EC.opc|3@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+      <c r="H12" s="14">
+        <f>(@@ENG_COST|EC.dpc|4@@+@@ENG_COST|EC.opc|4@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+      <c r="I12" s="14">
+        <f>(@@ENG_COST|EC.dpc|5@@+@@ENG_COST|EC.opc|5@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+      <c r="J12" s="14">
+        <f>(@@ENG_COST|EC.dpc|6@@+@@ENG_COST|EC.opc|6@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+      <c r="K12" s="14">
+        <f>(@@ENG_COST|EC.dpc|7@@+@@ENG_COST|EC.opc|7@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+      <c r="L12" s="14">
+        <f>(@@ENG_COST|EC.dpc|8@@+@@ENG_COST|EC.opc|8@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+      <c r="M12" s="14">
+        <f>(@@ENG_COST|EC.dpc|9@@+@@ENG_COST|EC.opc|9@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+      <c r="N12" s="14">
+        <f>(@@ENG_COST|EC.dpc|10@@+@@ENG_COST|EC.opc|10@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+      <c r="O12" s="14">
+        <f>(@@ENG_COST|EC.dpc|11@@+@@ENG_COST|EC.opc|11@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+      <c r="P12" s="14">
+        <f>(@@ENG_COST|EC.dpc|12@@+@@ENG_COST|EC.opc|12@@)/365*'IN_WC'!$D$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>موجودی مواد مصرفی و قطعات یدکی</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>WC.inv_cons</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|0@@+@@ENG_COST|EC.tot.9|0@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+      <c r="E13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|1@@+@@ENG_COST|EC.tot.9|1@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+      <c r="F13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|2@@+@@ENG_COST|EC.tot.9|2@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+      <c r="G13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|3@@+@@ENG_COST|EC.tot.9|3@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+      <c r="H13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|4@@+@@ENG_COST|EC.tot.9|4@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+      <c r="I13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|5@@+@@ENG_COST|EC.tot.9|5@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+      <c r="J13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|6@@+@@ENG_COST|EC.tot.9|6@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+      <c r="K13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|7@@+@@ENG_COST|EC.tot.9|7@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+      <c r="L13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|8@@+@@ENG_COST|EC.tot.9|8@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+      <c r="M13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|9@@+@@ENG_COST|EC.tot.9|9@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+      <c r="N13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|10@@+@@ENG_COST|EC.tot.9|10@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+      <c r="O13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|11@@+@@ENG_COST|EC.tot.9|11@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+      <c r="P13" s="14">
+        <f>(@@ENG_COST|EC.tot.1|12@@+@@ENG_COST|EC.tot.9|12@@)/365*'IN_WC'!$D$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>جمع موجودی‌ها</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>WC.inv</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D14" s="14">
+        <f>'ENG_WC'!$D$10+'ENG_WC'!$D$11+'ENG_WC'!$D$12+'ENG_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="E14" s="14">
+        <f>'ENG_WC'!$E$10+'ENG_WC'!$E$11+'ENG_WC'!$E$12+'ENG_WC'!$E$13</f>
+        <v/>
+      </c>
+      <c r="F14" s="14">
+        <f>'ENG_WC'!$F$10+'ENG_WC'!$F$11+'ENG_WC'!$F$12+'ENG_WC'!$F$13</f>
+        <v/>
+      </c>
+      <c r="G14" s="14">
+        <f>'ENG_WC'!$G$10+'ENG_WC'!$G$11+'ENG_WC'!$G$12+'ENG_WC'!$G$13</f>
+        <v/>
+      </c>
+      <c r="H14" s="14">
+        <f>'ENG_WC'!$H$10+'ENG_WC'!$H$11+'ENG_WC'!$H$12+'ENG_WC'!$H$13</f>
+        <v/>
+      </c>
+      <c r="I14" s="14">
+        <f>'ENG_WC'!$I$10+'ENG_WC'!$I$11+'ENG_WC'!$I$12+'ENG_WC'!$I$13</f>
+        <v/>
+      </c>
+      <c r="J14" s="14">
+        <f>'ENG_WC'!$J$10+'ENG_WC'!$J$11+'ENG_WC'!$J$12+'ENG_WC'!$J$13</f>
+        <v/>
+      </c>
+      <c r="K14" s="14">
+        <f>'ENG_WC'!$K$10+'ENG_WC'!$K$11+'ENG_WC'!$K$12+'ENG_WC'!$K$13</f>
+        <v/>
+      </c>
+      <c r="L14" s="14">
+        <f>'ENG_WC'!$L$10+'ENG_WC'!$L$11+'ENG_WC'!$L$12+'ENG_WC'!$L$13</f>
+        <v/>
+      </c>
+      <c r="M14" s="14">
+        <f>'ENG_WC'!$M$10+'ENG_WC'!$M$11+'ENG_WC'!$M$12+'ENG_WC'!$M$13</f>
+        <v/>
+      </c>
+      <c r="N14" s="14">
+        <f>'ENG_WC'!$N$10+'ENG_WC'!$N$11+'ENG_WC'!$N$12+'ENG_WC'!$N$13</f>
+        <v/>
+      </c>
+      <c r="O14" s="14">
+        <f>'ENG_WC'!$O$10+'ENG_WC'!$O$11+'ENG_WC'!$O$12+'ENG_WC'!$O$13</f>
+        <v/>
+      </c>
+      <c r="P14" s="14">
+        <f>'ENG_WC'!$P$10+'ENG_WC'!$P$11+'ENG_WC'!$P$12+'ENG_WC'!$P$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>حساب‌های دریافتنی</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>WC.ar</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D15" s="14">
+        <f>'ENG_OPS'!$D$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>'ENG_OPS'!$E$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+      <c r="F15" s="14">
+        <f>'ENG_OPS'!$F$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+      <c r="G15" s="14">
+        <f>'ENG_OPS'!$G$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+      <c r="H15" s="14">
+        <f>'ENG_OPS'!$H$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+      <c r="I15" s="14">
+        <f>'ENG_OPS'!$I$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+      <c r="J15" s="14">
+        <f>'ENG_OPS'!$J$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+      <c r="K15" s="14">
+        <f>'ENG_OPS'!$K$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+      <c r="L15" s="14">
+        <f>'ENG_OPS'!$L$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+      <c r="M15" s="14">
+        <f>'ENG_OPS'!$M$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+      <c r="N15" s="14">
+        <f>'ENG_OPS'!$N$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+      <c r="O15" s="14">
+        <f>'ENG_OPS'!$O$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+      <c r="P15" s="14">
+        <f>'ENG_OPS'!$P$81/365*'IN_WC'!$D$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>حساب‌های پرداختنی</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>WC.ap</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D16" s="14">
+        <f>(@@ENG_COST|EC.dpc|0@@+@@ENG_COST|EC.opc|0@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="E16" s="14">
+        <f>(@@ENG_COST|EC.dpc|1@@+@@ENG_COST|EC.opc|1@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="F16" s="14">
+        <f>(@@ENG_COST|EC.dpc|2@@+@@ENG_COST|EC.opc|2@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="G16" s="14">
+        <f>(@@ENG_COST|EC.dpc|3@@+@@ENG_COST|EC.opc|3@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="H16" s="14">
+        <f>(@@ENG_COST|EC.dpc|4@@+@@ENG_COST|EC.opc|4@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="I16" s="14">
+        <f>(@@ENG_COST|EC.dpc|5@@+@@ENG_COST|EC.opc|5@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="J16" s="14">
+        <f>(@@ENG_COST|EC.dpc|6@@+@@ENG_COST|EC.opc|6@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="K16" s="14">
+        <f>(@@ENG_COST|EC.dpc|7@@+@@ENG_COST|EC.opc|7@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="L16" s="14">
+        <f>(@@ENG_COST|EC.dpc|8@@+@@ENG_COST|EC.opc|8@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="M16" s="14">
+        <f>(@@ENG_COST|EC.dpc|9@@+@@ENG_COST|EC.opc|9@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="N16" s="14">
+        <f>(@@ENG_COST|EC.dpc|10@@+@@ENG_COST|EC.opc|10@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="O16" s="14">
+        <f>(@@ENG_COST|EC.dpc|11@@+@@ENG_COST|EC.opc|11@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+      <c r="P16" s="14">
+        <f>(@@ENG_COST|EC.dpc|12@@+@@ENG_COST|EC.opc|12@@)/365*'IN_WC'!$D$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>مالیات قابل پرداخت</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>WC.tax_pay</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D17" s="14">
+        <f>@@ENG_COST|EC.tax_op|0@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+      <c r="E17" s="14">
+        <f>@@ENG_COST|EC.tax_op|1@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+      <c r="F17" s="14">
+        <f>@@ENG_COST|EC.tax_op|2@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+      <c r="G17" s="14">
+        <f>@@ENG_COST|EC.tax_op|3@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+      <c r="H17" s="14">
+        <f>@@ENG_COST|EC.tax_op|4@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+      <c r="I17" s="14">
+        <f>@@ENG_COST|EC.tax_op|5@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+      <c r="J17" s="14">
+        <f>@@ENG_COST|EC.tax_op|6@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+      <c r="K17" s="14">
+        <f>@@ENG_COST|EC.tax_op|7@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+      <c r="L17" s="14">
+        <f>@@ENG_COST|EC.tax_op|8@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+      <c r="M17" s="14">
+        <f>@@ENG_COST|EC.tax_op|9@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+      <c r="N17" s="14">
+        <f>@@ENG_COST|EC.tax_op|10@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+      <c r="O17" s="14">
+        <f>@@ENG_COST|EC.tax_op|11@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+      <c r="P17" s="14">
+        <f>@@ENG_COST|EC.tax_op|12@@/365*'IN_WC'!$D$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>خالص سرمایه در گردش (NWC)</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>WC.nwc</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D18" s="14">
+        <f>'ENG_WC'!$D$14+'ENG_WC'!$D$15-'ENG_WC'!$D$16-'ENG_WC'!$D$17</f>
+        <v/>
+      </c>
+      <c r="E18" s="14">
+        <f>'ENG_WC'!$E$14+'ENG_WC'!$E$15-'ENG_WC'!$E$16-'ENG_WC'!$E$17</f>
+        <v/>
+      </c>
+      <c r="F18" s="14">
+        <f>'ENG_WC'!$F$14+'ENG_WC'!$F$15-'ENG_WC'!$F$16-'ENG_WC'!$F$17</f>
+        <v/>
+      </c>
+      <c r="G18" s="14">
+        <f>'ENG_WC'!$G$14+'ENG_WC'!$G$15-'ENG_WC'!$G$16-'ENG_WC'!$G$17</f>
+        <v/>
+      </c>
+      <c r="H18" s="14">
+        <f>'ENG_WC'!$H$14+'ENG_WC'!$H$15-'ENG_WC'!$H$16-'ENG_WC'!$H$17</f>
+        <v/>
+      </c>
+      <c r="I18" s="14">
+        <f>'ENG_WC'!$I$14+'ENG_WC'!$I$15-'ENG_WC'!$I$16-'ENG_WC'!$I$17</f>
+        <v/>
+      </c>
+      <c r="J18" s="14">
+        <f>'ENG_WC'!$J$14+'ENG_WC'!$J$15-'ENG_WC'!$J$16-'ENG_WC'!$J$17</f>
+        <v/>
+      </c>
+      <c r="K18" s="14">
+        <f>'ENG_WC'!$K$14+'ENG_WC'!$K$15-'ENG_WC'!$K$16-'ENG_WC'!$K$17</f>
+        <v/>
+      </c>
+      <c r="L18" s="14">
+        <f>'ENG_WC'!$L$14+'ENG_WC'!$L$15-'ENG_WC'!$L$16-'ENG_WC'!$L$17</f>
+        <v/>
+      </c>
+      <c r="M18" s="14">
+        <f>'ENG_WC'!$M$14+'ENG_WC'!$M$15-'ENG_WC'!$M$16-'ENG_WC'!$M$17</f>
+        <v/>
+      </c>
+      <c r="N18" s="14">
+        <f>'ENG_WC'!$N$14+'ENG_WC'!$N$15-'ENG_WC'!$N$16-'ENG_WC'!$N$17</f>
+        <v/>
+      </c>
+      <c r="O18" s="14">
+        <f>'ENG_WC'!$O$14+'ENG_WC'!$O$15-'ENG_WC'!$O$16-'ENG_WC'!$O$17</f>
+        <v/>
+      </c>
+      <c r="P18" s="14">
+        <f>'ENG_WC'!$P$14+'ENG_WC'!$P$15-'ENG_WC'!$P$16-'ENG_WC'!$P$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>تغییرات سرمایه در گردش (ΔWC)</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>WC.dwc</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D19" s="14">
+        <f>'ENG_WC'!$D$18</f>
+        <v/>
+      </c>
+      <c r="E19" s="14">
+        <f>'ENG_WC'!$E$18-'ENG_WC'!$D$18</f>
+        <v/>
+      </c>
+      <c r="F19" s="14">
+        <f>'ENG_WC'!$F$18-'ENG_WC'!$E$18</f>
+        <v/>
+      </c>
+      <c r="G19" s="14">
+        <f>'ENG_WC'!$G$18-'ENG_WC'!$F$18</f>
+        <v/>
+      </c>
+      <c r="H19" s="14">
+        <f>'ENG_WC'!$H$18-'ENG_WC'!$G$18</f>
+        <v/>
+      </c>
+      <c r="I19" s="14">
+        <f>'ENG_WC'!$I$18-'ENG_WC'!$H$18</f>
+        <v/>
+      </c>
+      <c r="J19" s="14">
+        <f>'ENG_WC'!$J$18-'ENG_WC'!$I$18</f>
+        <v/>
+      </c>
+      <c r="K19" s="14">
+        <f>'ENG_WC'!$K$18-'ENG_WC'!$J$18</f>
+        <v/>
+      </c>
+      <c r="L19" s="14">
+        <f>'ENG_WC'!$L$18-'ENG_WC'!$K$18</f>
+        <v/>
+      </c>
+      <c r="M19" s="14">
+        <f>'ENG_WC'!$M$18-'ENG_WC'!$L$18</f>
+        <v/>
+      </c>
+      <c r="N19" s="14">
+        <f>'ENG_WC'!$N$18-'ENG_WC'!$M$18</f>
+        <v/>
+      </c>
+      <c r="O19" s="14">
+        <f>'ENG_WC'!$O$18-'ENG_WC'!$N$18</f>
+        <v/>
+      </c>
+      <c r="P19" s="14">
+        <f>'ENG_WC'!$P$18-'ENG_WC'!$O$18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>تسهیلات کوتاه‌مدت (مانده)</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>WC.stloan</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D20" s="14">
+        <f>MAX(0,'ENG_WC'!$D$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="E20" s="14">
+        <f>MAX(0,'ENG_WC'!$E$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="F20" s="14">
+        <f>MAX(0,'ENG_WC'!$F$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="G20" s="14">
+        <f>MAX(0,'ENG_WC'!$G$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="H20" s="14">
+        <f>MAX(0,'ENG_WC'!$H$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="I20" s="14">
+        <f>MAX(0,'ENG_WC'!$I$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="J20" s="14">
+        <f>MAX(0,'ENG_WC'!$J$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="K20" s="14">
+        <f>MAX(0,'ENG_WC'!$K$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="L20" s="14">
+        <f>MAX(0,'ENG_WC'!$L$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="M20" s="14">
+        <f>MAX(0,'ENG_WC'!$M$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="N20" s="14">
+        <f>MAX(0,'ENG_WC'!$N$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="O20" s="14">
+        <f>MAX(0,'ENG_WC'!$O$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="P20" s="14">
+        <f>MAX(0,'ENG_WC'!$P$18*'IN_WC'!$D$18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>تغییرات تسهیلات کوتاه‌مدت</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>WC.dstloan</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D21" s="14">
+        <f>'ENG_WC'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E21" s="14">
+        <f>'ENG_WC'!$E$20-'ENG_WC'!$D$20</f>
+        <v/>
+      </c>
+      <c r="F21" s="14">
+        <f>'ENG_WC'!$F$20-'ENG_WC'!$E$20</f>
+        <v/>
+      </c>
+      <c r="G21" s="14">
+        <f>'ENG_WC'!$G$20-'ENG_WC'!$F$20</f>
+        <v/>
+      </c>
+      <c r="H21" s="14">
+        <f>'ENG_WC'!$H$20-'ENG_WC'!$G$20</f>
+        <v/>
+      </c>
+      <c r="I21" s="14">
+        <f>'ENG_WC'!$I$20-'ENG_WC'!$H$20</f>
+        <v/>
+      </c>
+      <c r="J21" s="14">
+        <f>'ENG_WC'!$J$20-'ENG_WC'!$I$20</f>
+        <v/>
+      </c>
+      <c r="K21" s="14">
+        <f>'ENG_WC'!$K$20-'ENG_WC'!$J$20</f>
+        <v/>
+      </c>
+      <c r="L21" s="14">
+        <f>'ENG_WC'!$L$20-'ENG_WC'!$K$20</f>
+        <v/>
+      </c>
+      <c r="M21" s="14">
+        <f>'ENG_WC'!$M$20-'ENG_WC'!$L$20</f>
+        <v/>
+      </c>
+      <c r="N21" s="14">
+        <f>'ENG_WC'!$N$20-'ENG_WC'!$M$20</f>
+        <v/>
+      </c>
+      <c r="O21" s="14">
+        <f>'ENG_WC'!$O$20-'ENG_WC'!$N$20</f>
+        <v/>
+      </c>
+      <c r="P21" s="14">
+        <f>'ENG_WC'!$P$20-'ENG_WC'!$O$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>ب) چرخه تبدیل نقد (CCC)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
+      <c r="N23" s="7" t="n"/>
+      <c r="O23" s="7" t="n"/>
+      <c r="P23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>دوره گردش موجودی (DIO)</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>WC.dio</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>روز</t>
+        </is>
+      </c>
+      <c r="D24" s="13">
+        <f>IFERROR('ENG_WC'!$D$14/((@@ENG_COST|EC.dpc|0@@+@@ENG_COST|EC.opc|0@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="E24" s="13">
+        <f>IFERROR('ENG_WC'!$E$14/((@@ENG_COST|EC.dpc|1@@+@@ENG_COST|EC.opc|1@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="13">
+        <f>IFERROR('ENG_WC'!$F$14/((@@ENG_COST|EC.dpc|2@@+@@ENG_COST|EC.opc|2@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="13">
+        <f>IFERROR('ENG_WC'!$G$14/((@@ENG_COST|EC.dpc|3@@+@@ENG_COST|EC.opc|3@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="13">
+        <f>IFERROR('ENG_WC'!$H$14/((@@ENG_COST|EC.dpc|4@@+@@ENG_COST|EC.opc|4@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="I24" s="13">
+        <f>IFERROR('ENG_WC'!$I$14/((@@ENG_COST|EC.dpc|5@@+@@ENG_COST|EC.opc|5@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="J24" s="13">
+        <f>IFERROR('ENG_WC'!$J$14/((@@ENG_COST|EC.dpc|6@@+@@ENG_COST|EC.opc|6@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="K24" s="13">
+        <f>IFERROR('ENG_WC'!$K$14/((@@ENG_COST|EC.dpc|7@@+@@ENG_COST|EC.opc|7@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="L24" s="13">
+        <f>IFERROR('ENG_WC'!$L$14/((@@ENG_COST|EC.dpc|8@@+@@ENG_COST|EC.opc|8@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="M24" s="13">
+        <f>IFERROR('ENG_WC'!$M$14/((@@ENG_COST|EC.dpc|9@@+@@ENG_COST|EC.opc|9@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="N24" s="13">
+        <f>IFERROR('ENG_WC'!$N$14/((@@ENG_COST|EC.dpc|10@@+@@ENG_COST|EC.opc|10@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="O24" s="13">
+        <f>IFERROR('ENG_WC'!$O$14/((@@ENG_COST|EC.dpc|11@@+@@ENG_COST|EC.opc|11@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="P24" s="13">
+        <f>IFERROR('ENG_WC'!$P$14/((@@ENG_COST|EC.dpc|12@@+@@ENG_COST|EC.opc|12@@)/365),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>دوره وصول مطالبات (DSO)</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>WC.dso_calc</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>روز</t>
+        </is>
+      </c>
+      <c r="D25" s="13">
+        <f>IFERROR('ENG_WC'!$D$15/('ENG_OPS'!$D$81/365),0)</f>
+        <v/>
+      </c>
+      <c r="E25" s="13">
+        <f>IFERROR('ENG_WC'!$E$15/('ENG_OPS'!$E$81/365),0)</f>
+        <v/>
+      </c>
+      <c r="F25" s="13">
+        <f>IFERROR('ENG_WC'!$F$15/('ENG_OPS'!$F$81/365),0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="13">
+        <f>IFERROR('ENG_WC'!$G$15/('ENG_OPS'!$G$81/365),0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="13">
+        <f>IFERROR('ENG_WC'!$H$15/('ENG_OPS'!$H$81/365),0)</f>
+        <v/>
+      </c>
+      <c r="I25" s="13">
+        <f>IFERROR('ENG_WC'!$I$15/('ENG_OPS'!$I$81/365),0)</f>
+        <v/>
+      </c>
+      <c r="J25" s="13">
+        <f>IFERROR('ENG_WC'!$J$15/('ENG_OPS'!$J$81/365),0)</f>
+        <v/>
+      </c>
+      <c r="K25" s="13">
+        <f>IFERROR('ENG_WC'!$K$15/('ENG_OPS'!$K$81/365),0)</f>
+        <v/>
+      </c>
+      <c r="L25" s="13">
+        <f>IFERROR('ENG_WC'!$L$15/('ENG_OPS'!$L$81/365),0)</f>
+        <v/>
+      </c>
+      <c r="M25" s="13">
+        <f>IFERROR('ENG_WC'!$M$15/('ENG_OPS'!$M$81/365),0)</f>
+        <v/>
+      </c>
+      <c r="N25" s="13">
+        <f>IFERROR('ENG_WC'!$N$15/('ENG_OPS'!$N$81/365),0)</f>
+        <v/>
+      </c>
+      <c r="O25" s="13">
+        <f>IFERROR('ENG_WC'!$O$15/('ENG_OPS'!$O$81/365),0)</f>
+        <v/>
+      </c>
+      <c r="P25" s="13">
+        <f>IFERROR('ENG_WC'!$P$15/('ENG_OPS'!$P$81/365),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>دوره پرداخت بدهی‌ها (DPO)</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>WC.dpo_calc</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>روز</t>
+        </is>
+      </c>
+      <c r="D26" s="13">
+        <f>IFERROR('ENG_WC'!$D$16/((@@ENG_COST|EC.dpc|0@@+@@ENG_COST|EC.opc|0@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="E26" s="13">
+        <f>IFERROR('ENG_WC'!$E$16/((@@ENG_COST|EC.dpc|1@@+@@ENG_COST|EC.opc|1@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="13">
+        <f>IFERROR('ENG_WC'!$F$16/((@@ENG_COST|EC.dpc|2@@+@@ENG_COST|EC.opc|2@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="13">
+        <f>IFERROR('ENG_WC'!$G$16/((@@ENG_COST|EC.dpc|3@@+@@ENG_COST|EC.opc|3@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="13">
+        <f>IFERROR('ENG_WC'!$H$16/((@@ENG_COST|EC.dpc|4@@+@@ENG_COST|EC.opc|4@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="I26" s="13">
+        <f>IFERROR('ENG_WC'!$I$16/((@@ENG_COST|EC.dpc|5@@+@@ENG_COST|EC.opc|5@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="J26" s="13">
+        <f>IFERROR('ENG_WC'!$J$16/((@@ENG_COST|EC.dpc|6@@+@@ENG_COST|EC.opc|6@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="13">
+        <f>IFERROR('ENG_WC'!$K$16/((@@ENG_COST|EC.dpc|7@@+@@ENG_COST|EC.opc|7@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="L26" s="13">
+        <f>IFERROR('ENG_WC'!$L$16/((@@ENG_COST|EC.dpc|8@@+@@ENG_COST|EC.opc|8@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="M26" s="13">
+        <f>IFERROR('ENG_WC'!$M$16/((@@ENG_COST|EC.dpc|9@@+@@ENG_COST|EC.opc|9@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="N26" s="13">
+        <f>IFERROR('ENG_WC'!$N$16/((@@ENG_COST|EC.dpc|10@@+@@ENG_COST|EC.opc|10@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="O26" s="13">
+        <f>IFERROR('ENG_WC'!$O$16/((@@ENG_COST|EC.dpc|11@@+@@ENG_COST|EC.opc|11@@)/365),0)</f>
+        <v/>
+      </c>
+      <c r="P26" s="13">
+        <f>IFERROR('ENG_WC'!$P$16/((@@ENG_COST|EC.dpc|12@@+@@ENG_COST|EC.opc|12@@)/365),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>چرخه تبدیل نقد (CCC)</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>WC.ccc</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>روز</t>
+        </is>
+      </c>
+      <c r="D27" s="13">
+        <f>'ENG_WC'!$D$24+'ENG_WC'!$D$25-'ENG_WC'!$D$26</f>
+        <v/>
+      </c>
+      <c r="E27" s="13">
+        <f>'ENG_WC'!$E$24+'ENG_WC'!$E$25-'ENG_WC'!$E$26</f>
+        <v/>
+      </c>
+      <c r="F27" s="13">
+        <f>'ENG_WC'!$F$24+'ENG_WC'!$F$25-'ENG_WC'!$F$26</f>
+        <v/>
+      </c>
+      <c r="G27" s="13">
+        <f>'ENG_WC'!$G$24+'ENG_WC'!$G$25-'ENG_WC'!$G$26</f>
+        <v/>
+      </c>
+      <c r="H27" s="13">
+        <f>'ENG_WC'!$H$24+'ENG_WC'!$H$25-'ENG_WC'!$H$26</f>
+        <v/>
+      </c>
+      <c r="I27" s="13">
+        <f>'ENG_WC'!$I$24+'ENG_WC'!$I$25-'ENG_WC'!$I$26</f>
+        <v/>
+      </c>
+      <c r="J27" s="13">
+        <f>'ENG_WC'!$J$24+'ENG_WC'!$J$25-'ENG_WC'!$J$26</f>
+        <v/>
+      </c>
+      <c r="K27" s="13">
+        <f>'ENG_WC'!$K$24+'ENG_WC'!$K$25-'ENG_WC'!$K$26</f>
+        <v/>
+      </c>
+      <c r="L27" s="13">
+        <f>'ENG_WC'!$L$24+'ENG_WC'!$L$25-'ENG_WC'!$L$26</f>
+        <v/>
+      </c>
+      <c r="M27" s="13">
+        <f>'ENG_WC'!$M$24+'ENG_WC'!$M$25-'ENG_WC'!$M$26</f>
+        <v/>
+      </c>
+      <c r="N27" s="13">
+        <f>'ENG_WC'!$N$24+'ENG_WC'!$N$25-'ENG_WC'!$N$26</f>
+        <v/>
+      </c>
+      <c r="O27" s="13">
+        <f>'ENG_WC'!$O$24+'ENG_WC'!$O$25-'ENG_WC'!$O$26</f>
+        <v/>
+      </c>
+      <c r="P27" s="13">
+        <f>'ENG_WC'!$P$24+'ENG_WC'!$P$25-'ENG_WC'!$P$26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>هزینه نقدی سالانه (مبنای حداقل نقد)</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>WC.cash_opex</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D28" s="14">
+        <f>@@ENG_COST|EC.var_total|0@@+@@ENG_COST|EC.fixed_cash|0@@</f>
+        <v/>
+      </c>
+      <c r="E28" s="14">
+        <f>@@ENG_COST|EC.var_total|1@@+@@ENG_COST|EC.fixed_cash|1@@</f>
+        <v/>
+      </c>
+      <c r="F28" s="14">
+        <f>@@ENG_COST|EC.var_total|2@@+@@ENG_COST|EC.fixed_cash|2@@</f>
+        <v/>
+      </c>
+      <c r="G28" s="14">
+        <f>@@ENG_COST|EC.var_total|3@@+@@ENG_COST|EC.fixed_cash|3@@</f>
+        <v/>
+      </c>
+      <c r="H28" s="14">
+        <f>@@ENG_COST|EC.var_total|4@@+@@ENG_COST|EC.fixed_cash|4@@</f>
+        <v/>
+      </c>
+      <c r="I28" s="14">
+        <f>@@ENG_COST|EC.var_total|5@@+@@ENG_COST|EC.fixed_cash|5@@</f>
+        <v/>
+      </c>
+      <c r="J28" s="14">
+        <f>@@ENG_COST|EC.var_total|6@@+@@ENG_COST|EC.fixed_cash|6@@</f>
+        <v/>
+      </c>
+      <c r="K28" s="14">
+        <f>@@ENG_COST|EC.var_total|7@@+@@ENG_COST|EC.fixed_cash|7@@</f>
+        <v/>
+      </c>
+      <c r="L28" s="14">
+        <f>@@ENG_COST|EC.var_total|8@@+@@ENG_COST|EC.fixed_cash|8@@</f>
+        <v/>
+      </c>
+      <c r="M28" s="14">
+        <f>@@ENG_COST|EC.var_total|9@@+@@ENG_COST|EC.fixed_cash|9@@</f>
+        <v/>
+      </c>
+      <c r="N28" s="14">
+        <f>@@ENG_COST|EC.var_total|10@@+@@ENG_COST|EC.fixed_cash|10@@</f>
+        <v/>
+      </c>
+      <c r="O28" s="14">
+        <f>@@ENG_COST|EC.var_total|11@@+@@ENG_COST|EC.fixed_cash|11@@</f>
+        <v/>
+      </c>
+      <c r="P28" s="14">
+        <f>@@ENG_COST|EC.var_total|12@@+@@ENG_COST|EC.fixed_cash|12@@</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>حداقل موجودی نقدی</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>WC.min_cash</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D29" s="14">
+        <f>MAX(0,'ENG_WC'!$D$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="E29" s="14">
+        <f>MAX(0,'ENG_WC'!$E$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="F29" s="14">
+        <f>MAX(0,'ENG_WC'!$F$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="G29" s="14">
+        <f>MAX(0,'ENG_WC'!$G$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="H29" s="14">
+        <f>MAX(0,'ENG_WC'!$H$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="I29" s="14">
+        <f>MAX(0,'ENG_WC'!$I$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="J29" s="14">
+        <f>MAX(0,'ENG_WC'!$J$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="K29" s="14">
+        <f>MAX(0,'ENG_WC'!$K$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="L29" s="14">
+        <f>MAX(0,'ENG_WC'!$L$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="M29" s="14">
+        <f>MAX(0,'ENG_WC'!$M$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="N29" s="14">
+        <f>MAX(0,'ENG_WC'!$N$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="O29" s="14">
+        <f>MAX(0,'ENG_WC'!$O$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="P29" s="14">
+        <f>MAX(0,'ENG_WC'!$P$28)/365*'IN_WC'!$D$15</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -17932,55 +19394,55 @@
         </is>
       </c>
       <c r="D54" s="14">
-        <f>@@ENG_WC|WC.dwc|0@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$D$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
       <c r="E54" s="14">
-        <f>@@ENG_WC|WC.dwc|1@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$E$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
       <c r="F54" s="14">
-        <f>@@ENG_WC|WC.dwc|2@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$F$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
       <c r="G54" s="14">
-        <f>@@ENG_WC|WC.dwc|3@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$G$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
       <c r="H54" s="14">
-        <f>@@ENG_WC|WC.dwc|4@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$H$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
       <c r="I54" s="14">
-        <f>@@ENG_WC|WC.dwc|5@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$I$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
       <c r="J54" s="14">
-        <f>@@ENG_WC|WC.dwc|6@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$J$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
       <c r="K54" s="14">
-        <f>@@ENG_WC|WC.dwc|7@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$K$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
       <c r="L54" s="14">
-        <f>@@ENG_WC|WC.dwc|8@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$L$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
       <c r="M54" s="14">
-        <f>@@ENG_WC|WC.dwc|9@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$M$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
       <c r="N54" s="14">
-        <f>@@ENG_WC|WC.dwc|10@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$N$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
       <c r="O54" s="14">
-        <f>@@ENG_WC|WC.dwc|11@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$O$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
       <c r="P54" s="14">
-        <f>@@ENG_WC|WC.dwc|12@@*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
+        <f>'ENG_WC'!$P$19*'IN_SCEN'!$D$13*'IN_SCEN'!$D$14</f>
         <v/>
       </c>
     </row>
@@ -19902,55 +21364,55 @@
         </is>
       </c>
       <c r="D88" s="14">
-        <f>@@ENG_WC|WC.dwc|0@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$D$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
       <c r="E88" s="14">
-        <f>@@ENG_WC|WC.dwc|1@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$E$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
       <c r="F88" s="14">
-        <f>@@ENG_WC|WC.dwc|2@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$F$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
       <c r="G88" s="14">
-        <f>@@ENG_WC|WC.dwc|3@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$G$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
       <c r="H88" s="14">
-        <f>@@ENG_WC|WC.dwc|4@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$H$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
       <c r="I88" s="14">
-        <f>@@ENG_WC|WC.dwc|5@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$I$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
       <c r="J88" s="14">
-        <f>@@ENG_WC|WC.dwc|6@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$J$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
       <c r="K88" s="14">
-        <f>@@ENG_WC|WC.dwc|7@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$K$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
       <c r="L88" s="14">
-        <f>@@ENG_WC|WC.dwc|8@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$L$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
       <c r="M88" s="14">
-        <f>@@ENG_WC|WC.dwc|9@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$M$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
       <c r="N88" s="14">
-        <f>@@ENG_WC|WC.dwc|10@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$N$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
       <c r="O88" s="14">
-        <f>@@ENG_WC|WC.dwc|11@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$O$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
       <c r="P88" s="14">
-        <f>@@ENG_WC|WC.dwc|12@@*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
+        <f>'ENG_WC'!$P$19*'IN_SCEN'!$E$13*'IN_SCEN'!$E$14</f>
         <v/>
       </c>
     </row>
@@ -21872,55 +23334,55 @@
         </is>
       </c>
       <c r="D122" s="14">
-        <f>@@ENG_WC|WC.dwc|0@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$D$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
       <c r="E122" s="14">
-        <f>@@ENG_WC|WC.dwc|1@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$E$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
       <c r="F122" s="14">
-        <f>@@ENG_WC|WC.dwc|2@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$F$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
       <c r="G122" s="14">
-        <f>@@ENG_WC|WC.dwc|3@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$G$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
       <c r="H122" s="14">
-        <f>@@ENG_WC|WC.dwc|4@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$H$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
       <c r="I122" s="14">
-        <f>@@ENG_WC|WC.dwc|5@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$I$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
       <c r="J122" s="14">
-        <f>@@ENG_WC|WC.dwc|6@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$J$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
       <c r="K122" s="14">
-        <f>@@ENG_WC|WC.dwc|7@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$K$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
       <c r="L122" s="14">
-        <f>@@ENG_WC|WC.dwc|8@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$L$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
       <c r="M122" s="14">
-        <f>@@ENG_WC|WC.dwc|9@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$M$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
       <c r="N122" s="14">
-        <f>@@ENG_WC|WC.dwc|10@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$N$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
       <c r="O122" s="14">
-        <f>@@ENG_WC|WC.dwc|11@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$O$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
       <c r="P122" s="14">
-        <f>@@ENG_WC|WC.dwc|12@@*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
+        <f>'ENG_WC'!$P$19*'IN_SCEN'!$F$13*'IN_SCEN'!$F$14</f>
         <v/>
       </c>
     </row>

--- a/models/lead_acid_recycling/build/out/built.xlsx
+++ b/models/lead_acid_recycling/build/out/built.xlsx
@@ -19,6 +19,8 @@
     <sheet name="ENG_CAPEX" sheetId="10" state="hidden" r:id="rId10"/>
     <sheet name="ENG_ALLOC" sheetId="11" state="hidden" r:id="rId11"/>
     <sheet name="ENG_WC" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet name="ENG_DCF" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet name="ENG_LEV" sheetId="14" state="hidden" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11563,6 +11565,2922 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>محاسبات DCF و ارزش‌گذاری</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>موتور محاسبات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>ساخت WACC، تنزیل FCFF، محاسبهٔ NPV، IRR، MIRR، دوره بازپرداشت و ارزش بنگاه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>دوره (t)</t>
+        </is>
+      </c>
+      <c r="D7" s="5">
+        <f>'IN_MACRO'!D$23</f>
+        <v/>
+      </c>
+      <c r="E7" s="5">
+        <f>'IN_MACRO'!E$23</f>
+        <v/>
+      </c>
+      <c r="F7" s="5">
+        <f>'IN_MACRO'!F$23</f>
+        <v/>
+      </c>
+      <c r="G7" s="5">
+        <f>'IN_MACRO'!G$23</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
+        <f>'IN_MACRO'!H$23</f>
+        <v/>
+      </c>
+      <c r="I7" s="5">
+        <f>'IN_MACRO'!I$23</f>
+        <v/>
+      </c>
+      <c r="J7" s="5">
+        <f>'IN_MACRO'!J$23</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
+        <f>'IN_MACRO'!K$23</f>
+        <v/>
+      </c>
+      <c r="L7" s="5">
+        <f>'IN_MACRO'!L$23</f>
+        <v/>
+      </c>
+      <c r="M7" s="5">
+        <f>'IN_MACRO'!M$23</f>
+        <v/>
+      </c>
+      <c r="N7" s="5">
+        <f>'IN_MACRO'!N$23</f>
+        <v/>
+      </c>
+      <c r="O7" s="5">
+        <f>'IN_MACRO'!O$23</f>
+        <v/>
+      </c>
+      <c r="P7" s="5">
+        <f>'IN_MACRO'!P$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>سال تقویمی</t>
+        </is>
+      </c>
+      <c r="D8" s="5">
+        <f>'IN_MACRO'!D$24</f>
+        <v/>
+      </c>
+      <c r="E8" s="5">
+        <f>'IN_MACRO'!E$24</f>
+        <v/>
+      </c>
+      <c r="F8" s="5">
+        <f>'IN_MACRO'!F$24</f>
+        <v/>
+      </c>
+      <c r="G8" s="5">
+        <f>'IN_MACRO'!G$24</f>
+        <v/>
+      </c>
+      <c r="H8" s="5">
+        <f>'IN_MACRO'!H$24</f>
+        <v/>
+      </c>
+      <c r="I8" s="5">
+        <f>'IN_MACRO'!I$24</f>
+        <v/>
+      </c>
+      <c r="J8" s="5">
+        <f>'IN_MACRO'!J$24</f>
+        <v/>
+      </c>
+      <c r="K8" s="5">
+        <f>'IN_MACRO'!K$24</f>
+        <v/>
+      </c>
+      <c r="L8" s="5">
+        <f>'IN_MACRO'!L$24</f>
+        <v/>
+      </c>
+      <c r="M8" s="5">
+        <f>'IN_MACRO'!M$24</f>
+        <v/>
+      </c>
+      <c r="N8" s="5">
+        <f>'IN_MACRO'!N$24</f>
+        <v/>
+      </c>
+      <c r="O8" s="5">
+        <f>'IN_MACRO'!O$24</f>
+        <v/>
+      </c>
+      <c r="P8" s="5">
+        <f>'IN_MACRO'!P$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>الف) ساختار سرمایه و نرخ تنزیل</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
+      <c r="P9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>بازده مورد انتظار سهامداران (Ke)</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>DCF.ke</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D10" s="11">
+        <f>'ENG_SCEN'!$D$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
+        <f>'ENG_SCEN'!$E$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+      <c r="F10" s="11">
+        <f>'ENG_SCEN'!$F$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>'ENG_SCEN'!$G$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+      <c r="H10" s="11">
+        <f>'ENG_SCEN'!$H$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+      <c r="I10" s="11">
+        <f>'ENG_SCEN'!$I$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+      <c r="J10" s="11">
+        <f>'ENG_SCEN'!$J$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+      <c r="K10" s="11">
+        <f>'ENG_SCEN'!$K$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+      <c r="L10" s="11">
+        <f>'ENG_SCEN'!$L$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+      <c r="M10" s="11">
+        <f>'ENG_SCEN'!$M$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+      <c r="N10" s="11">
+        <f>'ENG_SCEN'!$N$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+      <c r="O10" s="11">
+        <f>'ENG_SCEN'!$O$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+      <c r="P10" s="11">
+        <f>'ENG_SCEN'!$P$26+'IN_MACRO'!$D$16*'IN_MACRO'!$D$15+'IN_MACRO'!$D$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>هزینه بدهی پس از مالیات (Kd×(1−t))</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>DCF.kd_at</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="G11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="H11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="I11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="J11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="K11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="L11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="M11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="N11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="O11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+      <c r="P11" s="11">
+        <f>('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*(1-'IN_MACRO'!$D$14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>وزن حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>DCF.we</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="E12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="F12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="G12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="H12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="I12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="J12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="K12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="L12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="M12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="N12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="O12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="P12" s="11">
+        <f>1-'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>وزن بدهی</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>DCF.wd</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="E13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="F13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="H13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="I13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="J13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="K13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="L13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="M13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="N13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="O13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+      <c r="P13" s="11">
+        <f>'IN_FIN'!$D$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>میانگین موزون هزینه سرمایه (WACC)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>DCF.wacc</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D14" s="11">
+        <f>'ENG_DCF'!$D$12*'ENG_DCF'!$D$10+'ENG_DCF'!$D$13*'ENG_DCF'!$D$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>'ENG_DCF'!$E$12*'ENG_DCF'!$E$10+'ENG_DCF'!$E$13*'ENG_DCF'!$E$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+      <c r="F14" s="11">
+        <f>'ENG_DCF'!$F$12*'ENG_DCF'!$F$10+'ENG_DCF'!$F$13*'ENG_DCF'!$F$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
+        <f>'ENG_DCF'!$G$12*'ENG_DCF'!$G$10+'ENG_DCF'!$G$13*'ENG_DCF'!$G$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+      <c r="H14" s="11">
+        <f>'ENG_DCF'!$H$12*'ENG_DCF'!$H$10+'ENG_DCF'!$H$13*'ENG_DCF'!$H$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+      <c r="I14" s="11">
+        <f>'ENG_DCF'!$I$12*'ENG_DCF'!$I$10+'ENG_DCF'!$I$13*'ENG_DCF'!$I$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+      <c r="J14" s="11">
+        <f>'ENG_DCF'!$J$12*'ENG_DCF'!$J$10+'ENG_DCF'!$J$13*'ENG_DCF'!$J$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+      <c r="K14" s="11">
+        <f>'ENG_DCF'!$K$12*'ENG_DCF'!$K$10+'ENG_DCF'!$K$13*'ENG_DCF'!$K$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+      <c r="L14" s="11">
+        <f>'ENG_DCF'!$L$12*'ENG_DCF'!$L$10+'ENG_DCF'!$L$13*'ENG_DCF'!$L$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+      <c r="M14" s="11">
+        <f>'ENG_DCF'!$M$12*'ENG_DCF'!$M$10+'ENG_DCF'!$M$13*'ENG_DCF'!$M$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+      <c r="N14" s="11">
+        <f>'ENG_DCF'!$N$12*'ENG_DCF'!$N$10+'ENG_DCF'!$N$13*'ENG_DCF'!$N$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+      <c r="O14" s="11">
+        <f>'ENG_DCF'!$O$12*'ENG_DCF'!$O$10+'ENG_DCF'!$O$13*'ENG_DCF'!$O$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+      <c r="P14" s="11">
+        <f>'ENG_DCF'!$P$12*'ENG_DCF'!$P$10+'ENG_DCF'!$P$13*'ENG_DCF'!$P$11+'ENG_SCEN'!$G$18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ضریب تنزیل</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>DCF.df</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>ضریب</t>
+        </is>
+      </c>
+      <c r="D15" s="25">
+        <f>1</f>
+        <v/>
+      </c>
+      <c r="E15" s="25">
+        <f>'ENG_DCF'!$D$15/(1+'ENG_DCF'!$E$14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="25">
+        <f>'ENG_DCF'!$E$15/(1+'ENG_DCF'!$F$14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="25">
+        <f>'ENG_DCF'!$F$15/(1+'ENG_DCF'!$G$14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="25">
+        <f>'ENG_DCF'!$G$15/(1+'ENG_DCF'!$H$14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="25">
+        <f>'ENG_DCF'!$H$15/(1+'ENG_DCF'!$I$14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="25">
+        <f>'ENG_DCF'!$I$15/(1+'ENG_DCF'!$J$14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="25">
+        <f>'ENG_DCF'!$J$15/(1+'ENG_DCF'!$K$14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="25">
+        <f>'ENG_DCF'!$K$15/(1+'ENG_DCF'!$L$14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="25">
+        <f>'ENG_DCF'!$L$15/(1+'ENG_DCF'!$M$14)</f>
+        <v/>
+      </c>
+      <c r="N15" s="25">
+        <f>'ENG_DCF'!$M$15/(1+'ENG_DCF'!$N$14)</f>
+        <v/>
+      </c>
+      <c r="O15" s="25">
+        <f>'ENG_DCF'!$N$15/(1+'ENG_DCF'!$O$14)</f>
+        <v/>
+      </c>
+      <c r="P15" s="25">
+        <f>'ENG_DCF'!$O$15/(1+'ENG_DCF'!$P$14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>ب) تنزیل جریان‌های نقدی و ارزش پایانی</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="7" t="n"/>
+      <c r="O17" s="7" t="n"/>
+      <c r="P17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>جریان نقد آزاد پروژه (FCFF)</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>DCF.fcff</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|0@@</f>
+        <v/>
+      </c>
+      <c r="E18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|1@@</f>
+        <v/>
+      </c>
+      <c r="F18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|2@@</f>
+        <v/>
+      </c>
+      <c r="G18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|3@@</f>
+        <v/>
+      </c>
+      <c r="H18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|4@@</f>
+        <v/>
+      </c>
+      <c r="I18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|5@@</f>
+        <v/>
+      </c>
+      <c r="J18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|6@@</f>
+        <v/>
+      </c>
+      <c r="K18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|7@@</f>
+        <v/>
+      </c>
+      <c r="L18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|8@@</f>
+        <v/>
+      </c>
+      <c r="M18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|9@@</f>
+        <v/>
+      </c>
+      <c r="N18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|10@@</f>
+        <v/>
+      </c>
+      <c r="O18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|11@@</f>
+        <v/>
+      </c>
+      <c r="P18" s="14">
+        <f>@@ENG_FCF|FCF.fcff|12@@</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ارزش فعلی FCFF</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>DCF.pv</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D19" s="14">
+        <f>'ENG_DCF'!$D$18*'ENG_DCF'!$D$15</f>
+        <v/>
+      </c>
+      <c r="E19" s="14">
+        <f>'ENG_DCF'!$E$18*'ENG_DCF'!$E$15</f>
+        <v/>
+      </c>
+      <c r="F19" s="14">
+        <f>'ENG_DCF'!$F$18*'ENG_DCF'!$F$15</f>
+        <v/>
+      </c>
+      <c r="G19" s="14">
+        <f>'ENG_DCF'!$G$18*'ENG_DCF'!$G$15</f>
+        <v/>
+      </c>
+      <c r="H19" s="14">
+        <f>'ENG_DCF'!$H$18*'ENG_DCF'!$H$15</f>
+        <v/>
+      </c>
+      <c r="I19" s="14">
+        <f>'ENG_DCF'!$I$18*'ENG_DCF'!$I$15</f>
+        <v/>
+      </c>
+      <c r="J19" s="14">
+        <f>'ENG_DCF'!$J$18*'ENG_DCF'!$J$15</f>
+        <v/>
+      </c>
+      <c r="K19" s="14">
+        <f>'ENG_DCF'!$K$18*'ENG_DCF'!$K$15</f>
+        <v/>
+      </c>
+      <c r="L19" s="14">
+        <f>'ENG_DCF'!$L$18*'ENG_DCF'!$L$15</f>
+        <v/>
+      </c>
+      <c r="M19" s="14">
+        <f>'ENG_DCF'!$M$18*'ENG_DCF'!$M$15</f>
+        <v/>
+      </c>
+      <c r="N19" s="14">
+        <f>'ENG_DCF'!$N$18*'ENG_DCF'!$N$15</f>
+        <v/>
+      </c>
+      <c r="O19" s="14">
+        <f>'ENG_DCF'!$O$18*'ENG_DCF'!$O$15</f>
+        <v/>
+      </c>
+      <c r="P19" s="14">
+        <f>'ENG_DCF'!$P$18*'ENG_DCF'!$P$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ارزش فعلی تجمعی</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>DCF.pv_cum</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D20" s="14">
+        <f>'ENG_DCF'!$D$19</f>
+        <v/>
+      </c>
+      <c r="E20" s="14">
+        <f>'ENG_DCF'!$D$20+'ENG_DCF'!$E$19</f>
+        <v/>
+      </c>
+      <c r="F20" s="14">
+        <f>'ENG_DCF'!$E$20+'ENG_DCF'!$F$19</f>
+        <v/>
+      </c>
+      <c r="G20" s="14">
+        <f>'ENG_DCF'!$F$20+'ENG_DCF'!$G$19</f>
+        <v/>
+      </c>
+      <c r="H20" s="14">
+        <f>'ENG_DCF'!$G$20+'ENG_DCF'!$H$19</f>
+        <v/>
+      </c>
+      <c r="I20" s="14">
+        <f>'ENG_DCF'!$H$20+'ENG_DCF'!$I$19</f>
+        <v/>
+      </c>
+      <c r="J20" s="14">
+        <f>'ENG_DCF'!$I$20+'ENG_DCF'!$J$19</f>
+        <v/>
+      </c>
+      <c r="K20" s="14">
+        <f>'ENG_DCF'!$J$20+'ENG_DCF'!$K$19</f>
+        <v/>
+      </c>
+      <c r="L20" s="14">
+        <f>'ENG_DCF'!$K$20+'ENG_DCF'!$L$19</f>
+        <v/>
+      </c>
+      <c r="M20" s="14">
+        <f>'ENG_DCF'!$L$20+'ENG_DCF'!$M$19</f>
+        <v/>
+      </c>
+      <c r="N20" s="14">
+        <f>'ENG_DCF'!$M$20+'ENG_DCF'!$N$19</f>
+        <v/>
+      </c>
+      <c r="O20" s="14">
+        <f>'ENG_DCF'!$N$20+'ENG_DCF'!$O$19</f>
+        <v/>
+      </c>
+      <c r="P20" s="14">
+        <f>'ENG_DCF'!$O$20+'ENG_DCF'!$P$19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ارزش پایانی (Terminal Value)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>DCF.tv</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D21" s="14">
+        <f>IF('IN_MACRO'!$D$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+      <c r="E21" s="14">
+        <f>IF('IN_MACRO'!$E$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+      <c r="F21" s="14">
+        <f>IF('IN_MACRO'!$F$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+      <c r="G21" s="14">
+        <f>IF('IN_MACRO'!$G$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+      <c r="H21" s="14">
+        <f>IF('IN_MACRO'!$H$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+      <c r="I21" s="14">
+        <f>IF('IN_MACRO'!$I$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+      <c r="J21" s="14">
+        <f>IF('IN_MACRO'!$J$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+      <c r="K21" s="14">
+        <f>IF('IN_MACRO'!$K$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+      <c r="L21" s="14">
+        <f>IF('IN_MACRO'!$L$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+      <c r="M21" s="14">
+        <f>IF('IN_MACRO'!$M$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+      <c r="N21" s="14">
+        <f>IF('IN_MACRO'!$N$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+      <c r="O21" s="14">
+        <f>IF('IN_MACRO'!$O$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+      <c r="P21" s="14">
+        <f>IF('IN_MACRO'!$P$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ارزش فعلی ارزش پایانی</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>DCF.pv_tv</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D22" s="14">
+        <f>'ENG_DCF'!$D$21*'ENG_DCF'!$D$15</f>
+        <v/>
+      </c>
+      <c r="E22" s="14">
+        <f>'ENG_DCF'!$E$21*'ENG_DCF'!$E$15</f>
+        <v/>
+      </c>
+      <c r="F22" s="14">
+        <f>'ENG_DCF'!$F$21*'ENG_DCF'!$F$15</f>
+        <v/>
+      </c>
+      <c r="G22" s="14">
+        <f>'ENG_DCF'!$G$21*'ENG_DCF'!$G$15</f>
+        <v/>
+      </c>
+      <c r="H22" s="14">
+        <f>'ENG_DCF'!$H$21*'ENG_DCF'!$H$15</f>
+        <v/>
+      </c>
+      <c r="I22" s="14">
+        <f>'ENG_DCF'!$I$21*'ENG_DCF'!$I$15</f>
+        <v/>
+      </c>
+      <c r="J22" s="14">
+        <f>'ENG_DCF'!$J$21*'ENG_DCF'!$J$15</f>
+        <v/>
+      </c>
+      <c r="K22" s="14">
+        <f>'ENG_DCF'!$K$21*'ENG_DCF'!$K$15</f>
+        <v/>
+      </c>
+      <c r="L22" s="14">
+        <f>'ENG_DCF'!$L$21*'ENG_DCF'!$L$15</f>
+        <v/>
+      </c>
+      <c r="M22" s="14">
+        <f>'ENG_DCF'!$M$21*'ENG_DCF'!$M$15</f>
+        <v/>
+      </c>
+      <c r="N22" s="14">
+        <f>'ENG_DCF'!$N$21*'ENG_DCF'!$N$15</f>
+        <v/>
+      </c>
+      <c r="O22" s="14">
+        <f>'ENG_DCF'!$O$21*'ENG_DCF'!$O$15</f>
+        <v/>
+      </c>
+      <c r="P22" s="14">
+        <f>'ENG_DCF'!$P$21*'ENG_DCF'!$P$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>جریان قابل بازدهی (FCFF + ارزش پایانی)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>DCF.fcf_tv</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D23" s="14">
+        <f>'ENG_DCF'!$D$18+'ENG_DCF'!$D$21</f>
+        <v/>
+      </c>
+      <c r="E23" s="14">
+        <f>'ENG_DCF'!$E$18+'ENG_DCF'!$E$21</f>
+        <v/>
+      </c>
+      <c r="F23" s="14">
+        <f>'ENG_DCF'!$F$18+'ENG_DCF'!$F$21</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
+        <f>'ENG_DCF'!$G$18+'ENG_DCF'!$G$21</f>
+        <v/>
+      </c>
+      <c r="H23" s="14">
+        <f>'ENG_DCF'!$H$18+'ENG_DCF'!$H$21</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>'ENG_DCF'!$I$18+'ENG_DCF'!$I$21</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>'ENG_DCF'!$J$18+'ENG_DCF'!$J$21</f>
+        <v/>
+      </c>
+      <c r="K23" s="14">
+        <f>'ENG_DCF'!$K$18+'ENG_DCF'!$K$21</f>
+        <v/>
+      </c>
+      <c r="L23" s="14">
+        <f>'ENG_DCF'!$L$18+'ENG_DCF'!$L$21</f>
+        <v/>
+      </c>
+      <c r="M23" s="14">
+        <f>'ENG_DCF'!$M$18+'ENG_DCF'!$M$21</f>
+        <v/>
+      </c>
+      <c r="N23" s="14">
+        <f>'ENG_DCF'!$N$18+'ENG_DCF'!$N$21</f>
+        <v/>
+      </c>
+      <c r="O23" s="14">
+        <f>'ENG_DCF'!$O$18+'ENG_DCF'!$O$21</f>
+        <v/>
+      </c>
+      <c r="P23" s="14">
+        <f>'ENG_DCF'!$P$18+'ENG_DCF'!$P$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>ج) شاخص‌های ارزش‌گذاری</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="7" t="n"/>
+      <c r="O25" s="7" t="n"/>
+      <c r="P25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ارزش فعلی خالص (NPV)</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D26" s="14">
+        <f>SUM('ENG_DCF'!$D$19:$P$19)+SUM('ENG_DCF'!$D$22:$P$22)</f>
+        <v/>
+      </c>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="14" t="n"/>
+      <c r="I26" s="14" t="n"/>
+      <c r="J26" s="14" t="n"/>
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="14" t="n"/>
+      <c r="M26" s="14" t="n"/>
+      <c r="N26" s="14" t="n"/>
+      <c r="O26" s="14" t="n"/>
+      <c r="P26" s="14" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>نرخ بازده داخلی پروژه (IRR)</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D27" s="11">
+        <f>IFERROR(IRR('ENG_DCF'!$D$23:$P$23),NA())</f>
+        <v/>
+      </c>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="11" t="n"/>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="11" t="n"/>
+      <c r="N27" s="11" t="n"/>
+      <c r="O27" s="11" t="n"/>
+      <c r="P27" s="11" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>نرخ بازده داخلی تعدیل‌شده (MIRR)</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D28" s="11">
+        <f>IFERROR(MIRR('ENG_DCF'!$D$23:$P$23,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),AVERAGE('ENG_DCF'!$D$14:$P$14)),NA())</f>
+        <v/>
+      </c>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="11" t="n"/>
+      <c r="K28" s="11" t="n"/>
+      <c r="L28" s="11" t="n"/>
+      <c r="M28" s="11" t="n"/>
+      <c r="N28" s="11" t="n"/>
+      <c r="O28" s="11" t="n"/>
+      <c r="P28" s="11" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>نرخ بازده داخلی سهامداران (IRR روی FCFE)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D29" s="11">
+        <f>IFERROR(IRR(@@ENG_FCF|FCF.fcfe|0@@:@@ENG_FCF|FCF.fcfe|12@@),NA())</f>
+        <v/>
+      </c>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="11" t="n"/>
+      <c r="N29" s="11" t="n"/>
+      <c r="O29" s="11" t="n"/>
+      <c r="P29" s="11" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>دوره بازپرداشت ساده (سال)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>سال</t>
+        </is>
+      </c>
+      <c r="D30" s="13">
+        <f>IF(COUNTIF(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,"&lt;0")=0,0,IF(COUNTIF(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,"&lt;0")&gt;=13,NA(),INDEX('IN_MACRO'!$D$23:$P$23,COUNTIF(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,"&lt;0"))+(0-INDEX(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,COUNTIF(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,"&lt;0")))/(INDEX(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,COUNTIF(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,"&lt;0")+1)-INDEX(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,COUNTIF(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,"&lt;0")))))</f>
+        <v/>
+      </c>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="13" t="n"/>
+      <c r="J30" s="13" t="n"/>
+      <c r="K30" s="13" t="n"/>
+      <c r="L30" s="13" t="n"/>
+      <c r="M30" s="13" t="n"/>
+      <c r="N30" s="13" t="n"/>
+      <c r="O30" s="13" t="n"/>
+      <c r="P30" s="13" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>دوره بازپرداشت تنزیلی (سال)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>سال</t>
+        </is>
+      </c>
+      <c r="D31" s="13">
+        <f>IF(COUNTIF('ENG_DCF'!$D$20:$P$20,"&lt;0")=0,0,IF(COUNTIF('ENG_DCF'!$D$20:$P$20,"&lt;0")&gt;=13,NA(),INDEX('IN_MACRO'!$D$23:$P$23,COUNTIF('ENG_DCF'!$D$20:$P$20,"&lt;0"))+(0-INDEX('ENG_DCF'!$D$20:$P$20,COUNTIF('ENG_DCF'!$D$20:$P$20,"&lt;0")))/(INDEX('ENG_DCF'!$D$20:$P$20,COUNTIF('ENG_DCF'!$D$20:$P$20,"&lt;0")+1)-INDEX('ENG_DCF'!$D$20:$P$20,COUNTIF('ENG_DCF'!$D$20:$P$20,"&lt;0")))))</f>
+        <v/>
+      </c>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="13" t="n"/>
+      <c r="I31" s="13" t="n"/>
+      <c r="J31" s="13" t="n"/>
+      <c r="K31" s="13" t="n"/>
+      <c r="L31" s="13" t="n"/>
+      <c r="M31" s="13" t="n"/>
+      <c r="N31" s="13" t="n"/>
+      <c r="O31" s="13" t="n"/>
+      <c r="P31" s="13" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>شاخص سودآوری (PI)</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>ضریب</t>
+        </is>
+      </c>
+      <c r="D32" s="12">
+        <f>IFERROR((SUMIF('ENG_DCF'!$D$19:$P$19,"&gt;0")+SUM('ENG_DCF'!$D$22:$P$22))/ABS(SUMIF('ENG_DCF'!$D$19:$P$19,"&lt;0")),NA())</f>
+        <v/>
+      </c>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="12" t="n"/>
+      <c r="P32" s="12" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ارزش بنگاه (EV) - ارزش فعلی عملیات</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D33" s="14">
+        <f>SUM('ENG_DCF'!$D$19:$P$19)-'ENG_DCF'!$D$19+SUM('ENG_DCF'!$D$22:$P$22)</f>
+        <v/>
+      </c>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="n"/>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="14" t="n"/>
+      <c r="L33" s="14" t="n"/>
+      <c r="M33" s="14" t="n"/>
+      <c r="N33" s="14" t="n"/>
+      <c r="O33" s="14" t="n"/>
+      <c r="P33" s="14" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ارزش حقوق صاحبان سهام (EV − بدهی خالص)</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>DCF.eq_value</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|0@@-@@ENG_FCF|FCF.cash|0@@)</f>
+        <v/>
+      </c>
+      <c r="E34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|1@@-@@ENG_FCF|FCF.cash|1@@)</f>
+        <v/>
+      </c>
+      <c r="F34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|2@@-@@ENG_FCF|FCF.cash|2@@)</f>
+        <v/>
+      </c>
+      <c r="G34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|3@@-@@ENG_FCF|FCF.cash|3@@)</f>
+        <v/>
+      </c>
+      <c r="H34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|4@@-@@ENG_FCF|FCF.cash|4@@)</f>
+        <v/>
+      </c>
+      <c r="I34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|5@@-@@ENG_FCF|FCF.cash|5@@)</f>
+        <v/>
+      </c>
+      <c r="J34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|6@@-@@ENG_FCF|FCF.cash|6@@)</f>
+        <v/>
+      </c>
+      <c r="K34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|7@@-@@ENG_FCF|FCF.cash|7@@)</f>
+        <v/>
+      </c>
+      <c r="L34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|8@@-@@ENG_FCF|FCF.cash|8@@)</f>
+        <v/>
+      </c>
+      <c r="M34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|9@@-@@ENG_FCF|FCF.cash|9@@)</f>
+        <v/>
+      </c>
+      <c r="N34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|10@@-@@ENG_FCF|FCF.cash|10@@)</f>
+        <v/>
+      </c>
+      <c r="O34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|11@@-@@ENG_FCF|FCF.cash|11@@)</f>
+        <v/>
+      </c>
+      <c r="P34" s="14">
+        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|12@@-@@ENG_FCF|FCF.cash|12@@)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>تحلیل اهرم عملیاتی و مالی</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>موتور محاسبات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>درجه اهرم عملیاتی و مالی، نقطه سر‌به‌سر و اثر تغییر حجم فروش و ساختار سرمایه بر سودآوری.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>دوره (t)</t>
+        </is>
+      </c>
+      <c r="D7" s="5">
+        <f>'IN_MACRO'!D$23</f>
+        <v/>
+      </c>
+      <c r="E7" s="5">
+        <f>'IN_MACRO'!E$23</f>
+        <v/>
+      </c>
+      <c r="F7" s="5">
+        <f>'IN_MACRO'!F$23</f>
+        <v/>
+      </c>
+      <c r="G7" s="5">
+        <f>'IN_MACRO'!G$23</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
+        <f>'IN_MACRO'!H$23</f>
+        <v/>
+      </c>
+      <c r="I7" s="5">
+        <f>'IN_MACRO'!I$23</f>
+        <v/>
+      </c>
+      <c r="J7" s="5">
+        <f>'IN_MACRO'!J$23</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
+        <f>'IN_MACRO'!K$23</f>
+        <v/>
+      </c>
+      <c r="L7" s="5">
+        <f>'IN_MACRO'!L$23</f>
+        <v/>
+      </c>
+      <c r="M7" s="5">
+        <f>'IN_MACRO'!M$23</f>
+        <v/>
+      </c>
+      <c r="N7" s="5">
+        <f>'IN_MACRO'!N$23</f>
+        <v/>
+      </c>
+      <c r="O7" s="5">
+        <f>'IN_MACRO'!O$23</f>
+        <v/>
+      </c>
+      <c r="P7" s="5">
+        <f>'IN_MACRO'!P$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>سال تقویمی</t>
+        </is>
+      </c>
+      <c r="D8" s="5">
+        <f>'IN_MACRO'!D$24</f>
+        <v/>
+      </c>
+      <c r="E8" s="5">
+        <f>'IN_MACRO'!E$24</f>
+        <v/>
+      </c>
+      <c r="F8" s="5">
+        <f>'IN_MACRO'!F$24</f>
+        <v/>
+      </c>
+      <c r="G8" s="5">
+        <f>'IN_MACRO'!G$24</f>
+        <v/>
+      </c>
+      <c r="H8" s="5">
+        <f>'IN_MACRO'!H$24</f>
+        <v/>
+      </c>
+      <c r="I8" s="5">
+        <f>'IN_MACRO'!I$24</f>
+        <v/>
+      </c>
+      <c r="J8" s="5">
+        <f>'IN_MACRO'!J$24</f>
+        <v/>
+      </c>
+      <c r="K8" s="5">
+        <f>'IN_MACRO'!K$24</f>
+        <v/>
+      </c>
+      <c r="L8" s="5">
+        <f>'IN_MACRO'!L$24</f>
+        <v/>
+      </c>
+      <c r="M8" s="5">
+        <f>'IN_MACRO'!M$24</f>
+        <v/>
+      </c>
+      <c r="N8" s="5">
+        <f>'IN_MACRO'!N$24</f>
+        <v/>
+      </c>
+      <c r="O8" s="5">
+        <f>'IN_MACRO'!O$24</f>
+        <v/>
+      </c>
+      <c r="P8" s="5">
+        <f>'IN_MACRO'!P$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>الف) حاشیه مشارکت و نقطه سر‌به‌سر</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
+      <c r="P9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>درآمد خالص</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>LEV.rev</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D10" s="14">
+        <f>@@ENG_FCF|FCF.rev|0@@</f>
+        <v/>
+      </c>
+      <c r="E10" s="14">
+        <f>@@ENG_FCF|FCF.rev|1@@</f>
+        <v/>
+      </c>
+      <c r="F10" s="14">
+        <f>@@ENG_FCF|FCF.rev|2@@</f>
+        <v/>
+      </c>
+      <c r="G10" s="14">
+        <f>@@ENG_FCF|FCF.rev|3@@</f>
+        <v/>
+      </c>
+      <c r="H10" s="14">
+        <f>@@ENG_FCF|FCF.rev|4@@</f>
+        <v/>
+      </c>
+      <c r="I10" s="14">
+        <f>@@ENG_FCF|FCF.rev|5@@</f>
+        <v/>
+      </c>
+      <c r="J10" s="14">
+        <f>@@ENG_FCF|FCF.rev|6@@</f>
+        <v/>
+      </c>
+      <c r="K10" s="14">
+        <f>@@ENG_FCF|FCF.rev|7@@</f>
+        <v/>
+      </c>
+      <c r="L10" s="14">
+        <f>@@ENG_FCF|FCF.rev|8@@</f>
+        <v/>
+      </c>
+      <c r="M10" s="14">
+        <f>@@ENG_FCF|FCF.rev|9@@</f>
+        <v/>
+      </c>
+      <c r="N10" s="14">
+        <f>@@ENG_FCF|FCF.rev|10@@</f>
+        <v/>
+      </c>
+      <c r="O10" s="14">
+        <f>@@ENG_FCF|FCF.rev|11@@</f>
+        <v/>
+      </c>
+      <c r="P10" s="14">
+        <f>@@ENG_FCF|FCF.rev|12@@</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>هزینه‌های متغیر</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>LEV.var</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D11" s="14">
+        <f>@@ENG_COST|EC.var_total|0@@</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>@@ENG_COST|EC.var_total|1@@</f>
+        <v/>
+      </c>
+      <c r="F11" s="14">
+        <f>@@ENG_COST|EC.var_total|2@@</f>
+        <v/>
+      </c>
+      <c r="G11" s="14">
+        <f>@@ENG_COST|EC.var_total|3@@</f>
+        <v/>
+      </c>
+      <c r="H11" s="14">
+        <f>@@ENG_COST|EC.var_total|4@@</f>
+        <v/>
+      </c>
+      <c r="I11" s="14">
+        <f>@@ENG_COST|EC.var_total|5@@</f>
+        <v/>
+      </c>
+      <c r="J11" s="14">
+        <f>@@ENG_COST|EC.var_total|6@@</f>
+        <v/>
+      </c>
+      <c r="K11" s="14">
+        <f>@@ENG_COST|EC.var_total|7@@</f>
+        <v/>
+      </c>
+      <c r="L11" s="14">
+        <f>@@ENG_COST|EC.var_total|8@@</f>
+        <v/>
+      </c>
+      <c r="M11" s="14">
+        <f>@@ENG_COST|EC.var_total|9@@</f>
+        <v/>
+      </c>
+      <c r="N11" s="14">
+        <f>@@ENG_COST|EC.var_total|10@@</f>
+        <v/>
+      </c>
+      <c r="O11" s="14">
+        <f>@@ENG_COST|EC.var_total|11@@</f>
+        <v/>
+      </c>
+      <c r="P11" s="14">
+        <f>@@ENG_COST|EC.var_total|12@@</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>حاشیه مشارکت</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>LEV.cm</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D12" s="14">
+        <f>'ENG_LEV'!$D$10-'ENG_LEV'!$D$11</f>
+        <v/>
+      </c>
+      <c r="E12" s="14">
+        <f>'ENG_LEV'!$E$10-'ENG_LEV'!$E$11</f>
+        <v/>
+      </c>
+      <c r="F12" s="14">
+        <f>'ENG_LEV'!$F$10-'ENG_LEV'!$F$11</f>
+        <v/>
+      </c>
+      <c r="G12" s="14">
+        <f>'ENG_LEV'!$G$10-'ENG_LEV'!$G$11</f>
+        <v/>
+      </c>
+      <c r="H12" s="14">
+        <f>'ENG_LEV'!$H$10-'ENG_LEV'!$H$11</f>
+        <v/>
+      </c>
+      <c r="I12" s="14">
+        <f>'ENG_LEV'!$I$10-'ENG_LEV'!$I$11</f>
+        <v/>
+      </c>
+      <c r="J12" s="14">
+        <f>'ENG_LEV'!$J$10-'ENG_LEV'!$J$11</f>
+        <v/>
+      </c>
+      <c r="K12" s="14">
+        <f>'ENG_LEV'!$K$10-'ENG_LEV'!$K$11</f>
+        <v/>
+      </c>
+      <c r="L12" s="14">
+        <f>'ENG_LEV'!$L$10-'ENG_LEV'!$L$11</f>
+        <v/>
+      </c>
+      <c r="M12" s="14">
+        <f>'ENG_LEV'!$M$10-'ENG_LEV'!$M$11</f>
+        <v/>
+      </c>
+      <c r="N12" s="14">
+        <f>'ENG_LEV'!$N$10-'ENG_LEV'!$N$11</f>
+        <v/>
+      </c>
+      <c r="O12" s="14">
+        <f>'ENG_LEV'!$O$10-'ENG_LEV'!$O$11</f>
+        <v/>
+      </c>
+      <c r="P12" s="14">
+        <f>'ENG_LEV'!$P$10-'ENG_LEV'!$P$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>نسبت حاشیه مشارکت</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>LEV.cm_ratio</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D13" s="11">
+        <f>IFERROR('ENG_LEV'!$D$12/'ENG_LEV'!$D$10,0)</f>
+        <v/>
+      </c>
+      <c r="E13" s="11">
+        <f>IFERROR('ENG_LEV'!$E$12/'ENG_LEV'!$E$10,0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="11">
+        <f>IFERROR('ENG_LEV'!$F$12/'ENG_LEV'!$F$10,0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>IFERROR('ENG_LEV'!$G$12/'ENG_LEV'!$G$10,0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="11">
+        <f>IFERROR('ENG_LEV'!$H$12/'ENG_LEV'!$H$10,0)</f>
+        <v/>
+      </c>
+      <c r="I13" s="11">
+        <f>IFERROR('ENG_LEV'!$I$12/'ENG_LEV'!$I$10,0)</f>
+        <v/>
+      </c>
+      <c r="J13" s="11">
+        <f>IFERROR('ENG_LEV'!$J$12/'ENG_LEV'!$J$10,0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="11">
+        <f>IFERROR('ENG_LEV'!$K$12/'ENG_LEV'!$K$10,0)</f>
+        <v/>
+      </c>
+      <c r="L13" s="11">
+        <f>IFERROR('ENG_LEV'!$L$12/'ENG_LEV'!$L$10,0)</f>
+        <v/>
+      </c>
+      <c r="M13" s="11">
+        <f>IFERROR('ENG_LEV'!$M$12/'ENG_LEV'!$M$10,0)</f>
+        <v/>
+      </c>
+      <c r="N13" s="11">
+        <f>IFERROR('ENG_LEV'!$N$12/'ENG_LEV'!$N$10,0)</f>
+        <v/>
+      </c>
+      <c r="O13" s="11">
+        <f>IFERROR('ENG_LEV'!$O$12/'ENG_LEV'!$O$10,0)</f>
+        <v/>
+      </c>
+      <c r="P13" s="11">
+        <f>IFERROR('ENG_LEV'!$P$12/'ENG_LEV'!$P$10,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>حاشیه مشارکت هر تن</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>LEV.cm_ton</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال/تن</t>
+        </is>
+      </c>
+      <c r="D14" s="13">
+        <f>IFERROR('ENG_LEV'!$D$12/'ENG_OPS'!$D$82,0)</f>
+        <v/>
+      </c>
+      <c r="E14" s="13">
+        <f>IFERROR('ENG_LEV'!$E$12/'ENG_OPS'!$E$82,0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="13">
+        <f>IFERROR('ENG_LEV'!$F$12/'ENG_OPS'!$F$82,0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="13">
+        <f>IFERROR('ENG_LEV'!$G$12/'ENG_OPS'!$G$82,0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="13">
+        <f>IFERROR('ENG_LEV'!$H$12/'ENG_OPS'!$H$82,0)</f>
+        <v/>
+      </c>
+      <c r="I14" s="13">
+        <f>IFERROR('ENG_LEV'!$I$12/'ENG_OPS'!$I$82,0)</f>
+        <v/>
+      </c>
+      <c r="J14" s="13">
+        <f>IFERROR('ENG_LEV'!$J$12/'ENG_OPS'!$J$82,0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="13">
+        <f>IFERROR('ENG_LEV'!$K$12/'ENG_OPS'!$K$82,0)</f>
+        <v/>
+      </c>
+      <c r="L14" s="13">
+        <f>IFERROR('ENG_LEV'!$L$12/'ENG_OPS'!$L$82,0)</f>
+        <v/>
+      </c>
+      <c r="M14" s="13">
+        <f>IFERROR('ENG_LEV'!$M$12/'ENG_OPS'!$M$82,0)</f>
+        <v/>
+      </c>
+      <c r="N14" s="13">
+        <f>IFERROR('ENG_LEV'!$N$12/'ENG_OPS'!$N$82,0)</f>
+        <v/>
+      </c>
+      <c r="O14" s="13">
+        <f>IFERROR('ENG_LEV'!$O$12/'ENG_OPS'!$O$82,0)</f>
+        <v/>
+      </c>
+      <c r="P14" s="13">
+        <f>IFERROR('ENG_LEV'!$P$12/'ENG_OPS'!$P$82,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>هزینه ثابت نقدی</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>LEV.fixed_cash</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|0@@</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|1@@</f>
+        <v/>
+      </c>
+      <c r="F15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|2@@</f>
+        <v/>
+      </c>
+      <c r="G15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|3@@</f>
+        <v/>
+      </c>
+      <c r="H15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|4@@</f>
+        <v/>
+      </c>
+      <c r="I15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|5@@</f>
+        <v/>
+      </c>
+      <c r="J15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|6@@</f>
+        <v/>
+      </c>
+      <c r="K15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|7@@</f>
+        <v/>
+      </c>
+      <c r="L15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|8@@</f>
+        <v/>
+      </c>
+      <c r="M15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|9@@</f>
+        <v/>
+      </c>
+      <c r="N15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|10@@</f>
+        <v/>
+      </c>
+      <c r="O15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|11@@</f>
+        <v/>
+      </c>
+      <c r="P15" s="14">
+        <f>@@ENG_COST|EC.fixed_cash|12@@</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>نقطه سر‌به‌سر (تن محصول)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>LEV.be_ton</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>تن</t>
+        </is>
+      </c>
+      <c r="D16" s="14">
+        <f>IFERROR('ENG_LEV'!$D$15/'ENG_LEV'!$D$14,0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="14">
+        <f>IFERROR('ENG_LEV'!$E$15/'ENG_LEV'!$E$14,0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="14">
+        <f>IFERROR('ENG_LEV'!$F$15/'ENG_LEV'!$F$14,0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="14">
+        <f>IFERROR('ENG_LEV'!$G$15/'ENG_LEV'!$G$14,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="14">
+        <f>IFERROR('ENG_LEV'!$H$15/'ENG_LEV'!$H$14,0)</f>
+        <v/>
+      </c>
+      <c r="I16" s="14">
+        <f>IFERROR('ENG_LEV'!$I$15/'ENG_LEV'!$I$14,0)</f>
+        <v/>
+      </c>
+      <c r="J16" s="14">
+        <f>IFERROR('ENG_LEV'!$J$15/'ENG_LEV'!$J$14,0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="14">
+        <f>IFERROR('ENG_LEV'!$K$15/'ENG_LEV'!$K$14,0)</f>
+        <v/>
+      </c>
+      <c r="L16" s="14">
+        <f>IFERROR('ENG_LEV'!$L$15/'ENG_LEV'!$L$14,0)</f>
+        <v/>
+      </c>
+      <c r="M16" s="14">
+        <f>IFERROR('ENG_LEV'!$M$15/'ENG_LEV'!$M$14,0)</f>
+        <v/>
+      </c>
+      <c r="N16" s="14">
+        <f>IFERROR('ENG_LEV'!$N$15/'ENG_LEV'!$N$14,0)</f>
+        <v/>
+      </c>
+      <c r="O16" s="14">
+        <f>IFERROR('ENG_LEV'!$O$15/'ENG_LEV'!$O$14,0)</f>
+        <v/>
+      </c>
+      <c r="P16" s="14">
+        <f>IFERROR('ENG_LEV'!$P$15/'ENG_LEV'!$P$14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>نقطه سر‌به‌سر (تن باتری ورودی)</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>LEV.be_input</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>تن</t>
+        </is>
+      </c>
+      <c r="D17" s="14">
+        <f>IFERROR('ENG_LEV'!$D$16/'ENG_OPS'!$D$82*'ENG_OPS'!$D$20,0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="14">
+        <f>IFERROR('ENG_LEV'!$E$16/'ENG_OPS'!$E$82*'ENG_OPS'!$E$20,0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="14">
+        <f>IFERROR('ENG_LEV'!$F$16/'ENG_OPS'!$F$82*'ENG_OPS'!$F$20,0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="14">
+        <f>IFERROR('ENG_LEV'!$G$16/'ENG_OPS'!$G$82*'ENG_OPS'!$G$20,0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="14">
+        <f>IFERROR('ENG_LEV'!$H$16/'ENG_OPS'!$H$82*'ENG_OPS'!$H$20,0)</f>
+        <v/>
+      </c>
+      <c r="I17" s="14">
+        <f>IFERROR('ENG_LEV'!$I$16/'ENG_OPS'!$I$82*'ENG_OPS'!$I$20,0)</f>
+        <v/>
+      </c>
+      <c r="J17" s="14">
+        <f>IFERROR('ENG_LEV'!$J$16/'ENG_OPS'!$J$82*'ENG_OPS'!$J$20,0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="14">
+        <f>IFERROR('ENG_LEV'!$K$16/'ENG_OPS'!$K$82*'ENG_OPS'!$K$20,0)</f>
+        <v/>
+      </c>
+      <c r="L17" s="14">
+        <f>IFERROR('ENG_LEV'!$L$16/'ENG_OPS'!$L$82*'ENG_OPS'!$L$20,0)</f>
+        <v/>
+      </c>
+      <c r="M17" s="14">
+        <f>IFERROR('ENG_LEV'!$M$16/'ENG_OPS'!$M$82*'ENG_OPS'!$M$20,0)</f>
+        <v/>
+      </c>
+      <c r="N17" s="14">
+        <f>IFERROR('ENG_LEV'!$N$16/'ENG_OPS'!$N$82*'ENG_OPS'!$N$20,0)</f>
+        <v/>
+      </c>
+      <c r="O17" s="14">
+        <f>IFERROR('ENG_LEV'!$O$16/'ENG_OPS'!$O$82*'ENG_OPS'!$O$20,0)</f>
+        <v/>
+      </c>
+      <c r="P17" s="14">
+        <f>IFERROR('ENG_LEV'!$P$16/'ENG_OPS'!$P$82*'ENG_OPS'!$P$20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>حاشیه ایمنی</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>LEV.mos</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$D$16/'ENG_OPS'!$D$82,0)</f>
+        <v/>
+      </c>
+      <c r="E18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$E$16/'ENG_OPS'!$E$82,0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$F$16/'ENG_OPS'!$F$82,0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$G$16/'ENG_OPS'!$G$82,0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$H$16/'ENG_OPS'!$H$82,0)</f>
+        <v/>
+      </c>
+      <c r="I18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$I$16/'ENG_OPS'!$I$82,0)</f>
+        <v/>
+      </c>
+      <c r="J18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$J$16/'ENG_OPS'!$J$82,0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$K$16/'ENG_OPS'!$K$82,0)</f>
+        <v/>
+      </c>
+      <c r="L18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$L$16/'ENG_OPS'!$L$82,0)</f>
+        <v/>
+      </c>
+      <c r="M18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$M$16/'ENG_OPS'!$M$82,0)</f>
+        <v/>
+      </c>
+      <c r="N18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$N$16/'ENG_OPS'!$N$82,0)</f>
+        <v/>
+      </c>
+      <c r="O18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$O$16/'ENG_OPS'!$O$82,0)</f>
+        <v/>
+      </c>
+      <c r="P18" s="11">
+        <f>IFERROR(1-'ENG_LEV'!$P$16/'ENG_OPS'!$P$82,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>ب) درجات اهرم</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="7" t="n"/>
+      <c r="O20" s="7" t="n"/>
+      <c r="P20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>درجه اهرم عملیاتی (DOL)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>LEV.dol</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ضریب</t>
+        </is>
+      </c>
+      <c r="D21" s="12">
+        <f>IFERROR('ENG_LEV'!$D$12/@@ENG_FCF|FCF.ebit|0@@,0)</f>
+        <v/>
+      </c>
+      <c r="E21" s="12">
+        <f>IFERROR('ENG_LEV'!$E$12/@@ENG_FCF|FCF.ebit|1@@,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="12">
+        <f>IFERROR('ENG_LEV'!$F$12/@@ENG_FCF|FCF.ebit|2@@,0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="12">
+        <f>IFERROR('ENG_LEV'!$G$12/@@ENG_FCF|FCF.ebit|3@@,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="12">
+        <f>IFERROR('ENG_LEV'!$H$12/@@ENG_FCF|FCF.ebit|4@@,0)</f>
+        <v/>
+      </c>
+      <c r="I21" s="12">
+        <f>IFERROR('ENG_LEV'!$I$12/@@ENG_FCF|FCF.ebit|5@@,0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="12">
+        <f>IFERROR('ENG_LEV'!$J$12/@@ENG_FCF|FCF.ebit|6@@,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="12">
+        <f>IFERROR('ENG_LEV'!$K$12/@@ENG_FCF|FCF.ebit|7@@,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="12">
+        <f>IFERROR('ENG_LEV'!$L$12/@@ENG_FCF|FCF.ebit|8@@,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="12">
+        <f>IFERROR('ENG_LEV'!$M$12/@@ENG_FCF|FCF.ebit|9@@,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="12">
+        <f>IFERROR('ENG_LEV'!$N$12/@@ENG_FCF|FCF.ebit|10@@,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="12">
+        <f>IFERROR('ENG_LEV'!$O$12/@@ENG_FCF|FCF.ebit|11@@,0)</f>
+        <v/>
+      </c>
+      <c r="P21" s="12">
+        <f>IFERROR('ENG_LEV'!$P$12/@@ENG_FCF|FCF.ebit|12@@,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>درجه اهرم مالی (DFL)</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>LEV.dfl</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ضریب</t>
+        </is>
+      </c>
+      <c r="D22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|0@@/@@ENG_FCF|FCF.ebt|0@@,0)</f>
+        <v/>
+      </c>
+      <c r="E22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|1@@/@@ENG_FCF|FCF.ebt|1@@,0)</f>
+        <v/>
+      </c>
+      <c r="F22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|2@@/@@ENG_FCF|FCF.ebt|2@@,0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|3@@/@@ENG_FCF|FCF.ebt|3@@,0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|4@@/@@ENG_FCF|FCF.ebt|4@@,0)</f>
+        <v/>
+      </c>
+      <c r="I22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|5@@/@@ENG_FCF|FCF.ebt|5@@,0)</f>
+        <v/>
+      </c>
+      <c r="J22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|6@@/@@ENG_FCF|FCF.ebt|6@@,0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|7@@/@@ENG_FCF|FCF.ebt|7@@,0)</f>
+        <v/>
+      </c>
+      <c r="L22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|8@@/@@ENG_FCF|FCF.ebt|8@@,0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|9@@/@@ENG_FCF|FCF.ebt|9@@,0)</f>
+        <v/>
+      </c>
+      <c r="N22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|10@@/@@ENG_FCF|FCF.ebt|10@@,0)</f>
+        <v/>
+      </c>
+      <c r="O22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|11@@/@@ENG_FCF|FCF.ebt|11@@,0)</f>
+        <v/>
+      </c>
+      <c r="P22" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ebit|12@@/@@ENG_FCF|FCF.ebt|12@@,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>درجه اهرم ترکیبی (DTL)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>LEV.dtl</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ضریب</t>
+        </is>
+      </c>
+      <c r="D23" s="12">
+        <f>'ENG_LEV'!$D$21*'ENG_LEV'!$D$22</f>
+        <v/>
+      </c>
+      <c r="E23" s="12">
+        <f>'ENG_LEV'!$E$21*'ENG_LEV'!$E$22</f>
+        <v/>
+      </c>
+      <c r="F23" s="12">
+        <f>'ENG_LEV'!$F$21*'ENG_LEV'!$F$22</f>
+        <v/>
+      </c>
+      <c r="G23" s="12">
+        <f>'ENG_LEV'!$G$21*'ENG_LEV'!$G$22</f>
+        <v/>
+      </c>
+      <c r="H23" s="12">
+        <f>'ENG_LEV'!$H$21*'ENG_LEV'!$H$22</f>
+        <v/>
+      </c>
+      <c r="I23" s="12">
+        <f>'ENG_LEV'!$I$21*'ENG_LEV'!$I$22</f>
+        <v/>
+      </c>
+      <c r="J23" s="12">
+        <f>'ENG_LEV'!$J$21*'ENG_LEV'!$J$22</f>
+        <v/>
+      </c>
+      <c r="K23" s="12">
+        <f>'ENG_LEV'!$K$21*'ENG_LEV'!$K$22</f>
+        <v/>
+      </c>
+      <c r="L23" s="12">
+        <f>'ENG_LEV'!$L$21*'ENG_LEV'!$L$22</f>
+        <v/>
+      </c>
+      <c r="M23" s="12">
+        <f>'ENG_LEV'!$M$21*'ENG_LEV'!$M$22</f>
+        <v/>
+      </c>
+      <c r="N23" s="12">
+        <f>'ENG_LEV'!$N$21*'ENG_LEV'!$N$22</f>
+        <v/>
+      </c>
+      <c r="O23" s="12">
+        <f>'ENG_LEV'!$O$21*'ENG_LEV'!$O$22</f>
+        <v/>
+      </c>
+      <c r="P23" s="12">
+        <f>'ENG_LEV'!$P$21*'ENG_LEV'!$P$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>تغییر سود خالص به ازای ۱٪ تغییر فروش</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>LEV.sens_ni</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D24" s="11">
+        <f>'ENG_LEV'!$D$23</f>
+        <v/>
+      </c>
+      <c r="E24" s="11">
+        <f>'ENG_LEV'!$E$23</f>
+        <v/>
+      </c>
+      <c r="F24" s="11">
+        <f>'ENG_LEV'!$F$23</f>
+        <v/>
+      </c>
+      <c r="G24" s="11">
+        <f>'ENG_LEV'!$G$23</f>
+        <v/>
+      </c>
+      <c r="H24" s="11">
+        <f>'ENG_LEV'!$H$23</f>
+        <v/>
+      </c>
+      <c r="I24" s="11">
+        <f>'ENG_LEV'!$I$23</f>
+        <v/>
+      </c>
+      <c r="J24" s="11">
+        <f>'ENG_LEV'!$J$23</f>
+        <v/>
+      </c>
+      <c r="K24" s="11">
+        <f>'ENG_LEV'!$K$23</f>
+        <v/>
+      </c>
+      <c r="L24" s="11">
+        <f>'ENG_LEV'!$L$23</f>
+        <v/>
+      </c>
+      <c r="M24" s="11">
+        <f>'ENG_LEV'!$M$23</f>
+        <v/>
+      </c>
+      <c r="N24" s="11">
+        <f>'ENG_LEV'!$N$23</f>
+        <v/>
+      </c>
+      <c r="O24" s="11">
+        <f>'ENG_LEV'!$O$23</f>
+        <v/>
+      </c>
+      <c r="P24" s="11">
+        <f>'ENG_LEV'!$P$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>ج) بازدهی و ساختار سرمایه</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="n"/>
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="7" t="n"/>
+      <c r="M26" s="7" t="n"/>
+      <c r="N26" s="7" t="n"/>
+      <c r="O26" s="7" t="n"/>
+      <c r="P26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>بازده حقوق صاحبان سهام (ROE)</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>LEV.roe</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|0@@/@@ENG_FCF|FCF.equity|0@@,0)</f>
+        <v/>
+      </c>
+      <c r="E27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|1@@/@@ENG_FCF|FCF.equity|1@@,0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|2@@/@@ENG_FCF|FCF.equity|2@@,0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|3@@/@@ENG_FCF|FCF.equity|3@@,0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|4@@/@@ENG_FCF|FCF.equity|4@@,0)</f>
+        <v/>
+      </c>
+      <c r="I27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|5@@/@@ENG_FCF|FCF.equity|5@@,0)</f>
+        <v/>
+      </c>
+      <c r="J27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|6@@/@@ENG_FCF|FCF.equity|6@@,0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|7@@/@@ENG_FCF|FCF.equity|7@@,0)</f>
+        <v/>
+      </c>
+      <c r="L27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|8@@/@@ENG_FCF|FCF.equity|8@@,0)</f>
+        <v/>
+      </c>
+      <c r="M27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|9@@/@@ENG_FCF|FCF.equity|9@@,0)</f>
+        <v/>
+      </c>
+      <c r="N27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|10@@/@@ENG_FCF|FCF.equity|10@@,0)</f>
+        <v/>
+      </c>
+      <c r="O27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|11@@/@@ENG_FCF|FCF.equity|11@@,0)</f>
+        <v/>
+      </c>
+      <c r="P27" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|12@@/@@ENG_FCF|FCF.equity|12@@,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>بازده دارایی‌ها (ROA)</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>LEV.roa</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|0@@/@@ENG_FCF|FCF.assets|0@@,0)</f>
+        <v/>
+      </c>
+      <c r="E28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|1@@/@@ENG_FCF|FCF.assets|1@@,0)</f>
+        <v/>
+      </c>
+      <c r="F28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|2@@/@@ENG_FCF|FCF.assets|2@@,0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|3@@/@@ENG_FCF|FCF.assets|3@@,0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|4@@/@@ENG_FCF|FCF.assets|4@@,0)</f>
+        <v/>
+      </c>
+      <c r="I28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|5@@/@@ENG_FCF|FCF.assets|5@@,0)</f>
+        <v/>
+      </c>
+      <c r="J28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|6@@/@@ENG_FCF|FCF.assets|6@@,0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|7@@/@@ENG_FCF|FCF.assets|7@@,0)</f>
+        <v/>
+      </c>
+      <c r="L28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|8@@/@@ENG_FCF|FCF.assets|8@@,0)</f>
+        <v/>
+      </c>
+      <c r="M28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|9@@/@@ENG_FCF|FCF.assets|9@@,0)</f>
+        <v/>
+      </c>
+      <c r="N28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|10@@/@@ENG_FCF|FCF.assets|10@@,0)</f>
+        <v/>
+      </c>
+      <c r="O28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|11@@/@@ENG_FCF|FCF.assets|11@@,0)</f>
+        <v/>
+      </c>
+      <c r="P28" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.ni|12@@/@@ENG_FCF|FCF.assets|12@@,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>بازده سرمایه به‌کارگرفته‌شده (ROIC)</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>LEV.roic</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+      <c r="D29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|0@@/(@@ENG_FCF|FCF.ltd|0@@+@@ENG_FCF|FCF.equity|0@@),0)</f>
+        <v/>
+      </c>
+      <c r="E29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|1@@/(@@ENG_FCF|FCF.ltd|1@@+@@ENG_FCF|FCF.equity|1@@),0)</f>
+        <v/>
+      </c>
+      <c r="F29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|2@@/(@@ENG_FCF|FCF.ltd|2@@+@@ENG_FCF|FCF.equity|2@@),0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|3@@/(@@ENG_FCF|FCF.ltd|3@@+@@ENG_FCF|FCF.equity|3@@),0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|4@@/(@@ENG_FCF|FCF.ltd|4@@+@@ENG_FCF|FCF.equity|4@@),0)</f>
+        <v/>
+      </c>
+      <c r="I29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|5@@/(@@ENG_FCF|FCF.ltd|5@@+@@ENG_FCF|FCF.equity|5@@),0)</f>
+        <v/>
+      </c>
+      <c r="J29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|6@@/(@@ENG_FCF|FCF.ltd|6@@+@@ENG_FCF|FCF.equity|6@@),0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|7@@/(@@ENG_FCF|FCF.ltd|7@@+@@ENG_FCF|FCF.equity|7@@),0)</f>
+        <v/>
+      </c>
+      <c r="L29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|8@@/(@@ENG_FCF|FCF.ltd|8@@+@@ENG_FCF|FCF.equity|8@@),0)</f>
+        <v/>
+      </c>
+      <c r="M29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|9@@/(@@ENG_FCF|FCF.ltd|9@@+@@ENG_FCF|FCF.equity|9@@),0)</f>
+        <v/>
+      </c>
+      <c r="N29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|10@@/(@@ENG_FCF|FCF.ltd|10@@+@@ENG_FCF|FCF.equity|10@@),0)</f>
+        <v/>
+      </c>
+      <c r="O29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|11@@/(@@ENG_FCF|FCF.ltd|11@@+@@ENG_FCF|FCF.equity|11@@),0)</f>
+        <v/>
+      </c>
+      <c r="P29" s="11">
+        <f>IFERROR(@@ENG_FCF|FCF.nopat|12@@/(@@ENG_FCF|FCF.ltd|12@@+@@ENG_FCF|FCF.equity|12@@),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>نسبت بدهی به حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>LEV.de</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>ضریب</t>
+        </is>
+      </c>
+      <c r="D30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|0@@/@@ENG_FCF|FCF.equity|0@@,0)</f>
+        <v/>
+      </c>
+      <c r="E30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|1@@/@@ENG_FCF|FCF.equity|1@@,0)</f>
+        <v/>
+      </c>
+      <c r="F30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|2@@/@@ENG_FCF|FCF.equity|2@@,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|3@@/@@ENG_FCF|FCF.equity|3@@,0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|4@@/@@ENG_FCF|FCF.equity|4@@,0)</f>
+        <v/>
+      </c>
+      <c r="I30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|5@@/@@ENG_FCF|FCF.equity|5@@,0)</f>
+        <v/>
+      </c>
+      <c r="J30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|6@@/@@ENG_FCF|FCF.equity|6@@,0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|7@@/@@ENG_FCF|FCF.equity|7@@,0)</f>
+        <v/>
+      </c>
+      <c r="L30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|8@@/@@ENG_FCF|FCF.equity|8@@,0)</f>
+        <v/>
+      </c>
+      <c r="M30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|9@@/@@ENG_FCF|FCF.equity|9@@,0)</f>
+        <v/>
+      </c>
+      <c r="N30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|10@@/@@ENG_FCF|FCF.equity|10@@,0)</f>
+        <v/>
+      </c>
+      <c r="O30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|11@@/@@ENG_FCF|FCF.equity|11@@,0)</f>
+        <v/>
+      </c>
+      <c r="P30" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|12@@/@@ENG_FCF|FCF.equity|12@@,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>نسبت بدهی به EBITDA</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>LEV.debt_ebitda</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>ضریب</t>
+        </is>
+      </c>
+      <c r="D31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|0@@/@@ENG_FCF|FCF.ebitda|0@@,0)</f>
+        <v/>
+      </c>
+      <c r="E31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|1@@/@@ENG_FCF|FCF.ebitda|1@@,0)</f>
+        <v/>
+      </c>
+      <c r="F31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|2@@/@@ENG_FCF|FCF.ebitda|2@@,0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|3@@/@@ENG_FCF|FCF.ebitda|3@@,0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|4@@/@@ENG_FCF|FCF.ebitda|4@@,0)</f>
+        <v/>
+      </c>
+      <c r="I31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|5@@/@@ENG_FCF|FCF.ebitda|5@@,0)</f>
+        <v/>
+      </c>
+      <c r="J31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|6@@/@@ENG_FCF|FCF.ebitda|6@@,0)</f>
+        <v/>
+      </c>
+      <c r="K31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|7@@/@@ENG_FCF|FCF.ebitda|7@@,0)</f>
+        <v/>
+      </c>
+      <c r="L31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|8@@/@@ENG_FCF|FCF.ebitda|8@@,0)</f>
+        <v/>
+      </c>
+      <c r="M31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|9@@/@@ENG_FCF|FCF.ebitda|9@@,0)</f>
+        <v/>
+      </c>
+      <c r="N31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|10@@/@@ENG_FCF|FCF.ebitda|10@@,0)</f>
+        <v/>
+      </c>
+      <c r="O31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|11@@/@@ENG_FCF|FCF.ebitda|11@@,0)</f>
+        <v/>
+      </c>
+      <c r="P31" s="12">
+        <f>IFERROR(@@ENG_FCF|FCF.ltd|12@@/@@ENG_FCF|FCF.ebitda|12@@,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>بدهی خالص به EBITDA</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>LEV.net_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>ضریب</t>
+        </is>
+      </c>
+      <c r="D32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|0@@-@@ENG_FCF|FCF.cash|0@@)/@@ENG_FCF|FCF.ebitda|0@@,0)</f>
+        <v/>
+      </c>
+      <c r="E32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|1@@-@@ENG_FCF|FCF.cash|1@@)/@@ENG_FCF|FCF.ebitda|1@@,0)</f>
+        <v/>
+      </c>
+      <c r="F32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|2@@-@@ENG_FCF|FCF.cash|2@@)/@@ENG_FCF|FCF.ebitda|2@@,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|3@@-@@ENG_FCF|FCF.cash|3@@)/@@ENG_FCF|FCF.ebitda|3@@,0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|4@@-@@ENG_FCF|FCF.cash|4@@)/@@ENG_FCF|FCF.ebitda|4@@,0)</f>
+        <v/>
+      </c>
+      <c r="I32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|5@@-@@ENG_FCF|FCF.cash|5@@)/@@ENG_FCF|FCF.ebitda|5@@,0)</f>
+        <v/>
+      </c>
+      <c r="J32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|6@@-@@ENG_FCF|FCF.cash|6@@)/@@ENG_FCF|FCF.ebitda|6@@,0)</f>
+        <v/>
+      </c>
+      <c r="K32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|7@@-@@ENG_FCF|FCF.cash|7@@)/@@ENG_FCF|FCF.ebitda|7@@,0)</f>
+        <v/>
+      </c>
+      <c r="L32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|8@@-@@ENG_FCF|FCF.cash|8@@)/@@ENG_FCF|FCF.ebitda|8@@,0)</f>
+        <v/>
+      </c>
+      <c r="M32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|9@@-@@ENG_FCF|FCF.cash|9@@)/@@ENG_FCF|FCF.ebitda|9@@,0)</f>
+        <v/>
+      </c>
+      <c r="N32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|10@@-@@ENG_FCF|FCF.cash|10@@)/@@ENG_FCF|FCF.ebitda|10@@,0)</f>
+        <v/>
+      </c>
+      <c r="O32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|11@@-@@ENG_FCF|FCF.cash|11@@)/@@ENG_FCF|FCF.ebitda|11@@,0)</f>
+        <v/>
+      </c>
+      <c r="P32" s="12">
+        <f>IFERROR((@@ENG_FCF|FCF.ltd|12@@-@@ENG_FCF|FCF.cash|12@@)/@@ENG_FCF|FCF.ebitda|12@@,0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -19670,55 +22588,55 @@
         </is>
       </c>
       <c r="D58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|0@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$D$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
       <c r="E58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|1@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$E$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
       <c r="F58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|2@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$F$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
       <c r="G58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|3@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$G$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
       <c r="H58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|4@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$H$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
       <c r="I58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|5@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$I$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
       <c r="J58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|6@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$J$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
       <c r="K58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|7@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$K$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
       <c r="L58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|8@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$L$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
       <c r="M58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|9@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$M$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
       <c r="N58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|10@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$N$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
       <c r="O58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|11@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$O$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
       <c r="P58" s="11">
-        <f>@@ENG_DCF|DCF.wacc|12@@+'IN_SCEN'!$D$20</f>
+        <f>'ENG_DCF'!$P$14+'IN_SCEN'!$D$20</f>
         <v/>
       </c>
     </row>
@@ -21640,55 +24558,55 @@
         </is>
       </c>
       <c r="D92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|0@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$D$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
       <c r="E92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|1@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$E$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
       <c r="F92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|2@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$F$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
       <c r="G92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|3@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$G$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
       <c r="H92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|4@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$H$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
       <c r="I92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|5@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$I$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
       <c r="J92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|6@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$J$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
       <c r="K92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|7@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$K$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
       <c r="L92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|8@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$L$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
       <c r="M92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|9@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$M$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
       <c r="N92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|10@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$N$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
       <c r="O92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|11@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$O$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
       <c r="P92" s="11">
-        <f>@@ENG_DCF|DCF.wacc|12@@+'IN_SCEN'!$E$20</f>
+        <f>'ENG_DCF'!$P$14+'IN_SCEN'!$E$20</f>
         <v/>
       </c>
     </row>
@@ -23610,55 +26528,55 @@
         </is>
       </c>
       <c r="D126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|0@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$D$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
       <c r="E126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|1@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$E$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
       <c r="F126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|2@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$F$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
       <c r="G126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|3@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$G$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
       <c r="H126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|4@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$H$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
       <c r="I126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|5@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$I$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
       <c r="J126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|6@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$J$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
       <c r="K126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|7@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$K$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
       <c r="L126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|8@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$L$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
       <c r="M126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|9@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$M$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
       <c r="N126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|10@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$N$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
       <c r="O126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|11@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$O$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
       <c r="P126" s="11">
-        <f>@@ENG_DCF|DCF.wacc|12@@+'IN_SCEN'!$F$20</f>
+        <f>'ENG_DCF'!$P$14+'IN_SCEN'!$F$20</f>
         <v/>
       </c>
     </row>

--- a/models/lead_acid_recycling/build/out/built.xlsx
+++ b/models/lead_acid_recycling/build/out/built.xlsx
@@ -19,8 +19,9 @@
     <sheet name="ENG_CAPEX" sheetId="10" state="hidden" r:id="rId10"/>
     <sheet name="ENG_ALLOC" sheetId="11" state="hidden" r:id="rId11"/>
     <sheet name="ENG_WC" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet name="ENG_DCF" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet name="ENG_LEV" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet name="ENG_FCF" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet name="ENG_DCF" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet name="ENG_LEV" sheetId="15" state="hidden" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11572,6 +11573,3936 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>جریان‌های نقدی آزاد (FCF)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>موتور محاسبات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>تبدیل عملیات به EBITDA/EBIT/سود خالص، جریان نقد آزاد پروژه و سهامداران، جدول بدهی و ترازنامهٔ پروژه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>دوره (t)</t>
+        </is>
+      </c>
+      <c r="D7" s="5">
+        <f>'IN_MACRO'!D$23</f>
+        <v/>
+      </c>
+      <c r="E7" s="5">
+        <f>'IN_MACRO'!E$23</f>
+        <v/>
+      </c>
+      <c r="F7" s="5">
+        <f>'IN_MACRO'!F$23</f>
+        <v/>
+      </c>
+      <c r="G7" s="5">
+        <f>'IN_MACRO'!G$23</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
+        <f>'IN_MACRO'!H$23</f>
+        <v/>
+      </c>
+      <c r="I7" s="5">
+        <f>'IN_MACRO'!I$23</f>
+        <v/>
+      </c>
+      <c r="J7" s="5">
+        <f>'IN_MACRO'!J$23</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
+        <f>'IN_MACRO'!K$23</f>
+        <v/>
+      </c>
+      <c r="L7" s="5">
+        <f>'IN_MACRO'!L$23</f>
+        <v/>
+      </c>
+      <c r="M7" s="5">
+        <f>'IN_MACRO'!M$23</f>
+        <v/>
+      </c>
+      <c r="N7" s="5">
+        <f>'IN_MACRO'!N$23</f>
+        <v/>
+      </c>
+      <c r="O7" s="5">
+        <f>'IN_MACRO'!O$23</f>
+        <v/>
+      </c>
+      <c r="P7" s="5">
+        <f>'IN_MACRO'!P$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>سال تقویمی</t>
+        </is>
+      </c>
+      <c r="D8" s="5">
+        <f>'IN_MACRO'!D$24</f>
+        <v/>
+      </c>
+      <c r="E8" s="5">
+        <f>'IN_MACRO'!E$24</f>
+        <v/>
+      </c>
+      <c r="F8" s="5">
+        <f>'IN_MACRO'!F$24</f>
+        <v/>
+      </c>
+      <c r="G8" s="5">
+        <f>'IN_MACRO'!G$24</f>
+        <v/>
+      </c>
+      <c r="H8" s="5">
+        <f>'IN_MACRO'!H$24</f>
+        <v/>
+      </c>
+      <c r="I8" s="5">
+        <f>'IN_MACRO'!I$24</f>
+        <v/>
+      </c>
+      <c r="J8" s="5">
+        <f>'IN_MACRO'!J$24</f>
+        <v/>
+      </c>
+      <c r="K8" s="5">
+        <f>'IN_MACRO'!K$24</f>
+        <v/>
+      </c>
+      <c r="L8" s="5">
+        <f>'IN_MACRO'!L$24</f>
+        <v/>
+      </c>
+      <c r="M8" s="5">
+        <f>'IN_MACRO'!M$24</f>
+        <v/>
+      </c>
+      <c r="N8" s="5">
+        <f>'IN_MACRO'!N$24</f>
+        <v/>
+      </c>
+      <c r="O8" s="5">
+        <f>'IN_MACRO'!O$24</f>
+        <v/>
+      </c>
+      <c r="P8" s="5">
+        <f>'IN_MACRO'!P$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>الف) صورت سود و زیان</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
+      <c r="P9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>درآمد خالص</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>FCF.rev</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D10" s="14">
+        <f>'ENG_OPS'!$D$81</f>
+        <v/>
+      </c>
+      <c r="E10" s="14">
+        <f>'ENG_OPS'!$E$81</f>
+        <v/>
+      </c>
+      <c r="F10" s="14">
+        <f>'ENG_OPS'!$F$81</f>
+        <v/>
+      </c>
+      <c r="G10" s="14">
+        <f>'ENG_OPS'!$G$81</f>
+        <v/>
+      </c>
+      <c r="H10" s="14">
+        <f>'ENG_OPS'!$H$81</f>
+        <v/>
+      </c>
+      <c r="I10" s="14">
+        <f>'ENG_OPS'!$I$81</f>
+        <v/>
+      </c>
+      <c r="J10" s="14">
+        <f>'ENG_OPS'!$J$81</f>
+        <v/>
+      </c>
+      <c r="K10" s="14">
+        <f>'ENG_OPS'!$K$81</f>
+        <v/>
+      </c>
+      <c r="L10" s="14">
+        <f>'ENG_OPS'!$L$81</f>
+        <v/>
+      </c>
+      <c r="M10" s="14">
+        <f>'ENG_OPS'!$M$81</f>
+        <v/>
+      </c>
+      <c r="N10" s="14">
+        <f>'ENG_OPS'!$N$81</f>
+        <v/>
+      </c>
+      <c r="O10" s="14">
+        <f>'ENG_OPS'!$O$81</f>
+        <v/>
+      </c>
+      <c r="P10" s="14">
+        <f>'ENG_OPS'!$P$81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>هزینه‌های مستقیم تولید (DPC)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D11" s="14">
+        <f>@@ENG_COST|EC.dpc|0@@</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>@@ENG_COST|EC.dpc|1@@</f>
+        <v/>
+      </c>
+      <c r="F11" s="14">
+        <f>@@ENG_COST|EC.dpc|2@@</f>
+        <v/>
+      </c>
+      <c r="G11" s="14">
+        <f>@@ENG_COST|EC.dpc|3@@</f>
+        <v/>
+      </c>
+      <c r="H11" s="14">
+        <f>@@ENG_COST|EC.dpc|4@@</f>
+        <v/>
+      </c>
+      <c r="I11" s="14">
+        <f>@@ENG_COST|EC.dpc|5@@</f>
+        <v/>
+      </c>
+      <c r="J11" s="14">
+        <f>@@ENG_COST|EC.dpc|6@@</f>
+        <v/>
+      </c>
+      <c r="K11" s="14">
+        <f>@@ENG_COST|EC.dpc|7@@</f>
+        <v/>
+      </c>
+      <c r="L11" s="14">
+        <f>@@ENG_COST|EC.dpc|8@@</f>
+        <v/>
+      </c>
+      <c r="M11" s="14">
+        <f>@@ENG_COST|EC.dpc|9@@</f>
+        <v/>
+      </c>
+      <c r="N11" s="14">
+        <f>@@ENG_COST|EC.dpc|10@@</f>
+        <v/>
+      </c>
+      <c r="O11" s="14">
+        <f>@@ENG_COST|EC.dpc|11@@</f>
+        <v/>
+      </c>
+      <c r="P11" s="14">
+        <f>@@ENG_COST|EC.dpc|12@@</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>هزینه‌های عملیاتی تولید (OPC)</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D12" s="14">
+        <f>@@ENG_COST|EC.opc|0@@</f>
+        <v/>
+      </c>
+      <c r="E12" s="14">
+        <f>@@ENG_COST|EC.opc|1@@</f>
+        <v/>
+      </c>
+      <c r="F12" s="14">
+        <f>@@ENG_COST|EC.opc|2@@</f>
+        <v/>
+      </c>
+      <c r="G12" s="14">
+        <f>@@ENG_COST|EC.opc|3@@</f>
+        <v/>
+      </c>
+      <c r="H12" s="14">
+        <f>@@ENG_COST|EC.opc|4@@</f>
+        <v/>
+      </c>
+      <c r="I12" s="14">
+        <f>@@ENG_COST|EC.opc|5@@</f>
+        <v/>
+      </c>
+      <c r="J12" s="14">
+        <f>@@ENG_COST|EC.opc|6@@</f>
+        <v/>
+      </c>
+      <c r="K12" s="14">
+        <f>@@ENG_COST|EC.opc|7@@</f>
+        <v/>
+      </c>
+      <c r="L12" s="14">
+        <f>@@ENG_COST|EC.opc|8@@</f>
+        <v/>
+      </c>
+      <c r="M12" s="14">
+        <f>@@ENG_COST|EC.opc|9@@</f>
+        <v/>
+      </c>
+      <c r="N12" s="14">
+        <f>@@ENG_COST|EC.opc|10@@</f>
+        <v/>
+      </c>
+      <c r="O12" s="14">
+        <f>@@ENG_COST|EC.opc|11@@</f>
+        <v/>
+      </c>
+      <c r="P12" s="14">
+        <f>@@ENG_COST|EC.opc|12@@</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>هزینه‌های ثابت تولید (FPC)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D13" s="14">
+        <f>@@ENG_COST|EC.fpc|0@@</f>
+        <v/>
+      </c>
+      <c r="E13" s="14">
+        <f>@@ENG_COST|EC.fpc|1@@</f>
+        <v/>
+      </c>
+      <c r="F13" s="14">
+        <f>@@ENG_COST|EC.fpc|2@@</f>
+        <v/>
+      </c>
+      <c r="G13" s="14">
+        <f>@@ENG_COST|EC.fpc|3@@</f>
+        <v/>
+      </c>
+      <c r="H13" s="14">
+        <f>@@ENG_COST|EC.fpc|4@@</f>
+        <v/>
+      </c>
+      <c r="I13" s="14">
+        <f>@@ENG_COST|EC.fpc|5@@</f>
+        <v/>
+      </c>
+      <c r="J13" s="14">
+        <f>@@ENG_COST|EC.fpc|6@@</f>
+        <v/>
+      </c>
+      <c r="K13" s="14">
+        <f>@@ENG_COST|EC.fpc|7@@</f>
+        <v/>
+      </c>
+      <c r="L13" s="14">
+        <f>@@ENG_COST|EC.fpc|8@@</f>
+        <v/>
+      </c>
+      <c r="M13" s="14">
+        <f>@@ENG_COST|EC.fpc|9@@</f>
+        <v/>
+      </c>
+      <c r="N13" s="14">
+        <f>@@ENG_COST|EC.fpc|10@@</f>
+        <v/>
+      </c>
+      <c r="O13" s="14">
+        <f>@@ENG_COST|EC.fpc|11@@</f>
+        <v/>
+      </c>
+      <c r="P13" s="14">
+        <f>@@ENG_COST|EC.fpc|12@@</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>جمع هزینه‌ها</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>FCF.cost</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D14" s="14">
+        <f>@@ENG_COST|EC.dpc|0@@+@@ENG_COST|EC.opc|0@@+@@ENG_COST|EC.fpc|0@@</f>
+        <v/>
+      </c>
+      <c r="E14" s="14">
+        <f>@@ENG_COST|EC.dpc|1@@+@@ENG_COST|EC.opc|1@@+@@ENG_COST|EC.fpc|1@@</f>
+        <v/>
+      </c>
+      <c r="F14" s="14">
+        <f>@@ENG_COST|EC.dpc|2@@+@@ENG_COST|EC.opc|2@@+@@ENG_COST|EC.fpc|2@@</f>
+        <v/>
+      </c>
+      <c r="G14" s="14">
+        <f>@@ENG_COST|EC.dpc|3@@+@@ENG_COST|EC.opc|3@@+@@ENG_COST|EC.fpc|3@@</f>
+        <v/>
+      </c>
+      <c r="H14" s="14">
+        <f>@@ENG_COST|EC.dpc|4@@+@@ENG_COST|EC.opc|4@@+@@ENG_COST|EC.fpc|4@@</f>
+        <v/>
+      </c>
+      <c r="I14" s="14">
+        <f>@@ENG_COST|EC.dpc|5@@+@@ENG_COST|EC.opc|5@@+@@ENG_COST|EC.fpc|5@@</f>
+        <v/>
+      </c>
+      <c r="J14" s="14">
+        <f>@@ENG_COST|EC.dpc|6@@+@@ENG_COST|EC.opc|6@@+@@ENG_COST|EC.fpc|6@@</f>
+        <v/>
+      </c>
+      <c r="K14" s="14">
+        <f>@@ENG_COST|EC.dpc|7@@+@@ENG_COST|EC.opc|7@@+@@ENG_COST|EC.fpc|7@@</f>
+        <v/>
+      </c>
+      <c r="L14" s="14">
+        <f>@@ENG_COST|EC.dpc|8@@+@@ENG_COST|EC.opc|8@@+@@ENG_COST|EC.fpc|8@@</f>
+        <v/>
+      </c>
+      <c r="M14" s="14">
+        <f>@@ENG_COST|EC.dpc|9@@+@@ENG_COST|EC.opc|9@@+@@ENG_COST|EC.fpc|9@@</f>
+        <v/>
+      </c>
+      <c r="N14" s="14">
+        <f>@@ENG_COST|EC.dpc|10@@+@@ENG_COST|EC.opc|10@@+@@ENG_COST|EC.fpc|10@@</f>
+        <v/>
+      </c>
+      <c r="O14" s="14">
+        <f>@@ENG_COST|EC.dpc|11@@+@@ENG_COST|EC.opc|11@@+@@ENG_COST|EC.fpc|11@@</f>
+        <v/>
+      </c>
+      <c r="P14" s="14">
+        <f>@@ENG_COST|EC.dpc|12@@+@@ENG_COST|EC.opc|12@@+@@ENG_COST|EC.fpc|12@@</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>سود قبل بهره، مالیات و استهلاک (EBITDA)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>FCF.ebitda</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D15" s="14">
+        <f>@@ENG_COST|EC.ebitda|0@@</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>@@ENG_COST|EC.ebitda|1@@</f>
+        <v/>
+      </c>
+      <c r="F15" s="14">
+        <f>@@ENG_COST|EC.ebitda|2@@</f>
+        <v/>
+      </c>
+      <c r="G15" s="14">
+        <f>@@ENG_COST|EC.ebitda|3@@</f>
+        <v/>
+      </c>
+      <c r="H15" s="14">
+        <f>@@ENG_COST|EC.ebitda|4@@</f>
+        <v/>
+      </c>
+      <c r="I15" s="14">
+        <f>@@ENG_COST|EC.ebitda|5@@</f>
+        <v/>
+      </c>
+      <c r="J15" s="14">
+        <f>@@ENG_COST|EC.ebitda|6@@</f>
+        <v/>
+      </c>
+      <c r="K15" s="14">
+        <f>@@ENG_COST|EC.ebitda|7@@</f>
+        <v/>
+      </c>
+      <c r="L15" s="14">
+        <f>@@ENG_COST|EC.ebitda|8@@</f>
+        <v/>
+      </c>
+      <c r="M15" s="14">
+        <f>@@ENG_COST|EC.ebitda|9@@</f>
+        <v/>
+      </c>
+      <c r="N15" s="14">
+        <f>@@ENG_COST|EC.ebitda|10@@</f>
+        <v/>
+      </c>
+      <c r="O15" s="14">
+        <f>@@ENG_COST|EC.ebitda|11@@</f>
+        <v/>
+      </c>
+      <c r="P15" s="14">
+        <f>@@ENG_COST|EC.ebitda|12@@</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>استهلاک</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>FCF.dep</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D16" s="14">
+        <f>'ENG_CAPEX'!$D$81</f>
+        <v/>
+      </c>
+      <c r="E16" s="14">
+        <f>'ENG_CAPEX'!$E$81</f>
+        <v/>
+      </c>
+      <c r="F16" s="14">
+        <f>'ENG_CAPEX'!$F$81</f>
+        <v/>
+      </c>
+      <c r="G16" s="14">
+        <f>'ENG_CAPEX'!$G$81</f>
+        <v/>
+      </c>
+      <c r="H16" s="14">
+        <f>'ENG_CAPEX'!$H$81</f>
+        <v/>
+      </c>
+      <c r="I16" s="14">
+        <f>'ENG_CAPEX'!$I$81</f>
+        <v/>
+      </c>
+      <c r="J16" s="14">
+        <f>'ENG_CAPEX'!$J$81</f>
+        <v/>
+      </c>
+      <c r="K16" s="14">
+        <f>'ENG_CAPEX'!$K$81</f>
+        <v/>
+      </c>
+      <c r="L16" s="14">
+        <f>'ENG_CAPEX'!$L$81</f>
+        <v/>
+      </c>
+      <c r="M16" s="14">
+        <f>'ENG_CAPEX'!$M$81</f>
+        <v/>
+      </c>
+      <c r="N16" s="14">
+        <f>'ENG_CAPEX'!$N$81</f>
+        <v/>
+      </c>
+      <c r="O16" s="14">
+        <f>'ENG_CAPEX'!$O$81</f>
+        <v/>
+      </c>
+      <c r="P16" s="14">
+        <f>'ENG_CAPEX'!$P$81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>سود عملیاتی (EBIT)</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>FCF.ebit</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D17" s="14">
+        <f>@@ENG_COST|EC.ebit|0@@</f>
+        <v/>
+      </c>
+      <c r="E17" s="14">
+        <f>@@ENG_COST|EC.ebit|1@@</f>
+        <v/>
+      </c>
+      <c r="F17" s="14">
+        <f>@@ENG_COST|EC.ebit|2@@</f>
+        <v/>
+      </c>
+      <c r="G17" s="14">
+        <f>@@ENG_COST|EC.ebit|3@@</f>
+        <v/>
+      </c>
+      <c r="H17" s="14">
+        <f>@@ENG_COST|EC.ebit|4@@</f>
+        <v/>
+      </c>
+      <c r="I17" s="14">
+        <f>@@ENG_COST|EC.ebit|5@@</f>
+        <v/>
+      </c>
+      <c r="J17" s="14">
+        <f>@@ENG_COST|EC.ebit|6@@</f>
+        <v/>
+      </c>
+      <c r="K17" s="14">
+        <f>@@ENG_COST|EC.ebit|7@@</f>
+        <v/>
+      </c>
+      <c r="L17" s="14">
+        <f>@@ENG_COST|EC.ebit|8@@</f>
+        <v/>
+      </c>
+      <c r="M17" s="14">
+        <f>@@ENG_COST|EC.ebit|9@@</f>
+        <v/>
+      </c>
+      <c r="N17" s="14">
+        <f>@@ENG_COST|EC.ebit|10@@</f>
+        <v/>
+      </c>
+      <c r="O17" s="14">
+        <f>@@ENG_COST|EC.ebit|11@@</f>
+        <v/>
+      </c>
+      <c r="P17" s="14">
+        <f>@@ENG_COST|EC.ebit|12@@</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>ب) جدول بدهی، خدمت دین و هزینه‌های مالی</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="7" t="n"/>
+      <c r="O19" s="7" t="n"/>
+      <c r="P19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>مانده تسهیلات - افتتاحیه</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>FCF.debt_open</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D20" s="14">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E20" s="14">
+        <f>'ENG_FCF'!$D$25</f>
+        <v/>
+      </c>
+      <c r="F20" s="14">
+        <f>'ENG_FCF'!$E$25</f>
+        <v/>
+      </c>
+      <c r="G20" s="14">
+        <f>'ENG_FCF'!$F$25</f>
+        <v/>
+      </c>
+      <c r="H20" s="14">
+        <f>'ENG_FCF'!$G$25</f>
+        <v/>
+      </c>
+      <c r="I20" s="14">
+        <f>'ENG_FCF'!$H$25</f>
+        <v/>
+      </c>
+      <c r="J20" s="14">
+        <f>'ENG_FCF'!$I$25</f>
+        <v/>
+      </c>
+      <c r="K20" s="14">
+        <f>'ENG_FCF'!$J$25</f>
+        <v/>
+      </c>
+      <c r="L20" s="14">
+        <f>'ENG_FCF'!$K$25</f>
+        <v/>
+      </c>
+      <c r="M20" s="14">
+        <f>'ENG_FCF'!$L$25</f>
+        <v/>
+      </c>
+      <c r="N20" s="14">
+        <f>'ENG_FCF'!$M$25</f>
+        <v/>
+      </c>
+      <c r="O20" s="14">
+        <f>'ENG_FCF'!$N$25</f>
+        <v/>
+      </c>
+      <c r="P20" s="14">
+        <f>'ENG_FCF'!$O$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>برداشت تسهیلات</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>FCF.draw</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D21" s="14">
+        <f>IF('IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$D$21,0)</f>
+        <v/>
+      </c>
+      <c r="E21" s="14">
+        <f>IF('IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$E$21,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="14">
+        <f>IF('IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$F$21,0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="14">
+        <f>IF('IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$G$21,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="14">
+        <f>IF('IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$H$21,0)</f>
+        <v/>
+      </c>
+      <c r="I21" s="14">
+        <f>IF('IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$I$21,0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="14">
+        <f>IF('IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$J$21,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="14">
+        <f>IF('IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$K$21,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="14">
+        <f>IF('IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$L$21,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="14">
+        <f>IF('IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$M$21,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="14">
+        <f>IF('IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$N$21,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="14">
+        <f>IF('IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$O$21,0)</f>
+        <v/>
+      </c>
+      <c r="P21" s="14">
+        <f>IF('IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$24*'ENG_CAPEX'!$P$21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>سود سرمایه‌ای‌شده حین ساخت (IDC)</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>FCF.idc</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D22" s="14">
+        <f>'ENG_CAPEX'!$D$27</f>
+        <v/>
+      </c>
+      <c r="E22" s="14">
+        <f>'ENG_CAPEX'!$E$27</f>
+        <v/>
+      </c>
+      <c r="F22" s="14">
+        <f>'ENG_CAPEX'!$F$27</f>
+        <v/>
+      </c>
+      <c r="G22" s="14">
+        <f>'ENG_CAPEX'!$G$27</f>
+        <v/>
+      </c>
+      <c r="H22" s="14">
+        <f>'ENG_CAPEX'!$H$27</f>
+        <v/>
+      </c>
+      <c r="I22" s="14">
+        <f>'ENG_CAPEX'!$I$27</f>
+        <v/>
+      </c>
+      <c r="J22" s="14">
+        <f>'ENG_CAPEX'!$J$27</f>
+        <v/>
+      </c>
+      <c r="K22" s="14">
+        <f>'ENG_CAPEX'!$K$27</f>
+        <v/>
+      </c>
+      <c r="L22" s="14">
+        <f>'ENG_CAPEX'!$L$27</f>
+        <v/>
+      </c>
+      <c r="M22" s="14">
+        <f>'ENG_CAPEX'!$M$27</f>
+        <v/>
+      </c>
+      <c r="N22" s="14">
+        <f>'ENG_CAPEX'!$N$27</f>
+        <v/>
+      </c>
+      <c r="O22" s="14">
+        <f>'ENG_CAPEX'!$O$27</f>
+        <v/>
+      </c>
+      <c r="P22" s="14">
+        <f>'ENG_CAPEX'!$P$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>مبنای بازپرداخت (مانده در آستانهٔ بازپرداخت)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>FCF.debt_base</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+      <c r="E23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+      <c r="F23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+      <c r="H23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+      <c r="K23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+      <c r="L23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+      <c r="M23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+      <c r="N23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+      <c r="O23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+      <c r="P23" s="14">
+        <f>'IN_FIN'!$D$24*(INDEX('ENG_CAPEX'!$D$22:$P$22,1,'IN_FIN'!$D$28)+INDEX('ENG_CAPEX'!$D$28:$P$28,1,'IN_FIN'!$D$28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>بازپرداخت اصل تسهیلات</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>FCF.principal</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$D$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$D$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$D$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$D$20+'ENG_FCF'!$D$21+'ENG_FCF'!$D$22)</f>
+        <v/>
+      </c>
+      <c r="E24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$E$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$E$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$E$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$E$20+'ENG_FCF'!$E$21+'ENG_FCF'!$E$22)</f>
+        <v/>
+      </c>
+      <c r="F24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$F$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$F$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$F$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$F$20+'ENG_FCF'!$F$21+'ENG_FCF'!$F$22)</f>
+        <v/>
+      </c>
+      <c r="G24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$G$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$G$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$G$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$G$20+'ENG_FCF'!$G$21+'ENG_FCF'!$G$22)</f>
+        <v/>
+      </c>
+      <c r="H24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$H$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$H$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$H$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$H$20+'ENG_FCF'!$H$21+'ENG_FCF'!$H$22)</f>
+        <v/>
+      </c>
+      <c r="I24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$I$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$I$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$I$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$I$20+'ENG_FCF'!$I$21+'ENG_FCF'!$I$22)</f>
+        <v/>
+      </c>
+      <c r="J24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$J$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$J$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$J$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$J$20+'ENG_FCF'!$J$21+'ENG_FCF'!$J$22)</f>
+        <v/>
+      </c>
+      <c r="K24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$K$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$K$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$K$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$K$20+'ENG_FCF'!$K$21+'ENG_FCF'!$K$22)</f>
+        <v/>
+      </c>
+      <c r="L24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$L$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$L$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$L$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$L$20+'ENG_FCF'!$L$21+'ENG_FCF'!$L$22)</f>
+        <v/>
+      </c>
+      <c r="M24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$M$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$M$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$M$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$M$20+'ENG_FCF'!$M$21+'ENG_FCF'!$M$22)</f>
+        <v/>
+      </c>
+      <c r="N24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$N$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$N$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$N$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$N$20+'ENG_FCF'!$N$21+'ENG_FCF'!$N$22)</f>
+        <v/>
+      </c>
+      <c r="O24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$O$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$O$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$O$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$O$20+'ENG_FCF'!$O$21+'ENG_FCF'!$O$22)</f>
+        <v/>
+      </c>
+      <c r="P24" s="14">
+        <f>MIN(IF(AND('IN_MACRO'!$P$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$P$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),IF('IN_FIN'!$D$30=1,'ENG_FCF'!$D$23/'IN_FIN'!$D$29,-PPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$P$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23)),0),'ENG_FCF'!$P$20+'ENG_FCF'!$P$21+'ENG_FCF'!$P$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>مانده تسهیلات - اختتامیه</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>FCF.debt_close</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D25" s="14">
+        <f>'ENG_FCF'!$D$20+'ENG_FCF'!$D$21+'ENG_FCF'!$D$22-'ENG_FCF'!$D$24</f>
+        <v/>
+      </c>
+      <c r="E25" s="14">
+        <f>'ENG_FCF'!$E$20+'ENG_FCF'!$E$21+'ENG_FCF'!$E$22-'ENG_FCF'!$E$24</f>
+        <v/>
+      </c>
+      <c r="F25" s="14">
+        <f>'ENG_FCF'!$F$20+'ENG_FCF'!$F$21+'ENG_FCF'!$F$22-'ENG_FCF'!$F$24</f>
+        <v/>
+      </c>
+      <c r="G25" s="14">
+        <f>'ENG_FCF'!$G$20+'ENG_FCF'!$G$21+'ENG_FCF'!$G$22-'ENG_FCF'!$G$24</f>
+        <v/>
+      </c>
+      <c r="H25" s="14">
+        <f>'ENG_FCF'!$H$20+'ENG_FCF'!$H$21+'ENG_FCF'!$H$22-'ENG_FCF'!$H$24</f>
+        <v/>
+      </c>
+      <c r="I25" s="14">
+        <f>'ENG_FCF'!$I$20+'ENG_FCF'!$I$21+'ENG_FCF'!$I$22-'ENG_FCF'!$I$24</f>
+        <v/>
+      </c>
+      <c r="J25" s="14">
+        <f>'ENG_FCF'!$J$20+'ENG_FCF'!$J$21+'ENG_FCF'!$J$22-'ENG_FCF'!$J$24</f>
+        <v/>
+      </c>
+      <c r="K25" s="14">
+        <f>'ENG_FCF'!$K$20+'ENG_FCF'!$K$21+'ENG_FCF'!$K$22-'ENG_FCF'!$K$24</f>
+        <v/>
+      </c>
+      <c r="L25" s="14">
+        <f>'ENG_FCF'!$L$20+'ENG_FCF'!$L$21+'ENG_FCF'!$L$22-'ENG_FCF'!$L$24</f>
+        <v/>
+      </c>
+      <c r="M25" s="14">
+        <f>'ENG_FCF'!$M$20+'ENG_FCF'!$M$21+'ENG_FCF'!$M$22-'ENG_FCF'!$M$24</f>
+        <v/>
+      </c>
+      <c r="N25" s="14">
+        <f>'ENG_FCF'!$N$20+'ENG_FCF'!$N$21+'ENG_FCF'!$N$22-'ENG_FCF'!$N$24</f>
+        <v/>
+      </c>
+      <c r="O25" s="14">
+        <f>'ENG_FCF'!$O$20+'ENG_FCF'!$O$21+'ENG_FCF'!$O$22-'ENG_FCF'!$O$24</f>
+        <v/>
+      </c>
+      <c r="P25" s="14">
+        <f>'ENG_FCF'!$P$20+'ENG_FCF'!$P$21+'ENG_FCF'!$P$22-'ENG_FCF'!$P$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>هزینه سود تسهیلات بلندمدت</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>FCF.int_lt</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D26" s="14">
+        <f>IF('IN_MACRO'!$D$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$D$20,IF(AND('IN_MACRO'!$D$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$D$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$D$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$D$20)))</f>
+        <v/>
+      </c>
+      <c r="E26" s="14">
+        <f>IF('IN_MACRO'!$E$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$E$20,IF(AND('IN_MACRO'!$E$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$E$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$E$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$E$20)))</f>
+        <v/>
+      </c>
+      <c r="F26" s="14">
+        <f>IF('IN_MACRO'!$F$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$F$20,IF(AND('IN_MACRO'!$F$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$F$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$F$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$F$20)))</f>
+        <v/>
+      </c>
+      <c r="G26" s="14">
+        <f>IF('IN_MACRO'!$G$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$G$20,IF(AND('IN_MACRO'!$G$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$G$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$G$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$G$20)))</f>
+        <v/>
+      </c>
+      <c r="H26" s="14">
+        <f>IF('IN_MACRO'!$H$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$H$20,IF(AND('IN_MACRO'!$H$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$H$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$H$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$H$20)))</f>
+        <v/>
+      </c>
+      <c r="I26" s="14">
+        <f>IF('IN_MACRO'!$I$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$I$20,IF(AND('IN_MACRO'!$I$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$I$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$I$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$I$20)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="14">
+        <f>IF('IN_MACRO'!$J$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$J$20,IF(AND('IN_MACRO'!$J$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$J$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$J$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$J$20)))</f>
+        <v/>
+      </c>
+      <c r="K26" s="14">
+        <f>IF('IN_MACRO'!$K$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$K$20,IF(AND('IN_MACRO'!$K$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$K$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$K$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$K$20)))</f>
+        <v/>
+      </c>
+      <c r="L26" s="14">
+        <f>IF('IN_MACRO'!$L$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$L$20,IF(AND('IN_MACRO'!$L$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$L$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$L$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$L$20)))</f>
+        <v/>
+      </c>
+      <c r="M26" s="14">
+        <f>IF('IN_MACRO'!$M$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$M$20,IF(AND('IN_MACRO'!$M$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$M$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$M$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$M$20)))</f>
+        <v/>
+      </c>
+      <c r="N26" s="14">
+        <f>IF('IN_MACRO'!$N$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$N$20,IF(AND('IN_MACRO'!$N$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$N$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$N$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$N$20)))</f>
+        <v/>
+      </c>
+      <c r="O26" s="14">
+        <f>IF('IN_MACRO'!$O$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$O$20,IF(AND('IN_MACRO'!$O$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$O$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$O$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$O$20)))</f>
+        <v/>
+      </c>
+      <c r="P26" s="14">
+        <f>IF('IN_MACRO'!$P$33=1,0,IF('IN_FIN'!$D$30=1,('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$P$20,IF(AND('IN_MACRO'!$P$23&gt;='IN_FIN'!$D$28,'IN_MACRO'!$P$23&lt;='IN_FIN'!$D$28+'IN_FIN'!$D$29-1),-IPMT(('IN_FIN'!$D$25+'ENG_SCEN'!$G$19),'IN_MACRO'!$P$23-'IN_FIN'!$D$28+1,'IN_FIN'!$D$29,'ENG_FCF'!$D$23),('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)*'ENG_FCF'!$P$20)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>کارمزدها و هزینه‌های تأمین مالی</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>FCF.fees</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$D$21+IF('IN_MACRO'!$D$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$D$22),0)</f>
+        <v/>
+      </c>
+      <c r="E27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$E$21+IF('IN_MACRO'!$E$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$E$22),0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$F$21+IF('IN_MACRO'!$F$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$F$22),0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$G$21+IF('IN_MACRO'!$G$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$G$22),0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$H$21+IF('IN_MACRO'!$H$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$H$22),0)</f>
+        <v/>
+      </c>
+      <c r="I27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$I$21+IF('IN_MACRO'!$I$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$I$22),0)</f>
+        <v/>
+      </c>
+      <c r="J27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$J$21+IF('IN_MACRO'!$J$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$J$22),0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$K$21+IF('IN_MACRO'!$K$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$K$22),0)</f>
+        <v/>
+      </c>
+      <c r="L27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$L$21+IF('IN_MACRO'!$L$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$L$22),0)</f>
+        <v/>
+      </c>
+      <c r="M27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$M$21+IF('IN_MACRO'!$M$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$M$22),0)</f>
+        <v/>
+      </c>
+      <c r="N27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$N$21+IF('IN_MACRO'!$N$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$N$22),0)</f>
+        <v/>
+      </c>
+      <c r="O27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$O$21+IF('IN_MACRO'!$O$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$O$22),0)</f>
+        <v/>
+      </c>
+      <c r="P27" s="14">
+        <f>'IN_FIN'!$D$26*'ENG_FCF'!$P$21+IF('IN_MACRO'!$P$23&lt;='IN_MACRO'!$D$13,'IN_FIN'!$D$27*'IN_FIN'!$D$24*MAX(0,SUM('ENG_CAPEX'!$D$21:$P$21)-'ENG_CAPEX'!$P$22),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>هزینه سود تسهیلات کوتاه‌مدت</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>FCF.int_st</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$E$20</f>
+        <v/>
+      </c>
+      <c r="F28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$F$20</f>
+        <v/>
+      </c>
+      <c r="G28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$G$20</f>
+        <v/>
+      </c>
+      <c r="H28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$H$20</f>
+        <v/>
+      </c>
+      <c r="I28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$I$20</f>
+        <v/>
+      </c>
+      <c r="J28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$J$20</f>
+        <v/>
+      </c>
+      <c r="K28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$K$20</f>
+        <v/>
+      </c>
+      <c r="L28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$L$20</f>
+        <v/>
+      </c>
+      <c r="M28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$M$20</f>
+        <v/>
+      </c>
+      <c r="N28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$N$20</f>
+        <v/>
+      </c>
+      <c r="O28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$O$20</f>
+        <v/>
+      </c>
+      <c r="P28" s="14">
+        <f>'IN_FIN'!$D$31*'ENG_WC'!$P$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>درآمد غیرعملیاتی (سود سپرده)</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>FCF.int_inc</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$D$48</f>
+        <v/>
+      </c>
+      <c r="E29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$E$48</f>
+        <v/>
+      </c>
+      <c r="F29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$F$48</f>
+        <v/>
+      </c>
+      <c r="G29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$G$48</f>
+        <v/>
+      </c>
+      <c r="H29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$H$48</f>
+        <v/>
+      </c>
+      <c r="I29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$I$48</f>
+        <v/>
+      </c>
+      <c r="J29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$J$48</f>
+        <v/>
+      </c>
+      <c r="K29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$K$48</f>
+        <v/>
+      </c>
+      <c r="L29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$L$48</f>
+        <v/>
+      </c>
+      <c r="M29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$M$48</f>
+        <v/>
+      </c>
+      <c r="N29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$N$48</f>
+        <v/>
+      </c>
+      <c r="O29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$O$48</f>
+        <v/>
+      </c>
+      <c r="P29" s="14">
+        <f>'IN_FIN'!$D$34*'ENG_FCF'!$P$48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>سود قبل از مالیات (EBT)</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>FCF.ebt</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D30" s="14">
+        <f>'ENG_FCF'!$D$17-'ENG_FCF'!$D$26-'ENG_FCF'!$D$27-'ENG_FCF'!$D$28+'ENG_FCF'!$D$29</f>
+        <v/>
+      </c>
+      <c r="E30" s="14">
+        <f>'ENG_FCF'!$E$17-'ENG_FCF'!$E$26-'ENG_FCF'!$E$27-'ENG_FCF'!$E$28+'ENG_FCF'!$E$29</f>
+        <v/>
+      </c>
+      <c r="F30" s="14">
+        <f>'ENG_FCF'!$F$17-'ENG_FCF'!$F$26-'ENG_FCF'!$F$27-'ENG_FCF'!$F$28+'ENG_FCF'!$F$29</f>
+        <v/>
+      </c>
+      <c r="G30" s="14">
+        <f>'ENG_FCF'!$G$17-'ENG_FCF'!$G$26-'ENG_FCF'!$G$27-'ENG_FCF'!$G$28+'ENG_FCF'!$G$29</f>
+        <v/>
+      </c>
+      <c r="H30" s="14">
+        <f>'ENG_FCF'!$H$17-'ENG_FCF'!$H$26-'ENG_FCF'!$H$27-'ENG_FCF'!$H$28+'ENG_FCF'!$H$29</f>
+        <v/>
+      </c>
+      <c r="I30" s="14">
+        <f>'ENG_FCF'!$I$17-'ENG_FCF'!$I$26-'ENG_FCF'!$I$27-'ENG_FCF'!$I$28+'ENG_FCF'!$I$29</f>
+        <v/>
+      </c>
+      <c r="J30" s="14">
+        <f>'ENG_FCF'!$J$17-'ENG_FCF'!$J$26-'ENG_FCF'!$J$27-'ENG_FCF'!$J$28+'ENG_FCF'!$J$29</f>
+        <v/>
+      </c>
+      <c r="K30" s="14">
+        <f>'ENG_FCF'!$K$17-'ENG_FCF'!$K$26-'ENG_FCF'!$K$27-'ENG_FCF'!$K$28+'ENG_FCF'!$K$29</f>
+        <v/>
+      </c>
+      <c r="L30" s="14">
+        <f>'ENG_FCF'!$L$17-'ENG_FCF'!$L$26-'ENG_FCF'!$L$27-'ENG_FCF'!$L$28+'ENG_FCF'!$L$29</f>
+        <v/>
+      </c>
+      <c r="M30" s="14">
+        <f>'ENG_FCF'!$M$17-'ENG_FCF'!$M$26-'ENG_FCF'!$M$27-'ENG_FCF'!$M$28+'ENG_FCF'!$M$29</f>
+        <v/>
+      </c>
+      <c r="N30" s="14">
+        <f>'ENG_FCF'!$N$17-'ENG_FCF'!$N$26-'ENG_FCF'!$N$27-'ENG_FCF'!$N$28+'ENG_FCF'!$N$29</f>
+        <v/>
+      </c>
+      <c r="O30" s="14">
+        <f>'ENG_FCF'!$O$17-'ENG_FCF'!$O$26-'ENG_FCF'!$O$27-'ENG_FCF'!$O$28+'ENG_FCF'!$O$29</f>
+        <v/>
+      </c>
+      <c r="P30" s="14">
+        <f>'ENG_FCF'!$P$17-'ENG_FCF'!$P$26-'ENG_FCF'!$P$27-'ENG_FCF'!$P$28+'ENG_FCF'!$P$29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>مالیات بر درآمد</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>FCF.tax</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D31" s="14">
+        <f>MAX(0,'ENG_FCF'!$D$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+      <c r="E31" s="14">
+        <f>MAX(0,'ENG_FCF'!$E$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+      <c r="F31" s="14">
+        <f>MAX(0,'ENG_FCF'!$F$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+      <c r="G31" s="14">
+        <f>MAX(0,'ENG_FCF'!$G$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+      <c r="H31" s="14">
+        <f>MAX(0,'ENG_FCF'!$H$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+      <c r="I31" s="14">
+        <f>MAX(0,'ENG_FCF'!$I$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+      <c r="J31" s="14">
+        <f>MAX(0,'ENG_FCF'!$J$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+      <c r="K31" s="14">
+        <f>MAX(0,'ENG_FCF'!$K$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+      <c r="L31" s="14">
+        <f>MAX(0,'ENG_FCF'!$L$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+      <c r="M31" s="14">
+        <f>MAX(0,'ENG_FCF'!$M$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+      <c r="N31" s="14">
+        <f>MAX(0,'ENG_FCF'!$N$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+      <c r="O31" s="14">
+        <f>MAX(0,'ENG_FCF'!$O$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+      <c r="P31" s="14">
+        <f>MAX(0,'ENG_FCF'!$P$30)*'IN_MACRO'!$D$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>سود خالص</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>FCF.ni</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D32" s="14">
+        <f>'ENG_FCF'!$D$30-'ENG_FCF'!$D$31</f>
+        <v/>
+      </c>
+      <c r="E32" s="14">
+        <f>'ENG_FCF'!$E$30-'ENG_FCF'!$E$31</f>
+        <v/>
+      </c>
+      <c r="F32" s="14">
+        <f>'ENG_FCF'!$F$30-'ENG_FCF'!$F$31</f>
+        <v/>
+      </c>
+      <c r="G32" s="14">
+        <f>'ENG_FCF'!$G$30-'ENG_FCF'!$G$31</f>
+        <v/>
+      </c>
+      <c r="H32" s="14">
+        <f>'ENG_FCF'!$H$30-'ENG_FCF'!$H$31</f>
+        <v/>
+      </c>
+      <c r="I32" s="14">
+        <f>'ENG_FCF'!$I$30-'ENG_FCF'!$I$31</f>
+        <v/>
+      </c>
+      <c r="J32" s="14">
+        <f>'ENG_FCF'!$J$30-'ENG_FCF'!$J$31</f>
+        <v/>
+      </c>
+      <c r="K32" s="14">
+        <f>'ENG_FCF'!$K$30-'ENG_FCF'!$K$31</f>
+        <v/>
+      </c>
+      <c r="L32" s="14">
+        <f>'ENG_FCF'!$L$30-'ENG_FCF'!$L$31</f>
+        <v/>
+      </c>
+      <c r="M32" s="14">
+        <f>'ENG_FCF'!$M$30-'ENG_FCF'!$M$31</f>
+        <v/>
+      </c>
+      <c r="N32" s="14">
+        <f>'ENG_FCF'!$N$30-'ENG_FCF'!$N$31</f>
+        <v/>
+      </c>
+      <c r="O32" s="14">
+        <f>'ENG_FCF'!$O$30-'ENG_FCF'!$O$31</f>
+        <v/>
+      </c>
+      <c r="P32" s="14">
+        <f>'ENG_FCF'!$P$30-'ENG_FCF'!$P$31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>ج) جریان‌های نقدی آزاد</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="7" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="7" t="n"/>
+      <c r="P34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NOPAT</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>FCF.nopat</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D35" s="14">
+        <f>@@ENG_COST|EC.nopat|0@@</f>
+        <v/>
+      </c>
+      <c r="E35" s="14">
+        <f>@@ENG_COST|EC.nopat|1@@</f>
+        <v/>
+      </c>
+      <c r="F35" s="14">
+        <f>@@ENG_COST|EC.nopat|2@@</f>
+        <v/>
+      </c>
+      <c r="G35" s="14">
+        <f>@@ENG_COST|EC.nopat|3@@</f>
+        <v/>
+      </c>
+      <c r="H35" s="14">
+        <f>@@ENG_COST|EC.nopat|4@@</f>
+        <v/>
+      </c>
+      <c r="I35" s="14">
+        <f>@@ENG_COST|EC.nopat|5@@</f>
+        <v/>
+      </c>
+      <c r="J35" s="14">
+        <f>@@ENG_COST|EC.nopat|6@@</f>
+        <v/>
+      </c>
+      <c r="K35" s="14">
+        <f>@@ENG_COST|EC.nopat|7@@</f>
+        <v/>
+      </c>
+      <c r="L35" s="14">
+        <f>@@ENG_COST|EC.nopat|8@@</f>
+        <v/>
+      </c>
+      <c r="M35" s="14">
+        <f>@@ENG_COST|EC.nopat|9@@</f>
+        <v/>
+      </c>
+      <c r="N35" s="14">
+        <f>@@ENG_COST|EC.nopat|10@@</f>
+        <v/>
+      </c>
+      <c r="O35" s="14">
+        <f>@@ENG_COST|EC.nopat|11@@</f>
+        <v/>
+      </c>
+      <c r="P35" s="14">
+        <f>@@ENG_COST|EC.nopat|12@@</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>جریان نقد عملیاتیِ عملیاتی (NOPAT + استهلاک)</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>FCF.opcf</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D36" s="14">
+        <f>'ENG_FCF'!$D$35+'ENG_FCF'!$D$16</f>
+        <v/>
+      </c>
+      <c r="E36" s="14">
+        <f>'ENG_FCF'!$E$35+'ENG_FCF'!$E$16</f>
+        <v/>
+      </c>
+      <c r="F36" s="14">
+        <f>'ENG_FCF'!$F$35+'ENG_FCF'!$F$16</f>
+        <v/>
+      </c>
+      <c r="G36" s="14">
+        <f>'ENG_FCF'!$G$35+'ENG_FCF'!$G$16</f>
+        <v/>
+      </c>
+      <c r="H36" s="14">
+        <f>'ENG_FCF'!$H$35+'ENG_FCF'!$H$16</f>
+        <v/>
+      </c>
+      <c r="I36" s="14">
+        <f>'ENG_FCF'!$I$35+'ENG_FCF'!$I$16</f>
+        <v/>
+      </c>
+      <c r="J36" s="14">
+        <f>'ENG_FCF'!$J$35+'ENG_FCF'!$J$16</f>
+        <v/>
+      </c>
+      <c r="K36" s="14">
+        <f>'ENG_FCF'!$K$35+'ENG_FCF'!$K$16</f>
+        <v/>
+      </c>
+      <c r="L36" s="14">
+        <f>'ENG_FCF'!$L$35+'ENG_FCF'!$L$16</f>
+        <v/>
+      </c>
+      <c r="M36" s="14">
+        <f>'ENG_FCF'!$M$35+'ENG_FCF'!$M$16</f>
+        <v/>
+      </c>
+      <c r="N36" s="14">
+        <f>'ENG_FCF'!$N$35+'ENG_FCF'!$N$16</f>
+        <v/>
+      </c>
+      <c r="O36" s="14">
+        <f>'ENG_FCF'!$O$35+'ENG_FCF'!$O$16</f>
+        <v/>
+      </c>
+      <c r="P36" s="14">
+        <f>'ENG_FCF'!$P$35+'ENG_FCF'!$P$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>تغییرات سرمایه در گردش</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>FCF.dwc</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D37" s="14">
+        <f>'ENG_WC'!$D$19</f>
+        <v/>
+      </c>
+      <c r="E37" s="14">
+        <f>'ENG_WC'!$E$19</f>
+        <v/>
+      </c>
+      <c r="F37" s="14">
+        <f>'ENG_WC'!$F$19</f>
+        <v/>
+      </c>
+      <c r="G37" s="14">
+        <f>'ENG_WC'!$G$19</f>
+        <v/>
+      </c>
+      <c r="H37" s="14">
+        <f>'ENG_WC'!$H$19</f>
+        <v/>
+      </c>
+      <c r="I37" s="14">
+        <f>'ENG_WC'!$I$19</f>
+        <v/>
+      </c>
+      <c r="J37" s="14">
+        <f>'ENG_WC'!$J$19</f>
+        <v/>
+      </c>
+      <c r="K37" s="14">
+        <f>'ENG_WC'!$K$19</f>
+        <v/>
+      </c>
+      <c r="L37" s="14">
+        <f>'ENG_WC'!$L$19</f>
+        <v/>
+      </c>
+      <c r="M37" s="14">
+        <f>'ENG_WC'!$M$19</f>
+        <v/>
+      </c>
+      <c r="N37" s="14">
+        <f>'ENG_WC'!$N$19</f>
+        <v/>
+      </c>
+      <c r="O37" s="14">
+        <f>'ENG_WC'!$O$19</f>
+        <v/>
+      </c>
+      <c r="P37" s="14">
+        <f>'ENG_WC'!$P$19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری ثابت و جایگزینی</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>FCF.capex</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D38" s="14">
+        <f>'ENG_CAPEX'!$D$21+'ENG_CAPEX'!$D$42</f>
+        <v/>
+      </c>
+      <c r="E38" s="14">
+        <f>'ENG_CAPEX'!$E$21+'ENG_CAPEX'!$E$42</f>
+        <v/>
+      </c>
+      <c r="F38" s="14">
+        <f>'ENG_CAPEX'!$F$21+'ENG_CAPEX'!$F$42</f>
+        <v/>
+      </c>
+      <c r="G38" s="14">
+        <f>'ENG_CAPEX'!$G$21+'ENG_CAPEX'!$G$42</f>
+        <v/>
+      </c>
+      <c r="H38" s="14">
+        <f>'ENG_CAPEX'!$H$21+'ENG_CAPEX'!$H$42</f>
+        <v/>
+      </c>
+      <c r="I38" s="14">
+        <f>'ENG_CAPEX'!$I$21+'ENG_CAPEX'!$I$42</f>
+        <v/>
+      </c>
+      <c r="J38" s="14">
+        <f>'ENG_CAPEX'!$J$21+'ENG_CAPEX'!$J$42</f>
+        <v/>
+      </c>
+      <c r="K38" s="14">
+        <f>'ENG_CAPEX'!$K$21+'ENG_CAPEX'!$K$42</f>
+        <v/>
+      </c>
+      <c r="L38" s="14">
+        <f>'ENG_CAPEX'!$L$21+'ENG_CAPEX'!$L$42</f>
+        <v/>
+      </c>
+      <c r="M38" s="14">
+        <f>'ENG_CAPEX'!$M$21+'ENG_CAPEX'!$M$42</f>
+        <v/>
+      </c>
+      <c r="N38" s="14">
+        <f>'ENG_CAPEX'!$N$21+'ENG_CAPEX'!$N$42</f>
+        <v/>
+      </c>
+      <c r="O38" s="14">
+        <f>'ENG_CAPEX'!$O$21+'ENG_CAPEX'!$O$42</f>
+        <v/>
+      </c>
+      <c r="P38" s="14">
+        <f>'ENG_CAPEX'!$P$21+'ENG_CAPEX'!$P$42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>جریان نقد آزاد پروژه (FCFF)</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>FCF.fcff</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D39" s="14">
+        <f>'ENG_FCF'!$D$36-'ENG_FCF'!$D$38-'ENG_FCF'!$D$37</f>
+        <v/>
+      </c>
+      <c r="E39" s="14">
+        <f>'ENG_FCF'!$E$36-'ENG_FCF'!$E$38-'ENG_FCF'!$E$37</f>
+        <v/>
+      </c>
+      <c r="F39" s="14">
+        <f>'ENG_FCF'!$F$36-'ENG_FCF'!$F$38-'ENG_FCF'!$F$37</f>
+        <v/>
+      </c>
+      <c r="G39" s="14">
+        <f>'ENG_FCF'!$G$36-'ENG_FCF'!$G$38-'ENG_FCF'!$G$37</f>
+        <v/>
+      </c>
+      <c r="H39" s="14">
+        <f>'ENG_FCF'!$H$36-'ENG_FCF'!$H$38-'ENG_FCF'!$H$37</f>
+        <v/>
+      </c>
+      <c r="I39" s="14">
+        <f>'ENG_FCF'!$I$36-'ENG_FCF'!$I$38-'ENG_FCF'!$I$37</f>
+        <v/>
+      </c>
+      <c r="J39" s="14">
+        <f>'ENG_FCF'!$J$36-'ENG_FCF'!$J$38-'ENG_FCF'!$J$37</f>
+        <v/>
+      </c>
+      <c r="K39" s="14">
+        <f>'ENG_FCF'!$K$36-'ENG_FCF'!$K$38-'ENG_FCF'!$K$37</f>
+        <v/>
+      </c>
+      <c r="L39" s="14">
+        <f>'ENG_FCF'!$L$36-'ENG_FCF'!$L$38-'ENG_FCF'!$L$37</f>
+        <v/>
+      </c>
+      <c r="M39" s="14">
+        <f>'ENG_FCF'!$M$36-'ENG_FCF'!$M$38-'ENG_FCF'!$M$37</f>
+        <v/>
+      </c>
+      <c r="N39" s="14">
+        <f>'ENG_FCF'!$N$36-'ENG_FCF'!$N$38-'ENG_FCF'!$N$37</f>
+        <v/>
+      </c>
+      <c r="O39" s="14">
+        <f>'ENG_FCF'!$O$36-'ENG_FCF'!$O$38-'ENG_FCF'!$O$37</f>
+        <v/>
+      </c>
+      <c r="P39" s="14">
+        <f>'ENG_FCF'!$P$36-'ENG_FCF'!$P$38-'ENG_FCF'!$P$37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FCFF تجمعی</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>FCF.fcff_cum</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D40" s="14">
+        <f>'ENG_FCF'!$D$39</f>
+        <v/>
+      </c>
+      <c r="E40" s="14">
+        <f>'ENG_FCF'!$D$40+'ENG_FCF'!$E$39</f>
+        <v/>
+      </c>
+      <c r="F40" s="14">
+        <f>'ENG_FCF'!$E$40+'ENG_FCF'!$F$39</f>
+        <v/>
+      </c>
+      <c r="G40" s="14">
+        <f>'ENG_FCF'!$F$40+'ENG_FCF'!$G$39</f>
+        <v/>
+      </c>
+      <c r="H40" s="14">
+        <f>'ENG_FCF'!$G$40+'ENG_FCF'!$H$39</f>
+        <v/>
+      </c>
+      <c r="I40" s="14">
+        <f>'ENG_FCF'!$H$40+'ENG_FCF'!$I$39</f>
+        <v/>
+      </c>
+      <c r="J40" s="14">
+        <f>'ENG_FCF'!$I$40+'ENG_FCF'!$J$39</f>
+        <v/>
+      </c>
+      <c r="K40" s="14">
+        <f>'ENG_FCF'!$J$40+'ENG_FCF'!$K$39</f>
+        <v/>
+      </c>
+      <c r="L40" s="14">
+        <f>'ENG_FCF'!$K$40+'ENG_FCF'!$L$39</f>
+        <v/>
+      </c>
+      <c r="M40" s="14">
+        <f>'ENG_FCF'!$L$40+'ENG_FCF'!$M$39</f>
+        <v/>
+      </c>
+      <c r="N40" s="14">
+        <f>'ENG_FCF'!$M$40+'ENG_FCF'!$N$39</f>
+        <v/>
+      </c>
+      <c r="O40" s="14">
+        <f>'ENG_FCF'!$N$40+'ENG_FCF'!$O$39</f>
+        <v/>
+      </c>
+      <c r="P40" s="14">
+        <f>'ENG_FCF'!$O$40+'ENG_FCF'!$P$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FCFF تکرارپذیر (بدون CAPEX)</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>FCF.fcff_rep</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D41" s="14">
+        <f>'ENG_FCF'!$D$36-'ENG_FCF'!$D$37</f>
+        <v/>
+      </c>
+      <c r="E41" s="14">
+        <f>'ENG_FCF'!$E$36-'ENG_FCF'!$E$37</f>
+        <v/>
+      </c>
+      <c r="F41" s="14">
+        <f>'ENG_FCF'!$F$36-'ENG_FCF'!$F$37</f>
+        <v/>
+      </c>
+      <c r="G41" s="14">
+        <f>'ENG_FCF'!$G$36-'ENG_FCF'!$G$37</f>
+        <v/>
+      </c>
+      <c r="H41" s="14">
+        <f>'ENG_FCF'!$H$36-'ENG_FCF'!$H$37</f>
+        <v/>
+      </c>
+      <c r="I41" s="14">
+        <f>'ENG_FCF'!$I$36-'ENG_FCF'!$I$37</f>
+        <v/>
+      </c>
+      <c r="J41" s="14">
+        <f>'ENG_FCF'!$J$36-'ENG_FCF'!$J$37</f>
+        <v/>
+      </c>
+      <c r="K41" s="14">
+        <f>'ENG_FCF'!$K$36-'ENG_FCF'!$K$37</f>
+        <v/>
+      </c>
+      <c r="L41" s="14">
+        <f>'ENG_FCF'!$L$36-'ENG_FCF'!$L$37</f>
+        <v/>
+      </c>
+      <c r="M41" s="14">
+        <f>'ENG_FCF'!$M$36-'ENG_FCF'!$M$37</f>
+        <v/>
+      </c>
+      <c r="N41" s="14">
+        <f>'ENG_FCF'!$N$36-'ENG_FCF'!$N$37</f>
+        <v/>
+      </c>
+      <c r="O41" s="14">
+        <f>'ENG_FCF'!$O$36-'ENG_FCF'!$O$37</f>
+        <v/>
+      </c>
+      <c r="P41" s="14">
+        <f>'ENG_FCF'!$P$36-'ENG_FCF'!$P$37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>جریان نقد در دسترس خدمت دین (CFADS)</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>FCF.cfads</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D42" s="14">
+        <f>'ENG_FCF'!$D$15-'ENG_FCF'!$D$31-'ENG_FCF'!$D$37</f>
+        <v/>
+      </c>
+      <c r="E42" s="14">
+        <f>'ENG_FCF'!$E$15-'ENG_FCF'!$E$31-'ENG_FCF'!$E$37</f>
+        <v/>
+      </c>
+      <c r="F42" s="14">
+        <f>'ENG_FCF'!$F$15-'ENG_FCF'!$F$31-'ENG_FCF'!$F$37</f>
+        <v/>
+      </c>
+      <c r="G42" s="14">
+        <f>'ENG_FCF'!$G$15-'ENG_FCF'!$G$31-'ENG_FCF'!$G$37</f>
+        <v/>
+      </c>
+      <c r="H42" s="14">
+        <f>'ENG_FCF'!$H$15-'ENG_FCF'!$H$31-'ENG_FCF'!$H$37</f>
+        <v/>
+      </c>
+      <c r="I42" s="14">
+        <f>'ENG_FCF'!$I$15-'ENG_FCF'!$I$31-'ENG_FCF'!$I$37</f>
+        <v/>
+      </c>
+      <c r="J42" s="14">
+        <f>'ENG_FCF'!$J$15-'ENG_FCF'!$J$31-'ENG_FCF'!$J$37</f>
+        <v/>
+      </c>
+      <c r="K42" s="14">
+        <f>'ENG_FCF'!$K$15-'ENG_FCF'!$K$31-'ENG_FCF'!$K$37</f>
+        <v/>
+      </c>
+      <c r="L42" s="14">
+        <f>'ENG_FCF'!$L$15-'ENG_FCF'!$L$31-'ENG_FCF'!$L$37</f>
+        <v/>
+      </c>
+      <c r="M42" s="14">
+        <f>'ENG_FCF'!$M$15-'ENG_FCF'!$M$31-'ENG_FCF'!$M$37</f>
+        <v/>
+      </c>
+      <c r="N42" s="14">
+        <f>'ENG_FCF'!$N$15-'ENG_FCF'!$N$31-'ENG_FCF'!$N$37</f>
+        <v/>
+      </c>
+      <c r="O42" s="14">
+        <f>'ENG_FCF'!$O$15-'ENG_FCF'!$O$31-'ENG_FCF'!$O$37</f>
+        <v/>
+      </c>
+      <c r="P42" s="14">
+        <f>'ENG_FCF'!$P$15-'ENG_FCF'!$P$31-'ENG_FCF'!$P$37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>خدمت دین (اصل + سود + کارمزد + سود کوتاه‌مدت)</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>FCF.debt_service</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D43" s="14">
+        <f>'ENG_FCF'!$D$24+'ENG_FCF'!$D$26+'ENG_FCF'!$D$27+'ENG_FCF'!$D$28</f>
+        <v/>
+      </c>
+      <c r="E43" s="14">
+        <f>'ENG_FCF'!$E$24+'ENG_FCF'!$E$26+'ENG_FCF'!$E$27+'ENG_FCF'!$E$28</f>
+        <v/>
+      </c>
+      <c r="F43" s="14">
+        <f>'ENG_FCF'!$F$24+'ENG_FCF'!$F$26+'ENG_FCF'!$F$27+'ENG_FCF'!$F$28</f>
+        <v/>
+      </c>
+      <c r="G43" s="14">
+        <f>'ENG_FCF'!$G$24+'ENG_FCF'!$G$26+'ENG_FCF'!$G$27+'ENG_FCF'!$G$28</f>
+        <v/>
+      </c>
+      <c r="H43" s="14">
+        <f>'ENG_FCF'!$H$24+'ENG_FCF'!$H$26+'ENG_FCF'!$H$27+'ENG_FCF'!$H$28</f>
+        <v/>
+      </c>
+      <c r="I43" s="14">
+        <f>'ENG_FCF'!$I$24+'ENG_FCF'!$I$26+'ENG_FCF'!$I$27+'ENG_FCF'!$I$28</f>
+        <v/>
+      </c>
+      <c r="J43" s="14">
+        <f>'ENG_FCF'!$J$24+'ENG_FCF'!$J$26+'ENG_FCF'!$J$27+'ENG_FCF'!$J$28</f>
+        <v/>
+      </c>
+      <c r="K43" s="14">
+        <f>'ENG_FCF'!$K$24+'ENG_FCF'!$K$26+'ENG_FCF'!$K$27+'ENG_FCF'!$K$28</f>
+        <v/>
+      </c>
+      <c r="L43" s="14">
+        <f>'ENG_FCF'!$L$24+'ENG_FCF'!$L$26+'ENG_FCF'!$L$27+'ENG_FCF'!$L$28</f>
+        <v/>
+      </c>
+      <c r="M43" s="14">
+        <f>'ENG_FCF'!$M$24+'ENG_FCF'!$M$26+'ENG_FCF'!$M$27+'ENG_FCF'!$M$28</f>
+        <v/>
+      </c>
+      <c r="N43" s="14">
+        <f>'ENG_FCF'!$N$24+'ENG_FCF'!$N$26+'ENG_FCF'!$N$27+'ENG_FCF'!$N$28</f>
+        <v/>
+      </c>
+      <c r="O43" s="14">
+        <f>'ENG_FCF'!$O$24+'ENG_FCF'!$O$26+'ENG_FCF'!$O$27+'ENG_FCF'!$O$28</f>
+        <v/>
+      </c>
+      <c r="P43" s="14">
+        <f>'ENG_FCF'!$P$24+'ENG_FCF'!$P$26+'ENG_FCF'!$P$27+'ENG_FCF'!$P$28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DSCR</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>FCF.dscr</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>ضریب</t>
+        </is>
+      </c>
+      <c r="D44" s="12">
+        <f>IFERROR('ENG_FCF'!$D$42/'ENG_FCF'!$D$43,"─")</f>
+        <v/>
+      </c>
+      <c r="E44" s="12">
+        <f>IFERROR('ENG_FCF'!$E$42/'ENG_FCF'!$E$43,"─")</f>
+        <v/>
+      </c>
+      <c r="F44" s="12">
+        <f>IFERROR('ENG_FCF'!$F$42/'ENG_FCF'!$F$43,"─")</f>
+        <v/>
+      </c>
+      <c r="G44" s="12">
+        <f>IFERROR('ENG_FCF'!$G$42/'ENG_FCF'!$G$43,"─")</f>
+        <v/>
+      </c>
+      <c r="H44" s="12">
+        <f>IFERROR('ENG_FCF'!$H$42/'ENG_FCF'!$H$43,"─")</f>
+        <v/>
+      </c>
+      <c r="I44" s="12">
+        <f>IFERROR('ENG_FCF'!$I$42/'ENG_FCF'!$I$43,"─")</f>
+        <v/>
+      </c>
+      <c r="J44" s="12">
+        <f>IFERROR('ENG_FCF'!$J$42/'ENG_FCF'!$J$43,"─")</f>
+        <v/>
+      </c>
+      <c r="K44" s="12">
+        <f>IFERROR('ENG_FCF'!$K$42/'ENG_FCF'!$K$43,"─")</f>
+        <v/>
+      </c>
+      <c r="L44" s="12">
+        <f>IFERROR('ENG_FCF'!$L$42/'ENG_FCF'!$L$43,"─")</f>
+        <v/>
+      </c>
+      <c r="M44" s="12">
+        <f>IFERROR('ENG_FCF'!$M$42/'ENG_FCF'!$M$43,"─")</f>
+        <v/>
+      </c>
+      <c r="N44" s="12">
+        <f>IFERROR('ENG_FCF'!$N$42/'ENG_FCF'!$N$43,"─")</f>
+        <v/>
+      </c>
+      <c r="O44" s="12">
+        <f>IFERROR('ENG_FCF'!$O$42/'ENG_FCF'!$O$43,"─")</f>
+        <v/>
+      </c>
+      <c r="P44" s="12">
+        <f>IFERROR('ENG_FCF'!$P$42/'ENG_FCF'!$P$43,"─")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>نسبت پوشش بهره (ICR)</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>FCF.icr</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>ضریب</t>
+        </is>
+      </c>
+      <c r="D45" s="12">
+        <f>IFERROR('ENG_FCF'!$D$17/'ENG_FCF'!$D$26,"─")</f>
+        <v/>
+      </c>
+      <c r="E45" s="12">
+        <f>IFERROR('ENG_FCF'!$E$17/'ENG_FCF'!$E$26,"─")</f>
+        <v/>
+      </c>
+      <c r="F45" s="12">
+        <f>IFERROR('ENG_FCF'!$F$17/'ENG_FCF'!$F$26,"─")</f>
+        <v/>
+      </c>
+      <c r="G45" s="12">
+        <f>IFERROR('ENG_FCF'!$G$17/'ENG_FCF'!$G$26,"─")</f>
+        <v/>
+      </c>
+      <c r="H45" s="12">
+        <f>IFERROR('ENG_FCF'!$H$17/'ENG_FCF'!$H$26,"─")</f>
+        <v/>
+      </c>
+      <c r="I45" s="12">
+        <f>IFERROR('ENG_FCF'!$I$17/'ENG_FCF'!$I$26,"─")</f>
+        <v/>
+      </c>
+      <c r="J45" s="12">
+        <f>IFERROR('ENG_FCF'!$J$17/'ENG_FCF'!$J$26,"─")</f>
+        <v/>
+      </c>
+      <c r="K45" s="12">
+        <f>IFERROR('ENG_FCF'!$K$17/'ENG_FCF'!$K$26,"─")</f>
+        <v/>
+      </c>
+      <c r="L45" s="12">
+        <f>IFERROR('ENG_FCF'!$L$17/'ENG_FCF'!$L$26,"─")</f>
+        <v/>
+      </c>
+      <c r="M45" s="12">
+        <f>IFERROR('ENG_FCF'!$M$17/'ENG_FCF'!$M$26,"─")</f>
+        <v/>
+      </c>
+      <c r="N45" s="12">
+        <f>IFERROR('ENG_FCF'!$N$17/'ENG_FCF'!$N$26,"─")</f>
+        <v/>
+      </c>
+      <c r="O45" s="12">
+        <f>IFERROR('ENG_FCF'!$O$17/'ENG_FCF'!$O$26,"─")</f>
+        <v/>
+      </c>
+      <c r="P45" s="12">
+        <f>IFERROR('ENG_FCF'!$P$17/'ENG_FCF'!$P$26,"─")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>د) جریان وجوه نقد، آورده نقدی و تقسیم سود</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="7" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+      <c r="O47" s="7" t="n"/>
+      <c r="P47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>نقد افتتاحیه</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>FCF.cash_open</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D48" s="14">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E48" s="14">
+        <f>'ENG_FCF'!$D$56</f>
+        <v/>
+      </c>
+      <c r="F48" s="14">
+        <f>'ENG_FCF'!$E$56</f>
+        <v/>
+      </c>
+      <c r="G48" s="14">
+        <f>'ENG_FCF'!$F$56</f>
+        <v/>
+      </c>
+      <c r="H48" s="14">
+        <f>'ENG_FCF'!$G$56</f>
+        <v/>
+      </c>
+      <c r="I48" s="14">
+        <f>'ENG_FCF'!$H$56</f>
+        <v/>
+      </c>
+      <c r="J48" s="14">
+        <f>'ENG_FCF'!$I$56</f>
+        <v/>
+      </c>
+      <c r="K48" s="14">
+        <f>'ENG_FCF'!$J$56</f>
+        <v/>
+      </c>
+      <c r="L48" s="14">
+        <f>'ENG_FCF'!$K$56</f>
+        <v/>
+      </c>
+      <c r="M48" s="14">
+        <f>'ENG_FCF'!$L$56</f>
+        <v/>
+      </c>
+      <c r="N48" s="14">
+        <f>'ENG_FCF'!$M$56</f>
+        <v/>
+      </c>
+      <c r="O48" s="14">
+        <f>'ENG_FCF'!$N$56</f>
+        <v/>
+      </c>
+      <c r="P48" s="14">
+        <f>'ENG_FCF'!$O$56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>جریان نقد عملیاتی</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>FCF.cfo</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D49" s="14">
+        <f>'ENG_FCF'!$D$32+'ENG_FCF'!$D$16-'ENG_FCF'!$D$37</f>
+        <v/>
+      </c>
+      <c r="E49" s="14">
+        <f>'ENG_FCF'!$E$32+'ENG_FCF'!$E$16-'ENG_FCF'!$E$37</f>
+        <v/>
+      </c>
+      <c r="F49" s="14">
+        <f>'ENG_FCF'!$F$32+'ENG_FCF'!$F$16-'ENG_FCF'!$F$37</f>
+        <v/>
+      </c>
+      <c r="G49" s="14">
+        <f>'ENG_FCF'!$G$32+'ENG_FCF'!$G$16-'ENG_FCF'!$G$37</f>
+        <v/>
+      </c>
+      <c r="H49" s="14">
+        <f>'ENG_FCF'!$H$32+'ENG_FCF'!$H$16-'ENG_FCF'!$H$37</f>
+        <v/>
+      </c>
+      <c r="I49" s="14">
+        <f>'ENG_FCF'!$I$32+'ENG_FCF'!$I$16-'ENG_FCF'!$I$37</f>
+        <v/>
+      </c>
+      <c r="J49" s="14">
+        <f>'ENG_FCF'!$J$32+'ENG_FCF'!$J$16-'ENG_FCF'!$J$37</f>
+        <v/>
+      </c>
+      <c r="K49" s="14">
+        <f>'ENG_FCF'!$K$32+'ENG_FCF'!$K$16-'ENG_FCF'!$K$37</f>
+        <v/>
+      </c>
+      <c r="L49" s="14">
+        <f>'ENG_FCF'!$L$32+'ENG_FCF'!$L$16-'ENG_FCF'!$L$37</f>
+        <v/>
+      </c>
+      <c r="M49" s="14">
+        <f>'ENG_FCF'!$M$32+'ENG_FCF'!$M$16-'ENG_FCF'!$M$37</f>
+        <v/>
+      </c>
+      <c r="N49" s="14">
+        <f>'ENG_FCF'!$N$32+'ENG_FCF'!$N$16-'ENG_FCF'!$N$37</f>
+        <v/>
+      </c>
+      <c r="O49" s="14">
+        <f>'ENG_FCF'!$O$32+'ENG_FCF'!$O$16-'ENG_FCF'!$O$37</f>
+        <v/>
+      </c>
+      <c r="P49" s="14">
+        <f>'ENG_FCF'!$P$32+'ENG_FCF'!$P$16-'ENG_FCF'!$P$37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>جریان نقد سرمایه‌گذاری</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>FCF.cfi</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D50" s="14">
+        <f>-'ENG_FCF'!$D$38</f>
+        <v/>
+      </c>
+      <c r="E50" s="14">
+        <f>-'ENG_FCF'!$E$38</f>
+        <v/>
+      </c>
+      <c r="F50" s="14">
+        <f>-'ENG_FCF'!$F$38</f>
+        <v/>
+      </c>
+      <c r="G50" s="14">
+        <f>-'ENG_FCF'!$G$38</f>
+        <v/>
+      </c>
+      <c r="H50" s="14">
+        <f>-'ENG_FCF'!$H$38</f>
+        <v/>
+      </c>
+      <c r="I50" s="14">
+        <f>-'ENG_FCF'!$I$38</f>
+        <v/>
+      </c>
+      <c r="J50" s="14">
+        <f>-'ENG_FCF'!$J$38</f>
+        <v/>
+      </c>
+      <c r="K50" s="14">
+        <f>-'ENG_FCF'!$K$38</f>
+        <v/>
+      </c>
+      <c r="L50" s="14">
+        <f>-'ENG_FCF'!$L$38</f>
+        <v/>
+      </c>
+      <c r="M50" s="14">
+        <f>-'ENG_FCF'!$M$38</f>
+        <v/>
+      </c>
+      <c r="N50" s="14">
+        <f>-'ENG_FCF'!$N$38</f>
+        <v/>
+      </c>
+      <c r="O50" s="14">
+        <f>-'ENG_FCF'!$O$38</f>
+        <v/>
+      </c>
+      <c r="P50" s="14">
+        <f>-'ENG_FCF'!$P$38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>وجوه در دسترس پیش از تأمین مالی</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>FCF.cash_pre</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D51" s="14">
+        <f>'ENG_FCF'!$D$48+'ENG_FCF'!$D$49+'ENG_FCF'!$D$50+'ENG_FCF'!$D$21-'ENG_FCF'!$D$24+'ENG_WC'!$D$21</f>
+        <v/>
+      </c>
+      <c r="E51" s="14">
+        <f>'ENG_FCF'!$E$48+'ENG_FCF'!$E$49+'ENG_FCF'!$E$50+'ENG_FCF'!$E$21-'ENG_FCF'!$E$24+'ENG_WC'!$E$21</f>
+        <v/>
+      </c>
+      <c r="F51" s="14">
+        <f>'ENG_FCF'!$F$48+'ENG_FCF'!$F$49+'ENG_FCF'!$F$50+'ENG_FCF'!$F$21-'ENG_FCF'!$F$24+'ENG_WC'!$F$21</f>
+        <v/>
+      </c>
+      <c r="G51" s="14">
+        <f>'ENG_FCF'!$G$48+'ENG_FCF'!$G$49+'ENG_FCF'!$G$50+'ENG_FCF'!$G$21-'ENG_FCF'!$G$24+'ENG_WC'!$G$21</f>
+        <v/>
+      </c>
+      <c r="H51" s="14">
+        <f>'ENG_FCF'!$H$48+'ENG_FCF'!$H$49+'ENG_FCF'!$H$50+'ENG_FCF'!$H$21-'ENG_FCF'!$H$24+'ENG_WC'!$H$21</f>
+        <v/>
+      </c>
+      <c r="I51" s="14">
+        <f>'ENG_FCF'!$I$48+'ENG_FCF'!$I$49+'ENG_FCF'!$I$50+'ENG_FCF'!$I$21-'ENG_FCF'!$I$24+'ENG_WC'!$I$21</f>
+        <v/>
+      </c>
+      <c r="J51" s="14">
+        <f>'ENG_FCF'!$J$48+'ENG_FCF'!$J$49+'ENG_FCF'!$J$50+'ENG_FCF'!$J$21-'ENG_FCF'!$J$24+'ENG_WC'!$J$21</f>
+        <v/>
+      </c>
+      <c r="K51" s="14">
+        <f>'ENG_FCF'!$K$48+'ENG_FCF'!$K$49+'ENG_FCF'!$K$50+'ENG_FCF'!$K$21-'ENG_FCF'!$K$24+'ENG_WC'!$K$21</f>
+        <v/>
+      </c>
+      <c r="L51" s="14">
+        <f>'ENG_FCF'!$L$48+'ENG_FCF'!$L$49+'ENG_FCF'!$L$50+'ENG_FCF'!$L$21-'ENG_FCF'!$L$24+'ENG_WC'!$L$21</f>
+        <v/>
+      </c>
+      <c r="M51" s="14">
+        <f>'ENG_FCF'!$M$48+'ENG_FCF'!$M$49+'ENG_FCF'!$M$50+'ENG_FCF'!$M$21-'ENG_FCF'!$M$24+'ENG_WC'!$M$21</f>
+        <v/>
+      </c>
+      <c r="N51" s="14">
+        <f>'ENG_FCF'!$N$48+'ENG_FCF'!$N$49+'ENG_FCF'!$N$50+'ENG_FCF'!$N$21-'ENG_FCF'!$N$24+'ENG_WC'!$N$21</f>
+        <v/>
+      </c>
+      <c r="O51" s="14">
+        <f>'ENG_FCF'!$O$48+'ENG_FCF'!$O$49+'ENG_FCF'!$O$50+'ENG_FCF'!$O$21-'ENG_FCF'!$O$24+'ENG_WC'!$O$21</f>
+        <v/>
+      </c>
+      <c r="P51" s="14">
+        <f>'ENG_FCF'!$P$48+'ENG_FCF'!$P$49+'ENG_FCF'!$P$50+'ENG_FCF'!$P$21-'ENG_FCF'!$P$24+'ENG_WC'!$P$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>سود تقسیمی</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>FCF.div</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$D$32),MAX(0,'ENG_FCF'!$D$51-'ENG_WC'!$D$29))</f>
+        <v/>
+      </c>
+      <c r="E52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$E$32),MAX(0,'ENG_FCF'!$E$51-'ENG_WC'!$E$29))</f>
+        <v/>
+      </c>
+      <c r="F52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$F$32),MAX(0,'ENG_FCF'!$F$51-'ENG_WC'!$F$29))</f>
+        <v/>
+      </c>
+      <c r="G52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$G$32),MAX(0,'ENG_FCF'!$G$51-'ENG_WC'!$G$29))</f>
+        <v/>
+      </c>
+      <c r="H52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$H$32),MAX(0,'ENG_FCF'!$H$51-'ENG_WC'!$H$29))</f>
+        <v/>
+      </c>
+      <c r="I52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$I$32),MAX(0,'ENG_FCF'!$I$51-'ENG_WC'!$I$29))</f>
+        <v/>
+      </c>
+      <c r="J52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$J$32),MAX(0,'ENG_FCF'!$J$51-'ENG_WC'!$J$29))</f>
+        <v/>
+      </c>
+      <c r="K52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$K$32),MAX(0,'ENG_FCF'!$K$51-'ENG_WC'!$K$29))</f>
+        <v/>
+      </c>
+      <c r="L52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$L$32),MAX(0,'ENG_FCF'!$L$51-'ENG_WC'!$L$29))</f>
+        <v/>
+      </c>
+      <c r="M52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$M$32),MAX(0,'ENG_FCF'!$M$51-'ENG_WC'!$M$29))</f>
+        <v/>
+      </c>
+      <c r="N52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$N$32),MAX(0,'ENG_FCF'!$N$51-'ENG_WC'!$N$29))</f>
+        <v/>
+      </c>
+      <c r="O52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$O$32),MAX(0,'ENG_FCF'!$O$51-'ENG_WC'!$O$29))</f>
+        <v/>
+      </c>
+      <c r="P52" s="14">
+        <f>MIN('IN_FIN'!$D$33*MAX(0,'ENG_FCF'!$P$32),MAX(0,'ENG_FCF'!$P$51-'ENG_WC'!$P$29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>آورده نقدی سهامداران (تأمین کسری نقد)</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>FCF.equity_in</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D53" s="14">
+        <f>MAX(0,'ENG_WC'!$D$29-('ENG_FCF'!$D$51-'ENG_FCF'!$D$52))</f>
+        <v/>
+      </c>
+      <c r="E53" s="14">
+        <f>MAX(0,'ENG_WC'!$E$29-('ENG_FCF'!$E$51-'ENG_FCF'!$E$52))</f>
+        <v/>
+      </c>
+      <c r="F53" s="14">
+        <f>MAX(0,'ENG_WC'!$F$29-('ENG_FCF'!$F$51-'ENG_FCF'!$F$52))</f>
+        <v/>
+      </c>
+      <c r="G53" s="14">
+        <f>MAX(0,'ENG_WC'!$G$29-('ENG_FCF'!$G$51-'ENG_FCF'!$G$52))</f>
+        <v/>
+      </c>
+      <c r="H53" s="14">
+        <f>MAX(0,'ENG_WC'!$H$29-('ENG_FCF'!$H$51-'ENG_FCF'!$H$52))</f>
+        <v/>
+      </c>
+      <c r="I53" s="14">
+        <f>MAX(0,'ENG_WC'!$I$29-('ENG_FCF'!$I$51-'ENG_FCF'!$I$52))</f>
+        <v/>
+      </c>
+      <c r="J53" s="14">
+        <f>MAX(0,'ENG_WC'!$J$29-('ENG_FCF'!$J$51-'ENG_FCF'!$J$52))</f>
+        <v/>
+      </c>
+      <c r="K53" s="14">
+        <f>MAX(0,'ENG_WC'!$K$29-('ENG_FCF'!$K$51-'ENG_FCF'!$K$52))</f>
+        <v/>
+      </c>
+      <c r="L53" s="14">
+        <f>MAX(0,'ENG_WC'!$L$29-('ENG_FCF'!$L$51-'ENG_FCF'!$L$52))</f>
+        <v/>
+      </c>
+      <c r="M53" s="14">
+        <f>MAX(0,'ENG_WC'!$M$29-('ENG_FCF'!$M$51-'ENG_FCF'!$M$52))</f>
+        <v/>
+      </c>
+      <c r="N53" s="14">
+        <f>MAX(0,'ENG_WC'!$N$29-('ENG_FCF'!$N$51-'ENG_FCF'!$N$52))</f>
+        <v/>
+      </c>
+      <c r="O53" s="14">
+        <f>MAX(0,'ENG_WC'!$O$29-('ENG_FCF'!$O$51-'ENG_FCF'!$O$52))</f>
+        <v/>
+      </c>
+      <c r="P53" s="14">
+        <f>MAX(0,'ENG_WC'!$P$29-('ENG_FCF'!$P$51-'ENG_FCF'!$P$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>جریان نقد تأمین مالی</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>FCF.cff</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D54" s="14">
+        <f>'ENG_FCF'!$D$21-'ENG_FCF'!$D$24+'ENG_WC'!$D$21+'ENG_FCF'!$D$53-'ENG_FCF'!$D$52</f>
+        <v/>
+      </c>
+      <c r="E54" s="14">
+        <f>'ENG_FCF'!$E$21-'ENG_FCF'!$E$24+'ENG_WC'!$E$21+'ENG_FCF'!$E$53-'ENG_FCF'!$E$52</f>
+        <v/>
+      </c>
+      <c r="F54" s="14">
+        <f>'ENG_FCF'!$F$21-'ENG_FCF'!$F$24+'ENG_WC'!$F$21+'ENG_FCF'!$F$53-'ENG_FCF'!$F$52</f>
+        <v/>
+      </c>
+      <c r="G54" s="14">
+        <f>'ENG_FCF'!$G$21-'ENG_FCF'!$G$24+'ENG_WC'!$G$21+'ENG_FCF'!$G$53-'ENG_FCF'!$G$52</f>
+        <v/>
+      </c>
+      <c r="H54" s="14">
+        <f>'ENG_FCF'!$H$21-'ENG_FCF'!$H$24+'ENG_WC'!$H$21+'ENG_FCF'!$H$53-'ENG_FCF'!$H$52</f>
+        <v/>
+      </c>
+      <c r="I54" s="14">
+        <f>'ENG_FCF'!$I$21-'ENG_FCF'!$I$24+'ENG_WC'!$I$21+'ENG_FCF'!$I$53-'ENG_FCF'!$I$52</f>
+        <v/>
+      </c>
+      <c r="J54" s="14">
+        <f>'ENG_FCF'!$J$21-'ENG_FCF'!$J$24+'ENG_WC'!$J$21+'ENG_FCF'!$J$53-'ENG_FCF'!$J$52</f>
+        <v/>
+      </c>
+      <c r="K54" s="14">
+        <f>'ENG_FCF'!$K$21-'ENG_FCF'!$K$24+'ENG_WC'!$K$21+'ENG_FCF'!$K$53-'ENG_FCF'!$K$52</f>
+        <v/>
+      </c>
+      <c r="L54" s="14">
+        <f>'ENG_FCF'!$L$21-'ENG_FCF'!$L$24+'ENG_WC'!$L$21+'ENG_FCF'!$L$53-'ENG_FCF'!$L$52</f>
+        <v/>
+      </c>
+      <c r="M54" s="14">
+        <f>'ENG_FCF'!$M$21-'ENG_FCF'!$M$24+'ENG_WC'!$M$21+'ENG_FCF'!$M$53-'ENG_FCF'!$M$52</f>
+        <v/>
+      </c>
+      <c r="N54" s="14">
+        <f>'ENG_FCF'!$N$21-'ENG_FCF'!$N$24+'ENG_WC'!$N$21+'ENG_FCF'!$N$53-'ENG_FCF'!$N$52</f>
+        <v/>
+      </c>
+      <c r="O54" s="14">
+        <f>'ENG_FCF'!$O$21-'ENG_FCF'!$O$24+'ENG_WC'!$O$21+'ENG_FCF'!$O$53-'ENG_FCF'!$O$52</f>
+        <v/>
+      </c>
+      <c r="P54" s="14">
+        <f>'ENG_FCF'!$P$21-'ENG_FCF'!$P$24+'ENG_WC'!$P$21+'ENG_FCF'!$P$53-'ENG_FCF'!$P$52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>تغییرات نقد</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>FCF.dcash</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D55" s="14">
+        <f>'ENG_FCF'!$D$49+'ENG_FCF'!$D$50+'ENG_FCF'!$D$54</f>
+        <v/>
+      </c>
+      <c r="E55" s="14">
+        <f>'ENG_FCF'!$E$49+'ENG_FCF'!$E$50+'ENG_FCF'!$E$54</f>
+        <v/>
+      </c>
+      <c r="F55" s="14">
+        <f>'ENG_FCF'!$F$49+'ENG_FCF'!$F$50+'ENG_FCF'!$F$54</f>
+        <v/>
+      </c>
+      <c r="G55" s="14">
+        <f>'ENG_FCF'!$G$49+'ENG_FCF'!$G$50+'ENG_FCF'!$G$54</f>
+        <v/>
+      </c>
+      <c r="H55" s="14">
+        <f>'ENG_FCF'!$H$49+'ENG_FCF'!$H$50+'ENG_FCF'!$H$54</f>
+        <v/>
+      </c>
+      <c r="I55" s="14">
+        <f>'ENG_FCF'!$I$49+'ENG_FCF'!$I$50+'ENG_FCF'!$I$54</f>
+        <v/>
+      </c>
+      <c r="J55" s="14">
+        <f>'ENG_FCF'!$J$49+'ENG_FCF'!$J$50+'ENG_FCF'!$J$54</f>
+        <v/>
+      </c>
+      <c r="K55" s="14">
+        <f>'ENG_FCF'!$K$49+'ENG_FCF'!$K$50+'ENG_FCF'!$K$54</f>
+        <v/>
+      </c>
+      <c r="L55" s="14">
+        <f>'ENG_FCF'!$L$49+'ENG_FCF'!$L$50+'ENG_FCF'!$L$54</f>
+        <v/>
+      </c>
+      <c r="M55" s="14">
+        <f>'ENG_FCF'!$M$49+'ENG_FCF'!$M$50+'ENG_FCF'!$M$54</f>
+        <v/>
+      </c>
+      <c r="N55" s="14">
+        <f>'ENG_FCF'!$N$49+'ENG_FCF'!$N$50+'ENG_FCF'!$N$54</f>
+        <v/>
+      </c>
+      <c r="O55" s="14">
+        <f>'ENG_FCF'!$O$49+'ENG_FCF'!$O$50+'ENG_FCF'!$O$54</f>
+        <v/>
+      </c>
+      <c r="P55" s="14">
+        <f>'ENG_FCF'!$P$49+'ENG_FCF'!$P$50+'ENG_FCF'!$P$54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>نقد اختتامیه</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>FCF.cash</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D56" s="14">
+        <f>'ENG_FCF'!$D$48+'ENG_FCF'!$D$55</f>
+        <v/>
+      </c>
+      <c r="E56" s="14">
+        <f>'ENG_FCF'!$E$48+'ENG_FCF'!$E$55</f>
+        <v/>
+      </c>
+      <c r="F56" s="14">
+        <f>'ENG_FCF'!$F$48+'ENG_FCF'!$F$55</f>
+        <v/>
+      </c>
+      <c r="G56" s="14">
+        <f>'ENG_FCF'!$G$48+'ENG_FCF'!$G$55</f>
+        <v/>
+      </c>
+      <c r="H56" s="14">
+        <f>'ENG_FCF'!$H$48+'ENG_FCF'!$H$55</f>
+        <v/>
+      </c>
+      <c r="I56" s="14">
+        <f>'ENG_FCF'!$I$48+'ENG_FCF'!$I$55</f>
+        <v/>
+      </c>
+      <c r="J56" s="14">
+        <f>'ENG_FCF'!$J$48+'ENG_FCF'!$J$55</f>
+        <v/>
+      </c>
+      <c r="K56" s="14">
+        <f>'ENG_FCF'!$K$48+'ENG_FCF'!$K$55</f>
+        <v/>
+      </c>
+      <c r="L56" s="14">
+        <f>'ENG_FCF'!$L$48+'ENG_FCF'!$L$55</f>
+        <v/>
+      </c>
+      <c r="M56" s="14">
+        <f>'ENG_FCF'!$M$48+'ENG_FCF'!$M$55</f>
+        <v/>
+      </c>
+      <c r="N56" s="14">
+        <f>'ENG_FCF'!$N$48+'ENG_FCF'!$N$55</f>
+        <v/>
+      </c>
+      <c r="O56" s="14">
+        <f>'ENG_FCF'!$O$48+'ENG_FCF'!$O$55</f>
+        <v/>
+      </c>
+      <c r="P56" s="14">
+        <f>'ENG_FCF'!$P$48+'ENG_FCF'!$P$55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>سرمایه پرداختی انباشته</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>FCF.equity_cum</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D57" s="14">
+        <f>'ENG_FCF'!$D$53</f>
+        <v/>
+      </c>
+      <c r="E57" s="14">
+        <f>'ENG_FCF'!$D$57+'ENG_FCF'!$E$53</f>
+        <v/>
+      </c>
+      <c r="F57" s="14">
+        <f>'ENG_FCF'!$E$57+'ENG_FCF'!$F$53</f>
+        <v/>
+      </c>
+      <c r="G57" s="14">
+        <f>'ENG_FCF'!$F$57+'ENG_FCF'!$G$53</f>
+        <v/>
+      </c>
+      <c r="H57" s="14">
+        <f>'ENG_FCF'!$G$57+'ENG_FCF'!$H$53</f>
+        <v/>
+      </c>
+      <c r="I57" s="14">
+        <f>'ENG_FCF'!$H$57+'ENG_FCF'!$I$53</f>
+        <v/>
+      </c>
+      <c r="J57" s="14">
+        <f>'ENG_FCF'!$I$57+'ENG_FCF'!$J$53</f>
+        <v/>
+      </c>
+      <c r="K57" s="14">
+        <f>'ENG_FCF'!$J$57+'ENG_FCF'!$K$53</f>
+        <v/>
+      </c>
+      <c r="L57" s="14">
+        <f>'ENG_FCF'!$K$57+'ENG_FCF'!$L$53</f>
+        <v/>
+      </c>
+      <c r="M57" s="14">
+        <f>'ENG_FCF'!$L$57+'ENG_FCF'!$M$53</f>
+        <v/>
+      </c>
+      <c r="N57" s="14">
+        <f>'ENG_FCF'!$M$57+'ENG_FCF'!$N$53</f>
+        <v/>
+      </c>
+      <c r="O57" s="14">
+        <f>'ENG_FCF'!$N$57+'ENG_FCF'!$O$53</f>
+        <v/>
+      </c>
+      <c r="P57" s="14">
+        <f>'ENG_FCF'!$O$57+'ENG_FCF'!$P$53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>سود انباشته</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>FCF.re_cum</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D58" s="14">
+        <f>'ENG_FCF'!$D$32-'ENG_FCF'!$D$52</f>
+        <v/>
+      </c>
+      <c r="E58" s="14">
+        <f>'ENG_FCF'!$D$58+'ENG_FCF'!$E$32-'ENG_FCF'!$E$52</f>
+        <v/>
+      </c>
+      <c r="F58" s="14">
+        <f>'ENG_FCF'!$E$58+'ENG_FCF'!$F$32-'ENG_FCF'!$F$52</f>
+        <v/>
+      </c>
+      <c r="G58" s="14">
+        <f>'ENG_FCF'!$F$58+'ENG_FCF'!$G$32-'ENG_FCF'!$G$52</f>
+        <v/>
+      </c>
+      <c r="H58" s="14">
+        <f>'ENG_FCF'!$G$58+'ENG_FCF'!$H$32-'ENG_FCF'!$H$52</f>
+        <v/>
+      </c>
+      <c r="I58" s="14">
+        <f>'ENG_FCF'!$H$58+'ENG_FCF'!$I$32-'ENG_FCF'!$I$52</f>
+        <v/>
+      </c>
+      <c r="J58" s="14">
+        <f>'ENG_FCF'!$I$58+'ENG_FCF'!$J$32-'ENG_FCF'!$J$52</f>
+        <v/>
+      </c>
+      <c r="K58" s="14">
+        <f>'ENG_FCF'!$J$58+'ENG_FCF'!$K$32-'ENG_FCF'!$K$52</f>
+        <v/>
+      </c>
+      <c r="L58" s="14">
+        <f>'ENG_FCF'!$K$58+'ENG_FCF'!$L$32-'ENG_FCF'!$L$52</f>
+        <v/>
+      </c>
+      <c r="M58" s="14">
+        <f>'ENG_FCF'!$L$58+'ENG_FCF'!$M$32-'ENG_FCF'!$M$52</f>
+        <v/>
+      </c>
+      <c r="N58" s="14">
+        <f>'ENG_FCF'!$M$58+'ENG_FCF'!$N$32-'ENG_FCF'!$N$52</f>
+        <v/>
+      </c>
+      <c r="O58" s="14">
+        <f>'ENG_FCF'!$N$58+'ENG_FCF'!$O$32-'ENG_FCF'!$O$52</f>
+        <v/>
+      </c>
+      <c r="P58" s="14">
+        <f>'ENG_FCF'!$O$58+'ENG_FCF'!$P$32-'ENG_FCF'!$P$52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>FCF.equity</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D59" s="14">
+        <f>'ENG_FCF'!$D$57+'ENG_FCF'!$D$58</f>
+        <v/>
+      </c>
+      <c r="E59" s="14">
+        <f>'ENG_FCF'!$E$57+'ENG_FCF'!$E$58</f>
+        <v/>
+      </c>
+      <c r="F59" s="14">
+        <f>'ENG_FCF'!$F$57+'ENG_FCF'!$F$58</f>
+        <v/>
+      </c>
+      <c r="G59" s="14">
+        <f>'ENG_FCF'!$G$57+'ENG_FCF'!$G$58</f>
+        <v/>
+      </c>
+      <c r="H59" s="14">
+        <f>'ENG_FCF'!$H$57+'ENG_FCF'!$H$58</f>
+        <v/>
+      </c>
+      <c r="I59" s="14">
+        <f>'ENG_FCF'!$I$57+'ENG_FCF'!$I$58</f>
+        <v/>
+      </c>
+      <c r="J59" s="14">
+        <f>'ENG_FCF'!$J$57+'ENG_FCF'!$J$58</f>
+        <v/>
+      </c>
+      <c r="K59" s="14">
+        <f>'ENG_FCF'!$K$57+'ENG_FCF'!$K$58</f>
+        <v/>
+      </c>
+      <c r="L59" s="14">
+        <f>'ENG_FCF'!$L$57+'ENG_FCF'!$L$58</f>
+        <v/>
+      </c>
+      <c r="M59" s="14">
+        <f>'ENG_FCF'!$M$57+'ENG_FCF'!$M$58</f>
+        <v/>
+      </c>
+      <c r="N59" s="14">
+        <f>'ENG_FCF'!$N$57+'ENG_FCF'!$N$58</f>
+        <v/>
+      </c>
+      <c r="O59" s="14">
+        <f>'ENG_FCF'!$O$57+'ENG_FCF'!$O$58</f>
+        <v/>
+      </c>
+      <c r="P59" s="14">
+        <f>'ENG_FCF'!$P$57+'ENG_FCF'!$P$58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>جریان نقد آزاد سهامداران (FCFE)</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>FCF.fcfe</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D60" s="14">
+        <f>'ENG_FCF'!$D$32+'ENG_FCF'!$D$16-'ENG_FCF'!$D$38-'ENG_FCF'!$D$37+'ENG_FCF'!$D$21-'ENG_FCF'!$D$24+'ENG_WC'!$D$21</f>
+        <v/>
+      </c>
+      <c r="E60" s="14">
+        <f>'ENG_FCF'!$E$32+'ENG_FCF'!$E$16-'ENG_FCF'!$E$38-'ENG_FCF'!$E$37+'ENG_FCF'!$E$21-'ENG_FCF'!$E$24+'ENG_WC'!$E$21</f>
+        <v/>
+      </c>
+      <c r="F60" s="14">
+        <f>'ENG_FCF'!$F$32+'ENG_FCF'!$F$16-'ENG_FCF'!$F$38-'ENG_FCF'!$F$37+'ENG_FCF'!$F$21-'ENG_FCF'!$F$24+'ENG_WC'!$F$21</f>
+        <v/>
+      </c>
+      <c r="G60" s="14">
+        <f>'ENG_FCF'!$G$32+'ENG_FCF'!$G$16-'ENG_FCF'!$G$38-'ENG_FCF'!$G$37+'ENG_FCF'!$G$21-'ENG_FCF'!$G$24+'ENG_WC'!$G$21</f>
+        <v/>
+      </c>
+      <c r="H60" s="14">
+        <f>'ENG_FCF'!$H$32+'ENG_FCF'!$H$16-'ENG_FCF'!$H$38-'ENG_FCF'!$H$37+'ENG_FCF'!$H$21-'ENG_FCF'!$H$24+'ENG_WC'!$H$21</f>
+        <v/>
+      </c>
+      <c r="I60" s="14">
+        <f>'ENG_FCF'!$I$32+'ENG_FCF'!$I$16-'ENG_FCF'!$I$38-'ENG_FCF'!$I$37+'ENG_FCF'!$I$21-'ENG_FCF'!$I$24+'ENG_WC'!$I$21</f>
+        <v/>
+      </c>
+      <c r="J60" s="14">
+        <f>'ENG_FCF'!$J$32+'ENG_FCF'!$J$16-'ENG_FCF'!$J$38-'ENG_FCF'!$J$37+'ENG_FCF'!$J$21-'ENG_FCF'!$J$24+'ENG_WC'!$J$21</f>
+        <v/>
+      </c>
+      <c r="K60" s="14">
+        <f>'ENG_FCF'!$K$32+'ENG_FCF'!$K$16-'ENG_FCF'!$K$38-'ENG_FCF'!$K$37+'ENG_FCF'!$K$21-'ENG_FCF'!$K$24+'ENG_WC'!$K$21</f>
+        <v/>
+      </c>
+      <c r="L60" s="14">
+        <f>'ENG_FCF'!$L$32+'ENG_FCF'!$L$16-'ENG_FCF'!$L$38-'ENG_FCF'!$L$37+'ENG_FCF'!$L$21-'ENG_FCF'!$L$24+'ENG_WC'!$L$21</f>
+        <v/>
+      </c>
+      <c r="M60" s="14">
+        <f>'ENG_FCF'!$M$32+'ENG_FCF'!$M$16-'ENG_FCF'!$M$38-'ENG_FCF'!$M$37+'ENG_FCF'!$M$21-'ENG_FCF'!$M$24+'ENG_WC'!$M$21</f>
+        <v/>
+      </c>
+      <c r="N60" s="14">
+        <f>'ENG_FCF'!$N$32+'ENG_FCF'!$N$16-'ENG_FCF'!$N$38-'ENG_FCF'!$N$37+'ENG_FCF'!$N$21-'ENG_FCF'!$N$24+'ENG_WC'!$N$21</f>
+        <v/>
+      </c>
+      <c r="O60" s="14">
+        <f>'ENG_FCF'!$O$32+'ENG_FCF'!$O$16-'ENG_FCF'!$O$38-'ENG_FCF'!$O$37+'ENG_FCF'!$O$21-'ENG_FCF'!$O$24+'ENG_WC'!$O$21</f>
+        <v/>
+      </c>
+      <c r="P60" s="14">
+        <f>'ENG_FCF'!$P$32+'ENG_FCF'!$P$16-'ENG_FCF'!$P$38-'ENG_FCF'!$P$37+'ENG_FCF'!$P$21-'ENG_FCF'!$P$24+'ENG_WC'!$P$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61"/>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>ه‍) ترازنامهٔ پروژه</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+      <c r="E62" s="7" t="n"/>
+      <c r="F62" s="7" t="n"/>
+      <c r="G62" s="7" t="n"/>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
+      <c r="J62" s="7" t="n"/>
+      <c r="K62" s="7" t="n"/>
+      <c r="L62" s="7" t="n"/>
+      <c r="M62" s="7" t="n"/>
+      <c r="N62" s="7" t="n"/>
+      <c r="O62" s="7" t="n"/>
+      <c r="P62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>دارایی‌های جاری (نقد + موجودی + دریافتنی)</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>FCF.ca</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D63" s="14">
+        <f>'ENG_FCF'!$D$56+'ENG_WC'!$D$14+'ENG_WC'!$D$15</f>
+        <v/>
+      </c>
+      <c r="E63" s="14">
+        <f>'ENG_FCF'!$E$56+'ENG_WC'!$E$14+'ENG_WC'!$E$15</f>
+        <v/>
+      </c>
+      <c r="F63" s="14">
+        <f>'ENG_FCF'!$F$56+'ENG_WC'!$F$14+'ENG_WC'!$F$15</f>
+        <v/>
+      </c>
+      <c r="G63" s="14">
+        <f>'ENG_FCF'!$G$56+'ENG_WC'!$G$14+'ENG_WC'!$G$15</f>
+        <v/>
+      </c>
+      <c r="H63" s="14">
+        <f>'ENG_FCF'!$H$56+'ENG_WC'!$H$14+'ENG_WC'!$H$15</f>
+        <v/>
+      </c>
+      <c r="I63" s="14">
+        <f>'ENG_FCF'!$I$56+'ENG_WC'!$I$14+'ENG_WC'!$I$15</f>
+        <v/>
+      </c>
+      <c r="J63" s="14">
+        <f>'ENG_FCF'!$J$56+'ENG_WC'!$J$14+'ENG_WC'!$J$15</f>
+        <v/>
+      </c>
+      <c r="K63" s="14">
+        <f>'ENG_FCF'!$K$56+'ENG_WC'!$K$14+'ENG_WC'!$K$15</f>
+        <v/>
+      </c>
+      <c r="L63" s="14">
+        <f>'ENG_FCF'!$L$56+'ENG_WC'!$L$14+'ENG_WC'!$L$15</f>
+        <v/>
+      </c>
+      <c r="M63" s="14">
+        <f>'ENG_FCF'!$M$56+'ENG_WC'!$M$14+'ENG_WC'!$M$15</f>
+        <v/>
+      </c>
+      <c r="N63" s="14">
+        <f>'ENG_FCF'!$N$56+'ENG_WC'!$N$14+'ENG_WC'!$N$15</f>
+        <v/>
+      </c>
+      <c r="O63" s="14">
+        <f>'ENG_FCF'!$O$56+'ENG_WC'!$O$14+'ENG_WC'!$O$15</f>
+        <v/>
+      </c>
+      <c r="P63" s="14">
+        <f>'ENG_FCF'!$P$56+'ENG_WC'!$P$14+'ENG_WC'!$P$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>دارایی‌های ثابت خالص</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>FCF.nfa</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D64" s="14">
+        <f>'ENG_CAPEX'!$D$84</f>
+        <v/>
+      </c>
+      <c r="E64" s="14">
+        <f>'ENG_CAPEX'!$E$84</f>
+        <v/>
+      </c>
+      <c r="F64" s="14">
+        <f>'ENG_CAPEX'!$F$84</f>
+        <v/>
+      </c>
+      <c r="G64" s="14">
+        <f>'ENG_CAPEX'!$G$84</f>
+        <v/>
+      </c>
+      <c r="H64" s="14">
+        <f>'ENG_CAPEX'!$H$84</f>
+        <v/>
+      </c>
+      <c r="I64" s="14">
+        <f>'ENG_CAPEX'!$I$84</f>
+        <v/>
+      </c>
+      <c r="J64" s="14">
+        <f>'ENG_CAPEX'!$J$84</f>
+        <v/>
+      </c>
+      <c r="K64" s="14">
+        <f>'ENG_CAPEX'!$K$84</f>
+        <v/>
+      </c>
+      <c r="L64" s="14">
+        <f>'ENG_CAPEX'!$L$84</f>
+        <v/>
+      </c>
+      <c r="M64" s="14">
+        <f>'ENG_CAPEX'!$M$84</f>
+        <v/>
+      </c>
+      <c r="N64" s="14">
+        <f>'ENG_CAPEX'!$N$84</f>
+        <v/>
+      </c>
+      <c r="O64" s="14">
+        <f>'ENG_CAPEX'!$O$84</f>
+        <v/>
+      </c>
+      <c r="P64" s="14">
+        <f>'ENG_CAPEX'!$P$84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>جمع دارایی‌ها</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>FCF.assets</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D65" s="14">
+        <f>'ENG_FCF'!$D$63+'ENG_FCF'!$D$64</f>
+        <v/>
+      </c>
+      <c r="E65" s="14">
+        <f>'ENG_FCF'!$E$63+'ENG_FCF'!$E$64</f>
+        <v/>
+      </c>
+      <c r="F65" s="14">
+        <f>'ENG_FCF'!$F$63+'ENG_FCF'!$F$64</f>
+        <v/>
+      </c>
+      <c r="G65" s="14">
+        <f>'ENG_FCF'!$G$63+'ENG_FCF'!$G$64</f>
+        <v/>
+      </c>
+      <c r="H65" s="14">
+        <f>'ENG_FCF'!$H$63+'ENG_FCF'!$H$64</f>
+        <v/>
+      </c>
+      <c r="I65" s="14">
+        <f>'ENG_FCF'!$I$63+'ENG_FCF'!$I$64</f>
+        <v/>
+      </c>
+      <c r="J65" s="14">
+        <f>'ENG_FCF'!$J$63+'ENG_FCF'!$J$64</f>
+        <v/>
+      </c>
+      <c r="K65" s="14">
+        <f>'ENG_FCF'!$K$63+'ENG_FCF'!$K$64</f>
+        <v/>
+      </c>
+      <c r="L65" s="14">
+        <f>'ENG_FCF'!$L$63+'ENG_FCF'!$L$64</f>
+        <v/>
+      </c>
+      <c r="M65" s="14">
+        <f>'ENG_FCF'!$M$63+'ENG_FCF'!$M$64</f>
+        <v/>
+      </c>
+      <c r="N65" s="14">
+        <f>'ENG_FCF'!$N$63+'ENG_FCF'!$N$64</f>
+        <v/>
+      </c>
+      <c r="O65" s="14">
+        <f>'ENG_FCF'!$O$63+'ENG_FCF'!$O$64</f>
+        <v/>
+      </c>
+      <c r="P65" s="14">
+        <f>'ENG_FCF'!$P$63+'ENG_FCF'!$P$64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>بدهی‌های جاری (پرداختنی + مالیات + تسهیلات کوتاه‌مدت)</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>FCF.cl</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D66" s="14">
+        <f>'ENG_WC'!$D$16+'ENG_WC'!$D$17+'ENG_WC'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E66" s="14">
+        <f>'ENG_WC'!$E$16+'ENG_WC'!$E$17+'ENG_WC'!$E$20</f>
+        <v/>
+      </c>
+      <c r="F66" s="14">
+        <f>'ENG_WC'!$F$16+'ENG_WC'!$F$17+'ENG_WC'!$F$20</f>
+        <v/>
+      </c>
+      <c r="G66" s="14">
+        <f>'ENG_WC'!$G$16+'ENG_WC'!$G$17+'ENG_WC'!$G$20</f>
+        <v/>
+      </c>
+      <c r="H66" s="14">
+        <f>'ENG_WC'!$H$16+'ENG_WC'!$H$17+'ENG_WC'!$H$20</f>
+        <v/>
+      </c>
+      <c r="I66" s="14">
+        <f>'ENG_WC'!$I$16+'ENG_WC'!$I$17+'ENG_WC'!$I$20</f>
+        <v/>
+      </c>
+      <c r="J66" s="14">
+        <f>'ENG_WC'!$J$16+'ENG_WC'!$J$17+'ENG_WC'!$J$20</f>
+        <v/>
+      </c>
+      <c r="K66" s="14">
+        <f>'ENG_WC'!$K$16+'ENG_WC'!$K$17+'ENG_WC'!$K$20</f>
+        <v/>
+      </c>
+      <c r="L66" s="14">
+        <f>'ENG_WC'!$L$16+'ENG_WC'!$L$17+'ENG_WC'!$L$20</f>
+        <v/>
+      </c>
+      <c r="M66" s="14">
+        <f>'ENG_WC'!$M$16+'ENG_WC'!$M$17+'ENG_WC'!$M$20</f>
+        <v/>
+      </c>
+      <c r="N66" s="14">
+        <f>'ENG_WC'!$N$16+'ENG_WC'!$N$17+'ENG_WC'!$N$20</f>
+        <v/>
+      </c>
+      <c r="O66" s="14">
+        <f>'ENG_WC'!$O$16+'ENG_WC'!$O$17+'ENG_WC'!$O$20</f>
+        <v/>
+      </c>
+      <c r="P66" s="14">
+        <f>'ENG_WC'!$P$16+'ENG_WC'!$P$17+'ENG_WC'!$P$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>تسهیلات بلندمدت</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>FCF.ltd</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D67" s="14">
+        <f>'ENG_FCF'!$D$25</f>
+        <v/>
+      </c>
+      <c r="E67" s="14">
+        <f>'ENG_FCF'!$E$25</f>
+        <v/>
+      </c>
+      <c r="F67" s="14">
+        <f>'ENG_FCF'!$F$25</f>
+        <v/>
+      </c>
+      <c r="G67" s="14">
+        <f>'ENG_FCF'!$G$25</f>
+        <v/>
+      </c>
+      <c r="H67" s="14">
+        <f>'ENG_FCF'!$H$25</f>
+        <v/>
+      </c>
+      <c r="I67" s="14">
+        <f>'ENG_FCF'!$I$25</f>
+        <v/>
+      </c>
+      <c r="J67" s="14">
+        <f>'ENG_FCF'!$J$25</f>
+        <v/>
+      </c>
+      <c r="K67" s="14">
+        <f>'ENG_FCF'!$K$25</f>
+        <v/>
+      </c>
+      <c r="L67" s="14">
+        <f>'ENG_FCF'!$L$25</f>
+        <v/>
+      </c>
+      <c r="M67" s="14">
+        <f>'ENG_FCF'!$M$25</f>
+        <v/>
+      </c>
+      <c r="N67" s="14">
+        <f>'ENG_FCF'!$N$25</f>
+        <v/>
+      </c>
+      <c r="O67" s="14">
+        <f>'ENG_FCF'!$O$25</f>
+        <v/>
+      </c>
+      <c r="P67" s="14">
+        <f>'ENG_FCF'!$P$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>جمع بدهی‌ها</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>FCF.liab</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D68" s="14">
+        <f>'ENG_FCF'!$D$66+'ENG_FCF'!$D$67</f>
+        <v/>
+      </c>
+      <c r="E68" s="14">
+        <f>'ENG_FCF'!$E$66+'ENG_FCF'!$E$67</f>
+        <v/>
+      </c>
+      <c r="F68" s="14">
+        <f>'ENG_FCF'!$F$66+'ENG_FCF'!$F$67</f>
+        <v/>
+      </c>
+      <c r="G68" s="14">
+        <f>'ENG_FCF'!$G$66+'ENG_FCF'!$G$67</f>
+        <v/>
+      </c>
+      <c r="H68" s="14">
+        <f>'ENG_FCF'!$H$66+'ENG_FCF'!$H$67</f>
+        <v/>
+      </c>
+      <c r="I68" s="14">
+        <f>'ENG_FCF'!$I$66+'ENG_FCF'!$I$67</f>
+        <v/>
+      </c>
+      <c r="J68" s="14">
+        <f>'ENG_FCF'!$J$66+'ENG_FCF'!$J$67</f>
+        <v/>
+      </c>
+      <c r="K68" s="14">
+        <f>'ENG_FCF'!$K$66+'ENG_FCF'!$K$67</f>
+        <v/>
+      </c>
+      <c r="L68" s="14">
+        <f>'ENG_FCF'!$L$66+'ENG_FCF'!$L$67</f>
+        <v/>
+      </c>
+      <c r="M68" s="14">
+        <f>'ENG_FCF'!$M$66+'ENG_FCF'!$M$67</f>
+        <v/>
+      </c>
+      <c r="N68" s="14">
+        <f>'ENG_FCF'!$N$66+'ENG_FCF'!$N$67</f>
+        <v/>
+      </c>
+      <c r="O68" s="14">
+        <f>'ENG_FCF'!$O$66+'ENG_FCF'!$O$67</f>
+        <v/>
+      </c>
+      <c r="P68" s="14">
+        <f>'ENG_FCF'!$P$66+'ENG_FCF'!$P$67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>FCF.eq_bs</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D69" s="14">
+        <f>'ENG_FCF'!$D$59</f>
+        <v/>
+      </c>
+      <c r="E69" s="14">
+        <f>'ENG_FCF'!$E$59</f>
+        <v/>
+      </c>
+      <c r="F69" s="14">
+        <f>'ENG_FCF'!$F$59</f>
+        <v/>
+      </c>
+      <c r="G69" s="14">
+        <f>'ENG_FCF'!$G$59</f>
+        <v/>
+      </c>
+      <c r="H69" s="14">
+        <f>'ENG_FCF'!$H$59</f>
+        <v/>
+      </c>
+      <c r="I69" s="14">
+        <f>'ENG_FCF'!$I$59</f>
+        <v/>
+      </c>
+      <c r="J69" s="14">
+        <f>'ENG_FCF'!$J$59</f>
+        <v/>
+      </c>
+      <c r="K69" s="14">
+        <f>'ENG_FCF'!$K$59</f>
+        <v/>
+      </c>
+      <c r="L69" s="14">
+        <f>'ENG_FCF'!$L$59</f>
+        <v/>
+      </c>
+      <c r="M69" s="14">
+        <f>'ENG_FCF'!$M$59</f>
+        <v/>
+      </c>
+      <c r="N69" s="14">
+        <f>'ENG_FCF'!$N$59</f>
+        <v/>
+      </c>
+      <c r="O69" s="14">
+        <f>'ENG_FCF'!$O$59</f>
+        <v/>
+      </c>
+      <c r="P69" s="14">
+        <f>'ENG_FCF'!$P$59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>کنترل تراز (باید صفر باشد)</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>FCF.bs_check</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>میلیون ریال</t>
+        </is>
+      </c>
+      <c r="D70" s="13">
+        <f>'ENG_FCF'!$D$65-'ENG_FCF'!$D$68-'ENG_FCF'!$D$69</f>
+        <v/>
+      </c>
+      <c r="E70" s="13">
+        <f>'ENG_FCF'!$E$65-'ENG_FCF'!$E$68-'ENG_FCF'!$E$69</f>
+        <v/>
+      </c>
+      <c r="F70" s="13">
+        <f>'ENG_FCF'!$F$65-'ENG_FCF'!$F$68-'ENG_FCF'!$F$69</f>
+        <v/>
+      </c>
+      <c r="G70" s="13">
+        <f>'ENG_FCF'!$G$65-'ENG_FCF'!$G$68-'ENG_FCF'!$G$69</f>
+        <v/>
+      </c>
+      <c r="H70" s="13">
+        <f>'ENG_FCF'!$H$65-'ENG_FCF'!$H$68-'ENG_FCF'!$H$69</f>
+        <v/>
+      </c>
+      <c r="I70" s="13">
+        <f>'ENG_FCF'!$I$65-'ENG_FCF'!$I$68-'ENG_FCF'!$I$69</f>
+        <v/>
+      </c>
+      <c r="J70" s="13">
+        <f>'ENG_FCF'!$J$65-'ENG_FCF'!$J$68-'ENG_FCF'!$J$69</f>
+        <v/>
+      </c>
+      <c r="K70" s="13">
+        <f>'ENG_FCF'!$K$65-'ENG_FCF'!$K$68-'ENG_FCF'!$K$69</f>
+        <v/>
+      </c>
+      <c r="L70" s="13">
+        <f>'ENG_FCF'!$L$65-'ENG_FCF'!$L$68-'ENG_FCF'!$L$69</f>
+        <v/>
+      </c>
+      <c r="M70" s="13">
+        <f>'ENG_FCF'!$M$65-'ENG_FCF'!$M$68-'ENG_FCF'!$M$69</f>
+        <v/>
+      </c>
+      <c r="N70" s="13">
+        <f>'ENG_FCF'!$N$65-'ENG_FCF'!$N$68-'ENG_FCF'!$N$69</f>
+        <v/>
+      </c>
+      <c r="O70" s="13">
+        <f>'ENG_FCF'!$O$65-'ENG_FCF'!$O$68-'ENG_FCF'!$O$69</f>
+        <v/>
+      </c>
+      <c r="P70" s="13">
+        <f>'ENG_FCF'!$P$65-'ENG_FCF'!$P$68-'ENG_FCF'!$P$69</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12210,55 +16141,55 @@
         </is>
       </c>
       <c r="D18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|0@@</f>
+        <f>'ENG_FCF'!$D$39</f>
         <v/>
       </c>
       <c r="E18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|1@@</f>
+        <f>'ENG_FCF'!$E$39</f>
         <v/>
       </c>
       <c r="F18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|2@@</f>
+        <f>'ENG_FCF'!$F$39</f>
         <v/>
       </c>
       <c r="G18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|3@@</f>
+        <f>'ENG_FCF'!$G$39</f>
         <v/>
       </c>
       <c r="H18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|4@@</f>
+        <f>'ENG_FCF'!$H$39</f>
         <v/>
       </c>
       <c r="I18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|5@@</f>
+        <f>'ENG_FCF'!$I$39</f>
         <v/>
       </c>
       <c r="J18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|6@@</f>
+        <f>'ENG_FCF'!$J$39</f>
         <v/>
       </c>
       <c r="K18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|7@@</f>
+        <f>'ENG_FCF'!$K$39</f>
         <v/>
       </c>
       <c r="L18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|8@@</f>
+        <f>'ENG_FCF'!$L$39</f>
         <v/>
       </c>
       <c r="M18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|9@@</f>
+        <f>'ENG_FCF'!$M$39</f>
         <v/>
       </c>
       <c r="N18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|10@@</f>
+        <f>'ENG_FCF'!$N$39</f>
         <v/>
       </c>
       <c r="O18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|11@@</f>
+        <f>'ENG_FCF'!$O$39</f>
         <v/>
       </c>
       <c r="P18" s="14">
-        <f>@@ENG_FCF|FCF.fcff|12@@</f>
+        <f>'ENG_FCF'!$P$39</f>
         <v/>
       </c>
     </row>
@@ -12417,55 +16348,55 @@
         </is>
       </c>
       <c r="D21" s="14">
-        <f>IF('IN_MACRO'!$D$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$D$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
       <c r="E21" s="14">
-        <f>IF('IN_MACRO'!$E$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$E$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
       <c r="F21" s="14">
-        <f>IF('IN_MACRO'!$F$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$F$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
       <c r="G21" s="14">
-        <f>IF('IN_MACRO'!$G$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$G$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
       <c r="H21" s="14">
-        <f>IF('IN_MACRO'!$H$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$H$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
       <c r="I21" s="14">
-        <f>IF('IN_MACRO'!$I$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$I$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
       <c r="J21" s="14">
-        <f>IF('IN_MACRO'!$J$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$J$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
       <c r="K21" s="14">
-        <f>IF('IN_MACRO'!$K$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$K$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
       <c r="L21" s="14">
-        <f>IF('IN_MACRO'!$L$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$L$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
       <c r="M21" s="14">
-        <f>IF('IN_MACRO'!$M$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$M$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
       <c r="N21" s="14">
-        <f>IF('IN_MACRO'!$N$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$N$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
       <c r="O21" s="14">
-        <f>IF('IN_MACRO'!$O$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$O$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
       <c r="P21" s="14">
-        <f>IF('IN_MACRO'!$P$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,@@ENG_FCF|FCF.fcff_rep|12@@)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),@@ENG_FCF|FCF.ebitda|12@@*'IN_MACRO'!$D$20))</f>
+        <f>IF('IN_MACRO'!$P$23&lt;'IN_MACRO'!$D$11,0,IF('IN_MACRO'!$D$19=1,MAX(0,'ENG_FCF'!$P$41)*(1+'IN_MACRO'!$D$18)/MAX(0.005,'ENG_DCF'!$P$14-'IN_MACRO'!$D$18),'ENG_FCF'!$P$15*'IN_MACRO'!$D$20))</f>
         <v/>
       </c>
     </row>
@@ -12726,7 +16657,7 @@
         </is>
       </c>
       <c r="D29" s="11">
-        <f>IFERROR(IRR(@@ENG_FCF|FCF.fcfe|0@@:@@ENG_FCF|FCF.fcfe|12@@),NA())</f>
+        <f>IFERROR(IRR('ENG_FCF'!$D$60:$P$60),NA())</f>
         <v/>
       </c>
       <c r="E29" s="11" t="n"/>
@@ -12754,7 +16685,7 @@
         </is>
       </c>
       <c r="D30" s="13">
-        <f>IF(COUNTIF(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,"&lt;0")=0,0,IF(COUNTIF(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,"&lt;0")&gt;=13,NA(),INDEX('IN_MACRO'!$D$23:$P$23,COUNTIF(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,"&lt;0"))+(0-INDEX(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,COUNTIF(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,"&lt;0")))/(INDEX(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,COUNTIF(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,"&lt;0")+1)-INDEX(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,COUNTIF(@@ENG_FCF|FCF.fcff_cum|0@@:@@ENG_FCF|FCF.fcff_cum|12@@,"&lt;0")))))</f>
+        <f>IF(COUNTIF('ENG_FCF'!$D$40:$P$40,"&lt;0")=0,0,IF(COUNTIF('ENG_FCF'!$D$40:$P$40,"&lt;0")&gt;=13,NA(),INDEX('IN_MACRO'!$D$23:$P$23,COUNTIF('ENG_FCF'!$D$40:$P$40,"&lt;0"))+(0-INDEX('ENG_FCF'!$D$40:$P$40,COUNTIF('ENG_FCF'!$D$40:$P$40,"&lt;0")))/(INDEX('ENG_FCF'!$D$40:$P$40,COUNTIF('ENG_FCF'!$D$40:$P$40,"&lt;0")+1)-INDEX('ENG_FCF'!$D$40:$P$40,COUNTIF('ENG_FCF'!$D$40:$P$40,"&lt;0")))))</f>
         <v/>
       </c>
       <c r="E30" s="13" t="n"/>
@@ -12871,64 +16802,28 @@
         </is>
       </c>
       <c r="D34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|0@@-@@ENG_FCF|FCF.cash|0@@)</f>
-        <v/>
-      </c>
-      <c r="E34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|1@@-@@ENG_FCF|FCF.cash|1@@)</f>
-        <v/>
-      </c>
-      <c r="F34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|2@@-@@ENG_FCF|FCF.cash|2@@)</f>
-        <v/>
-      </c>
-      <c r="G34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|3@@-@@ENG_FCF|FCF.cash|3@@)</f>
-        <v/>
-      </c>
-      <c r="H34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|4@@-@@ENG_FCF|FCF.cash|4@@)</f>
-        <v/>
-      </c>
-      <c r="I34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|5@@-@@ENG_FCF|FCF.cash|5@@)</f>
-        <v/>
-      </c>
-      <c r="J34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|6@@-@@ENG_FCF|FCF.cash|6@@)</f>
-        <v/>
-      </c>
-      <c r="K34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|7@@-@@ENG_FCF|FCF.cash|7@@)</f>
-        <v/>
-      </c>
-      <c r="L34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|8@@-@@ENG_FCF|FCF.cash|8@@)</f>
-        <v/>
-      </c>
-      <c r="M34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|9@@-@@ENG_FCF|FCF.cash|9@@)</f>
-        <v/>
-      </c>
-      <c r="N34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|10@@-@@ENG_FCF|FCF.cash|10@@)</f>
-        <v/>
-      </c>
-      <c r="O34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|11@@-@@ENG_FCF|FCF.cash|11@@)</f>
-        <v/>
-      </c>
-      <c r="P34" s="14">
-        <f>'ENG_DCF'!$D$33-(@@ENG_FCF|FCF.debt_close|12@@-@@ENG_FCF|FCF.cash|12@@)</f>
-        <v/>
-      </c>
+        <f>'ENG_DCF'!$D$33-('ENG_FCF'!$D$25-'ENG_FCF'!$D$56)</f>
+        <v/>
+      </c>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="14" t="n"/>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="14" t="n"/>
+      <c r="N34" s="14" t="n"/>
+      <c r="O34" s="14" t="n"/>
+      <c r="P34" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
@@ -13136,55 +17031,55 @@
         </is>
       </c>
       <c r="D10" s="14">
-        <f>@@ENG_FCF|FCF.rev|0@@</f>
+        <f>'ENG_FCF'!$D$10</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>@@ENG_FCF|FCF.rev|1@@</f>
+        <f>'ENG_FCF'!$E$10</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>@@ENG_FCF|FCF.rev|2@@</f>
+        <f>'ENG_FCF'!$F$10</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>@@ENG_FCF|FCF.rev|3@@</f>
+        <f>'ENG_FCF'!$G$10</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>@@ENG_FCF|FCF.rev|4@@</f>
+        <f>'ENG_FCF'!$H$10</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>@@ENG_FCF|FCF.rev|5@@</f>
+        <f>'ENG_FCF'!$I$10</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>@@ENG_FCF|FCF.rev|6@@</f>
+        <f>'ENG_FCF'!$J$10</f>
         <v/>
       </c>
       <c r="K10" s="14">
-        <f>@@ENG_FCF|FCF.rev|7@@</f>
+        <f>'ENG_FCF'!$K$10</f>
         <v/>
       </c>
       <c r="L10" s="14">
-        <f>@@ENG_FCF|FCF.rev|8@@</f>
+        <f>'ENG_FCF'!$L$10</f>
         <v/>
       </c>
       <c r="M10" s="14">
-        <f>@@ENG_FCF|FCF.rev|9@@</f>
+        <f>'ENG_FCF'!$M$10</f>
         <v/>
       </c>
       <c r="N10" s="14">
-        <f>@@ENG_FCF|FCF.rev|10@@</f>
+        <f>'ENG_FCF'!$N$10</f>
         <v/>
       </c>
       <c r="O10" s="14">
-        <f>@@ENG_FCF|FCF.rev|11@@</f>
+        <f>'ENG_FCF'!$O$10</f>
         <v/>
       </c>
       <c r="P10" s="14">
-        <f>@@ENG_FCF|FCF.rev|12@@</f>
+        <f>'ENG_FCF'!$P$10</f>
         <v/>
       </c>
     </row>
@@ -13780,55 +17675,55 @@
         </is>
       </c>
       <c r="D21" s="12">
-        <f>IFERROR('ENG_LEV'!$D$12/@@ENG_FCF|FCF.ebit|0@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$D$12/'ENG_FCF'!$D$17,0)</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>IFERROR('ENG_LEV'!$E$12/@@ENG_FCF|FCF.ebit|1@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$E$12/'ENG_FCF'!$E$17,0)</f>
         <v/>
       </c>
       <c r="F21" s="12">
-        <f>IFERROR('ENG_LEV'!$F$12/@@ENG_FCF|FCF.ebit|2@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$F$12/'ENG_FCF'!$F$17,0)</f>
         <v/>
       </c>
       <c r="G21" s="12">
-        <f>IFERROR('ENG_LEV'!$G$12/@@ENG_FCF|FCF.ebit|3@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$G$12/'ENG_FCF'!$G$17,0)</f>
         <v/>
       </c>
       <c r="H21" s="12">
-        <f>IFERROR('ENG_LEV'!$H$12/@@ENG_FCF|FCF.ebit|4@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$H$12/'ENG_FCF'!$H$17,0)</f>
         <v/>
       </c>
       <c r="I21" s="12">
-        <f>IFERROR('ENG_LEV'!$I$12/@@ENG_FCF|FCF.ebit|5@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$I$12/'ENG_FCF'!$I$17,0)</f>
         <v/>
       </c>
       <c r="J21" s="12">
-        <f>IFERROR('ENG_LEV'!$J$12/@@ENG_FCF|FCF.ebit|6@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$J$12/'ENG_FCF'!$J$17,0)</f>
         <v/>
       </c>
       <c r="K21" s="12">
-        <f>IFERROR('ENG_LEV'!$K$12/@@ENG_FCF|FCF.ebit|7@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$K$12/'ENG_FCF'!$K$17,0)</f>
         <v/>
       </c>
       <c r="L21" s="12">
-        <f>IFERROR('ENG_LEV'!$L$12/@@ENG_FCF|FCF.ebit|8@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$L$12/'ENG_FCF'!$L$17,0)</f>
         <v/>
       </c>
       <c r="M21" s="12">
-        <f>IFERROR('ENG_LEV'!$M$12/@@ENG_FCF|FCF.ebit|9@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$M$12/'ENG_FCF'!$M$17,0)</f>
         <v/>
       </c>
       <c r="N21" s="12">
-        <f>IFERROR('ENG_LEV'!$N$12/@@ENG_FCF|FCF.ebit|10@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$N$12/'ENG_FCF'!$N$17,0)</f>
         <v/>
       </c>
       <c r="O21" s="12">
-        <f>IFERROR('ENG_LEV'!$O$12/@@ENG_FCF|FCF.ebit|11@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$O$12/'ENG_FCF'!$O$17,0)</f>
         <v/>
       </c>
       <c r="P21" s="12">
-        <f>IFERROR('ENG_LEV'!$P$12/@@ENG_FCF|FCF.ebit|12@@,0)</f>
+        <f>IFERROR('ENG_LEV'!$P$12/'ENG_FCF'!$P$17,0)</f>
         <v/>
       </c>
     </row>
@@ -13849,55 +17744,55 @@
         </is>
       </c>
       <c r="D22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|0@@/@@ENG_FCF|FCF.ebt|0@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$D$17/'ENG_FCF'!$D$30,0)</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|1@@/@@ENG_FCF|FCF.ebt|1@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$E$17/'ENG_FCF'!$E$30,0)</f>
         <v/>
       </c>
       <c r="F22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|2@@/@@ENG_FCF|FCF.ebt|2@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$F$17/'ENG_FCF'!$F$30,0)</f>
         <v/>
       </c>
       <c r="G22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|3@@/@@ENG_FCF|FCF.ebt|3@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$G$17/'ENG_FCF'!$G$30,0)</f>
         <v/>
       </c>
       <c r="H22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|4@@/@@ENG_FCF|FCF.ebt|4@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$H$17/'ENG_FCF'!$H$30,0)</f>
         <v/>
       </c>
       <c r="I22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|5@@/@@ENG_FCF|FCF.ebt|5@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$I$17/'ENG_FCF'!$I$30,0)</f>
         <v/>
       </c>
       <c r="J22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|6@@/@@ENG_FCF|FCF.ebt|6@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$J$17/'ENG_FCF'!$J$30,0)</f>
         <v/>
       </c>
       <c r="K22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|7@@/@@ENG_FCF|FCF.ebt|7@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$K$17/'ENG_FCF'!$K$30,0)</f>
         <v/>
       </c>
       <c r="L22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|8@@/@@ENG_FCF|FCF.ebt|8@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$L$17/'ENG_FCF'!$L$30,0)</f>
         <v/>
       </c>
       <c r="M22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|9@@/@@ENG_FCF|FCF.ebt|9@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$M$17/'ENG_FCF'!$M$30,0)</f>
         <v/>
       </c>
       <c r="N22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|10@@/@@ENG_FCF|FCF.ebt|10@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$N$17/'ENG_FCF'!$N$30,0)</f>
         <v/>
       </c>
       <c r="O22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|11@@/@@ENG_FCF|FCF.ebt|11@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$O$17/'ENG_FCF'!$O$30,0)</f>
         <v/>
       </c>
       <c r="P22" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ebit|12@@/@@ENG_FCF|FCF.ebt|12@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$P$17/'ENG_FCF'!$P$30,0)</f>
         <v/>
       </c>
     </row>
@@ -14079,55 +17974,55 @@
         </is>
       </c>
       <c r="D27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|0@@/@@ENG_FCF|FCF.equity|0@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$D$32/'ENG_FCF'!$D$59,0)</f>
         <v/>
       </c>
       <c r="E27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|1@@/@@ENG_FCF|FCF.equity|1@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$E$32/'ENG_FCF'!$E$59,0)</f>
         <v/>
       </c>
       <c r="F27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|2@@/@@ENG_FCF|FCF.equity|2@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$F$32/'ENG_FCF'!$F$59,0)</f>
         <v/>
       </c>
       <c r="G27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|3@@/@@ENG_FCF|FCF.equity|3@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$G$32/'ENG_FCF'!$G$59,0)</f>
         <v/>
       </c>
       <c r="H27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|4@@/@@ENG_FCF|FCF.equity|4@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$H$32/'ENG_FCF'!$H$59,0)</f>
         <v/>
       </c>
       <c r="I27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|5@@/@@ENG_FCF|FCF.equity|5@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$I$32/'ENG_FCF'!$I$59,0)</f>
         <v/>
       </c>
       <c r="J27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|6@@/@@ENG_FCF|FCF.equity|6@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$J$32/'ENG_FCF'!$J$59,0)</f>
         <v/>
       </c>
       <c r="K27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|7@@/@@ENG_FCF|FCF.equity|7@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$K$32/'ENG_FCF'!$K$59,0)</f>
         <v/>
       </c>
       <c r="L27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|8@@/@@ENG_FCF|FCF.equity|8@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$L$32/'ENG_FCF'!$L$59,0)</f>
         <v/>
       </c>
       <c r="M27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|9@@/@@ENG_FCF|FCF.equity|9@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$M$32/'ENG_FCF'!$M$59,0)</f>
         <v/>
       </c>
       <c r="N27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|10@@/@@ENG_FCF|FCF.equity|10@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$N$32/'ENG_FCF'!$N$59,0)</f>
         <v/>
       </c>
       <c r="O27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|11@@/@@ENG_FCF|FCF.equity|11@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$O$32/'ENG_FCF'!$O$59,0)</f>
         <v/>
       </c>
       <c r="P27" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|12@@/@@ENG_FCF|FCF.equity|12@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$P$32/'ENG_FCF'!$P$59,0)</f>
         <v/>
       </c>
     </row>
@@ -14148,55 +18043,55 @@
         </is>
       </c>
       <c r="D28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|0@@/@@ENG_FCF|FCF.assets|0@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$D$32/'ENG_FCF'!$D$65,0)</f>
         <v/>
       </c>
       <c r="E28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|1@@/@@ENG_FCF|FCF.assets|1@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$E$32/'ENG_FCF'!$E$65,0)</f>
         <v/>
       </c>
       <c r="F28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|2@@/@@ENG_FCF|FCF.assets|2@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$F$32/'ENG_FCF'!$F$65,0)</f>
         <v/>
       </c>
       <c r="G28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|3@@/@@ENG_FCF|FCF.assets|3@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$G$32/'ENG_FCF'!$G$65,0)</f>
         <v/>
       </c>
       <c r="H28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|4@@/@@ENG_FCF|FCF.assets|4@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$H$32/'ENG_FCF'!$H$65,0)</f>
         <v/>
       </c>
       <c r="I28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|5@@/@@ENG_FCF|FCF.assets|5@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$I$32/'ENG_FCF'!$I$65,0)</f>
         <v/>
       </c>
       <c r="J28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|6@@/@@ENG_FCF|FCF.assets|6@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$J$32/'ENG_FCF'!$J$65,0)</f>
         <v/>
       </c>
       <c r="K28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|7@@/@@ENG_FCF|FCF.assets|7@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$K$32/'ENG_FCF'!$K$65,0)</f>
         <v/>
       </c>
       <c r="L28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|8@@/@@ENG_FCF|FCF.assets|8@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$L$32/'ENG_FCF'!$L$65,0)</f>
         <v/>
       </c>
       <c r="M28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|9@@/@@ENG_FCF|FCF.assets|9@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$M$32/'ENG_FCF'!$M$65,0)</f>
         <v/>
       </c>
       <c r="N28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|10@@/@@ENG_FCF|FCF.assets|10@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$N$32/'ENG_FCF'!$N$65,0)</f>
         <v/>
       </c>
       <c r="O28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|11@@/@@ENG_FCF|FCF.assets|11@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$O$32/'ENG_FCF'!$O$65,0)</f>
         <v/>
       </c>
       <c r="P28" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.ni|12@@/@@ENG_FCF|FCF.assets|12@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$P$32/'ENG_FCF'!$P$65,0)</f>
         <v/>
       </c>
     </row>
@@ -14217,55 +18112,55 @@
         </is>
       </c>
       <c r="D29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|0@@/(@@ENG_FCF|FCF.ltd|0@@+@@ENG_FCF|FCF.equity|0@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$D$35/('ENG_FCF'!$D$67+'ENG_FCF'!$D$59),0)</f>
         <v/>
       </c>
       <c r="E29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|1@@/(@@ENG_FCF|FCF.ltd|1@@+@@ENG_FCF|FCF.equity|1@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$E$35/('ENG_FCF'!$E$67+'ENG_FCF'!$E$59),0)</f>
         <v/>
       </c>
       <c r="F29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|2@@/(@@ENG_FCF|FCF.ltd|2@@+@@ENG_FCF|FCF.equity|2@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$F$35/('ENG_FCF'!$F$67+'ENG_FCF'!$F$59),0)</f>
         <v/>
       </c>
       <c r="G29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|3@@/(@@ENG_FCF|FCF.ltd|3@@+@@ENG_FCF|FCF.equity|3@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$G$35/('ENG_FCF'!$G$67+'ENG_FCF'!$G$59),0)</f>
         <v/>
       </c>
       <c r="H29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|4@@/(@@ENG_FCF|FCF.ltd|4@@+@@ENG_FCF|FCF.equity|4@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$H$35/('ENG_FCF'!$H$67+'ENG_FCF'!$H$59),0)</f>
         <v/>
       </c>
       <c r="I29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|5@@/(@@ENG_FCF|FCF.ltd|5@@+@@ENG_FCF|FCF.equity|5@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$I$35/('ENG_FCF'!$I$67+'ENG_FCF'!$I$59),0)</f>
         <v/>
       </c>
       <c r="J29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|6@@/(@@ENG_FCF|FCF.ltd|6@@+@@ENG_FCF|FCF.equity|6@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$J$35/('ENG_FCF'!$J$67+'ENG_FCF'!$J$59),0)</f>
         <v/>
       </c>
       <c r="K29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|7@@/(@@ENG_FCF|FCF.ltd|7@@+@@ENG_FCF|FCF.equity|7@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$K$35/('ENG_FCF'!$K$67+'ENG_FCF'!$K$59),0)</f>
         <v/>
       </c>
       <c r="L29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|8@@/(@@ENG_FCF|FCF.ltd|8@@+@@ENG_FCF|FCF.equity|8@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$L$35/('ENG_FCF'!$L$67+'ENG_FCF'!$L$59),0)</f>
         <v/>
       </c>
       <c r="M29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|9@@/(@@ENG_FCF|FCF.ltd|9@@+@@ENG_FCF|FCF.equity|9@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$M$35/('ENG_FCF'!$M$67+'ENG_FCF'!$M$59),0)</f>
         <v/>
       </c>
       <c r="N29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|10@@/(@@ENG_FCF|FCF.ltd|10@@+@@ENG_FCF|FCF.equity|10@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$N$35/('ENG_FCF'!$N$67+'ENG_FCF'!$N$59),0)</f>
         <v/>
       </c>
       <c r="O29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|11@@/(@@ENG_FCF|FCF.ltd|11@@+@@ENG_FCF|FCF.equity|11@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$O$35/('ENG_FCF'!$O$67+'ENG_FCF'!$O$59),0)</f>
         <v/>
       </c>
       <c r="P29" s="11">
-        <f>IFERROR(@@ENG_FCF|FCF.nopat|12@@/(@@ENG_FCF|FCF.ltd|12@@+@@ENG_FCF|FCF.equity|12@@),0)</f>
+        <f>IFERROR('ENG_FCF'!$P$35/('ENG_FCF'!$P$67+'ENG_FCF'!$P$59),0)</f>
         <v/>
       </c>
     </row>
@@ -14286,55 +18181,55 @@
         </is>
       </c>
       <c r="D30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|0@@/@@ENG_FCF|FCF.equity|0@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$D$67/'ENG_FCF'!$D$59,0)</f>
         <v/>
       </c>
       <c r="E30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|1@@/@@ENG_FCF|FCF.equity|1@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$E$67/'ENG_FCF'!$E$59,0)</f>
         <v/>
       </c>
       <c r="F30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|2@@/@@ENG_FCF|FCF.equity|2@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$F$67/'ENG_FCF'!$F$59,0)</f>
         <v/>
       </c>
       <c r="G30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|3@@/@@ENG_FCF|FCF.equity|3@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$G$67/'ENG_FCF'!$G$59,0)</f>
         <v/>
       </c>
       <c r="H30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|4@@/@@ENG_FCF|FCF.equity|4@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$H$67/'ENG_FCF'!$H$59,0)</f>
         <v/>
       </c>
       <c r="I30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|5@@/@@ENG_FCF|FCF.equity|5@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$I$67/'ENG_FCF'!$I$59,0)</f>
         <v/>
       </c>
       <c r="J30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|6@@/@@ENG_FCF|FCF.equity|6@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$J$67/'ENG_FCF'!$J$59,0)</f>
         <v/>
       </c>
       <c r="K30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|7@@/@@ENG_FCF|FCF.equity|7@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$K$67/'ENG_FCF'!$K$59,0)</f>
         <v/>
       </c>
       <c r="L30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|8@@/@@ENG_FCF|FCF.equity|8@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$L$67/'ENG_FCF'!$L$59,0)</f>
         <v/>
       </c>
       <c r="M30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|9@@/@@ENG_FCF|FCF.equity|9@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$M$67/'ENG_FCF'!$M$59,0)</f>
         <v/>
       </c>
       <c r="N30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|10@@/@@ENG_FCF|FCF.equity|10@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$N$67/'ENG_FCF'!$N$59,0)</f>
         <v/>
       </c>
       <c r="O30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|11@@/@@ENG_FCF|FCF.equity|11@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$O$67/'ENG_FCF'!$O$59,0)</f>
         <v/>
       </c>
       <c r="P30" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|12@@/@@ENG_FCF|FCF.equity|12@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$P$67/'ENG_FCF'!$P$59,0)</f>
         <v/>
       </c>
     </row>
@@ -14355,55 +18250,55 @@
         </is>
       </c>
       <c r="D31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|0@@/@@ENG_FCF|FCF.ebitda|0@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$D$67/'ENG_FCF'!$D$15,0)</f>
         <v/>
       </c>
       <c r="E31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|1@@/@@ENG_FCF|FCF.ebitda|1@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$E$67/'ENG_FCF'!$E$15,0)</f>
         <v/>
       </c>
       <c r="F31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|2@@/@@ENG_FCF|FCF.ebitda|2@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$F$67/'ENG_FCF'!$F$15,0)</f>
         <v/>
       </c>
       <c r="G31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|3@@/@@ENG_FCF|FCF.ebitda|3@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$G$67/'ENG_FCF'!$G$15,0)</f>
         <v/>
       </c>
       <c r="H31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|4@@/@@ENG_FCF|FCF.ebitda|4@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$H$67/'ENG_FCF'!$H$15,0)</f>
         <v/>
       </c>
       <c r="I31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|5@@/@@ENG_FCF|FCF.ebitda|5@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$I$67/'ENG_FCF'!$I$15,0)</f>
         <v/>
       </c>
       <c r="J31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|6@@/@@ENG_FCF|FCF.ebitda|6@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$J$67/'ENG_FCF'!$J$15,0)</f>
         <v/>
       </c>
       <c r="K31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|7@@/@@ENG_FCF|FCF.ebitda|7@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$K$67/'ENG_FCF'!$K$15,0)</f>
         <v/>
       </c>
       <c r="L31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|8@@/@@ENG_FCF|FCF.ebitda|8@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$L$67/'ENG_FCF'!$L$15,0)</f>
         <v/>
       </c>
       <c r="M31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|9@@/@@ENG_FCF|FCF.ebitda|9@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$M$67/'ENG_FCF'!$M$15,0)</f>
         <v/>
       </c>
       <c r="N31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|10@@/@@ENG_FCF|FCF.ebitda|10@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$N$67/'ENG_FCF'!$N$15,0)</f>
         <v/>
       </c>
       <c r="O31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|11@@/@@ENG_FCF|FCF.ebitda|11@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$O$67/'ENG_FCF'!$O$15,0)</f>
         <v/>
       </c>
       <c r="P31" s="12">
-        <f>IFERROR(@@ENG_FCF|FCF.ltd|12@@/@@ENG_FCF|FCF.ebitda|12@@,0)</f>
+        <f>IFERROR('ENG_FCF'!$P$67/'ENG_FCF'!$P$15,0)</f>
         <v/>
       </c>
     </row>
@@ -14424,55 +18319,55 @@
         </is>
       </c>
       <c r="D32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|0@@-@@ENG_FCF|FCF.cash|0@@)/@@ENG_FCF|FCF.ebitda|0@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$D$67-'ENG_FCF'!$D$56)/'ENG_FCF'!$D$15,0)</f>
         <v/>
       </c>
       <c r="E32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|1@@-@@ENG_FCF|FCF.cash|1@@)/@@ENG_FCF|FCF.ebitda|1@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$E$67-'ENG_FCF'!$E$56)/'ENG_FCF'!$E$15,0)</f>
         <v/>
       </c>
       <c r="F32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|2@@-@@ENG_FCF|FCF.cash|2@@)/@@ENG_FCF|FCF.ebitda|2@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$F$67-'ENG_FCF'!$F$56)/'ENG_FCF'!$F$15,0)</f>
         <v/>
       </c>
       <c r="G32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|3@@-@@ENG_FCF|FCF.cash|3@@)/@@ENG_FCF|FCF.ebitda|3@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$G$67-'ENG_FCF'!$G$56)/'ENG_FCF'!$G$15,0)</f>
         <v/>
       </c>
       <c r="H32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|4@@-@@ENG_FCF|FCF.cash|4@@)/@@ENG_FCF|FCF.ebitda|4@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$H$67-'ENG_FCF'!$H$56)/'ENG_FCF'!$H$15,0)</f>
         <v/>
       </c>
       <c r="I32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|5@@-@@ENG_FCF|FCF.cash|5@@)/@@ENG_FCF|FCF.ebitda|5@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$I$67-'ENG_FCF'!$I$56)/'ENG_FCF'!$I$15,0)</f>
         <v/>
       </c>
       <c r="J32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|6@@-@@ENG_FCF|FCF.cash|6@@)/@@ENG_FCF|FCF.ebitda|6@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$J$67-'ENG_FCF'!$J$56)/'ENG_FCF'!$J$15,0)</f>
         <v/>
       </c>
       <c r="K32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|7@@-@@ENG_FCF|FCF.cash|7@@)/@@ENG_FCF|FCF.ebitda|7@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$K$67-'ENG_FCF'!$K$56)/'ENG_FCF'!$K$15,0)</f>
         <v/>
       </c>
       <c r="L32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|8@@-@@ENG_FCF|FCF.cash|8@@)/@@ENG_FCF|FCF.ebitda|8@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$L$67-'ENG_FCF'!$L$56)/'ENG_FCF'!$L$15,0)</f>
         <v/>
       </c>
       <c r="M32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|9@@-@@ENG_FCF|FCF.cash|9@@)/@@ENG_FCF|FCF.ebitda|9@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$M$67-'ENG_FCF'!$M$56)/'ENG_FCF'!$M$15,0)</f>
         <v/>
       </c>
       <c r="N32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|10@@-@@ENG_FCF|FCF.cash|10@@)/@@ENG_FCF|FCF.ebitda|10@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$N$67-'ENG_FCF'!$N$56)/'ENG_FCF'!$N$15,0)</f>
         <v/>
       </c>
       <c r="O32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|11@@-@@ENG_FCF|FCF.cash|11@@)/@@ENG_FCF|FCF.ebitda|11@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$O$67-'ENG_FCF'!$O$56)/'ENG_FCF'!$O$15,0)</f>
         <v/>
       </c>
       <c r="P32" s="12">
-        <f>IFERROR((@@ENG_FCF|FCF.ltd|12@@-@@ENG_FCF|FCF.cash|12@@)/@@ENG_FCF|FCF.ebitda|12@@,0)</f>
+        <f>IFERROR(('ENG_FCF'!$P$67-'ENG_FCF'!$P$56)/'ENG_FCF'!$P$15,0)</f>
         <v/>
       </c>
     </row>
@@ -23071,55 +26966,55 @@
         </is>
       </c>
       <c r="D65" s="14">
-        <f>'ENG_SCEN'!$D$49-MAX(0,'ENG_SCEN'!$D$50-(@@ENG_FCF|FCF.int_lt|0@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|0@@+@@ENG_FCF|FCF.int_st|0@@-@@ENG_FCF|FCF.int_inc|0@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$D$54</f>
+        <f>'ENG_SCEN'!$D$49-MAX(0,'ENG_SCEN'!$D$50-('ENG_FCF'!$D$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$D$27+'ENG_FCF'!$D$28-'ENG_FCF'!$D$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$D$54</f>
         <v/>
       </c>
       <c r="E65" s="14">
-        <f>'ENG_SCEN'!$E$49-MAX(0,'ENG_SCEN'!$E$50-(@@ENG_FCF|FCF.int_lt|1@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|1@@+@@ENG_FCF|FCF.int_st|1@@-@@ENG_FCF|FCF.int_inc|1@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$E$54</f>
+        <f>'ENG_SCEN'!$E$49-MAX(0,'ENG_SCEN'!$E$50-('ENG_FCF'!$E$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$E$27+'ENG_FCF'!$E$28-'ENG_FCF'!$E$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$E$54</f>
         <v/>
       </c>
       <c r="F65" s="14">
-        <f>'ENG_SCEN'!$F$49-MAX(0,'ENG_SCEN'!$F$50-(@@ENG_FCF|FCF.int_lt|2@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|2@@+@@ENG_FCF|FCF.int_st|2@@-@@ENG_FCF|FCF.int_inc|2@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$F$54</f>
+        <f>'ENG_SCEN'!$F$49-MAX(0,'ENG_SCEN'!$F$50-('ENG_FCF'!$F$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$F$27+'ENG_FCF'!$F$28-'ENG_FCF'!$F$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$F$54</f>
         <v/>
       </c>
       <c r="G65" s="14">
-        <f>'ENG_SCEN'!$G$49-MAX(0,'ENG_SCEN'!$G$50-(@@ENG_FCF|FCF.int_lt|3@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|3@@+@@ENG_FCF|FCF.int_st|3@@-@@ENG_FCF|FCF.int_inc|3@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$G$54</f>
+        <f>'ENG_SCEN'!$G$49-MAX(0,'ENG_SCEN'!$G$50-('ENG_FCF'!$G$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$G$27+'ENG_FCF'!$G$28-'ENG_FCF'!$G$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$G$54</f>
         <v/>
       </c>
       <c r="H65" s="14">
-        <f>'ENG_SCEN'!$H$49-MAX(0,'ENG_SCEN'!$H$50-(@@ENG_FCF|FCF.int_lt|4@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|4@@+@@ENG_FCF|FCF.int_st|4@@-@@ENG_FCF|FCF.int_inc|4@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$H$54</f>
+        <f>'ENG_SCEN'!$H$49-MAX(0,'ENG_SCEN'!$H$50-('ENG_FCF'!$H$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$H$27+'ENG_FCF'!$H$28-'ENG_FCF'!$H$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$H$54</f>
         <v/>
       </c>
       <c r="I65" s="14">
-        <f>'ENG_SCEN'!$I$49-MAX(0,'ENG_SCEN'!$I$50-(@@ENG_FCF|FCF.int_lt|5@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|5@@+@@ENG_FCF|FCF.int_st|5@@-@@ENG_FCF|FCF.int_inc|5@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$I$54</f>
+        <f>'ENG_SCEN'!$I$49-MAX(0,'ENG_SCEN'!$I$50-('ENG_FCF'!$I$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$I$27+'ENG_FCF'!$I$28-'ENG_FCF'!$I$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$I$54</f>
         <v/>
       </c>
       <c r="J65" s="14">
-        <f>'ENG_SCEN'!$J$49-MAX(0,'ENG_SCEN'!$J$50-(@@ENG_FCF|FCF.int_lt|6@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|6@@+@@ENG_FCF|FCF.int_st|6@@-@@ENG_FCF|FCF.int_inc|6@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$J$54</f>
+        <f>'ENG_SCEN'!$J$49-MAX(0,'ENG_SCEN'!$J$50-('ENG_FCF'!$J$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$J$27+'ENG_FCF'!$J$28-'ENG_FCF'!$J$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$J$54</f>
         <v/>
       </c>
       <c r="K65" s="14">
-        <f>'ENG_SCEN'!$K$49-MAX(0,'ENG_SCEN'!$K$50-(@@ENG_FCF|FCF.int_lt|7@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|7@@+@@ENG_FCF|FCF.int_st|7@@-@@ENG_FCF|FCF.int_inc|7@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$K$54</f>
+        <f>'ENG_SCEN'!$K$49-MAX(0,'ENG_SCEN'!$K$50-('ENG_FCF'!$K$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$K$27+'ENG_FCF'!$K$28-'ENG_FCF'!$K$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$K$54</f>
         <v/>
       </c>
       <c r="L65" s="14">
-        <f>'ENG_SCEN'!$L$49-MAX(0,'ENG_SCEN'!$L$50-(@@ENG_FCF|FCF.int_lt|8@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|8@@+@@ENG_FCF|FCF.int_st|8@@-@@ENG_FCF|FCF.int_inc|8@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$L$54</f>
+        <f>'ENG_SCEN'!$L$49-MAX(0,'ENG_SCEN'!$L$50-('ENG_FCF'!$L$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$L$27+'ENG_FCF'!$L$28-'ENG_FCF'!$L$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$L$54</f>
         <v/>
       </c>
       <c r="M65" s="14">
-        <f>'ENG_SCEN'!$M$49-MAX(0,'ENG_SCEN'!$M$50-(@@ENG_FCF|FCF.int_lt|9@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|9@@+@@ENG_FCF|FCF.int_st|9@@-@@ENG_FCF|FCF.int_inc|9@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$M$54</f>
+        <f>'ENG_SCEN'!$M$49-MAX(0,'ENG_SCEN'!$M$50-('ENG_FCF'!$M$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$M$27+'ENG_FCF'!$M$28-'ENG_FCF'!$M$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$M$54</f>
         <v/>
       </c>
       <c r="N65" s="14">
-        <f>'ENG_SCEN'!$N$49-MAX(0,'ENG_SCEN'!$N$50-(@@ENG_FCF|FCF.int_lt|10@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|10@@+@@ENG_FCF|FCF.int_st|10@@-@@ENG_FCF|FCF.int_inc|10@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$N$54</f>
+        <f>'ENG_SCEN'!$N$49-MAX(0,'ENG_SCEN'!$N$50-('ENG_FCF'!$N$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$N$27+'ENG_FCF'!$N$28-'ENG_FCF'!$N$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$N$54</f>
         <v/>
       </c>
       <c r="O65" s="14">
-        <f>'ENG_SCEN'!$O$49-MAX(0,'ENG_SCEN'!$O$50-(@@ENG_FCF|FCF.int_lt|11@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|11@@+@@ENG_FCF|FCF.int_st|11@@-@@ENG_FCF|FCF.int_inc|11@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$O$54</f>
+        <f>'ENG_SCEN'!$O$49-MAX(0,'ENG_SCEN'!$O$50-('ENG_FCF'!$O$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$O$27+'ENG_FCF'!$O$28-'ENG_FCF'!$O$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$O$54</f>
         <v/>
       </c>
       <c r="P65" s="14">
-        <f>'ENG_SCEN'!$P$49-MAX(0,'ENG_SCEN'!$P$50-(@@ENG_FCF|FCF.int_lt|12@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|12@@+@@ENG_FCF|FCF.int_st|12@@-@@ENG_FCF|FCF.int_inc|12@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$P$54</f>
+        <f>'ENG_SCEN'!$P$49-MAX(0,'ENG_SCEN'!$P$50-('ENG_FCF'!$P$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$P$27+'ENG_FCF'!$P$28-'ENG_FCF'!$P$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$P$54</f>
         <v/>
       </c>
     </row>
@@ -23140,55 +27035,55 @@
         </is>
       </c>
       <c r="D66" s="14">
-        <f>@@ENG_FCF|FCF.principal|0@@+@@ENG_FCF|FCF.int_lt|0@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|0@@+@@ENG_FCF|FCF.int_st|0@@</f>
+        <f>'ENG_FCF'!$D$24+'ENG_FCF'!$D$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$D$27+'ENG_FCF'!$D$28</f>
         <v/>
       </c>
       <c r="E66" s="14">
-        <f>@@ENG_FCF|FCF.principal|1@@+@@ENG_FCF|FCF.int_lt|1@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|1@@+@@ENG_FCF|FCF.int_st|1@@</f>
+        <f>'ENG_FCF'!$E$24+'ENG_FCF'!$E$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$E$27+'ENG_FCF'!$E$28</f>
         <v/>
       </c>
       <c r="F66" s="14">
-        <f>@@ENG_FCF|FCF.principal|2@@+@@ENG_FCF|FCF.int_lt|2@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|2@@+@@ENG_FCF|FCF.int_st|2@@</f>
+        <f>'ENG_FCF'!$F$24+'ENG_FCF'!$F$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$F$27+'ENG_FCF'!$F$28</f>
         <v/>
       </c>
       <c r="G66" s="14">
-        <f>@@ENG_FCF|FCF.principal|3@@+@@ENG_FCF|FCF.int_lt|3@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|3@@+@@ENG_FCF|FCF.int_st|3@@</f>
+        <f>'ENG_FCF'!$G$24+'ENG_FCF'!$G$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$G$27+'ENG_FCF'!$G$28</f>
         <v/>
       </c>
       <c r="H66" s="14">
-        <f>@@ENG_FCF|FCF.principal|4@@+@@ENG_FCF|FCF.int_lt|4@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|4@@+@@ENG_FCF|FCF.int_st|4@@</f>
+        <f>'ENG_FCF'!$H$24+'ENG_FCF'!$H$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$H$27+'ENG_FCF'!$H$28</f>
         <v/>
       </c>
       <c r="I66" s="14">
-        <f>@@ENG_FCF|FCF.principal|5@@+@@ENG_FCF|FCF.int_lt|5@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|5@@+@@ENG_FCF|FCF.int_st|5@@</f>
+        <f>'ENG_FCF'!$I$24+'ENG_FCF'!$I$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$I$27+'ENG_FCF'!$I$28</f>
         <v/>
       </c>
       <c r="J66" s="14">
-        <f>@@ENG_FCF|FCF.principal|6@@+@@ENG_FCF|FCF.int_lt|6@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|6@@+@@ENG_FCF|FCF.int_st|6@@</f>
+        <f>'ENG_FCF'!$J$24+'ENG_FCF'!$J$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$J$27+'ENG_FCF'!$J$28</f>
         <v/>
       </c>
       <c r="K66" s="14">
-        <f>@@ENG_FCF|FCF.principal|7@@+@@ENG_FCF|FCF.int_lt|7@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|7@@+@@ENG_FCF|FCF.int_st|7@@</f>
+        <f>'ENG_FCF'!$K$24+'ENG_FCF'!$K$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$K$27+'ENG_FCF'!$K$28</f>
         <v/>
       </c>
       <c r="L66" s="14">
-        <f>@@ENG_FCF|FCF.principal|8@@+@@ENG_FCF|FCF.int_lt|8@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|8@@+@@ENG_FCF|FCF.int_st|8@@</f>
+        <f>'ENG_FCF'!$L$24+'ENG_FCF'!$L$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$L$27+'ENG_FCF'!$L$28</f>
         <v/>
       </c>
       <c r="M66" s="14">
-        <f>@@ENG_FCF|FCF.principal|9@@+@@ENG_FCF|FCF.int_lt|9@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|9@@+@@ENG_FCF|FCF.int_st|9@@</f>
+        <f>'ENG_FCF'!$M$24+'ENG_FCF'!$M$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$M$27+'ENG_FCF'!$M$28</f>
         <v/>
       </c>
       <c r="N66" s="14">
-        <f>@@ENG_FCF|FCF.principal|10@@+@@ENG_FCF|FCF.int_lt|10@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|10@@+@@ENG_FCF|FCF.int_st|10@@</f>
+        <f>'ENG_FCF'!$N$24+'ENG_FCF'!$N$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$N$27+'ENG_FCF'!$N$28</f>
         <v/>
       </c>
       <c r="O66" s="14">
-        <f>@@ENG_FCF|FCF.principal|11@@+@@ENG_FCF|FCF.int_lt|11@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|11@@+@@ENG_FCF|FCF.int_st|11@@</f>
+        <f>'ENG_FCF'!$O$24+'ENG_FCF'!$O$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$O$27+'ENG_FCF'!$O$28</f>
         <v/>
       </c>
       <c r="P66" s="14">
-        <f>@@ENG_FCF|FCF.principal|12@@+@@ENG_FCF|FCF.int_lt|12@@*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|12@@+@@ENG_FCF|FCF.int_st|12@@</f>
+        <f>'ENG_FCF'!$P$24+'ENG_FCF'!$P$26*('IN_FIN'!$D$25+'IN_SCEN'!$D$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$P$27+'ENG_FCF'!$P$28</f>
         <v/>
       </c>
     </row>
@@ -25041,55 +28936,55 @@
         </is>
       </c>
       <c r="D99" s="14">
-        <f>'ENG_SCEN'!$D$83-MAX(0,'ENG_SCEN'!$D$84-(@@ENG_FCF|FCF.int_lt|0@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|0@@+@@ENG_FCF|FCF.int_st|0@@-@@ENG_FCF|FCF.int_inc|0@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$D$88</f>
+        <f>'ENG_SCEN'!$D$83-MAX(0,'ENG_SCEN'!$D$84-('ENG_FCF'!$D$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$D$27+'ENG_FCF'!$D$28-'ENG_FCF'!$D$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$D$88</f>
         <v/>
       </c>
       <c r="E99" s="14">
-        <f>'ENG_SCEN'!$E$83-MAX(0,'ENG_SCEN'!$E$84-(@@ENG_FCF|FCF.int_lt|1@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|1@@+@@ENG_FCF|FCF.int_st|1@@-@@ENG_FCF|FCF.int_inc|1@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$E$88</f>
+        <f>'ENG_SCEN'!$E$83-MAX(0,'ENG_SCEN'!$E$84-('ENG_FCF'!$E$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$E$27+'ENG_FCF'!$E$28-'ENG_FCF'!$E$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$E$88</f>
         <v/>
       </c>
       <c r="F99" s="14">
-        <f>'ENG_SCEN'!$F$83-MAX(0,'ENG_SCEN'!$F$84-(@@ENG_FCF|FCF.int_lt|2@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|2@@+@@ENG_FCF|FCF.int_st|2@@-@@ENG_FCF|FCF.int_inc|2@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$F$88</f>
+        <f>'ENG_SCEN'!$F$83-MAX(0,'ENG_SCEN'!$F$84-('ENG_FCF'!$F$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$F$27+'ENG_FCF'!$F$28-'ENG_FCF'!$F$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$F$88</f>
         <v/>
       </c>
       <c r="G99" s="14">
-        <f>'ENG_SCEN'!$G$83-MAX(0,'ENG_SCEN'!$G$84-(@@ENG_FCF|FCF.int_lt|3@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|3@@+@@ENG_FCF|FCF.int_st|3@@-@@ENG_FCF|FCF.int_inc|3@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$G$88</f>
+        <f>'ENG_SCEN'!$G$83-MAX(0,'ENG_SCEN'!$G$84-('ENG_FCF'!$G$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$G$27+'ENG_FCF'!$G$28-'ENG_FCF'!$G$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$G$88</f>
         <v/>
       </c>
       <c r="H99" s="14">
-        <f>'ENG_SCEN'!$H$83-MAX(0,'ENG_SCEN'!$H$84-(@@ENG_FCF|FCF.int_lt|4@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|4@@+@@ENG_FCF|FCF.int_st|4@@-@@ENG_FCF|FCF.int_inc|4@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$H$88</f>
+        <f>'ENG_SCEN'!$H$83-MAX(0,'ENG_SCEN'!$H$84-('ENG_FCF'!$H$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$H$27+'ENG_FCF'!$H$28-'ENG_FCF'!$H$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$H$88</f>
         <v/>
       </c>
       <c r="I99" s="14">
-        <f>'ENG_SCEN'!$I$83-MAX(0,'ENG_SCEN'!$I$84-(@@ENG_FCF|FCF.int_lt|5@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|5@@+@@ENG_FCF|FCF.int_st|5@@-@@ENG_FCF|FCF.int_inc|5@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$I$88</f>
+        <f>'ENG_SCEN'!$I$83-MAX(0,'ENG_SCEN'!$I$84-('ENG_FCF'!$I$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$I$27+'ENG_FCF'!$I$28-'ENG_FCF'!$I$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$I$88</f>
         <v/>
       </c>
       <c r="J99" s="14">
-        <f>'ENG_SCEN'!$J$83-MAX(0,'ENG_SCEN'!$J$84-(@@ENG_FCF|FCF.int_lt|6@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|6@@+@@ENG_FCF|FCF.int_st|6@@-@@ENG_FCF|FCF.int_inc|6@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$J$88</f>
+        <f>'ENG_SCEN'!$J$83-MAX(0,'ENG_SCEN'!$J$84-('ENG_FCF'!$J$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$J$27+'ENG_FCF'!$J$28-'ENG_FCF'!$J$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$J$88</f>
         <v/>
       </c>
       <c r="K99" s="14">
-        <f>'ENG_SCEN'!$K$83-MAX(0,'ENG_SCEN'!$K$84-(@@ENG_FCF|FCF.int_lt|7@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|7@@+@@ENG_FCF|FCF.int_st|7@@-@@ENG_FCF|FCF.int_inc|7@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$K$88</f>
+        <f>'ENG_SCEN'!$K$83-MAX(0,'ENG_SCEN'!$K$84-('ENG_FCF'!$K$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$K$27+'ENG_FCF'!$K$28-'ENG_FCF'!$K$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$K$88</f>
         <v/>
       </c>
       <c r="L99" s="14">
-        <f>'ENG_SCEN'!$L$83-MAX(0,'ENG_SCEN'!$L$84-(@@ENG_FCF|FCF.int_lt|8@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|8@@+@@ENG_FCF|FCF.int_st|8@@-@@ENG_FCF|FCF.int_inc|8@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$L$88</f>
+        <f>'ENG_SCEN'!$L$83-MAX(0,'ENG_SCEN'!$L$84-('ENG_FCF'!$L$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$L$27+'ENG_FCF'!$L$28-'ENG_FCF'!$L$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$L$88</f>
         <v/>
       </c>
       <c r="M99" s="14">
-        <f>'ENG_SCEN'!$M$83-MAX(0,'ENG_SCEN'!$M$84-(@@ENG_FCF|FCF.int_lt|9@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|9@@+@@ENG_FCF|FCF.int_st|9@@-@@ENG_FCF|FCF.int_inc|9@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$M$88</f>
+        <f>'ENG_SCEN'!$M$83-MAX(0,'ENG_SCEN'!$M$84-('ENG_FCF'!$M$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$M$27+'ENG_FCF'!$M$28-'ENG_FCF'!$M$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$M$88</f>
         <v/>
       </c>
       <c r="N99" s="14">
-        <f>'ENG_SCEN'!$N$83-MAX(0,'ENG_SCEN'!$N$84-(@@ENG_FCF|FCF.int_lt|10@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|10@@+@@ENG_FCF|FCF.int_st|10@@-@@ENG_FCF|FCF.int_inc|10@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$N$88</f>
+        <f>'ENG_SCEN'!$N$83-MAX(0,'ENG_SCEN'!$N$84-('ENG_FCF'!$N$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$N$27+'ENG_FCF'!$N$28-'ENG_FCF'!$N$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$N$88</f>
         <v/>
       </c>
       <c r="O99" s="14">
-        <f>'ENG_SCEN'!$O$83-MAX(0,'ENG_SCEN'!$O$84-(@@ENG_FCF|FCF.int_lt|11@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|11@@+@@ENG_FCF|FCF.int_st|11@@-@@ENG_FCF|FCF.int_inc|11@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$O$88</f>
+        <f>'ENG_SCEN'!$O$83-MAX(0,'ENG_SCEN'!$O$84-('ENG_FCF'!$O$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$O$27+'ENG_FCF'!$O$28-'ENG_FCF'!$O$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$O$88</f>
         <v/>
       </c>
       <c r="P99" s="14">
-        <f>'ENG_SCEN'!$P$83-MAX(0,'ENG_SCEN'!$P$84-(@@ENG_FCF|FCF.int_lt|12@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|12@@+@@ENG_FCF|FCF.int_st|12@@-@@ENG_FCF|FCF.int_inc|12@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$P$88</f>
+        <f>'ENG_SCEN'!$P$83-MAX(0,'ENG_SCEN'!$P$84-('ENG_FCF'!$P$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$P$27+'ENG_FCF'!$P$28-'ENG_FCF'!$P$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$P$88</f>
         <v/>
       </c>
     </row>
@@ -25110,55 +29005,55 @@
         </is>
       </c>
       <c r="D100" s="14">
-        <f>@@ENG_FCF|FCF.principal|0@@+@@ENG_FCF|FCF.int_lt|0@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|0@@+@@ENG_FCF|FCF.int_st|0@@</f>
+        <f>'ENG_FCF'!$D$24+'ENG_FCF'!$D$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$D$27+'ENG_FCF'!$D$28</f>
         <v/>
       </c>
       <c r="E100" s="14">
-        <f>@@ENG_FCF|FCF.principal|1@@+@@ENG_FCF|FCF.int_lt|1@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|1@@+@@ENG_FCF|FCF.int_st|1@@</f>
+        <f>'ENG_FCF'!$E$24+'ENG_FCF'!$E$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$E$27+'ENG_FCF'!$E$28</f>
         <v/>
       </c>
       <c r="F100" s="14">
-        <f>@@ENG_FCF|FCF.principal|2@@+@@ENG_FCF|FCF.int_lt|2@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|2@@+@@ENG_FCF|FCF.int_st|2@@</f>
+        <f>'ENG_FCF'!$F$24+'ENG_FCF'!$F$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$F$27+'ENG_FCF'!$F$28</f>
         <v/>
       </c>
       <c r="G100" s="14">
-        <f>@@ENG_FCF|FCF.principal|3@@+@@ENG_FCF|FCF.int_lt|3@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|3@@+@@ENG_FCF|FCF.int_st|3@@</f>
+        <f>'ENG_FCF'!$G$24+'ENG_FCF'!$G$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$G$27+'ENG_FCF'!$G$28</f>
         <v/>
       </c>
       <c r="H100" s="14">
-        <f>@@ENG_FCF|FCF.principal|4@@+@@ENG_FCF|FCF.int_lt|4@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|4@@+@@ENG_FCF|FCF.int_st|4@@</f>
+        <f>'ENG_FCF'!$H$24+'ENG_FCF'!$H$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$H$27+'ENG_FCF'!$H$28</f>
         <v/>
       </c>
       <c r="I100" s="14">
-        <f>@@ENG_FCF|FCF.principal|5@@+@@ENG_FCF|FCF.int_lt|5@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|5@@+@@ENG_FCF|FCF.int_st|5@@</f>
+        <f>'ENG_FCF'!$I$24+'ENG_FCF'!$I$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$I$27+'ENG_FCF'!$I$28</f>
         <v/>
       </c>
       <c r="J100" s="14">
-        <f>@@ENG_FCF|FCF.principal|6@@+@@ENG_FCF|FCF.int_lt|6@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|6@@+@@ENG_FCF|FCF.int_st|6@@</f>
+        <f>'ENG_FCF'!$J$24+'ENG_FCF'!$J$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$J$27+'ENG_FCF'!$J$28</f>
         <v/>
       </c>
       <c r="K100" s="14">
-        <f>@@ENG_FCF|FCF.principal|7@@+@@ENG_FCF|FCF.int_lt|7@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|7@@+@@ENG_FCF|FCF.int_st|7@@</f>
+        <f>'ENG_FCF'!$K$24+'ENG_FCF'!$K$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$K$27+'ENG_FCF'!$K$28</f>
         <v/>
       </c>
       <c r="L100" s="14">
-        <f>@@ENG_FCF|FCF.principal|8@@+@@ENG_FCF|FCF.int_lt|8@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|8@@+@@ENG_FCF|FCF.int_st|8@@</f>
+        <f>'ENG_FCF'!$L$24+'ENG_FCF'!$L$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$L$27+'ENG_FCF'!$L$28</f>
         <v/>
       </c>
       <c r="M100" s="14">
-        <f>@@ENG_FCF|FCF.principal|9@@+@@ENG_FCF|FCF.int_lt|9@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|9@@+@@ENG_FCF|FCF.int_st|9@@</f>
+        <f>'ENG_FCF'!$M$24+'ENG_FCF'!$M$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$M$27+'ENG_FCF'!$M$28</f>
         <v/>
       </c>
       <c r="N100" s="14">
-        <f>@@ENG_FCF|FCF.principal|10@@+@@ENG_FCF|FCF.int_lt|10@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|10@@+@@ENG_FCF|FCF.int_st|10@@</f>
+        <f>'ENG_FCF'!$N$24+'ENG_FCF'!$N$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$N$27+'ENG_FCF'!$N$28</f>
         <v/>
       </c>
       <c r="O100" s="14">
-        <f>@@ENG_FCF|FCF.principal|11@@+@@ENG_FCF|FCF.int_lt|11@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|11@@+@@ENG_FCF|FCF.int_st|11@@</f>
+        <f>'ENG_FCF'!$O$24+'ENG_FCF'!$O$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$O$27+'ENG_FCF'!$O$28</f>
         <v/>
       </c>
       <c r="P100" s="14">
-        <f>@@ENG_FCF|FCF.principal|12@@+@@ENG_FCF|FCF.int_lt|12@@*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|12@@+@@ENG_FCF|FCF.int_st|12@@</f>
+        <f>'ENG_FCF'!$P$24+'ENG_FCF'!$P$26*('IN_FIN'!$D$25+'IN_SCEN'!$E$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$P$27+'ENG_FCF'!$P$28</f>
         <v/>
       </c>
     </row>
@@ -27011,55 +30906,55 @@
         </is>
       </c>
       <c r="D133" s="14">
-        <f>'ENG_SCEN'!$D$117-MAX(0,'ENG_SCEN'!$D$118-(@@ENG_FCF|FCF.int_lt|0@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|0@@+@@ENG_FCF|FCF.int_st|0@@-@@ENG_FCF|FCF.int_inc|0@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$D$122</f>
+        <f>'ENG_SCEN'!$D$117-MAX(0,'ENG_SCEN'!$D$118-('ENG_FCF'!$D$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$D$27+'ENG_FCF'!$D$28-'ENG_FCF'!$D$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$D$122</f>
         <v/>
       </c>
       <c r="E133" s="14">
-        <f>'ENG_SCEN'!$E$117-MAX(0,'ENG_SCEN'!$E$118-(@@ENG_FCF|FCF.int_lt|1@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|1@@+@@ENG_FCF|FCF.int_st|1@@-@@ENG_FCF|FCF.int_inc|1@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$E$122</f>
+        <f>'ENG_SCEN'!$E$117-MAX(0,'ENG_SCEN'!$E$118-('ENG_FCF'!$E$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$E$27+'ENG_FCF'!$E$28-'ENG_FCF'!$E$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$E$122</f>
         <v/>
       </c>
       <c r="F133" s="14">
-        <f>'ENG_SCEN'!$F$117-MAX(0,'ENG_SCEN'!$F$118-(@@ENG_FCF|FCF.int_lt|2@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|2@@+@@ENG_FCF|FCF.int_st|2@@-@@ENG_FCF|FCF.int_inc|2@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$F$122</f>
+        <f>'ENG_SCEN'!$F$117-MAX(0,'ENG_SCEN'!$F$118-('ENG_FCF'!$F$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$F$27+'ENG_FCF'!$F$28-'ENG_FCF'!$F$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$F$122</f>
         <v/>
       </c>
       <c r="G133" s="14">
-        <f>'ENG_SCEN'!$G$117-MAX(0,'ENG_SCEN'!$G$118-(@@ENG_FCF|FCF.int_lt|3@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|3@@+@@ENG_FCF|FCF.int_st|3@@-@@ENG_FCF|FCF.int_inc|3@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$G$122</f>
+        <f>'ENG_SCEN'!$G$117-MAX(0,'ENG_SCEN'!$G$118-('ENG_FCF'!$G$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$G$27+'ENG_FCF'!$G$28-'ENG_FCF'!$G$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$G$122</f>
         <v/>
       </c>
       <c r="H133" s="14">
-        <f>'ENG_SCEN'!$H$117-MAX(0,'ENG_SCEN'!$H$118-(@@ENG_FCF|FCF.int_lt|4@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|4@@+@@ENG_FCF|FCF.int_st|4@@-@@ENG_FCF|FCF.int_inc|4@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$H$122</f>
+        <f>'ENG_SCEN'!$H$117-MAX(0,'ENG_SCEN'!$H$118-('ENG_FCF'!$H$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$H$27+'ENG_FCF'!$H$28-'ENG_FCF'!$H$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$H$122</f>
         <v/>
       </c>
       <c r="I133" s="14">
-        <f>'ENG_SCEN'!$I$117-MAX(0,'ENG_SCEN'!$I$118-(@@ENG_FCF|FCF.int_lt|5@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|5@@+@@ENG_FCF|FCF.int_st|5@@-@@ENG_FCF|FCF.int_inc|5@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$I$122</f>
+        <f>'ENG_SCEN'!$I$117-MAX(0,'ENG_SCEN'!$I$118-('ENG_FCF'!$I$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$I$27+'ENG_FCF'!$I$28-'ENG_FCF'!$I$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$I$122</f>
         <v/>
       </c>
       <c r="J133" s="14">
-        <f>'ENG_SCEN'!$J$117-MAX(0,'ENG_SCEN'!$J$118-(@@ENG_FCF|FCF.int_lt|6@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|6@@+@@ENG_FCF|FCF.int_st|6@@-@@ENG_FCF|FCF.int_inc|6@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$J$122</f>
+        <f>'ENG_SCEN'!$J$117-MAX(0,'ENG_SCEN'!$J$118-('ENG_FCF'!$J$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$J$27+'ENG_FCF'!$J$28-'ENG_FCF'!$J$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$J$122</f>
         <v/>
       </c>
       <c r="K133" s="14">
-        <f>'ENG_SCEN'!$K$117-MAX(0,'ENG_SCEN'!$K$118-(@@ENG_FCF|FCF.int_lt|7@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|7@@+@@ENG_FCF|FCF.int_st|7@@-@@ENG_FCF|FCF.int_inc|7@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$K$122</f>
+        <f>'ENG_SCEN'!$K$117-MAX(0,'ENG_SCEN'!$K$118-('ENG_FCF'!$K$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$K$27+'ENG_FCF'!$K$28-'ENG_FCF'!$K$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$K$122</f>
         <v/>
       </c>
       <c r="L133" s="14">
-        <f>'ENG_SCEN'!$L$117-MAX(0,'ENG_SCEN'!$L$118-(@@ENG_FCF|FCF.int_lt|8@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|8@@+@@ENG_FCF|FCF.int_st|8@@-@@ENG_FCF|FCF.int_inc|8@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$L$122</f>
+        <f>'ENG_SCEN'!$L$117-MAX(0,'ENG_SCEN'!$L$118-('ENG_FCF'!$L$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$L$27+'ENG_FCF'!$L$28-'ENG_FCF'!$L$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$L$122</f>
         <v/>
       </c>
       <c r="M133" s="14">
-        <f>'ENG_SCEN'!$M$117-MAX(0,'ENG_SCEN'!$M$118-(@@ENG_FCF|FCF.int_lt|9@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|9@@+@@ENG_FCF|FCF.int_st|9@@-@@ENG_FCF|FCF.int_inc|9@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$M$122</f>
+        <f>'ENG_SCEN'!$M$117-MAX(0,'ENG_SCEN'!$M$118-('ENG_FCF'!$M$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$M$27+'ENG_FCF'!$M$28-'ENG_FCF'!$M$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$M$122</f>
         <v/>
       </c>
       <c r="N133" s="14">
-        <f>'ENG_SCEN'!$N$117-MAX(0,'ENG_SCEN'!$N$118-(@@ENG_FCF|FCF.int_lt|10@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|10@@+@@ENG_FCF|FCF.int_st|10@@-@@ENG_FCF|FCF.int_inc|10@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$N$122</f>
+        <f>'ENG_SCEN'!$N$117-MAX(0,'ENG_SCEN'!$N$118-('ENG_FCF'!$N$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$N$27+'ENG_FCF'!$N$28-'ENG_FCF'!$N$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$N$122</f>
         <v/>
       </c>
       <c r="O133" s="14">
-        <f>'ENG_SCEN'!$O$117-MAX(0,'ENG_SCEN'!$O$118-(@@ENG_FCF|FCF.int_lt|11@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|11@@+@@ENG_FCF|FCF.int_st|11@@-@@ENG_FCF|FCF.int_inc|11@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$O$122</f>
+        <f>'ENG_SCEN'!$O$117-MAX(0,'ENG_SCEN'!$O$118-('ENG_FCF'!$O$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$O$27+'ENG_FCF'!$O$28-'ENG_FCF'!$O$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$O$122</f>
         <v/>
       </c>
       <c r="P133" s="14">
-        <f>'ENG_SCEN'!$P$117-MAX(0,'ENG_SCEN'!$P$118-(@@ENG_FCF|FCF.int_lt|12@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|12@@+@@ENG_FCF|FCF.int_st|12@@-@@ENG_FCF|FCF.int_inc|12@@))*'IN_MACRO'!$D$14-'ENG_SCEN'!$P$122</f>
+        <f>'ENG_SCEN'!$P$117-MAX(0,'ENG_SCEN'!$P$118-('ENG_FCF'!$P$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$P$27+'ENG_FCF'!$P$28-'ENG_FCF'!$P$29))*'IN_MACRO'!$D$14-'ENG_SCEN'!$P$122</f>
         <v/>
       </c>
     </row>
@@ -27080,55 +30975,55 @@
         </is>
       </c>
       <c r="D134" s="14">
-        <f>@@ENG_FCF|FCF.principal|0@@+@@ENG_FCF|FCF.int_lt|0@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|0@@+@@ENG_FCF|FCF.int_st|0@@</f>
+        <f>'ENG_FCF'!$D$24+'ENG_FCF'!$D$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$D$27+'ENG_FCF'!$D$28</f>
         <v/>
       </c>
       <c r="E134" s="14">
-        <f>@@ENG_FCF|FCF.principal|1@@+@@ENG_FCF|FCF.int_lt|1@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|1@@+@@ENG_FCF|FCF.int_st|1@@</f>
+        <f>'ENG_FCF'!$E$24+'ENG_FCF'!$E$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$E$27+'ENG_FCF'!$E$28</f>
         <v/>
       </c>
       <c r="F134" s="14">
-        <f>@@ENG_FCF|FCF.principal|2@@+@@ENG_FCF|FCF.int_lt|2@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|2@@+@@ENG_FCF|FCF.int_st|2@@</f>
+        <f>'ENG_FCF'!$F$24+'ENG_FCF'!$F$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$F$27+'ENG_FCF'!$F$28</f>
         <v/>
       </c>
       <c r="G134" s="14">
-        <f>@@ENG_FCF|FCF.principal|3@@+@@ENG_FCF|FCF.int_lt|3@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|3@@+@@ENG_FCF|FCF.int_st|3@@</f>
+        <f>'ENG_FCF'!$G$24+'ENG_FCF'!$G$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$G$27+'ENG_FCF'!$G$28</f>
         <v/>
       </c>
       <c r="H134" s="14">
-        <f>@@ENG_FCF|FCF.principal|4@@+@@ENG_FCF|FCF.int_lt|4@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|4@@+@@ENG_FCF|FCF.int_st|4@@</f>
+        <f>'ENG_FCF'!$H$24+'ENG_FCF'!$H$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$H$27+'ENG_FCF'!$H$28</f>
         <v/>
       </c>
       <c r="I134" s="14">
-        <f>@@ENG_FCF|FCF.principal|5@@+@@ENG_FCF|FCF.int_lt|5@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|5@@+@@ENG_FCF|FCF.int_st|5@@</f>
+        <f>'ENG_FCF'!$I$24+'ENG_FCF'!$I$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$I$27+'ENG_FCF'!$I$28</f>
         <v/>
       </c>
       <c r="J134" s="14">
-        <f>@@ENG_FCF|FCF.principal|6@@+@@ENG_FCF|FCF.int_lt|6@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|6@@+@@ENG_FCF|FCF.int_st|6@@</f>
+        <f>'ENG_FCF'!$J$24+'ENG_FCF'!$J$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$J$27+'ENG_FCF'!$J$28</f>
         <v/>
       </c>
       <c r="K134" s="14">
-        <f>@@ENG_FCF|FCF.principal|7@@+@@ENG_FCF|FCF.int_lt|7@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|7@@+@@ENG_FCF|FCF.int_st|7@@</f>
+        <f>'ENG_FCF'!$K$24+'ENG_FCF'!$K$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$K$27+'ENG_FCF'!$K$28</f>
         <v/>
       </c>
       <c r="L134" s="14">
-        <f>@@ENG_FCF|FCF.principal|8@@+@@ENG_FCF|FCF.int_lt|8@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|8@@+@@ENG_FCF|FCF.int_st|8@@</f>
+        <f>'ENG_FCF'!$L$24+'ENG_FCF'!$L$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$L$27+'ENG_FCF'!$L$28</f>
         <v/>
       </c>
       <c r="M134" s="14">
-        <f>@@ENG_FCF|FCF.principal|9@@+@@ENG_FCF|FCF.int_lt|9@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|9@@+@@ENG_FCF|FCF.int_st|9@@</f>
+        <f>'ENG_FCF'!$M$24+'ENG_FCF'!$M$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$M$27+'ENG_FCF'!$M$28</f>
         <v/>
       </c>
       <c r="N134" s="14">
-        <f>@@ENG_FCF|FCF.principal|10@@+@@ENG_FCF|FCF.int_lt|10@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|10@@+@@ENG_FCF|FCF.int_st|10@@</f>
+        <f>'ENG_FCF'!$N$24+'ENG_FCF'!$N$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$N$27+'ENG_FCF'!$N$28</f>
         <v/>
       </c>
       <c r="O134" s="14">
-        <f>@@ENG_FCF|FCF.principal|11@@+@@ENG_FCF|FCF.int_lt|11@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|11@@+@@ENG_FCF|FCF.int_st|11@@</f>
+        <f>'ENG_FCF'!$O$24+'ENG_FCF'!$O$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$O$27+'ENG_FCF'!$O$28</f>
         <v/>
       </c>
       <c r="P134" s="14">
-        <f>@@ENG_FCF|FCF.principal|12@@+@@ENG_FCF|FCF.int_lt|12@@*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+@@ENG_FCF|FCF.fees|12@@+@@ENG_FCF|FCF.int_st|12@@</f>
+        <f>'ENG_FCF'!$P$24+'ENG_FCF'!$P$26*('IN_FIN'!$D$25+'IN_SCEN'!$F$21)/('IN_FIN'!$D$25+'ENG_SCEN'!$G$19)+'ENG_FCF'!$P$27+'ENG_FCF'!$P$28</f>
         <v/>
       </c>
     </row>
